--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -20,7 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0&quot;%&quot;"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -73,13 +75,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -834,3801 +842,4101 @@
       </c>
     </row>
     <row r="3">
-      <c r="M3">
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="5">
         <f>IF(TODAY()&lt;F3, 0, IF(TODAY()&gt;G3, H3, H3 * (TODAY()-F3)/(G3-F3+1)))</f>
         <v/>
       </c>
-      <c r="N3">
-        <f>H3 * L3</f>
-        <v/>
-      </c>
-      <c r="O3">
+      <c r="N3" s="5">
+        <f>H3 * (L3/100)</f>
+        <v/>
+      </c>
+      <c r="O3" s="5">
         <f>K3</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="X3" s="4" t="n"/>
+      <c r="Y3" s="5">
         <f>IF(TODAY()&lt;R3, 0, IF(TODAY()&gt;S3, T3, T3 * (TODAY()-R3)/(S3-R3+1)))</f>
         <v/>
       </c>
-      <c r="Z3">
-        <f>T3 * X3</f>
-        <v/>
-      </c>
-      <c r="AA3">
+      <c r="Z3" s="5">
+        <f>T3 * (X3/100)</f>
+        <v/>
+      </c>
+      <c r="AA3" s="5">
         <f>W3</f>
         <v/>
       </c>
-      <c r="AK3">
+      <c r="AJ3" s="4" t="n"/>
+      <c r="AK3" s="5">
         <f>IF(TODAY()&lt;AD3, 0, IF(TODAY()&gt;AE3, AF3, AF3 * (TODAY()-AD3)/(AE3-AD3+1)))</f>
         <v/>
       </c>
-      <c r="AL3">
-        <f>AF3 * AJ3</f>
-        <v/>
-      </c>
-      <c r="AM3">
+      <c r="AL3" s="5">
+        <f>AF3 * (AJ3/100)</f>
+        <v/>
+      </c>
+      <c r="AM3" s="5">
         <f>AI3</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="M4">
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="5">
         <f>IF(TODAY()&lt;F4, 0, IF(TODAY()&gt;G4, H4, H4 * (TODAY()-F4)/(G4-F4+1)))</f>
         <v/>
       </c>
-      <c r="N4">
-        <f>H4 * L4</f>
-        <v/>
-      </c>
-      <c r="O4">
+      <c r="N4" s="5">
+        <f>H4 * (L4/100)</f>
+        <v/>
+      </c>
+      <c r="O4" s="5">
         <f>K4</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="X4" s="4" t="n"/>
+      <c r="Y4" s="5">
         <f>IF(TODAY()&lt;R4, 0, IF(TODAY()&gt;S4, T4, T4 * (TODAY()-R4)/(S4-R4+1)))</f>
         <v/>
       </c>
-      <c r="Z4">
-        <f>T4 * X4</f>
-        <v/>
-      </c>
-      <c r="AA4">
+      <c r="Z4" s="5">
+        <f>T4 * (X4/100)</f>
+        <v/>
+      </c>
+      <c r="AA4" s="5">
         <f>W4</f>
         <v/>
       </c>
-      <c r="AK4">
+      <c r="AJ4" s="4" t="n"/>
+      <c r="AK4" s="5">
         <f>IF(TODAY()&lt;AD4, 0, IF(TODAY()&gt;AE4, AF4, AF4 * (TODAY()-AD4)/(AE4-AD4+1)))</f>
         <v/>
       </c>
-      <c r="AL4">
-        <f>AF4 * AJ4</f>
-        <v/>
-      </c>
-      <c r="AM4">
+      <c r="AL4" s="5">
+        <f>AF4 * (AJ4/100)</f>
+        <v/>
+      </c>
+      <c r="AM4" s="5">
         <f>AI4</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="M5">
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="5">
         <f>IF(TODAY()&lt;F5, 0, IF(TODAY()&gt;G5, H5, H5 * (TODAY()-F5)/(G5-F5+1)))</f>
         <v/>
       </c>
-      <c r="N5">
-        <f>H5 * L5</f>
-        <v/>
-      </c>
-      <c r="O5">
+      <c r="N5" s="5">
+        <f>H5 * (L5/100)</f>
+        <v/>
+      </c>
+      <c r="O5" s="5">
         <f>K5</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="X5" s="4" t="n"/>
+      <c r="Y5" s="5">
         <f>IF(TODAY()&lt;R5, 0, IF(TODAY()&gt;S5, T5, T5 * (TODAY()-R5)/(S5-R5+1)))</f>
         <v/>
       </c>
-      <c r="Z5">
-        <f>T5 * X5</f>
-        <v/>
-      </c>
-      <c r="AA5">
+      <c r="Z5" s="5">
+        <f>T5 * (X5/100)</f>
+        <v/>
+      </c>
+      <c r="AA5" s="5">
         <f>W5</f>
         <v/>
       </c>
-      <c r="AK5">
+      <c r="AJ5" s="4" t="n"/>
+      <c r="AK5" s="5">
         <f>IF(TODAY()&lt;AD5, 0, IF(TODAY()&gt;AE5, AF5, AF5 * (TODAY()-AD5)/(AE5-AD5+1)))</f>
         <v/>
       </c>
-      <c r="AL5">
-        <f>AF5 * AJ5</f>
-        <v/>
-      </c>
-      <c r="AM5">
+      <c r="AL5" s="5">
+        <f>AF5 * (AJ5/100)</f>
+        <v/>
+      </c>
+      <c r="AM5" s="5">
         <f>AI5</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="M6">
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="5">
         <f>IF(TODAY()&lt;F6, 0, IF(TODAY()&gt;G6, H6, H6 * (TODAY()-F6)/(G6-F6+1)))</f>
         <v/>
       </c>
-      <c r="N6">
-        <f>H6 * L6</f>
-        <v/>
-      </c>
-      <c r="O6">
+      <c r="N6" s="5">
+        <f>H6 * (L6/100)</f>
+        <v/>
+      </c>
+      <c r="O6" s="5">
         <f>K6</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="X6" s="4" t="n"/>
+      <c r="Y6" s="5">
         <f>IF(TODAY()&lt;R6, 0, IF(TODAY()&gt;S6, T6, T6 * (TODAY()-R6)/(S6-R6+1)))</f>
         <v/>
       </c>
-      <c r="Z6">
-        <f>T6 * X6</f>
-        <v/>
-      </c>
-      <c r="AA6">
+      <c r="Z6" s="5">
+        <f>T6 * (X6/100)</f>
+        <v/>
+      </c>
+      <c r="AA6" s="5">
         <f>W6</f>
         <v/>
       </c>
-      <c r="AK6">
+      <c r="AJ6" s="4" t="n"/>
+      <c r="AK6" s="5">
         <f>IF(TODAY()&lt;AD6, 0, IF(TODAY()&gt;AE6, AF6, AF6 * (TODAY()-AD6)/(AE6-AD6+1)))</f>
         <v/>
       </c>
-      <c r="AL6">
-        <f>AF6 * AJ6</f>
-        <v/>
-      </c>
-      <c r="AM6">
+      <c r="AL6" s="5">
+        <f>AF6 * (AJ6/100)</f>
+        <v/>
+      </c>
+      <c r="AM6" s="5">
         <f>AI6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="M7">
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="5">
         <f>IF(TODAY()&lt;F7, 0, IF(TODAY()&gt;G7, H7, H7 * (TODAY()-F7)/(G7-F7+1)))</f>
         <v/>
       </c>
-      <c r="N7">
-        <f>H7 * L7</f>
-        <v/>
-      </c>
-      <c r="O7">
+      <c r="N7" s="5">
+        <f>H7 * (L7/100)</f>
+        <v/>
+      </c>
+      <c r="O7" s="5">
         <f>K7</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="X7" s="4" t="n"/>
+      <c r="Y7" s="5">
         <f>IF(TODAY()&lt;R7, 0, IF(TODAY()&gt;S7, T7, T7 * (TODAY()-R7)/(S7-R7+1)))</f>
         <v/>
       </c>
-      <c r="Z7">
-        <f>T7 * X7</f>
-        <v/>
-      </c>
-      <c r="AA7">
+      <c r="Z7" s="5">
+        <f>T7 * (X7/100)</f>
+        <v/>
+      </c>
+      <c r="AA7" s="5">
         <f>W7</f>
         <v/>
       </c>
-      <c r="AK7">
+      <c r="AJ7" s="4" t="n"/>
+      <c r="AK7" s="5">
         <f>IF(TODAY()&lt;AD7, 0, IF(TODAY()&gt;AE7, AF7, AF7 * (TODAY()-AD7)/(AE7-AD7+1)))</f>
         <v/>
       </c>
-      <c r="AL7">
-        <f>AF7 * AJ7</f>
-        <v/>
-      </c>
-      <c r="AM7">
+      <c r="AL7" s="5">
+        <f>AF7 * (AJ7/100)</f>
+        <v/>
+      </c>
+      <c r="AM7" s="5">
         <f>AI7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="M8">
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="5">
         <f>IF(TODAY()&lt;F8, 0, IF(TODAY()&gt;G8, H8, H8 * (TODAY()-F8)/(G8-F8+1)))</f>
         <v/>
       </c>
-      <c r="N8">
-        <f>H8 * L8</f>
-        <v/>
-      </c>
-      <c r="O8">
+      <c r="N8" s="5">
+        <f>H8 * (L8/100)</f>
+        <v/>
+      </c>
+      <c r="O8" s="5">
         <f>K8</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="X8" s="4" t="n"/>
+      <c r="Y8" s="5">
         <f>IF(TODAY()&lt;R8, 0, IF(TODAY()&gt;S8, T8, T8 * (TODAY()-R8)/(S8-R8+1)))</f>
         <v/>
       </c>
-      <c r="Z8">
-        <f>T8 * X8</f>
-        <v/>
-      </c>
-      <c r="AA8">
+      <c r="Z8" s="5">
+        <f>T8 * (X8/100)</f>
+        <v/>
+      </c>
+      <c r="AA8" s="5">
         <f>W8</f>
         <v/>
       </c>
-      <c r="AK8">
+      <c r="AJ8" s="4" t="n"/>
+      <c r="AK8" s="5">
         <f>IF(TODAY()&lt;AD8, 0, IF(TODAY()&gt;AE8, AF8, AF8 * (TODAY()-AD8)/(AE8-AD8+1)))</f>
         <v/>
       </c>
-      <c r="AL8">
-        <f>AF8 * AJ8</f>
-        <v/>
-      </c>
-      <c r="AM8">
+      <c r="AL8" s="5">
+        <f>AF8 * (AJ8/100)</f>
+        <v/>
+      </c>
+      <c r="AM8" s="5">
         <f>AI8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="M9">
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="5">
         <f>IF(TODAY()&lt;F9, 0, IF(TODAY()&gt;G9, H9, H9 * (TODAY()-F9)/(G9-F9+1)))</f>
         <v/>
       </c>
-      <c r="N9">
-        <f>H9 * L9</f>
-        <v/>
-      </c>
-      <c r="O9">
+      <c r="N9" s="5">
+        <f>H9 * (L9/100)</f>
+        <v/>
+      </c>
+      <c r="O9" s="5">
         <f>K9</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="X9" s="4" t="n"/>
+      <c r="Y9" s="5">
         <f>IF(TODAY()&lt;R9, 0, IF(TODAY()&gt;S9, T9, T9 * (TODAY()-R9)/(S9-R9+1)))</f>
         <v/>
       </c>
-      <c r="Z9">
-        <f>T9 * X9</f>
-        <v/>
-      </c>
-      <c r="AA9">
+      <c r="Z9" s="5">
+        <f>T9 * (X9/100)</f>
+        <v/>
+      </c>
+      <c r="AA9" s="5">
         <f>W9</f>
         <v/>
       </c>
-      <c r="AK9">
+      <c r="AJ9" s="4" t="n"/>
+      <c r="AK9" s="5">
         <f>IF(TODAY()&lt;AD9, 0, IF(TODAY()&gt;AE9, AF9, AF9 * (TODAY()-AD9)/(AE9-AD9+1)))</f>
         <v/>
       </c>
-      <c r="AL9">
-        <f>AF9 * AJ9</f>
-        <v/>
-      </c>
-      <c r="AM9">
+      <c r="AL9" s="5">
+        <f>AF9 * (AJ9/100)</f>
+        <v/>
+      </c>
+      <c r="AM9" s="5">
         <f>AI9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="M10">
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="5">
         <f>IF(TODAY()&lt;F10, 0, IF(TODAY()&gt;G10, H10, H10 * (TODAY()-F10)/(G10-F10+1)))</f>
         <v/>
       </c>
-      <c r="N10">
-        <f>H10 * L10</f>
-        <v/>
-      </c>
-      <c r="O10">
+      <c r="N10" s="5">
+        <f>H10 * (L10/100)</f>
+        <v/>
+      </c>
+      <c r="O10" s="5">
         <f>K10</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="X10" s="4" t="n"/>
+      <c r="Y10" s="5">
         <f>IF(TODAY()&lt;R10, 0, IF(TODAY()&gt;S10, T10, T10 * (TODAY()-R10)/(S10-R10+1)))</f>
         <v/>
       </c>
-      <c r="Z10">
-        <f>T10 * X10</f>
-        <v/>
-      </c>
-      <c r="AA10">
+      <c r="Z10" s="5">
+        <f>T10 * (X10/100)</f>
+        <v/>
+      </c>
+      <c r="AA10" s="5">
         <f>W10</f>
         <v/>
       </c>
-      <c r="AK10">
+      <c r="AJ10" s="4" t="n"/>
+      <c r="AK10" s="5">
         <f>IF(TODAY()&lt;AD10, 0, IF(TODAY()&gt;AE10, AF10, AF10 * (TODAY()-AD10)/(AE10-AD10+1)))</f>
         <v/>
       </c>
-      <c r="AL10">
-        <f>AF10 * AJ10</f>
-        <v/>
-      </c>
-      <c r="AM10">
+      <c r="AL10" s="5">
+        <f>AF10 * (AJ10/100)</f>
+        <v/>
+      </c>
+      <c r="AM10" s="5">
         <f>AI10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="M11">
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="5">
         <f>IF(TODAY()&lt;F11, 0, IF(TODAY()&gt;G11, H11, H11 * (TODAY()-F11)/(G11-F11+1)))</f>
         <v/>
       </c>
-      <c r="N11">
-        <f>H11 * L11</f>
-        <v/>
-      </c>
-      <c r="O11">
+      <c r="N11" s="5">
+        <f>H11 * (L11/100)</f>
+        <v/>
+      </c>
+      <c r="O11" s="5">
         <f>K11</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="X11" s="4" t="n"/>
+      <c r="Y11" s="5">
         <f>IF(TODAY()&lt;R11, 0, IF(TODAY()&gt;S11, T11, T11 * (TODAY()-R11)/(S11-R11+1)))</f>
         <v/>
       </c>
-      <c r="Z11">
-        <f>T11 * X11</f>
-        <v/>
-      </c>
-      <c r="AA11">
+      <c r="Z11" s="5">
+        <f>T11 * (X11/100)</f>
+        <v/>
+      </c>
+      <c r="AA11" s="5">
         <f>W11</f>
         <v/>
       </c>
-      <c r="AK11">
+      <c r="AJ11" s="4" t="n"/>
+      <c r="AK11" s="5">
         <f>IF(TODAY()&lt;AD11, 0, IF(TODAY()&gt;AE11, AF11, AF11 * (TODAY()-AD11)/(AE11-AD11+1)))</f>
         <v/>
       </c>
-      <c r="AL11">
-        <f>AF11 * AJ11</f>
-        <v/>
-      </c>
-      <c r="AM11">
+      <c r="AL11" s="5">
+        <f>AF11 * (AJ11/100)</f>
+        <v/>
+      </c>
+      <c r="AM11" s="5">
         <f>AI11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="M12">
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="5">
         <f>IF(TODAY()&lt;F12, 0, IF(TODAY()&gt;G12, H12, H12 * (TODAY()-F12)/(G12-F12+1)))</f>
         <v/>
       </c>
-      <c r="N12">
-        <f>H12 * L12</f>
-        <v/>
-      </c>
-      <c r="O12">
+      <c r="N12" s="5">
+        <f>H12 * (L12/100)</f>
+        <v/>
+      </c>
+      <c r="O12" s="5">
         <f>K12</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="X12" s="4" t="n"/>
+      <c r="Y12" s="5">
         <f>IF(TODAY()&lt;R12, 0, IF(TODAY()&gt;S12, T12, T12 * (TODAY()-R12)/(S12-R12+1)))</f>
         <v/>
       </c>
-      <c r="Z12">
-        <f>T12 * X12</f>
-        <v/>
-      </c>
-      <c r="AA12">
+      <c r="Z12" s="5">
+        <f>T12 * (X12/100)</f>
+        <v/>
+      </c>
+      <c r="AA12" s="5">
         <f>W12</f>
         <v/>
       </c>
-      <c r="AK12">
+      <c r="AJ12" s="4" t="n"/>
+      <c r="AK12" s="5">
         <f>IF(TODAY()&lt;AD12, 0, IF(TODAY()&gt;AE12, AF12, AF12 * (TODAY()-AD12)/(AE12-AD12+1)))</f>
         <v/>
       </c>
-      <c r="AL12">
-        <f>AF12 * AJ12</f>
-        <v/>
-      </c>
-      <c r="AM12">
+      <c r="AL12" s="5">
+        <f>AF12 * (AJ12/100)</f>
+        <v/>
+      </c>
+      <c r="AM12" s="5">
         <f>AI12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="M13">
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="5">
         <f>IF(TODAY()&lt;F13, 0, IF(TODAY()&gt;G13, H13, H13 * (TODAY()-F13)/(G13-F13+1)))</f>
         <v/>
       </c>
-      <c r="N13">
-        <f>H13 * L13</f>
-        <v/>
-      </c>
-      <c r="O13">
+      <c r="N13" s="5">
+        <f>H13 * (L13/100)</f>
+        <v/>
+      </c>
+      <c r="O13" s="5">
         <f>K13</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="X13" s="4" t="n"/>
+      <c r="Y13" s="5">
         <f>IF(TODAY()&lt;R13, 0, IF(TODAY()&gt;S13, T13, T13 * (TODAY()-R13)/(S13-R13+1)))</f>
         <v/>
       </c>
-      <c r="Z13">
-        <f>T13 * X13</f>
-        <v/>
-      </c>
-      <c r="AA13">
+      <c r="Z13" s="5">
+        <f>T13 * (X13/100)</f>
+        <v/>
+      </c>
+      <c r="AA13" s="5">
         <f>W13</f>
         <v/>
       </c>
-      <c r="AK13">
+      <c r="AJ13" s="4" t="n"/>
+      <c r="AK13" s="5">
         <f>IF(TODAY()&lt;AD13, 0, IF(TODAY()&gt;AE13, AF13, AF13 * (TODAY()-AD13)/(AE13-AD13+1)))</f>
         <v/>
       </c>
-      <c r="AL13">
-        <f>AF13 * AJ13</f>
-        <v/>
-      </c>
-      <c r="AM13">
+      <c r="AL13" s="5">
+        <f>AF13 * (AJ13/100)</f>
+        <v/>
+      </c>
+      <c r="AM13" s="5">
         <f>AI13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="M14">
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="5">
         <f>IF(TODAY()&lt;F14, 0, IF(TODAY()&gt;G14, H14, H14 * (TODAY()-F14)/(G14-F14+1)))</f>
         <v/>
       </c>
-      <c r="N14">
-        <f>H14 * L14</f>
-        <v/>
-      </c>
-      <c r="O14">
+      <c r="N14" s="5">
+        <f>H14 * (L14/100)</f>
+        <v/>
+      </c>
+      <c r="O14" s="5">
         <f>K14</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="X14" s="4" t="n"/>
+      <c r="Y14" s="5">
         <f>IF(TODAY()&lt;R14, 0, IF(TODAY()&gt;S14, T14, T14 * (TODAY()-R14)/(S14-R14+1)))</f>
         <v/>
       </c>
-      <c r="Z14">
-        <f>T14 * X14</f>
-        <v/>
-      </c>
-      <c r="AA14">
+      <c r="Z14" s="5">
+        <f>T14 * (X14/100)</f>
+        <v/>
+      </c>
+      <c r="AA14" s="5">
         <f>W14</f>
         <v/>
       </c>
-      <c r="AK14">
+      <c r="AJ14" s="4" t="n"/>
+      <c r="AK14" s="5">
         <f>IF(TODAY()&lt;AD14, 0, IF(TODAY()&gt;AE14, AF14, AF14 * (TODAY()-AD14)/(AE14-AD14+1)))</f>
         <v/>
       </c>
-      <c r="AL14">
-        <f>AF14 * AJ14</f>
-        <v/>
-      </c>
-      <c r="AM14">
+      <c r="AL14" s="5">
+        <f>AF14 * (AJ14/100)</f>
+        <v/>
+      </c>
+      <c r="AM14" s="5">
         <f>AI14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="M15">
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="5">
         <f>IF(TODAY()&lt;F15, 0, IF(TODAY()&gt;G15, H15, H15 * (TODAY()-F15)/(G15-F15+1)))</f>
         <v/>
       </c>
-      <c r="N15">
-        <f>H15 * L15</f>
-        <v/>
-      </c>
-      <c r="O15">
+      <c r="N15" s="5">
+        <f>H15 * (L15/100)</f>
+        <v/>
+      </c>
+      <c r="O15" s="5">
         <f>K15</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="X15" s="4" t="n"/>
+      <c r="Y15" s="5">
         <f>IF(TODAY()&lt;R15, 0, IF(TODAY()&gt;S15, T15, T15 * (TODAY()-R15)/(S15-R15+1)))</f>
         <v/>
       </c>
-      <c r="Z15">
-        <f>T15 * X15</f>
-        <v/>
-      </c>
-      <c r="AA15">
+      <c r="Z15" s="5">
+        <f>T15 * (X15/100)</f>
+        <v/>
+      </c>
+      <c r="AA15" s="5">
         <f>W15</f>
         <v/>
       </c>
-      <c r="AK15">
+      <c r="AJ15" s="4" t="n"/>
+      <c r="AK15" s="5">
         <f>IF(TODAY()&lt;AD15, 0, IF(TODAY()&gt;AE15, AF15, AF15 * (TODAY()-AD15)/(AE15-AD15+1)))</f>
         <v/>
       </c>
-      <c r="AL15">
-        <f>AF15 * AJ15</f>
-        <v/>
-      </c>
-      <c r="AM15">
+      <c r="AL15" s="5">
+        <f>AF15 * (AJ15/100)</f>
+        <v/>
+      </c>
+      <c r="AM15" s="5">
         <f>AI15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="M16">
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="5">
         <f>IF(TODAY()&lt;F16, 0, IF(TODAY()&gt;G16, H16, H16 * (TODAY()-F16)/(G16-F16+1)))</f>
         <v/>
       </c>
-      <c r="N16">
-        <f>H16 * L16</f>
-        <v/>
-      </c>
-      <c r="O16">
+      <c r="N16" s="5">
+        <f>H16 * (L16/100)</f>
+        <v/>
+      </c>
+      <c r="O16" s="5">
         <f>K16</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="X16" s="4" t="n"/>
+      <c r="Y16" s="5">
         <f>IF(TODAY()&lt;R16, 0, IF(TODAY()&gt;S16, T16, T16 * (TODAY()-R16)/(S16-R16+1)))</f>
         <v/>
       </c>
-      <c r="Z16">
-        <f>T16 * X16</f>
-        <v/>
-      </c>
-      <c r="AA16">
+      <c r="Z16" s="5">
+        <f>T16 * (X16/100)</f>
+        <v/>
+      </c>
+      <c r="AA16" s="5">
         <f>W16</f>
         <v/>
       </c>
-      <c r="AK16">
+      <c r="AJ16" s="4" t="n"/>
+      <c r="AK16" s="5">
         <f>IF(TODAY()&lt;AD16, 0, IF(TODAY()&gt;AE16, AF16, AF16 * (TODAY()-AD16)/(AE16-AD16+1)))</f>
         <v/>
       </c>
-      <c r="AL16">
-        <f>AF16 * AJ16</f>
-        <v/>
-      </c>
-      <c r="AM16">
+      <c r="AL16" s="5">
+        <f>AF16 * (AJ16/100)</f>
+        <v/>
+      </c>
+      <c r="AM16" s="5">
         <f>AI16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="M17">
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="5">
         <f>IF(TODAY()&lt;F17, 0, IF(TODAY()&gt;G17, H17, H17 * (TODAY()-F17)/(G17-F17+1)))</f>
         <v/>
       </c>
-      <c r="N17">
-        <f>H17 * L17</f>
-        <v/>
-      </c>
-      <c r="O17">
+      <c r="N17" s="5">
+        <f>H17 * (L17/100)</f>
+        <v/>
+      </c>
+      <c r="O17" s="5">
         <f>K17</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="X17" s="4" t="n"/>
+      <c r="Y17" s="5">
         <f>IF(TODAY()&lt;R17, 0, IF(TODAY()&gt;S17, T17, T17 * (TODAY()-R17)/(S17-R17+1)))</f>
         <v/>
       </c>
-      <c r="Z17">
-        <f>T17 * X17</f>
-        <v/>
-      </c>
-      <c r="AA17">
+      <c r="Z17" s="5">
+        <f>T17 * (X17/100)</f>
+        <v/>
+      </c>
+      <c r="AA17" s="5">
         <f>W17</f>
         <v/>
       </c>
-      <c r="AK17">
+      <c r="AJ17" s="4" t="n"/>
+      <c r="AK17" s="5">
         <f>IF(TODAY()&lt;AD17, 0, IF(TODAY()&gt;AE17, AF17, AF17 * (TODAY()-AD17)/(AE17-AD17+1)))</f>
         <v/>
       </c>
-      <c r="AL17">
-        <f>AF17 * AJ17</f>
-        <v/>
-      </c>
-      <c r="AM17">
+      <c r="AL17" s="5">
+        <f>AF17 * (AJ17/100)</f>
+        <v/>
+      </c>
+      <c r="AM17" s="5">
         <f>AI17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="M18">
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="5">
         <f>IF(TODAY()&lt;F18, 0, IF(TODAY()&gt;G18, H18, H18 * (TODAY()-F18)/(G18-F18+1)))</f>
         <v/>
       </c>
-      <c r="N18">
-        <f>H18 * L18</f>
-        <v/>
-      </c>
-      <c r="O18">
+      <c r="N18" s="5">
+        <f>H18 * (L18/100)</f>
+        <v/>
+      </c>
+      <c r="O18" s="5">
         <f>K18</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="X18" s="4" t="n"/>
+      <c r="Y18" s="5">
         <f>IF(TODAY()&lt;R18, 0, IF(TODAY()&gt;S18, T18, T18 * (TODAY()-R18)/(S18-R18+1)))</f>
         <v/>
       </c>
-      <c r="Z18">
-        <f>T18 * X18</f>
-        <v/>
-      </c>
-      <c r="AA18">
+      <c r="Z18" s="5">
+        <f>T18 * (X18/100)</f>
+        <v/>
+      </c>
+      <c r="AA18" s="5">
         <f>W18</f>
         <v/>
       </c>
-      <c r="AK18">
+      <c r="AJ18" s="4" t="n"/>
+      <c r="AK18" s="5">
         <f>IF(TODAY()&lt;AD18, 0, IF(TODAY()&gt;AE18, AF18, AF18 * (TODAY()-AD18)/(AE18-AD18+1)))</f>
         <v/>
       </c>
-      <c r="AL18">
-        <f>AF18 * AJ18</f>
-        <v/>
-      </c>
-      <c r="AM18">
+      <c r="AL18" s="5">
+        <f>AF18 * (AJ18/100)</f>
+        <v/>
+      </c>
+      <c r="AM18" s="5">
         <f>AI18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="M19">
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="5">
         <f>IF(TODAY()&lt;F19, 0, IF(TODAY()&gt;G19, H19, H19 * (TODAY()-F19)/(G19-F19+1)))</f>
         <v/>
       </c>
-      <c r="N19">
-        <f>H19 * L19</f>
-        <v/>
-      </c>
-      <c r="O19">
+      <c r="N19" s="5">
+        <f>H19 * (L19/100)</f>
+        <v/>
+      </c>
+      <c r="O19" s="5">
         <f>K19</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="X19" s="4" t="n"/>
+      <c r="Y19" s="5">
         <f>IF(TODAY()&lt;R19, 0, IF(TODAY()&gt;S19, T19, T19 * (TODAY()-R19)/(S19-R19+1)))</f>
         <v/>
       </c>
-      <c r="Z19">
-        <f>T19 * X19</f>
-        <v/>
-      </c>
-      <c r="AA19">
+      <c r="Z19" s="5">
+        <f>T19 * (X19/100)</f>
+        <v/>
+      </c>
+      <c r="AA19" s="5">
         <f>W19</f>
         <v/>
       </c>
-      <c r="AK19">
+      <c r="AJ19" s="4" t="n"/>
+      <c r="AK19" s="5">
         <f>IF(TODAY()&lt;AD19, 0, IF(TODAY()&gt;AE19, AF19, AF19 * (TODAY()-AD19)/(AE19-AD19+1)))</f>
         <v/>
       </c>
-      <c r="AL19">
-        <f>AF19 * AJ19</f>
-        <v/>
-      </c>
-      <c r="AM19">
+      <c r="AL19" s="5">
+        <f>AF19 * (AJ19/100)</f>
+        <v/>
+      </c>
+      <c r="AM19" s="5">
         <f>AI19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="M20">
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="5">
         <f>IF(TODAY()&lt;F20, 0, IF(TODAY()&gt;G20, H20, H20 * (TODAY()-F20)/(G20-F20+1)))</f>
         <v/>
       </c>
-      <c r="N20">
-        <f>H20 * L20</f>
-        <v/>
-      </c>
-      <c r="O20">
+      <c r="N20" s="5">
+        <f>H20 * (L20/100)</f>
+        <v/>
+      </c>
+      <c r="O20" s="5">
         <f>K20</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="X20" s="4" t="n"/>
+      <c r="Y20" s="5">
         <f>IF(TODAY()&lt;R20, 0, IF(TODAY()&gt;S20, T20, T20 * (TODAY()-R20)/(S20-R20+1)))</f>
         <v/>
       </c>
-      <c r="Z20">
-        <f>T20 * X20</f>
-        <v/>
-      </c>
-      <c r="AA20">
+      <c r="Z20" s="5">
+        <f>T20 * (X20/100)</f>
+        <v/>
+      </c>
+      <c r="AA20" s="5">
         <f>W20</f>
         <v/>
       </c>
-      <c r="AK20">
+      <c r="AJ20" s="4" t="n"/>
+      <c r="AK20" s="5">
         <f>IF(TODAY()&lt;AD20, 0, IF(TODAY()&gt;AE20, AF20, AF20 * (TODAY()-AD20)/(AE20-AD20+1)))</f>
         <v/>
       </c>
-      <c r="AL20">
-        <f>AF20 * AJ20</f>
-        <v/>
-      </c>
-      <c r="AM20">
+      <c r="AL20" s="5">
+        <f>AF20 * (AJ20/100)</f>
+        <v/>
+      </c>
+      <c r="AM20" s="5">
         <f>AI20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="M21">
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="5">
         <f>IF(TODAY()&lt;F21, 0, IF(TODAY()&gt;G21, H21, H21 * (TODAY()-F21)/(G21-F21+1)))</f>
         <v/>
       </c>
-      <c r="N21">
-        <f>H21 * L21</f>
-        <v/>
-      </c>
-      <c r="O21">
+      <c r="N21" s="5">
+        <f>H21 * (L21/100)</f>
+        <v/>
+      </c>
+      <c r="O21" s="5">
         <f>K21</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="X21" s="4" t="n"/>
+      <c r="Y21" s="5">
         <f>IF(TODAY()&lt;R21, 0, IF(TODAY()&gt;S21, T21, T21 * (TODAY()-R21)/(S21-R21+1)))</f>
         <v/>
       </c>
-      <c r="Z21">
-        <f>T21 * X21</f>
-        <v/>
-      </c>
-      <c r="AA21">
+      <c r="Z21" s="5">
+        <f>T21 * (X21/100)</f>
+        <v/>
+      </c>
+      <c r="AA21" s="5">
         <f>W21</f>
         <v/>
       </c>
-      <c r="AK21">
+      <c r="AJ21" s="4" t="n"/>
+      <c r="AK21" s="5">
         <f>IF(TODAY()&lt;AD21, 0, IF(TODAY()&gt;AE21, AF21, AF21 * (TODAY()-AD21)/(AE21-AD21+1)))</f>
         <v/>
       </c>
-      <c r="AL21">
-        <f>AF21 * AJ21</f>
-        <v/>
-      </c>
-      <c r="AM21">
+      <c r="AL21" s="5">
+        <f>AF21 * (AJ21/100)</f>
+        <v/>
+      </c>
+      <c r="AM21" s="5">
         <f>AI21</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="M22">
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="5">
         <f>IF(TODAY()&lt;F22, 0, IF(TODAY()&gt;G22, H22, H22 * (TODAY()-F22)/(G22-F22+1)))</f>
         <v/>
       </c>
-      <c r="N22">
-        <f>H22 * L22</f>
-        <v/>
-      </c>
-      <c r="O22">
+      <c r="N22" s="5">
+        <f>H22 * (L22/100)</f>
+        <v/>
+      </c>
+      <c r="O22" s="5">
         <f>K22</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="X22" s="4" t="n"/>
+      <c r="Y22" s="5">
         <f>IF(TODAY()&lt;R22, 0, IF(TODAY()&gt;S22, T22, T22 * (TODAY()-R22)/(S22-R22+1)))</f>
         <v/>
       </c>
-      <c r="Z22">
-        <f>T22 * X22</f>
-        <v/>
-      </c>
-      <c r="AA22">
+      <c r="Z22" s="5">
+        <f>T22 * (X22/100)</f>
+        <v/>
+      </c>
+      <c r="AA22" s="5">
         <f>W22</f>
         <v/>
       </c>
-      <c r="AK22">
+      <c r="AJ22" s="4" t="n"/>
+      <c r="AK22" s="5">
         <f>IF(TODAY()&lt;AD22, 0, IF(TODAY()&gt;AE22, AF22, AF22 * (TODAY()-AD22)/(AE22-AD22+1)))</f>
         <v/>
       </c>
-      <c r="AL22">
-        <f>AF22 * AJ22</f>
-        <v/>
-      </c>
-      <c r="AM22">
+      <c r="AL22" s="5">
+        <f>AF22 * (AJ22/100)</f>
+        <v/>
+      </c>
+      <c r="AM22" s="5">
         <f>AI22</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="M23">
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="5">
         <f>IF(TODAY()&lt;F23, 0, IF(TODAY()&gt;G23, H23, H23 * (TODAY()-F23)/(G23-F23+1)))</f>
         <v/>
       </c>
-      <c r="N23">
-        <f>H23 * L23</f>
-        <v/>
-      </c>
-      <c r="O23">
+      <c r="N23" s="5">
+        <f>H23 * (L23/100)</f>
+        <v/>
+      </c>
+      <c r="O23" s="5">
         <f>K23</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="X23" s="4" t="n"/>
+      <c r="Y23" s="5">
         <f>IF(TODAY()&lt;R23, 0, IF(TODAY()&gt;S23, T23, T23 * (TODAY()-R23)/(S23-R23+1)))</f>
         <v/>
       </c>
-      <c r="Z23">
-        <f>T23 * X23</f>
-        <v/>
-      </c>
-      <c r="AA23">
+      <c r="Z23" s="5">
+        <f>T23 * (X23/100)</f>
+        <v/>
+      </c>
+      <c r="AA23" s="5">
         <f>W23</f>
         <v/>
       </c>
-      <c r="AK23">
+      <c r="AJ23" s="4" t="n"/>
+      <c r="AK23" s="5">
         <f>IF(TODAY()&lt;AD23, 0, IF(TODAY()&gt;AE23, AF23, AF23 * (TODAY()-AD23)/(AE23-AD23+1)))</f>
         <v/>
       </c>
-      <c r="AL23">
-        <f>AF23 * AJ23</f>
-        <v/>
-      </c>
-      <c r="AM23">
+      <c r="AL23" s="5">
+        <f>AF23 * (AJ23/100)</f>
+        <v/>
+      </c>
+      <c r="AM23" s="5">
         <f>AI23</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="M24">
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="5">
         <f>IF(TODAY()&lt;F24, 0, IF(TODAY()&gt;G24, H24, H24 * (TODAY()-F24)/(G24-F24+1)))</f>
         <v/>
       </c>
-      <c r="N24">
-        <f>H24 * L24</f>
-        <v/>
-      </c>
-      <c r="O24">
+      <c r="N24" s="5">
+        <f>H24 * (L24/100)</f>
+        <v/>
+      </c>
+      <c r="O24" s="5">
         <f>K24</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="X24" s="4" t="n"/>
+      <c r="Y24" s="5">
         <f>IF(TODAY()&lt;R24, 0, IF(TODAY()&gt;S24, T24, T24 * (TODAY()-R24)/(S24-R24+1)))</f>
         <v/>
       </c>
-      <c r="Z24">
-        <f>T24 * X24</f>
-        <v/>
-      </c>
-      <c r="AA24">
+      <c r="Z24" s="5">
+        <f>T24 * (X24/100)</f>
+        <v/>
+      </c>
+      <c r="AA24" s="5">
         <f>W24</f>
         <v/>
       </c>
-      <c r="AK24">
+      <c r="AJ24" s="4" t="n"/>
+      <c r="AK24" s="5">
         <f>IF(TODAY()&lt;AD24, 0, IF(TODAY()&gt;AE24, AF24, AF24 * (TODAY()-AD24)/(AE24-AD24+1)))</f>
         <v/>
       </c>
-      <c r="AL24">
-        <f>AF24 * AJ24</f>
-        <v/>
-      </c>
-      <c r="AM24">
+      <c r="AL24" s="5">
+        <f>AF24 * (AJ24/100)</f>
+        <v/>
+      </c>
+      <c r="AM24" s="5">
         <f>AI24</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="M25">
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="5">
         <f>IF(TODAY()&lt;F25, 0, IF(TODAY()&gt;G25, H25, H25 * (TODAY()-F25)/(G25-F25+1)))</f>
         <v/>
       </c>
-      <c r="N25">
-        <f>H25 * L25</f>
-        <v/>
-      </c>
-      <c r="O25">
+      <c r="N25" s="5">
+        <f>H25 * (L25/100)</f>
+        <v/>
+      </c>
+      <c r="O25" s="5">
         <f>K25</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="X25" s="4" t="n"/>
+      <c r="Y25" s="5">
         <f>IF(TODAY()&lt;R25, 0, IF(TODAY()&gt;S25, T25, T25 * (TODAY()-R25)/(S25-R25+1)))</f>
         <v/>
       </c>
-      <c r="Z25">
-        <f>T25 * X25</f>
-        <v/>
-      </c>
-      <c r="AA25">
+      <c r="Z25" s="5">
+        <f>T25 * (X25/100)</f>
+        <v/>
+      </c>
+      <c r="AA25" s="5">
         <f>W25</f>
         <v/>
       </c>
-      <c r="AK25">
+      <c r="AJ25" s="4" t="n"/>
+      <c r="AK25" s="5">
         <f>IF(TODAY()&lt;AD25, 0, IF(TODAY()&gt;AE25, AF25, AF25 * (TODAY()-AD25)/(AE25-AD25+1)))</f>
         <v/>
       </c>
-      <c r="AL25">
-        <f>AF25 * AJ25</f>
-        <v/>
-      </c>
-      <c r="AM25">
+      <c r="AL25" s="5">
+        <f>AF25 * (AJ25/100)</f>
+        <v/>
+      </c>
+      <c r="AM25" s="5">
         <f>AI25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="M26">
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="5">
         <f>IF(TODAY()&lt;F26, 0, IF(TODAY()&gt;G26, H26, H26 * (TODAY()-F26)/(G26-F26+1)))</f>
         <v/>
       </c>
-      <c r="N26">
-        <f>H26 * L26</f>
-        <v/>
-      </c>
-      <c r="O26">
+      <c r="N26" s="5">
+        <f>H26 * (L26/100)</f>
+        <v/>
+      </c>
+      <c r="O26" s="5">
         <f>K26</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="X26" s="4" t="n"/>
+      <c r="Y26" s="5">
         <f>IF(TODAY()&lt;R26, 0, IF(TODAY()&gt;S26, T26, T26 * (TODAY()-R26)/(S26-R26+1)))</f>
         <v/>
       </c>
-      <c r="Z26">
-        <f>T26 * X26</f>
-        <v/>
-      </c>
-      <c r="AA26">
+      <c r="Z26" s="5">
+        <f>T26 * (X26/100)</f>
+        <v/>
+      </c>
+      <c r="AA26" s="5">
         <f>W26</f>
         <v/>
       </c>
-      <c r="AK26">
+      <c r="AJ26" s="4" t="n"/>
+      <c r="AK26" s="5">
         <f>IF(TODAY()&lt;AD26, 0, IF(TODAY()&gt;AE26, AF26, AF26 * (TODAY()-AD26)/(AE26-AD26+1)))</f>
         <v/>
       </c>
-      <c r="AL26">
-        <f>AF26 * AJ26</f>
-        <v/>
-      </c>
-      <c r="AM26">
+      <c r="AL26" s="5">
+        <f>AF26 * (AJ26/100)</f>
+        <v/>
+      </c>
+      <c r="AM26" s="5">
         <f>AI26</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="M27">
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="5">
         <f>IF(TODAY()&lt;F27, 0, IF(TODAY()&gt;G27, H27, H27 * (TODAY()-F27)/(G27-F27+1)))</f>
         <v/>
       </c>
-      <c r="N27">
-        <f>H27 * L27</f>
-        <v/>
-      </c>
-      <c r="O27">
+      <c r="N27" s="5">
+        <f>H27 * (L27/100)</f>
+        <v/>
+      </c>
+      <c r="O27" s="5">
         <f>K27</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="X27" s="4" t="n"/>
+      <c r="Y27" s="5">
         <f>IF(TODAY()&lt;R27, 0, IF(TODAY()&gt;S27, T27, T27 * (TODAY()-R27)/(S27-R27+1)))</f>
         <v/>
       </c>
-      <c r="Z27">
-        <f>T27 * X27</f>
-        <v/>
-      </c>
-      <c r="AA27">
+      <c r="Z27" s="5">
+        <f>T27 * (X27/100)</f>
+        <v/>
+      </c>
+      <c r="AA27" s="5">
         <f>W27</f>
         <v/>
       </c>
-      <c r="AK27">
+      <c r="AJ27" s="4" t="n"/>
+      <c r="AK27" s="5">
         <f>IF(TODAY()&lt;AD27, 0, IF(TODAY()&gt;AE27, AF27, AF27 * (TODAY()-AD27)/(AE27-AD27+1)))</f>
         <v/>
       </c>
-      <c r="AL27">
-        <f>AF27 * AJ27</f>
-        <v/>
-      </c>
-      <c r="AM27">
+      <c r="AL27" s="5">
+        <f>AF27 * (AJ27/100)</f>
+        <v/>
+      </c>
+      <c r="AM27" s="5">
         <f>AI27</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="M28">
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="5">
         <f>IF(TODAY()&lt;F28, 0, IF(TODAY()&gt;G28, H28, H28 * (TODAY()-F28)/(G28-F28+1)))</f>
         <v/>
       </c>
-      <c r="N28">
-        <f>H28 * L28</f>
-        <v/>
-      </c>
-      <c r="O28">
+      <c r="N28" s="5">
+        <f>H28 * (L28/100)</f>
+        <v/>
+      </c>
+      <c r="O28" s="5">
         <f>K28</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="X28" s="4" t="n"/>
+      <c r="Y28" s="5">
         <f>IF(TODAY()&lt;R28, 0, IF(TODAY()&gt;S28, T28, T28 * (TODAY()-R28)/(S28-R28+1)))</f>
         <v/>
       </c>
-      <c r="Z28">
-        <f>T28 * X28</f>
-        <v/>
-      </c>
-      <c r="AA28">
+      <c r="Z28" s="5">
+        <f>T28 * (X28/100)</f>
+        <v/>
+      </c>
+      <c r="AA28" s="5">
         <f>W28</f>
         <v/>
       </c>
-      <c r="AK28">
+      <c r="AJ28" s="4" t="n"/>
+      <c r="AK28" s="5">
         <f>IF(TODAY()&lt;AD28, 0, IF(TODAY()&gt;AE28, AF28, AF28 * (TODAY()-AD28)/(AE28-AD28+1)))</f>
         <v/>
       </c>
-      <c r="AL28">
-        <f>AF28 * AJ28</f>
-        <v/>
-      </c>
-      <c r="AM28">
+      <c r="AL28" s="5">
+        <f>AF28 * (AJ28/100)</f>
+        <v/>
+      </c>
+      <c r="AM28" s="5">
         <f>AI28</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="M29">
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="5">
         <f>IF(TODAY()&lt;F29, 0, IF(TODAY()&gt;G29, H29, H29 * (TODAY()-F29)/(G29-F29+1)))</f>
         <v/>
       </c>
-      <c r="N29">
-        <f>H29 * L29</f>
-        <v/>
-      </c>
-      <c r="O29">
+      <c r="N29" s="5">
+        <f>H29 * (L29/100)</f>
+        <v/>
+      </c>
+      <c r="O29" s="5">
         <f>K29</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="X29" s="4" t="n"/>
+      <c r="Y29" s="5">
         <f>IF(TODAY()&lt;R29, 0, IF(TODAY()&gt;S29, T29, T29 * (TODAY()-R29)/(S29-R29+1)))</f>
         <v/>
       </c>
-      <c r="Z29">
-        <f>T29 * X29</f>
-        <v/>
-      </c>
-      <c r="AA29">
+      <c r="Z29" s="5">
+        <f>T29 * (X29/100)</f>
+        <v/>
+      </c>
+      <c r="AA29" s="5">
         <f>W29</f>
         <v/>
       </c>
-      <c r="AK29">
+      <c r="AJ29" s="4" t="n"/>
+      <c r="AK29" s="5">
         <f>IF(TODAY()&lt;AD29, 0, IF(TODAY()&gt;AE29, AF29, AF29 * (TODAY()-AD29)/(AE29-AD29+1)))</f>
         <v/>
       </c>
-      <c r="AL29">
-        <f>AF29 * AJ29</f>
-        <v/>
-      </c>
-      <c r="AM29">
+      <c r="AL29" s="5">
+        <f>AF29 * (AJ29/100)</f>
+        <v/>
+      </c>
+      <c r="AM29" s="5">
         <f>AI29</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="M30">
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="5">
         <f>IF(TODAY()&lt;F30, 0, IF(TODAY()&gt;G30, H30, H30 * (TODAY()-F30)/(G30-F30+1)))</f>
         <v/>
       </c>
-      <c r="N30">
-        <f>H30 * L30</f>
-        <v/>
-      </c>
-      <c r="O30">
+      <c r="N30" s="5">
+        <f>H30 * (L30/100)</f>
+        <v/>
+      </c>
+      <c r="O30" s="5">
         <f>K30</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="X30" s="4" t="n"/>
+      <c r="Y30" s="5">
         <f>IF(TODAY()&lt;R30, 0, IF(TODAY()&gt;S30, T30, T30 * (TODAY()-R30)/(S30-R30+1)))</f>
         <v/>
       </c>
-      <c r="Z30">
-        <f>T30 * X30</f>
-        <v/>
-      </c>
-      <c r="AA30">
+      <c r="Z30" s="5">
+        <f>T30 * (X30/100)</f>
+        <v/>
+      </c>
+      <c r="AA30" s="5">
         <f>W30</f>
         <v/>
       </c>
-      <c r="AK30">
+      <c r="AJ30" s="4" t="n"/>
+      <c r="AK30" s="5">
         <f>IF(TODAY()&lt;AD30, 0, IF(TODAY()&gt;AE30, AF30, AF30 * (TODAY()-AD30)/(AE30-AD30+1)))</f>
         <v/>
       </c>
-      <c r="AL30">
-        <f>AF30 * AJ30</f>
-        <v/>
-      </c>
-      <c r="AM30">
+      <c r="AL30" s="5">
+        <f>AF30 * (AJ30/100)</f>
+        <v/>
+      </c>
+      <c r="AM30" s="5">
         <f>AI30</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="M31">
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="5">
         <f>IF(TODAY()&lt;F31, 0, IF(TODAY()&gt;G31, H31, H31 * (TODAY()-F31)/(G31-F31+1)))</f>
         <v/>
       </c>
-      <c r="N31">
-        <f>H31 * L31</f>
-        <v/>
-      </c>
-      <c r="O31">
+      <c r="N31" s="5">
+        <f>H31 * (L31/100)</f>
+        <v/>
+      </c>
+      <c r="O31" s="5">
         <f>K31</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="X31" s="4" t="n"/>
+      <c r="Y31" s="5">
         <f>IF(TODAY()&lt;R31, 0, IF(TODAY()&gt;S31, T31, T31 * (TODAY()-R31)/(S31-R31+1)))</f>
         <v/>
       </c>
-      <c r="Z31">
-        <f>T31 * X31</f>
-        <v/>
-      </c>
-      <c r="AA31">
+      <c r="Z31" s="5">
+        <f>T31 * (X31/100)</f>
+        <v/>
+      </c>
+      <c r="AA31" s="5">
         <f>W31</f>
         <v/>
       </c>
-      <c r="AK31">
+      <c r="AJ31" s="4" t="n"/>
+      <c r="AK31" s="5">
         <f>IF(TODAY()&lt;AD31, 0, IF(TODAY()&gt;AE31, AF31, AF31 * (TODAY()-AD31)/(AE31-AD31+1)))</f>
         <v/>
       </c>
-      <c r="AL31">
-        <f>AF31 * AJ31</f>
-        <v/>
-      </c>
-      <c r="AM31">
+      <c r="AL31" s="5">
+        <f>AF31 * (AJ31/100)</f>
+        <v/>
+      </c>
+      <c r="AM31" s="5">
         <f>AI31</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="M32">
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="5">
         <f>IF(TODAY()&lt;F32, 0, IF(TODAY()&gt;G32, H32, H32 * (TODAY()-F32)/(G32-F32+1)))</f>
         <v/>
       </c>
-      <c r="N32">
-        <f>H32 * L32</f>
-        <v/>
-      </c>
-      <c r="O32">
+      <c r="N32" s="5">
+        <f>H32 * (L32/100)</f>
+        <v/>
+      </c>
+      <c r="O32" s="5">
         <f>K32</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="X32" s="4" t="n"/>
+      <c r="Y32" s="5">
         <f>IF(TODAY()&lt;R32, 0, IF(TODAY()&gt;S32, T32, T32 * (TODAY()-R32)/(S32-R32+1)))</f>
         <v/>
       </c>
-      <c r="Z32">
-        <f>T32 * X32</f>
-        <v/>
-      </c>
-      <c r="AA32">
+      <c r="Z32" s="5">
+        <f>T32 * (X32/100)</f>
+        <v/>
+      </c>
+      <c r="AA32" s="5">
         <f>W32</f>
         <v/>
       </c>
-      <c r="AK32">
+      <c r="AJ32" s="4" t="n"/>
+      <c r="AK32" s="5">
         <f>IF(TODAY()&lt;AD32, 0, IF(TODAY()&gt;AE32, AF32, AF32 * (TODAY()-AD32)/(AE32-AD32+1)))</f>
         <v/>
       </c>
-      <c r="AL32">
-        <f>AF32 * AJ32</f>
-        <v/>
-      </c>
-      <c r="AM32">
+      <c r="AL32" s="5">
+        <f>AF32 * (AJ32/100)</f>
+        <v/>
+      </c>
+      <c r="AM32" s="5">
         <f>AI32</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="M33">
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="5">
         <f>IF(TODAY()&lt;F33, 0, IF(TODAY()&gt;G33, H33, H33 * (TODAY()-F33)/(G33-F33+1)))</f>
         <v/>
       </c>
-      <c r="N33">
-        <f>H33 * L33</f>
-        <v/>
-      </c>
-      <c r="O33">
+      <c r="N33" s="5">
+        <f>H33 * (L33/100)</f>
+        <v/>
+      </c>
+      <c r="O33" s="5">
         <f>K33</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="X33" s="4" t="n"/>
+      <c r="Y33" s="5">
         <f>IF(TODAY()&lt;R33, 0, IF(TODAY()&gt;S33, T33, T33 * (TODAY()-R33)/(S33-R33+1)))</f>
         <v/>
       </c>
-      <c r="Z33">
-        <f>T33 * X33</f>
-        <v/>
-      </c>
-      <c r="AA33">
+      <c r="Z33" s="5">
+        <f>T33 * (X33/100)</f>
+        <v/>
+      </c>
+      <c r="AA33" s="5">
         <f>W33</f>
         <v/>
       </c>
-      <c r="AK33">
+      <c r="AJ33" s="4" t="n"/>
+      <c r="AK33" s="5">
         <f>IF(TODAY()&lt;AD33, 0, IF(TODAY()&gt;AE33, AF33, AF33 * (TODAY()-AD33)/(AE33-AD33+1)))</f>
         <v/>
       </c>
-      <c r="AL33">
-        <f>AF33 * AJ33</f>
-        <v/>
-      </c>
-      <c r="AM33">
+      <c r="AL33" s="5">
+        <f>AF33 * (AJ33/100)</f>
+        <v/>
+      </c>
+      <c r="AM33" s="5">
         <f>AI33</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="M34">
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="5">
         <f>IF(TODAY()&lt;F34, 0, IF(TODAY()&gt;G34, H34, H34 * (TODAY()-F34)/(G34-F34+1)))</f>
         <v/>
       </c>
-      <c r="N34">
-        <f>H34 * L34</f>
-        <v/>
-      </c>
-      <c r="O34">
+      <c r="N34" s="5">
+        <f>H34 * (L34/100)</f>
+        <v/>
+      </c>
+      <c r="O34" s="5">
         <f>K34</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="X34" s="4" t="n"/>
+      <c r="Y34" s="5">
         <f>IF(TODAY()&lt;R34, 0, IF(TODAY()&gt;S34, T34, T34 * (TODAY()-R34)/(S34-R34+1)))</f>
         <v/>
       </c>
-      <c r="Z34">
-        <f>T34 * X34</f>
-        <v/>
-      </c>
-      <c r="AA34">
+      <c r="Z34" s="5">
+        <f>T34 * (X34/100)</f>
+        <v/>
+      </c>
+      <c r="AA34" s="5">
         <f>W34</f>
         <v/>
       </c>
-      <c r="AK34">
+      <c r="AJ34" s="4" t="n"/>
+      <c r="AK34" s="5">
         <f>IF(TODAY()&lt;AD34, 0, IF(TODAY()&gt;AE34, AF34, AF34 * (TODAY()-AD34)/(AE34-AD34+1)))</f>
         <v/>
       </c>
-      <c r="AL34">
-        <f>AF34 * AJ34</f>
-        <v/>
-      </c>
-      <c r="AM34">
+      <c r="AL34" s="5">
+        <f>AF34 * (AJ34/100)</f>
+        <v/>
+      </c>
+      <c r="AM34" s="5">
         <f>AI34</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="M35">
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="5">
         <f>IF(TODAY()&lt;F35, 0, IF(TODAY()&gt;G35, H35, H35 * (TODAY()-F35)/(G35-F35+1)))</f>
         <v/>
       </c>
-      <c r="N35">
-        <f>H35 * L35</f>
-        <v/>
-      </c>
-      <c r="O35">
+      <c r="N35" s="5">
+        <f>H35 * (L35/100)</f>
+        <v/>
+      </c>
+      <c r="O35" s="5">
         <f>K35</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="X35" s="4" t="n"/>
+      <c r="Y35" s="5">
         <f>IF(TODAY()&lt;R35, 0, IF(TODAY()&gt;S35, T35, T35 * (TODAY()-R35)/(S35-R35+1)))</f>
         <v/>
       </c>
-      <c r="Z35">
-        <f>T35 * X35</f>
-        <v/>
-      </c>
-      <c r="AA35">
+      <c r="Z35" s="5">
+        <f>T35 * (X35/100)</f>
+        <v/>
+      </c>
+      <c r="AA35" s="5">
         <f>W35</f>
         <v/>
       </c>
-      <c r="AK35">
+      <c r="AJ35" s="4" t="n"/>
+      <c r="AK35" s="5">
         <f>IF(TODAY()&lt;AD35, 0, IF(TODAY()&gt;AE35, AF35, AF35 * (TODAY()-AD35)/(AE35-AD35+1)))</f>
         <v/>
       </c>
-      <c r="AL35">
-        <f>AF35 * AJ35</f>
-        <v/>
-      </c>
-      <c r="AM35">
+      <c r="AL35" s="5">
+        <f>AF35 * (AJ35/100)</f>
+        <v/>
+      </c>
+      <c r="AM35" s="5">
         <f>AI35</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="M36">
+      <c r="L36" s="4" t="n"/>
+      <c r="M36" s="5">
         <f>IF(TODAY()&lt;F36, 0, IF(TODAY()&gt;G36, H36, H36 * (TODAY()-F36)/(G36-F36+1)))</f>
         <v/>
       </c>
-      <c r="N36">
-        <f>H36 * L36</f>
-        <v/>
-      </c>
-      <c r="O36">
+      <c r="N36" s="5">
+        <f>H36 * (L36/100)</f>
+        <v/>
+      </c>
+      <c r="O36" s="5">
         <f>K36</f>
         <v/>
       </c>
-      <c r="Y36">
+      <c r="X36" s="4" t="n"/>
+      <c r="Y36" s="5">
         <f>IF(TODAY()&lt;R36, 0, IF(TODAY()&gt;S36, T36, T36 * (TODAY()-R36)/(S36-R36+1)))</f>
         <v/>
       </c>
-      <c r="Z36">
-        <f>T36 * X36</f>
-        <v/>
-      </c>
-      <c r="AA36">
+      <c r="Z36" s="5">
+        <f>T36 * (X36/100)</f>
+        <v/>
+      </c>
+      <c r="AA36" s="5">
         <f>W36</f>
         <v/>
       </c>
-      <c r="AK36">
+      <c r="AJ36" s="4" t="n"/>
+      <c r="AK36" s="5">
         <f>IF(TODAY()&lt;AD36, 0, IF(TODAY()&gt;AE36, AF36, AF36 * (TODAY()-AD36)/(AE36-AD36+1)))</f>
         <v/>
       </c>
-      <c r="AL36">
-        <f>AF36 * AJ36</f>
-        <v/>
-      </c>
-      <c r="AM36">
+      <c r="AL36" s="5">
+        <f>AF36 * (AJ36/100)</f>
+        <v/>
+      </c>
+      <c r="AM36" s="5">
         <f>AI36</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="M37">
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="5">
         <f>IF(TODAY()&lt;F37, 0, IF(TODAY()&gt;G37, H37, H37 * (TODAY()-F37)/(G37-F37+1)))</f>
         <v/>
       </c>
-      <c r="N37">
-        <f>H37 * L37</f>
-        <v/>
-      </c>
-      <c r="O37">
+      <c r="N37" s="5">
+        <f>H37 * (L37/100)</f>
+        <v/>
+      </c>
+      <c r="O37" s="5">
         <f>K37</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="X37" s="4" t="n"/>
+      <c r="Y37" s="5">
         <f>IF(TODAY()&lt;R37, 0, IF(TODAY()&gt;S37, T37, T37 * (TODAY()-R37)/(S37-R37+1)))</f>
         <v/>
       </c>
-      <c r="Z37">
-        <f>T37 * X37</f>
-        <v/>
-      </c>
-      <c r="AA37">
+      <c r="Z37" s="5">
+        <f>T37 * (X37/100)</f>
+        <v/>
+      </c>
+      <c r="AA37" s="5">
         <f>W37</f>
         <v/>
       </c>
-      <c r="AK37">
+      <c r="AJ37" s="4" t="n"/>
+      <c r="AK37" s="5">
         <f>IF(TODAY()&lt;AD37, 0, IF(TODAY()&gt;AE37, AF37, AF37 * (TODAY()-AD37)/(AE37-AD37+1)))</f>
         <v/>
       </c>
-      <c r="AL37">
-        <f>AF37 * AJ37</f>
-        <v/>
-      </c>
-      <c r="AM37">
+      <c r="AL37" s="5">
+        <f>AF37 * (AJ37/100)</f>
+        <v/>
+      </c>
+      <c r="AM37" s="5">
         <f>AI37</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="M38">
+      <c r="L38" s="4" t="n"/>
+      <c r="M38" s="5">
         <f>IF(TODAY()&lt;F38, 0, IF(TODAY()&gt;G38, H38, H38 * (TODAY()-F38)/(G38-F38+1)))</f>
         <v/>
       </c>
-      <c r="N38">
-        <f>H38 * L38</f>
-        <v/>
-      </c>
-      <c r="O38">
+      <c r="N38" s="5">
+        <f>H38 * (L38/100)</f>
+        <v/>
+      </c>
+      <c r="O38" s="5">
         <f>K38</f>
         <v/>
       </c>
-      <c r="Y38">
+      <c r="X38" s="4" t="n"/>
+      <c r="Y38" s="5">
         <f>IF(TODAY()&lt;R38, 0, IF(TODAY()&gt;S38, T38, T38 * (TODAY()-R38)/(S38-R38+1)))</f>
         <v/>
       </c>
-      <c r="Z38">
-        <f>T38 * X38</f>
-        <v/>
-      </c>
-      <c r="AA38">
+      <c r="Z38" s="5">
+        <f>T38 * (X38/100)</f>
+        <v/>
+      </c>
+      <c r="AA38" s="5">
         <f>W38</f>
         <v/>
       </c>
-      <c r="AK38">
+      <c r="AJ38" s="4" t="n"/>
+      <c r="AK38" s="5">
         <f>IF(TODAY()&lt;AD38, 0, IF(TODAY()&gt;AE38, AF38, AF38 * (TODAY()-AD38)/(AE38-AD38+1)))</f>
         <v/>
       </c>
-      <c r="AL38">
-        <f>AF38 * AJ38</f>
-        <v/>
-      </c>
-      <c r="AM38">
+      <c r="AL38" s="5">
+        <f>AF38 * (AJ38/100)</f>
+        <v/>
+      </c>
+      <c r="AM38" s="5">
         <f>AI38</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="M39">
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="5">
         <f>IF(TODAY()&lt;F39, 0, IF(TODAY()&gt;G39, H39, H39 * (TODAY()-F39)/(G39-F39+1)))</f>
         <v/>
       </c>
-      <c r="N39">
-        <f>H39 * L39</f>
-        <v/>
-      </c>
-      <c r="O39">
+      <c r="N39" s="5">
+        <f>H39 * (L39/100)</f>
+        <v/>
+      </c>
+      <c r="O39" s="5">
         <f>K39</f>
         <v/>
       </c>
-      <c r="Y39">
+      <c r="X39" s="4" t="n"/>
+      <c r="Y39" s="5">
         <f>IF(TODAY()&lt;R39, 0, IF(TODAY()&gt;S39, T39, T39 * (TODAY()-R39)/(S39-R39+1)))</f>
         <v/>
       </c>
-      <c r="Z39">
-        <f>T39 * X39</f>
-        <v/>
-      </c>
-      <c r="AA39">
+      <c r="Z39" s="5">
+        <f>T39 * (X39/100)</f>
+        <v/>
+      </c>
+      <c r="AA39" s="5">
         <f>W39</f>
         <v/>
       </c>
-      <c r="AK39">
+      <c r="AJ39" s="4" t="n"/>
+      <c r="AK39" s="5">
         <f>IF(TODAY()&lt;AD39, 0, IF(TODAY()&gt;AE39, AF39, AF39 * (TODAY()-AD39)/(AE39-AD39+1)))</f>
         <v/>
       </c>
-      <c r="AL39">
-        <f>AF39 * AJ39</f>
-        <v/>
-      </c>
-      <c r="AM39">
+      <c r="AL39" s="5">
+        <f>AF39 * (AJ39/100)</f>
+        <v/>
+      </c>
+      <c r="AM39" s="5">
         <f>AI39</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="M40">
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="5">
         <f>IF(TODAY()&lt;F40, 0, IF(TODAY()&gt;G40, H40, H40 * (TODAY()-F40)/(G40-F40+1)))</f>
         <v/>
       </c>
-      <c r="N40">
-        <f>H40 * L40</f>
-        <v/>
-      </c>
-      <c r="O40">
+      <c r="N40" s="5">
+        <f>H40 * (L40/100)</f>
+        <v/>
+      </c>
+      <c r="O40" s="5">
         <f>K40</f>
         <v/>
       </c>
-      <c r="Y40">
+      <c r="X40" s="4" t="n"/>
+      <c r="Y40" s="5">
         <f>IF(TODAY()&lt;R40, 0, IF(TODAY()&gt;S40, T40, T40 * (TODAY()-R40)/(S40-R40+1)))</f>
         <v/>
       </c>
-      <c r="Z40">
-        <f>T40 * X40</f>
-        <v/>
-      </c>
-      <c r="AA40">
+      <c r="Z40" s="5">
+        <f>T40 * (X40/100)</f>
+        <v/>
+      </c>
+      <c r="AA40" s="5">
         <f>W40</f>
         <v/>
       </c>
-      <c r="AK40">
+      <c r="AJ40" s="4" t="n"/>
+      <c r="AK40" s="5">
         <f>IF(TODAY()&lt;AD40, 0, IF(TODAY()&gt;AE40, AF40, AF40 * (TODAY()-AD40)/(AE40-AD40+1)))</f>
         <v/>
       </c>
-      <c r="AL40">
-        <f>AF40 * AJ40</f>
-        <v/>
-      </c>
-      <c r="AM40">
+      <c r="AL40" s="5">
+        <f>AF40 * (AJ40/100)</f>
+        <v/>
+      </c>
+      <c r="AM40" s="5">
         <f>AI40</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="M41">
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="5">
         <f>IF(TODAY()&lt;F41, 0, IF(TODAY()&gt;G41, H41, H41 * (TODAY()-F41)/(G41-F41+1)))</f>
         <v/>
       </c>
-      <c r="N41">
-        <f>H41 * L41</f>
-        <v/>
-      </c>
-      <c r="O41">
+      <c r="N41" s="5">
+        <f>H41 * (L41/100)</f>
+        <v/>
+      </c>
+      <c r="O41" s="5">
         <f>K41</f>
         <v/>
       </c>
-      <c r="Y41">
+      <c r="X41" s="4" t="n"/>
+      <c r="Y41" s="5">
         <f>IF(TODAY()&lt;R41, 0, IF(TODAY()&gt;S41, T41, T41 * (TODAY()-R41)/(S41-R41+1)))</f>
         <v/>
       </c>
-      <c r="Z41">
-        <f>T41 * X41</f>
-        <v/>
-      </c>
-      <c r="AA41">
+      <c r="Z41" s="5">
+        <f>T41 * (X41/100)</f>
+        <v/>
+      </c>
+      <c r="AA41" s="5">
         <f>W41</f>
         <v/>
       </c>
-      <c r="AK41">
+      <c r="AJ41" s="4" t="n"/>
+      <c r="AK41" s="5">
         <f>IF(TODAY()&lt;AD41, 0, IF(TODAY()&gt;AE41, AF41, AF41 * (TODAY()-AD41)/(AE41-AD41+1)))</f>
         <v/>
       </c>
-      <c r="AL41">
-        <f>AF41 * AJ41</f>
-        <v/>
-      </c>
-      <c r="AM41">
+      <c r="AL41" s="5">
+        <f>AF41 * (AJ41/100)</f>
+        <v/>
+      </c>
+      <c r="AM41" s="5">
         <f>AI41</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="M42">
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="5">
         <f>IF(TODAY()&lt;F42, 0, IF(TODAY()&gt;G42, H42, H42 * (TODAY()-F42)/(G42-F42+1)))</f>
         <v/>
       </c>
-      <c r="N42">
-        <f>H42 * L42</f>
-        <v/>
-      </c>
-      <c r="O42">
+      <c r="N42" s="5">
+        <f>H42 * (L42/100)</f>
+        <v/>
+      </c>
+      <c r="O42" s="5">
         <f>K42</f>
         <v/>
       </c>
-      <c r="Y42">
+      <c r="X42" s="4" t="n"/>
+      <c r="Y42" s="5">
         <f>IF(TODAY()&lt;R42, 0, IF(TODAY()&gt;S42, T42, T42 * (TODAY()-R42)/(S42-R42+1)))</f>
         <v/>
       </c>
-      <c r="Z42">
-        <f>T42 * X42</f>
-        <v/>
-      </c>
-      <c r="AA42">
+      <c r="Z42" s="5">
+        <f>T42 * (X42/100)</f>
+        <v/>
+      </c>
+      <c r="AA42" s="5">
         <f>W42</f>
         <v/>
       </c>
-      <c r="AK42">
+      <c r="AJ42" s="4" t="n"/>
+      <c r="AK42" s="5">
         <f>IF(TODAY()&lt;AD42, 0, IF(TODAY()&gt;AE42, AF42, AF42 * (TODAY()-AD42)/(AE42-AD42+1)))</f>
         <v/>
       </c>
-      <c r="AL42">
-        <f>AF42 * AJ42</f>
-        <v/>
-      </c>
-      <c r="AM42">
+      <c r="AL42" s="5">
+        <f>AF42 * (AJ42/100)</f>
+        <v/>
+      </c>
+      <c r="AM42" s="5">
         <f>AI42</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="M43">
+      <c r="L43" s="4" t="n"/>
+      <c r="M43" s="5">
         <f>IF(TODAY()&lt;F43, 0, IF(TODAY()&gt;G43, H43, H43 * (TODAY()-F43)/(G43-F43+1)))</f>
         <v/>
       </c>
-      <c r="N43">
-        <f>H43 * L43</f>
-        <v/>
-      </c>
-      <c r="O43">
+      <c r="N43" s="5">
+        <f>H43 * (L43/100)</f>
+        <v/>
+      </c>
+      <c r="O43" s="5">
         <f>K43</f>
         <v/>
       </c>
-      <c r="Y43">
+      <c r="X43" s="4" t="n"/>
+      <c r="Y43" s="5">
         <f>IF(TODAY()&lt;R43, 0, IF(TODAY()&gt;S43, T43, T43 * (TODAY()-R43)/(S43-R43+1)))</f>
         <v/>
       </c>
-      <c r="Z43">
-        <f>T43 * X43</f>
-        <v/>
-      </c>
-      <c r="AA43">
+      <c r="Z43" s="5">
+        <f>T43 * (X43/100)</f>
+        <v/>
+      </c>
+      <c r="AA43" s="5">
         <f>W43</f>
         <v/>
       </c>
-      <c r="AK43">
+      <c r="AJ43" s="4" t="n"/>
+      <c r="AK43" s="5">
         <f>IF(TODAY()&lt;AD43, 0, IF(TODAY()&gt;AE43, AF43, AF43 * (TODAY()-AD43)/(AE43-AD43+1)))</f>
         <v/>
       </c>
-      <c r="AL43">
-        <f>AF43 * AJ43</f>
-        <v/>
-      </c>
-      <c r="AM43">
+      <c r="AL43" s="5">
+        <f>AF43 * (AJ43/100)</f>
+        <v/>
+      </c>
+      <c r="AM43" s="5">
         <f>AI43</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="M44">
+      <c r="L44" s="4" t="n"/>
+      <c r="M44" s="5">
         <f>IF(TODAY()&lt;F44, 0, IF(TODAY()&gt;G44, H44, H44 * (TODAY()-F44)/(G44-F44+1)))</f>
         <v/>
       </c>
-      <c r="N44">
-        <f>H44 * L44</f>
-        <v/>
-      </c>
-      <c r="O44">
+      <c r="N44" s="5">
+        <f>H44 * (L44/100)</f>
+        <v/>
+      </c>
+      <c r="O44" s="5">
         <f>K44</f>
         <v/>
       </c>
-      <c r="Y44">
+      <c r="X44" s="4" t="n"/>
+      <c r="Y44" s="5">
         <f>IF(TODAY()&lt;R44, 0, IF(TODAY()&gt;S44, T44, T44 * (TODAY()-R44)/(S44-R44+1)))</f>
         <v/>
       </c>
-      <c r="Z44">
-        <f>T44 * X44</f>
-        <v/>
-      </c>
-      <c r="AA44">
+      <c r="Z44" s="5">
+        <f>T44 * (X44/100)</f>
+        <v/>
+      </c>
+      <c r="AA44" s="5">
         <f>W44</f>
         <v/>
       </c>
-      <c r="AK44">
+      <c r="AJ44" s="4" t="n"/>
+      <c r="AK44" s="5">
         <f>IF(TODAY()&lt;AD44, 0, IF(TODAY()&gt;AE44, AF44, AF44 * (TODAY()-AD44)/(AE44-AD44+1)))</f>
         <v/>
       </c>
-      <c r="AL44">
-        <f>AF44 * AJ44</f>
-        <v/>
-      </c>
-      <c r="AM44">
+      <c r="AL44" s="5">
+        <f>AF44 * (AJ44/100)</f>
+        <v/>
+      </c>
+      <c r="AM44" s="5">
         <f>AI44</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="M45">
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="5">
         <f>IF(TODAY()&lt;F45, 0, IF(TODAY()&gt;G45, H45, H45 * (TODAY()-F45)/(G45-F45+1)))</f>
         <v/>
       </c>
-      <c r="N45">
-        <f>H45 * L45</f>
-        <v/>
-      </c>
-      <c r="O45">
+      <c r="N45" s="5">
+        <f>H45 * (L45/100)</f>
+        <v/>
+      </c>
+      <c r="O45" s="5">
         <f>K45</f>
         <v/>
       </c>
-      <c r="Y45">
+      <c r="X45" s="4" t="n"/>
+      <c r="Y45" s="5">
         <f>IF(TODAY()&lt;R45, 0, IF(TODAY()&gt;S45, T45, T45 * (TODAY()-R45)/(S45-R45+1)))</f>
         <v/>
       </c>
-      <c r="Z45">
-        <f>T45 * X45</f>
-        <v/>
-      </c>
-      <c r="AA45">
+      <c r="Z45" s="5">
+        <f>T45 * (X45/100)</f>
+        <v/>
+      </c>
+      <c r="AA45" s="5">
         <f>W45</f>
         <v/>
       </c>
-      <c r="AK45">
+      <c r="AJ45" s="4" t="n"/>
+      <c r="AK45" s="5">
         <f>IF(TODAY()&lt;AD45, 0, IF(TODAY()&gt;AE45, AF45, AF45 * (TODAY()-AD45)/(AE45-AD45+1)))</f>
         <v/>
       </c>
-      <c r="AL45">
-        <f>AF45 * AJ45</f>
-        <v/>
-      </c>
-      <c r="AM45">
+      <c r="AL45" s="5">
+        <f>AF45 * (AJ45/100)</f>
+        <v/>
+      </c>
+      <c r="AM45" s="5">
         <f>AI45</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="M46">
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="5">
         <f>IF(TODAY()&lt;F46, 0, IF(TODAY()&gt;G46, H46, H46 * (TODAY()-F46)/(G46-F46+1)))</f>
         <v/>
       </c>
-      <c r="N46">
-        <f>H46 * L46</f>
-        <v/>
-      </c>
-      <c r="O46">
+      <c r="N46" s="5">
+        <f>H46 * (L46/100)</f>
+        <v/>
+      </c>
+      <c r="O46" s="5">
         <f>K46</f>
         <v/>
       </c>
-      <c r="Y46">
+      <c r="X46" s="4" t="n"/>
+      <c r="Y46" s="5">
         <f>IF(TODAY()&lt;R46, 0, IF(TODAY()&gt;S46, T46, T46 * (TODAY()-R46)/(S46-R46+1)))</f>
         <v/>
       </c>
-      <c r="Z46">
-        <f>T46 * X46</f>
-        <v/>
-      </c>
-      <c r="AA46">
+      <c r="Z46" s="5">
+        <f>T46 * (X46/100)</f>
+        <v/>
+      </c>
+      <c r="AA46" s="5">
         <f>W46</f>
         <v/>
       </c>
-      <c r="AK46">
+      <c r="AJ46" s="4" t="n"/>
+      <c r="AK46" s="5">
         <f>IF(TODAY()&lt;AD46, 0, IF(TODAY()&gt;AE46, AF46, AF46 * (TODAY()-AD46)/(AE46-AD46+1)))</f>
         <v/>
       </c>
-      <c r="AL46">
-        <f>AF46 * AJ46</f>
-        <v/>
-      </c>
-      <c r="AM46">
+      <c r="AL46" s="5">
+        <f>AF46 * (AJ46/100)</f>
+        <v/>
+      </c>
+      <c r="AM46" s="5">
         <f>AI46</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="M47">
+      <c r="L47" s="4" t="n"/>
+      <c r="M47" s="5">
         <f>IF(TODAY()&lt;F47, 0, IF(TODAY()&gt;G47, H47, H47 * (TODAY()-F47)/(G47-F47+1)))</f>
         <v/>
       </c>
-      <c r="N47">
-        <f>H47 * L47</f>
-        <v/>
-      </c>
-      <c r="O47">
+      <c r="N47" s="5">
+        <f>H47 * (L47/100)</f>
+        <v/>
+      </c>
+      <c r="O47" s="5">
         <f>K47</f>
         <v/>
       </c>
-      <c r="Y47">
+      <c r="X47" s="4" t="n"/>
+      <c r="Y47" s="5">
         <f>IF(TODAY()&lt;R47, 0, IF(TODAY()&gt;S47, T47, T47 * (TODAY()-R47)/(S47-R47+1)))</f>
         <v/>
       </c>
-      <c r="Z47">
-        <f>T47 * X47</f>
-        <v/>
-      </c>
-      <c r="AA47">
+      <c r="Z47" s="5">
+        <f>T47 * (X47/100)</f>
+        <v/>
+      </c>
+      <c r="AA47" s="5">
         <f>W47</f>
         <v/>
       </c>
-      <c r="AK47">
+      <c r="AJ47" s="4" t="n"/>
+      <c r="AK47" s="5">
         <f>IF(TODAY()&lt;AD47, 0, IF(TODAY()&gt;AE47, AF47, AF47 * (TODAY()-AD47)/(AE47-AD47+1)))</f>
         <v/>
       </c>
-      <c r="AL47">
-        <f>AF47 * AJ47</f>
-        <v/>
-      </c>
-      <c r="AM47">
+      <c r="AL47" s="5">
+        <f>AF47 * (AJ47/100)</f>
+        <v/>
+      </c>
+      <c r="AM47" s="5">
         <f>AI47</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="M48">
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="5">
         <f>IF(TODAY()&lt;F48, 0, IF(TODAY()&gt;G48, H48, H48 * (TODAY()-F48)/(G48-F48+1)))</f>
         <v/>
       </c>
-      <c r="N48">
-        <f>H48 * L48</f>
-        <v/>
-      </c>
-      <c r="O48">
+      <c r="N48" s="5">
+        <f>H48 * (L48/100)</f>
+        <v/>
+      </c>
+      <c r="O48" s="5">
         <f>K48</f>
         <v/>
       </c>
-      <c r="Y48">
+      <c r="X48" s="4" t="n"/>
+      <c r="Y48" s="5">
         <f>IF(TODAY()&lt;R48, 0, IF(TODAY()&gt;S48, T48, T48 * (TODAY()-R48)/(S48-R48+1)))</f>
         <v/>
       </c>
-      <c r="Z48">
-        <f>T48 * X48</f>
-        <v/>
-      </c>
-      <c r="AA48">
+      <c r="Z48" s="5">
+        <f>T48 * (X48/100)</f>
+        <v/>
+      </c>
+      <c r="AA48" s="5">
         <f>W48</f>
         <v/>
       </c>
-      <c r="AK48">
+      <c r="AJ48" s="4" t="n"/>
+      <c r="AK48" s="5">
         <f>IF(TODAY()&lt;AD48, 0, IF(TODAY()&gt;AE48, AF48, AF48 * (TODAY()-AD48)/(AE48-AD48+1)))</f>
         <v/>
       </c>
-      <c r="AL48">
-        <f>AF48 * AJ48</f>
-        <v/>
-      </c>
-      <c r="AM48">
+      <c r="AL48" s="5">
+        <f>AF48 * (AJ48/100)</f>
+        <v/>
+      </c>
+      <c r="AM48" s="5">
         <f>AI48</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="M49">
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="5">
         <f>IF(TODAY()&lt;F49, 0, IF(TODAY()&gt;G49, H49, H49 * (TODAY()-F49)/(G49-F49+1)))</f>
         <v/>
       </c>
-      <c r="N49">
-        <f>H49 * L49</f>
-        <v/>
-      </c>
-      <c r="O49">
+      <c r="N49" s="5">
+        <f>H49 * (L49/100)</f>
+        <v/>
+      </c>
+      <c r="O49" s="5">
         <f>K49</f>
         <v/>
       </c>
-      <c r="Y49">
+      <c r="X49" s="4" t="n"/>
+      <c r="Y49" s="5">
         <f>IF(TODAY()&lt;R49, 0, IF(TODAY()&gt;S49, T49, T49 * (TODAY()-R49)/(S49-R49+1)))</f>
         <v/>
       </c>
-      <c r="Z49">
-        <f>T49 * X49</f>
-        <v/>
-      </c>
-      <c r="AA49">
+      <c r="Z49" s="5">
+        <f>T49 * (X49/100)</f>
+        <v/>
+      </c>
+      <c r="AA49" s="5">
         <f>W49</f>
         <v/>
       </c>
-      <c r="AK49">
+      <c r="AJ49" s="4" t="n"/>
+      <c r="AK49" s="5">
         <f>IF(TODAY()&lt;AD49, 0, IF(TODAY()&gt;AE49, AF49, AF49 * (TODAY()-AD49)/(AE49-AD49+1)))</f>
         <v/>
       </c>
-      <c r="AL49">
-        <f>AF49 * AJ49</f>
-        <v/>
-      </c>
-      <c r="AM49">
+      <c r="AL49" s="5">
+        <f>AF49 * (AJ49/100)</f>
+        <v/>
+      </c>
+      <c r="AM49" s="5">
         <f>AI49</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="M50">
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="5">
         <f>IF(TODAY()&lt;F50, 0, IF(TODAY()&gt;G50, H50, H50 * (TODAY()-F50)/(G50-F50+1)))</f>
         <v/>
       </c>
-      <c r="N50">
-        <f>H50 * L50</f>
-        <v/>
-      </c>
-      <c r="O50">
+      <c r="N50" s="5">
+        <f>H50 * (L50/100)</f>
+        <v/>
+      </c>
+      <c r="O50" s="5">
         <f>K50</f>
         <v/>
       </c>
-      <c r="Y50">
+      <c r="X50" s="4" t="n"/>
+      <c r="Y50" s="5">
         <f>IF(TODAY()&lt;R50, 0, IF(TODAY()&gt;S50, T50, T50 * (TODAY()-R50)/(S50-R50+1)))</f>
         <v/>
       </c>
-      <c r="Z50">
-        <f>T50 * X50</f>
-        <v/>
-      </c>
-      <c r="AA50">
+      <c r="Z50" s="5">
+        <f>T50 * (X50/100)</f>
+        <v/>
+      </c>
+      <c r="AA50" s="5">
         <f>W50</f>
         <v/>
       </c>
-      <c r="AK50">
+      <c r="AJ50" s="4" t="n"/>
+      <c r="AK50" s="5">
         <f>IF(TODAY()&lt;AD50, 0, IF(TODAY()&gt;AE50, AF50, AF50 * (TODAY()-AD50)/(AE50-AD50+1)))</f>
         <v/>
       </c>
-      <c r="AL50">
-        <f>AF50 * AJ50</f>
-        <v/>
-      </c>
-      <c r="AM50">
+      <c r="AL50" s="5">
+        <f>AF50 * (AJ50/100)</f>
+        <v/>
+      </c>
+      <c r="AM50" s="5">
         <f>AI50</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="M51">
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="5">
         <f>IF(TODAY()&lt;F51, 0, IF(TODAY()&gt;G51, H51, H51 * (TODAY()-F51)/(G51-F51+1)))</f>
         <v/>
       </c>
-      <c r="N51">
-        <f>H51 * L51</f>
-        <v/>
-      </c>
-      <c r="O51">
+      <c r="N51" s="5">
+        <f>H51 * (L51/100)</f>
+        <v/>
+      </c>
+      <c r="O51" s="5">
         <f>K51</f>
         <v/>
       </c>
-      <c r="Y51">
+      <c r="X51" s="4" t="n"/>
+      <c r="Y51" s="5">
         <f>IF(TODAY()&lt;R51, 0, IF(TODAY()&gt;S51, T51, T51 * (TODAY()-R51)/(S51-R51+1)))</f>
         <v/>
       </c>
-      <c r="Z51">
-        <f>T51 * X51</f>
-        <v/>
-      </c>
-      <c r="AA51">
+      <c r="Z51" s="5">
+        <f>T51 * (X51/100)</f>
+        <v/>
+      </c>
+      <c r="AA51" s="5">
         <f>W51</f>
         <v/>
       </c>
-      <c r="AK51">
+      <c r="AJ51" s="4" t="n"/>
+      <c r="AK51" s="5">
         <f>IF(TODAY()&lt;AD51, 0, IF(TODAY()&gt;AE51, AF51, AF51 * (TODAY()-AD51)/(AE51-AD51+1)))</f>
         <v/>
       </c>
-      <c r="AL51">
-        <f>AF51 * AJ51</f>
-        <v/>
-      </c>
-      <c r="AM51">
+      <c r="AL51" s="5">
+        <f>AF51 * (AJ51/100)</f>
+        <v/>
+      </c>
+      <c r="AM51" s="5">
         <f>AI51</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="M52">
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="5">
         <f>IF(TODAY()&lt;F52, 0, IF(TODAY()&gt;G52, H52, H52 * (TODAY()-F52)/(G52-F52+1)))</f>
         <v/>
       </c>
-      <c r="N52">
-        <f>H52 * L52</f>
-        <v/>
-      </c>
-      <c r="O52">
+      <c r="N52" s="5">
+        <f>H52 * (L52/100)</f>
+        <v/>
+      </c>
+      <c r="O52" s="5">
         <f>K52</f>
         <v/>
       </c>
-      <c r="Y52">
+      <c r="X52" s="4" t="n"/>
+      <c r="Y52" s="5">
         <f>IF(TODAY()&lt;R52, 0, IF(TODAY()&gt;S52, T52, T52 * (TODAY()-R52)/(S52-R52+1)))</f>
         <v/>
       </c>
-      <c r="Z52">
-        <f>T52 * X52</f>
-        <v/>
-      </c>
-      <c r="AA52">
+      <c r="Z52" s="5">
+        <f>T52 * (X52/100)</f>
+        <v/>
+      </c>
+      <c r="AA52" s="5">
         <f>W52</f>
         <v/>
       </c>
-      <c r="AK52">
+      <c r="AJ52" s="4" t="n"/>
+      <c r="AK52" s="5">
         <f>IF(TODAY()&lt;AD52, 0, IF(TODAY()&gt;AE52, AF52, AF52 * (TODAY()-AD52)/(AE52-AD52+1)))</f>
         <v/>
       </c>
-      <c r="AL52">
-        <f>AF52 * AJ52</f>
-        <v/>
-      </c>
-      <c r="AM52">
+      <c r="AL52" s="5">
+        <f>AF52 * (AJ52/100)</f>
+        <v/>
+      </c>
+      <c r="AM52" s="5">
         <f>AI52</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="M53">
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="5">
         <f>IF(TODAY()&lt;F53, 0, IF(TODAY()&gt;G53, H53, H53 * (TODAY()-F53)/(G53-F53+1)))</f>
         <v/>
       </c>
-      <c r="N53">
-        <f>H53 * L53</f>
-        <v/>
-      </c>
-      <c r="O53">
+      <c r="N53" s="5">
+        <f>H53 * (L53/100)</f>
+        <v/>
+      </c>
+      <c r="O53" s="5">
         <f>K53</f>
         <v/>
       </c>
-      <c r="Y53">
+      <c r="X53" s="4" t="n"/>
+      <c r="Y53" s="5">
         <f>IF(TODAY()&lt;R53, 0, IF(TODAY()&gt;S53, T53, T53 * (TODAY()-R53)/(S53-R53+1)))</f>
         <v/>
       </c>
-      <c r="Z53">
-        <f>T53 * X53</f>
-        <v/>
-      </c>
-      <c r="AA53">
+      <c r="Z53" s="5">
+        <f>T53 * (X53/100)</f>
+        <v/>
+      </c>
+      <c r="AA53" s="5">
         <f>W53</f>
         <v/>
       </c>
-      <c r="AK53">
+      <c r="AJ53" s="4" t="n"/>
+      <c r="AK53" s="5">
         <f>IF(TODAY()&lt;AD53, 0, IF(TODAY()&gt;AE53, AF53, AF53 * (TODAY()-AD53)/(AE53-AD53+1)))</f>
         <v/>
       </c>
-      <c r="AL53">
-        <f>AF53 * AJ53</f>
-        <v/>
-      </c>
-      <c r="AM53">
+      <c r="AL53" s="5">
+        <f>AF53 * (AJ53/100)</f>
+        <v/>
+      </c>
+      <c r="AM53" s="5">
         <f>AI53</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="M54">
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="5">
         <f>IF(TODAY()&lt;F54, 0, IF(TODAY()&gt;G54, H54, H54 * (TODAY()-F54)/(G54-F54+1)))</f>
         <v/>
       </c>
-      <c r="N54">
-        <f>H54 * L54</f>
-        <v/>
-      </c>
-      <c r="O54">
+      <c r="N54" s="5">
+        <f>H54 * (L54/100)</f>
+        <v/>
+      </c>
+      <c r="O54" s="5">
         <f>K54</f>
         <v/>
       </c>
-      <c r="Y54">
+      <c r="X54" s="4" t="n"/>
+      <c r="Y54" s="5">
         <f>IF(TODAY()&lt;R54, 0, IF(TODAY()&gt;S54, T54, T54 * (TODAY()-R54)/(S54-R54+1)))</f>
         <v/>
       </c>
-      <c r="Z54">
-        <f>T54 * X54</f>
-        <v/>
-      </c>
-      <c r="AA54">
+      <c r="Z54" s="5">
+        <f>T54 * (X54/100)</f>
+        <v/>
+      </c>
+      <c r="AA54" s="5">
         <f>W54</f>
         <v/>
       </c>
-      <c r="AK54">
+      <c r="AJ54" s="4" t="n"/>
+      <c r="AK54" s="5">
         <f>IF(TODAY()&lt;AD54, 0, IF(TODAY()&gt;AE54, AF54, AF54 * (TODAY()-AD54)/(AE54-AD54+1)))</f>
         <v/>
       </c>
-      <c r="AL54">
-        <f>AF54 * AJ54</f>
-        <v/>
-      </c>
-      <c r="AM54">
+      <c r="AL54" s="5">
+        <f>AF54 * (AJ54/100)</f>
+        <v/>
+      </c>
+      <c r="AM54" s="5">
         <f>AI54</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="M55">
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="5">
         <f>IF(TODAY()&lt;F55, 0, IF(TODAY()&gt;G55, H55, H55 * (TODAY()-F55)/(G55-F55+1)))</f>
         <v/>
       </c>
-      <c r="N55">
-        <f>H55 * L55</f>
-        <v/>
-      </c>
-      <c r="O55">
+      <c r="N55" s="5">
+        <f>H55 * (L55/100)</f>
+        <v/>
+      </c>
+      <c r="O55" s="5">
         <f>K55</f>
         <v/>
       </c>
-      <c r="Y55">
+      <c r="X55" s="4" t="n"/>
+      <c r="Y55" s="5">
         <f>IF(TODAY()&lt;R55, 0, IF(TODAY()&gt;S55, T55, T55 * (TODAY()-R55)/(S55-R55+1)))</f>
         <v/>
       </c>
-      <c r="Z55">
-        <f>T55 * X55</f>
-        <v/>
-      </c>
-      <c r="AA55">
+      <c r="Z55" s="5">
+        <f>T55 * (X55/100)</f>
+        <v/>
+      </c>
+      <c r="AA55" s="5">
         <f>W55</f>
         <v/>
       </c>
-      <c r="AK55">
+      <c r="AJ55" s="4" t="n"/>
+      <c r="AK55" s="5">
         <f>IF(TODAY()&lt;AD55, 0, IF(TODAY()&gt;AE55, AF55, AF55 * (TODAY()-AD55)/(AE55-AD55+1)))</f>
         <v/>
       </c>
-      <c r="AL55">
-        <f>AF55 * AJ55</f>
-        <v/>
-      </c>
-      <c r="AM55">
+      <c r="AL55" s="5">
+        <f>AF55 * (AJ55/100)</f>
+        <v/>
+      </c>
+      <c r="AM55" s="5">
         <f>AI55</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="M56">
+      <c r="L56" s="4" t="n"/>
+      <c r="M56" s="5">
         <f>IF(TODAY()&lt;F56, 0, IF(TODAY()&gt;G56, H56, H56 * (TODAY()-F56)/(G56-F56+1)))</f>
         <v/>
       </c>
-      <c r="N56">
-        <f>H56 * L56</f>
-        <v/>
-      </c>
-      <c r="O56">
+      <c r="N56" s="5">
+        <f>H56 * (L56/100)</f>
+        <v/>
+      </c>
+      <c r="O56" s="5">
         <f>K56</f>
         <v/>
       </c>
-      <c r="Y56">
+      <c r="X56" s="4" t="n"/>
+      <c r="Y56" s="5">
         <f>IF(TODAY()&lt;R56, 0, IF(TODAY()&gt;S56, T56, T56 * (TODAY()-R56)/(S56-R56+1)))</f>
         <v/>
       </c>
-      <c r="Z56">
-        <f>T56 * X56</f>
-        <v/>
-      </c>
-      <c r="AA56">
+      <c r="Z56" s="5">
+        <f>T56 * (X56/100)</f>
+        <v/>
+      </c>
+      <c r="AA56" s="5">
         <f>W56</f>
         <v/>
       </c>
-      <c r="AK56">
+      <c r="AJ56" s="4" t="n"/>
+      <c r="AK56" s="5">
         <f>IF(TODAY()&lt;AD56, 0, IF(TODAY()&gt;AE56, AF56, AF56 * (TODAY()-AD56)/(AE56-AD56+1)))</f>
         <v/>
       </c>
-      <c r="AL56">
-        <f>AF56 * AJ56</f>
-        <v/>
-      </c>
-      <c r="AM56">
+      <c r="AL56" s="5">
+        <f>AF56 * (AJ56/100)</f>
+        <v/>
+      </c>
+      <c r="AM56" s="5">
         <f>AI56</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="M57">
+      <c r="L57" s="4" t="n"/>
+      <c r="M57" s="5">
         <f>IF(TODAY()&lt;F57, 0, IF(TODAY()&gt;G57, H57, H57 * (TODAY()-F57)/(G57-F57+1)))</f>
         <v/>
       </c>
-      <c r="N57">
-        <f>H57 * L57</f>
-        <v/>
-      </c>
-      <c r="O57">
+      <c r="N57" s="5">
+        <f>H57 * (L57/100)</f>
+        <v/>
+      </c>
+      <c r="O57" s="5">
         <f>K57</f>
         <v/>
       </c>
-      <c r="Y57">
+      <c r="X57" s="4" t="n"/>
+      <c r="Y57" s="5">
         <f>IF(TODAY()&lt;R57, 0, IF(TODAY()&gt;S57, T57, T57 * (TODAY()-R57)/(S57-R57+1)))</f>
         <v/>
       </c>
-      <c r="Z57">
-        <f>T57 * X57</f>
-        <v/>
-      </c>
-      <c r="AA57">
+      <c r="Z57" s="5">
+        <f>T57 * (X57/100)</f>
+        <v/>
+      </c>
+      <c r="AA57" s="5">
         <f>W57</f>
         <v/>
       </c>
-      <c r="AK57">
+      <c r="AJ57" s="4" t="n"/>
+      <c r="AK57" s="5">
         <f>IF(TODAY()&lt;AD57, 0, IF(TODAY()&gt;AE57, AF57, AF57 * (TODAY()-AD57)/(AE57-AD57+1)))</f>
         <v/>
       </c>
-      <c r="AL57">
-        <f>AF57 * AJ57</f>
-        <v/>
-      </c>
-      <c r="AM57">
+      <c r="AL57" s="5">
+        <f>AF57 * (AJ57/100)</f>
+        <v/>
+      </c>
+      <c r="AM57" s="5">
         <f>AI57</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="M58">
+      <c r="L58" s="4" t="n"/>
+      <c r="M58" s="5">
         <f>IF(TODAY()&lt;F58, 0, IF(TODAY()&gt;G58, H58, H58 * (TODAY()-F58)/(G58-F58+1)))</f>
         <v/>
       </c>
-      <c r="N58">
-        <f>H58 * L58</f>
-        <v/>
-      </c>
-      <c r="O58">
+      <c r="N58" s="5">
+        <f>H58 * (L58/100)</f>
+        <v/>
+      </c>
+      <c r="O58" s="5">
         <f>K58</f>
         <v/>
       </c>
-      <c r="Y58">
+      <c r="X58" s="4" t="n"/>
+      <c r="Y58" s="5">
         <f>IF(TODAY()&lt;R58, 0, IF(TODAY()&gt;S58, T58, T58 * (TODAY()-R58)/(S58-R58+1)))</f>
         <v/>
       </c>
-      <c r="Z58">
-        <f>T58 * X58</f>
-        <v/>
-      </c>
-      <c r="AA58">
+      <c r="Z58" s="5">
+        <f>T58 * (X58/100)</f>
+        <v/>
+      </c>
+      <c r="AA58" s="5">
         <f>W58</f>
         <v/>
       </c>
-      <c r="AK58">
+      <c r="AJ58" s="4" t="n"/>
+      <c r="AK58" s="5">
         <f>IF(TODAY()&lt;AD58, 0, IF(TODAY()&gt;AE58, AF58, AF58 * (TODAY()-AD58)/(AE58-AD58+1)))</f>
         <v/>
       </c>
-      <c r="AL58">
-        <f>AF58 * AJ58</f>
-        <v/>
-      </c>
-      <c r="AM58">
+      <c r="AL58" s="5">
+        <f>AF58 * (AJ58/100)</f>
+        <v/>
+      </c>
+      <c r="AM58" s="5">
         <f>AI58</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="M59">
+      <c r="L59" s="4" t="n"/>
+      <c r="M59" s="5">
         <f>IF(TODAY()&lt;F59, 0, IF(TODAY()&gt;G59, H59, H59 * (TODAY()-F59)/(G59-F59+1)))</f>
         <v/>
       </c>
-      <c r="N59">
-        <f>H59 * L59</f>
-        <v/>
-      </c>
-      <c r="O59">
+      <c r="N59" s="5">
+        <f>H59 * (L59/100)</f>
+        <v/>
+      </c>
+      <c r="O59" s="5">
         <f>K59</f>
         <v/>
       </c>
-      <c r="Y59">
+      <c r="X59" s="4" t="n"/>
+      <c r="Y59" s="5">
         <f>IF(TODAY()&lt;R59, 0, IF(TODAY()&gt;S59, T59, T59 * (TODAY()-R59)/(S59-R59+1)))</f>
         <v/>
       </c>
-      <c r="Z59">
-        <f>T59 * X59</f>
-        <v/>
-      </c>
-      <c r="AA59">
+      <c r="Z59" s="5">
+        <f>T59 * (X59/100)</f>
+        <v/>
+      </c>
+      <c r="AA59" s="5">
         <f>W59</f>
         <v/>
       </c>
-      <c r="AK59">
+      <c r="AJ59" s="4" t="n"/>
+      <c r="AK59" s="5">
         <f>IF(TODAY()&lt;AD59, 0, IF(TODAY()&gt;AE59, AF59, AF59 * (TODAY()-AD59)/(AE59-AD59+1)))</f>
         <v/>
       </c>
-      <c r="AL59">
-        <f>AF59 * AJ59</f>
-        <v/>
-      </c>
-      <c r="AM59">
+      <c r="AL59" s="5">
+        <f>AF59 * (AJ59/100)</f>
+        <v/>
+      </c>
+      <c r="AM59" s="5">
         <f>AI59</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="M60">
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="5">
         <f>IF(TODAY()&lt;F60, 0, IF(TODAY()&gt;G60, H60, H60 * (TODAY()-F60)/(G60-F60+1)))</f>
         <v/>
       </c>
-      <c r="N60">
-        <f>H60 * L60</f>
-        <v/>
-      </c>
-      <c r="O60">
+      <c r="N60" s="5">
+        <f>H60 * (L60/100)</f>
+        <v/>
+      </c>
+      <c r="O60" s="5">
         <f>K60</f>
         <v/>
       </c>
-      <c r="Y60">
+      <c r="X60" s="4" t="n"/>
+      <c r="Y60" s="5">
         <f>IF(TODAY()&lt;R60, 0, IF(TODAY()&gt;S60, T60, T60 * (TODAY()-R60)/(S60-R60+1)))</f>
         <v/>
       </c>
-      <c r="Z60">
-        <f>T60 * X60</f>
-        <v/>
-      </c>
-      <c r="AA60">
+      <c r="Z60" s="5">
+        <f>T60 * (X60/100)</f>
+        <v/>
+      </c>
+      <c r="AA60" s="5">
         <f>W60</f>
         <v/>
       </c>
-      <c r="AK60">
+      <c r="AJ60" s="4" t="n"/>
+      <c r="AK60" s="5">
         <f>IF(TODAY()&lt;AD60, 0, IF(TODAY()&gt;AE60, AF60, AF60 * (TODAY()-AD60)/(AE60-AD60+1)))</f>
         <v/>
       </c>
-      <c r="AL60">
-        <f>AF60 * AJ60</f>
-        <v/>
-      </c>
-      <c r="AM60">
+      <c r="AL60" s="5">
+        <f>AF60 * (AJ60/100)</f>
+        <v/>
+      </c>
+      <c r="AM60" s="5">
         <f>AI60</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="M61">
+      <c r="L61" s="4" t="n"/>
+      <c r="M61" s="5">
         <f>IF(TODAY()&lt;F61, 0, IF(TODAY()&gt;G61, H61, H61 * (TODAY()-F61)/(G61-F61+1)))</f>
         <v/>
       </c>
-      <c r="N61">
-        <f>H61 * L61</f>
-        <v/>
-      </c>
-      <c r="O61">
+      <c r="N61" s="5">
+        <f>H61 * (L61/100)</f>
+        <v/>
+      </c>
+      <c r="O61" s="5">
         <f>K61</f>
         <v/>
       </c>
-      <c r="Y61">
+      <c r="X61" s="4" t="n"/>
+      <c r="Y61" s="5">
         <f>IF(TODAY()&lt;R61, 0, IF(TODAY()&gt;S61, T61, T61 * (TODAY()-R61)/(S61-R61+1)))</f>
         <v/>
       </c>
-      <c r="Z61">
-        <f>T61 * X61</f>
-        <v/>
-      </c>
-      <c r="AA61">
+      <c r="Z61" s="5">
+        <f>T61 * (X61/100)</f>
+        <v/>
+      </c>
+      <c r="AA61" s="5">
         <f>W61</f>
         <v/>
       </c>
-      <c r="AK61">
+      <c r="AJ61" s="4" t="n"/>
+      <c r="AK61" s="5">
         <f>IF(TODAY()&lt;AD61, 0, IF(TODAY()&gt;AE61, AF61, AF61 * (TODAY()-AD61)/(AE61-AD61+1)))</f>
         <v/>
       </c>
-      <c r="AL61">
-        <f>AF61 * AJ61</f>
-        <v/>
-      </c>
-      <c r="AM61">
+      <c r="AL61" s="5">
+        <f>AF61 * (AJ61/100)</f>
+        <v/>
+      </c>
+      <c r="AM61" s="5">
         <f>AI61</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="M62">
+      <c r="L62" s="4" t="n"/>
+      <c r="M62" s="5">
         <f>IF(TODAY()&lt;F62, 0, IF(TODAY()&gt;G62, H62, H62 * (TODAY()-F62)/(G62-F62+1)))</f>
         <v/>
       </c>
-      <c r="N62">
-        <f>H62 * L62</f>
-        <v/>
-      </c>
-      <c r="O62">
+      <c r="N62" s="5">
+        <f>H62 * (L62/100)</f>
+        <v/>
+      </c>
+      <c r="O62" s="5">
         <f>K62</f>
         <v/>
       </c>
-      <c r="Y62">
+      <c r="X62" s="4" t="n"/>
+      <c r="Y62" s="5">
         <f>IF(TODAY()&lt;R62, 0, IF(TODAY()&gt;S62, T62, T62 * (TODAY()-R62)/(S62-R62+1)))</f>
         <v/>
       </c>
-      <c r="Z62">
-        <f>T62 * X62</f>
-        <v/>
-      </c>
-      <c r="AA62">
+      <c r="Z62" s="5">
+        <f>T62 * (X62/100)</f>
+        <v/>
+      </c>
+      <c r="AA62" s="5">
         <f>W62</f>
         <v/>
       </c>
-      <c r="AK62">
+      <c r="AJ62" s="4" t="n"/>
+      <c r="AK62" s="5">
         <f>IF(TODAY()&lt;AD62, 0, IF(TODAY()&gt;AE62, AF62, AF62 * (TODAY()-AD62)/(AE62-AD62+1)))</f>
         <v/>
       </c>
-      <c r="AL62">
-        <f>AF62 * AJ62</f>
-        <v/>
-      </c>
-      <c r="AM62">
+      <c r="AL62" s="5">
+        <f>AF62 * (AJ62/100)</f>
+        <v/>
+      </c>
+      <c r="AM62" s="5">
         <f>AI62</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="M63">
+      <c r="L63" s="4" t="n"/>
+      <c r="M63" s="5">
         <f>IF(TODAY()&lt;F63, 0, IF(TODAY()&gt;G63, H63, H63 * (TODAY()-F63)/(G63-F63+1)))</f>
         <v/>
       </c>
-      <c r="N63">
-        <f>H63 * L63</f>
-        <v/>
-      </c>
-      <c r="O63">
+      <c r="N63" s="5">
+        <f>H63 * (L63/100)</f>
+        <v/>
+      </c>
+      <c r="O63" s="5">
         <f>K63</f>
         <v/>
       </c>
-      <c r="Y63">
+      <c r="X63" s="4" t="n"/>
+      <c r="Y63" s="5">
         <f>IF(TODAY()&lt;R63, 0, IF(TODAY()&gt;S63, T63, T63 * (TODAY()-R63)/(S63-R63+1)))</f>
         <v/>
       </c>
-      <c r="Z63">
-        <f>T63 * X63</f>
-        <v/>
-      </c>
-      <c r="AA63">
+      <c r="Z63" s="5">
+        <f>T63 * (X63/100)</f>
+        <v/>
+      </c>
+      <c r="AA63" s="5">
         <f>W63</f>
         <v/>
       </c>
-      <c r="AK63">
+      <c r="AJ63" s="4" t="n"/>
+      <c r="AK63" s="5">
         <f>IF(TODAY()&lt;AD63, 0, IF(TODAY()&gt;AE63, AF63, AF63 * (TODAY()-AD63)/(AE63-AD63+1)))</f>
         <v/>
       </c>
-      <c r="AL63">
-        <f>AF63 * AJ63</f>
-        <v/>
-      </c>
-      <c r="AM63">
+      <c r="AL63" s="5">
+        <f>AF63 * (AJ63/100)</f>
+        <v/>
+      </c>
+      <c r="AM63" s="5">
         <f>AI63</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="M64">
+      <c r="L64" s="4" t="n"/>
+      <c r="M64" s="5">
         <f>IF(TODAY()&lt;F64, 0, IF(TODAY()&gt;G64, H64, H64 * (TODAY()-F64)/(G64-F64+1)))</f>
         <v/>
       </c>
-      <c r="N64">
-        <f>H64 * L64</f>
-        <v/>
-      </c>
-      <c r="O64">
+      <c r="N64" s="5">
+        <f>H64 * (L64/100)</f>
+        <v/>
+      </c>
+      <c r="O64" s="5">
         <f>K64</f>
         <v/>
       </c>
-      <c r="Y64">
+      <c r="X64" s="4" t="n"/>
+      <c r="Y64" s="5">
         <f>IF(TODAY()&lt;R64, 0, IF(TODAY()&gt;S64, T64, T64 * (TODAY()-R64)/(S64-R64+1)))</f>
         <v/>
       </c>
-      <c r="Z64">
-        <f>T64 * X64</f>
-        <v/>
-      </c>
-      <c r="AA64">
+      <c r="Z64" s="5">
+        <f>T64 * (X64/100)</f>
+        <v/>
+      </c>
+      <c r="AA64" s="5">
         <f>W64</f>
         <v/>
       </c>
-      <c r="AK64">
+      <c r="AJ64" s="4" t="n"/>
+      <c r="AK64" s="5">
         <f>IF(TODAY()&lt;AD64, 0, IF(TODAY()&gt;AE64, AF64, AF64 * (TODAY()-AD64)/(AE64-AD64+1)))</f>
         <v/>
       </c>
-      <c r="AL64">
-        <f>AF64 * AJ64</f>
-        <v/>
-      </c>
-      <c r="AM64">
+      <c r="AL64" s="5">
+        <f>AF64 * (AJ64/100)</f>
+        <v/>
+      </c>
+      <c r="AM64" s="5">
         <f>AI64</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="M65">
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="5">
         <f>IF(TODAY()&lt;F65, 0, IF(TODAY()&gt;G65, H65, H65 * (TODAY()-F65)/(G65-F65+1)))</f>
         <v/>
       </c>
-      <c r="N65">
-        <f>H65 * L65</f>
-        <v/>
-      </c>
-      <c r="O65">
+      <c r="N65" s="5">
+        <f>H65 * (L65/100)</f>
+        <v/>
+      </c>
+      <c r="O65" s="5">
         <f>K65</f>
         <v/>
       </c>
-      <c r="Y65">
+      <c r="X65" s="4" t="n"/>
+      <c r="Y65" s="5">
         <f>IF(TODAY()&lt;R65, 0, IF(TODAY()&gt;S65, T65, T65 * (TODAY()-R65)/(S65-R65+1)))</f>
         <v/>
       </c>
-      <c r="Z65">
-        <f>T65 * X65</f>
-        <v/>
-      </c>
-      <c r="AA65">
+      <c r="Z65" s="5">
+        <f>T65 * (X65/100)</f>
+        <v/>
+      </c>
+      <c r="AA65" s="5">
         <f>W65</f>
         <v/>
       </c>
-      <c r="AK65">
+      <c r="AJ65" s="4" t="n"/>
+      <c r="AK65" s="5">
         <f>IF(TODAY()&lt;AD65, 0, IF(TODAY()&gt;AE65, AF65, AF65 * (TODAY()-AD65)/(AE65-AD65+1)))</f>
         <v/>
       </c>
-      <c r="AL65">
-        <f>AF65 * AJ65</f>
-        <v/>
-      </c>
-      <c r="AM65">
+      <c r="AL65" s="5">
+        <f>AF65 * (AJ65/100)</f>
+        <v/>
+      </c>
+      <c r="AM65" s="5">
         <f>AI65</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="M66">
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="5">
         <f>IF(TODAY()&lt;F66, 0, IF(TODAY()&gt;G66, H66, H66 * (TODAY()-F66)/(G66-F66+1)))</f>
         <v/>
       </c>
-      <c r="N66">
-        <f>H66 * L66</f>
-        <v/>
-      </c>
-      <c r="O66">
+      <c r="N66" s="5">
+        <f>H66 * (L66/100)</f>
+        <v/>
+      </c>
+      <c r="O66" s="5">
         <f>K66</f>
         <v/>
       </c>
-      <c r="Y66">
+      <c r="X66" s="4" t="n"/>
+      <c r="Y66" s="5">
         <f>IF(TODAY()&lt;R66, 0, IF(TODAY()&gt;S66, T66, T66 * (TODAY()-R66)/(S66-R66+1)))</f>
         <v/>
       </c>
-      <c r="Z66">
-        <f>T66 * X66</f>
-        <v/>
-      </c>
-      <c r="AA66">
+      <c r="Z66" s="5">
+        <f>T66 * (X66/100)</f>
+        <v/>
+      </c>
+      <c r="AA66" s="5">
         <f>W66</f>
         <v/>
       </c>
-      <c r="AK66">
+      <c r="AJ66" s="4" t="n"/>
+      <c r="AK66" s="5">
         <f>IF(TODAY()&lt;AD66, 0, IF(TODAY()&gt;AE66, AF66, AF66 * (TODAY()-AD66)/(AE66-AD66+1)))</f>
         <v/>
       </c>
-      <c r="AL66">
-        <f>AF66 * AJ66</f>
-        <v/>
-      </c>
-      <c r="AM66">
+      <c r="AL66" s="5">
+        <f>AF66 * (AJ66/100)</f>
+        <v/>
+      </c>
+      <c r="AM66" s="5">
         <f>AI66</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="M67">
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="5">
         <f>IF(TODAY()&lt;F67, 0, IF(TODAY()&gt;G67, H67, H67 * (TODAY()-F67)/(G67-F67+1)))</f>
         <v/>
       </c>
-      <c r="N67">
-        <f>H67 * L67</f>
-        <v/>
-      </c>
-      <c r="O67">
+      <c r="N67" s="5">
+        <f>H67 * (L67/100)</f>
+        <v/>
+      </c>
+      <c r="O67" s="5">
         <f>K67</f>
         <v/>
       </c>
-      <c r="Y67">
+      <c r="X67" s="4" t="n"/>
+      <c r="Y67" s="5">
         <f>IF(TODAY()&lt;R67, 0, IF(TODAY()&gt;S67, T67, T67 * (TODAY()-R67)/(S67-R67+1)))</f>
         <v/>
       </c>
-      <c r="Z67">
-        <f>T67 * X67</f>
-        <v/>
-      </c>
-      <c r="AA67">
+      <c r="Z67" s="5">
+        <f>T67 * (X67/100)</f>
+        <v/>
+      </c>
+      <c r="AA67" s="5">
         <f>W67</f>
         <v/>
       </c>
-      <c r="AK67">
+      <c r="AJ67" s="4" t="n"/>
+      <c r="AK67" s="5">
         <f>IF(TODAY()&lt;AD67, 0, IF(TODAY()&gt;AE67, AF67, AF67 * (TODAY()-AD67)/(AE67-AD67+1)))</f>
         <v/>
       </c>
-      <c r="AL67">
-        <f>AF67 * AJ67</f>
-        <v/>
-      </c>
-      <c r="AM67">
+      <c r="AL67" s="5">
+        <f>AF67 * (AJ67/100)</f>
+        <v/>
+      </c>
+      <c r="AM67" s="5">
         <f>AI67</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="M68">
+      <c r="L68" s="4" t="n"/>
+      <c r="M68" s="5">
         <f>IF(TODAY()&lt;F68, 0, IF(TODAY()&gt;G68, H68, H68 * (TODAY()-F68)/(G68-F68+1)))</f>
         <v/>
       </c>
-      <c r="N68">
-        <f>H68 * L68</f>
-        <v/>
-      </c>
-      <c r="O68">
+      <c r="N68" s="5">
+        <f>H68 * (L68/100)</f>
+        <v/>
+      </c>
+      <c r="O68" s="5">
         <f>K68</f>
         <v/>
       </c>
-      <c r="Y68">
+      <c r="X68" s="4" t="n"/>
+      <c r="Y68" s="5">
         <f>IF(TODAY()&lt;R68, 0, IF(TODAY()&gt;S68, T68, T68 * (TODAY()-R68)/(S68-R68+1)))</f>
         <v/>
       </c>
-      <c r="Z68">
-        <f>T68 * X68</f>
-        <v/>
-      </c>
-      <c r="AA68">
+      <c r="Z68" s="5">
+        <f>T68 * (X68/100)</f>
+        <v/>
+      </c>
+      <c r="AA68" s="5">
         <f>W68</f>
         <v/>
       </c>
-      <c r="AK68">
+      <c r="AJ68" s="4" t="n"/>
+      <c r="AK68" s="5">
         <f>IF(TODAY()&lt;AD68, 0, IF(TODAY()&gt;AE68, AF68, AF68 * (TODAY()-AD68)/(AE68-AD68+1)))</f>
         <v/>
       </c>
-      <c r="AL68">
-        <f>AF68 * AJ68</f>
-        <v/>
-      </c>
-      <c r="AM68">
+      <c r="AL68" s="5">
+        <f>AF68 * (AJ68/100)</f>
+        <v/>
+      </c>
+      <c r="AM68" s="5">
         <f>AI68</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="M69">
+      <c r="L69" s="4" t="n"/>
+      <c r="M69" s="5">
         <f>IF(TODAY()&lt;F69, 0, IF(TODAY()&gt;G69, H69, H69 * (TODAY()-F69)/(G69-F69+1)))</f>
         <v/>
       </c>
-      <c r="N69">
-        <f>H69 * L69</f>
-        <v/>
-      </c>
-      <c r="O69">
+      <c r="N69" s="5">
+        <f>H69 * (L69/100)</f>
+        <v/>
+      </c>
+      <c r="O69" s="5">
         <f>K69</f>
         <v/>
       </c>
-      <c r="Y69">
+      <c r="X69" s="4" t="n"/>
+      <c r="Y69" s="5">
         <f>IF(TODAY()&lt;R69, 0, IF(TODAY()&gt;S69, T69, T69 * (TODAY()-R69)/(S69-R69+1)))</f>
         <v/>
       </c>
-      <c r="Z69">
-        <f>T69 * X69</f>
-        <v/>
-      </c>
-      <c r="AA69">
+      <c r="Z69" s="5">
+        <f>T69 * (X69/100)</f>
+        <v/>
+      </c>
+      <c r="AA69" s="5">
         <f>W69</f>
         <v/>
       </c>
-      <c r="AK69">
+      <c r="AJ69" s="4" t="n"/>
+      <c r="AK69" s="5">
         <f>IF(TODAY()&lt;AD69, 0, IF(TODAY()&gt;AE69, AF69, AF69 * (TODAY()-AD69)/(AE69-AD69+1)))</f>
         <v/>
       </c>
-      <c r="AL69">
-        <f>AF69 * AJ69</f>
-        <v/>
-      </c>
-      <c r="AM69">
+      <c r="AL69" s="5">
+        <f>AF69 * (AJ69/100)</f>
+        <v/>
+      </c>
+      <c r="AM69" s="5">
         <f>AI69</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="M70">
+      <c r="L70" s="4" t="n"/>
+      <c r="M70" s="5">
         <f>IF(TODAY()&lt;F70, 0, IF(TODAY()&gt;G70, H70, H70 * (TODAY()-F70)/(G70-F70+1)))</f>
         <v/>
       </c>
-      <c r="N70">
-        <f>H70 * L70</f>
-        <v/>
-      </c>
-      <c r="O70">
+      <c r="N70" s="5">
+        <f>H70 * (L70/100)</f>
+        <v/>
+      </c>
+      <c r="O70" s="5">
         <f>K70</f>
         <v/>
       </c>
-      <c r="Y70">
+      <c r="X70" s="4" t="n"/>
+      <c r="Y70" s="5">
         <f>IF(TODAY()&lt;R70, 0, IF(TODAY()&gt;S70, T70, T70 * (TODAY()-R70)/(S70-R70+1)))</f>
         <v/>
       </c>
-      <c r="Z70">
-        <f>T70 * X70</f>
-        <v/>
-      </c>
-      <c r="AA70">
+      <c r="Z70" s="5">
+        <f>T70 * (X70/100)</f>
+        <v/>
+      </c>
+      <c r="AA70" s="5">
         <f>W70</f>
         <v/>
       </c>
-      <c r="AK70">
+      <c r="AJ70" s="4" t="n"/>
+      <c r="AK70" s="5">
         <f>IF(TODAY()&lt;AD70, 0, IF(TODAY()&gt;AE70, AF70, AF70 * (TODAY()-AD70)/(AE70-AD70+1)))</f>
         <v/>
       </c>
-      <c r="AL70">
-        <f>AF70 * AJ70</f>
-        <v/>
-      </c>
-      <c r="AM70">
+      <c r="AL70" s="5">
+        <f>AF70 * (AJ70/100)</f>
+        <v/>
+      </c>
+      <c r="AM70" s="5">
         <f>AI70</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="M71">
+      <c r="L71" s="4" t="n"/>
+      <c r="M71" s="5">
         <f>IF(TODAY()&lt;F71, 0, IF(TODAY()&gt;G71, H71, H71 * (TODAY()-F71)/(G71-F71+1)))</f>
         <v/>
       </c>
-      <c r="N71">
-        <f>H71 * L71</f>
-        <v/>
-      </c>
-      <c r="O71">
+      <c r="N71" s="5">
+        <f>H71 * (L71/100)</f>
+        <v/>
+      </c>
+      <c r="O71" s="5">
         <f>K71</f>
         <v/>
       </c>
-      <c r="Y71">
+      <c r="X71" s="4" t="n"/>
+      <c r="Y71" s="5">
         <f>IF(TODAY()&lt;R71, 0, IF(TODAY()&gt;S71, T71, T71 * (TODAY()-R71)/(S71-R71+1)))</f>
         <v/>
       </c>
-      <c r="Z71">
-        <f>T71 * X71</f>
-        <v/>
-      </c>
-      <c r="AA71">
+      <c r="Z71" s="5">
+        <f>T71 * (X71/100)</f>
+        <v/>
+      </c>
+      <c r="AA71" s="5">
         <f>W71</f>
         <v/>
       </c>
-      <c r="AK71">
+      <c r="AJ71" s="4" t="n"/>
+      <c r="AK71" s="5">
         <f>IF(TODAY()&lt;AD71, 0, IF(TODAY()&gt;AE71, AF71, AF71 * (TODAY()-AD71)/(AE71-AD71+1)))</f>
         <v/>
       </c>
-      <c r="AL71">
-        <f>AF71 * AJ71</f>
-        <v/>
-      </c>
-      <c r="AM71">
+      <c r="AL71" s="5">
+        <f>AF71 * (AJ71/100)</f>
+        <v/>
+      </c>
+      <c r="AM71" s="5">
         <f>AI71</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="M72">
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="5">
         <f>IF(TODAY()&lt;F72, 0, IF(TODAY()&gt;G72, H72, H72 * (TODAY()-F72)/(G72-F72+1)))</f>
         <v/>
       </c>
-      <c r="N72">
-        <f>H72 * L72</f>
-        <v/>
-      </c>
-      <c r="O72">
+      <c r="N72" s="5">
+        <f>H72 * (L72/100)</f>
+        <v/>
+      </c>
+      <c r="O72" s="5">
         <f>K72</f>
         <v/>
       </c>
-      <c r="Y72">
+      <c r="X72" s="4" t="n"/>
+      <c r="Y72" s="5">
         <f>IF(TODAY()&lt;R72, 0, IF(TODAY()&gt;S72, T72, T72 * (TODAY()-R72)/(S72-R72+1)))</f>
         <v/>
       </c>
-      <c r="Z72">
-        <f>T72 * X72</f>
-        <v/>
-      </c>
-      <c r="AA72">
+      <c r="Z72" s="5">
+        <f>T72 * (X72/100)</f>
+        <v/>
+      </c>
+      <c r="AA72" s="5">
         <f>W72</f>
         <v/>
       </c>
-      <c r="AK72">
+      <c r="AJ72" s="4" t="n"/>
+      <c r="AK72" s="5">
         <f>IF(TODAY()&lt;AD72, 0, IF(TODAY()&gt;AE72, AF72, AF72 * (TODAY()-AD72)/(AE72-AD72+1)))</f>
         <v/>
       </c>
-      <c r="AL72">
-        <f>AF72 * AJ72</f>
-        <v/>
-      </c>
-      <c r="AM72">
+      <c r="AL72" s="5">
+        <f>AF72 * (AJ72/100)</f>
+        <v/>
+      </c>
+      <c r="AM72" s="5">
         <f>AI72</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="M73">
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="5">
         <f>IF(TODAY()&lt;F73, 0, IF(TODAY()&gt;G73, H73, H73 * (TODAY()-F73)/(G73-F73+1)))</f>
         <v/>
       </c>
-      <c r="N73">
-        <f>H73 * L73</f>
-        <v/>
-      </c>
-      <c r="O73">
+      <c r="N73" s="5">
+        <f>H73 * (L73/100)</f>
+        <v/>
+      </c>
+      <c r="O73" s="5">
         <f>K73</f>
         <v/>
       </c>
-      <c r="Y73">
+      <c r="X73" s="4" t="n"/>
+      <c r="Y73" s="5">
         <f>IF(TODAY()&lt;R73, 0, IF(TODAY()&gt;S73, T73, T73 * (TODAY()-R73)/(S73-R73+1)))</f>
         <v/>
       </c>
-      <c r="Z73">
-        <f>T73 * X73</f>
-        <v/>
-      </c>
-      <c r="AA73">
+      <c r="Z73" s="5">
+        <f>T73 * (X73/100)</f>
+        <v/>
+      </c>
+      <c r="AA73" s="5">
         <f>W73</f>
         <v/>
       </c>
-      <c r="AK73">
+      <c r="AJ73" s="4" t="n"/>
+      <c r="AK73" s="5">
         <f>IF(TODAY()&lt;AD73, 0, IF(TODAY()&gt;AE73, AF73, AF73 * (TODAY()-AD73)/(AE73-AD73+1)))</f>
         <v/>
       </c>
-      <c r="AL73">
-        <f>AF73 * AJ73</f>
-        <v/>
-      </c>
-      <c r="AM73">
+      <c r="AL73" s="5">
+        <f>AF73 * (AJ73/100)</f>
+        <v/>
+      </c>
+      <c r="AM73" s="5">
         <f>AI73</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="M74">
+      <c r="L74" s="4" t="n"/>
+      <c r="M74" s="5">
         <f>IF(TODAY()&lt;F74, 0, IF(TODAY()&gt;G74, H74, H74 * (TODAY()-F74)/(G74-F74+1)))</f>
         <v/>
       </c>
-      <c r="N74">
-        <f>H74 * L74</f>
-        <v/>
-      </c>
-      <c r="O74">
+      <c r="N74" s="5">
+        <f>H74 * (L74/100)</f>
+        <v/>
+      </c>
+      <c r="O74" s="5">
         <f>K74</f>
         <v/>
       </c>
-      <c r="Y74">
+      <c r="X74" s="4" t="n"/>
+      <c r="Y74" s="5">
         <f>IF(TODAY()&lt;R74, 0, IF(TODAY()&gt;S74, T74, T74 * (TODAY()-R74)/(S74-R74+1)))</f>
         <v/>
       </c>
-      <c r="Z74">
-        <f>T74 * X74</f>
-        <v/>
-      </c>
-      <c r="AA74">
+      <c r="Z74" s="5">
+        <f>T74 * (X74/100)</f>
+        <v/>
+      </c>
+      <c r="AA74" s="5">
         <f>W74</f>
         <v/>
       </c>
-      <c r="AK74">
+      <c r="AJ74" s="4" t="n"/>
+      <c r="AK74" s="5">
         <f>IF(TODAY()&lt;AD74, 0, IF(TODAY()&gt;AE74, AF74, AF74 * (TODAY()-AD74)/(AE74-AD74+1)))</f>
         <v/>
       </c>
-      <c r="AL74">
-        <f>AF74 * AJ74</f>
-        <v/>
-      </c>
-      <c r="AM74">
+      <c r="AL74" s="5">
+        <f>AF74 * (AJ74/100)</f>
+        <v/>
+      </c>
+      <c r="AM74" s="5">
         <f>AI74</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="M75">
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="5">
         <f>IF(TODAY()&lt;F75, 0, IF(TODAY()&gt;G75, H75, H75 * (TODAY()-F75)/(G75-F75+1)))</f>
         <v/>
       </c>
-      <c r="N75">
-        <f>H75 * L75</f>
-        <v/>
-      </c>
-      <c r="O75">
+      <c r="N75" s="5">
+        <f>H75 * (L75/100)</f>
+        <v/>
+      </c>
+      <c r="O75" s="5">
         <f>K75</f>
         <v/>
       </c>
-      <c r="Y75">
+      <c r="X75" s="4" t="n"/>
+      <c r="Y75" s="5">
         <f>IF(TODAY()&lt;R75, 0, IF(TODAY()&gt;S75, T75, T75 * (TODAY()-R75)/(S75-R75+1)))</f>
         <v/>
       </c>
-      <c r="Z75">
-        <f>T75 * X75</f>
-        <v/>
-      </c>
-      <c r="AA75">
+      <c r="Z75" s="5">
+        <f>T75 * (X75/100)</f>
+        <v/>
+      </c>
+      <c r="AA75" s="5">
         <f>W75</f>
         <v/>
       </c>
-      <c r="AK75">
+      <c r="AJ75" s="4" t="n"/>
+      <c r="AK75" s="5">
         <f>IF(TODAY()&lt;AD75, 0, IF(TODAY()&gt;AE75, AF75, AF75 * (TODAY()-AD75)/(AE75-AD75+1)))</f>
         <v/>
       </c>
-      <c r="AL75">
-        <f>AF75 * AJ75</f>
-        <v/>
-      </c>
-      <c r="AM75">
+      <c r="AL75" s="5">
+        <f>AF75 * (AJ75/100)</f>
+        <v/>
+      </c>
+      <c r="AM75" s="5">
         <f>AI75</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="M76">
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="5">
         <f>IF(TODAY()&lt;F76, 0, IF(TODAY()&gt;G76, H76, H76 * (TODAY()-F76)/(G76-F76+1)))</f>
         <v/>
       </c>
-      <c r="N76">
-        <f>H76 * L76</f>
-        <v/>
-      </c>
-      <c r="O76">
+      <c r="N76" s="5">
+        <f>H76 * (L76/100)</f>
+        <v/>
+      </c>
+      <c r="O76" s="5">
         <f>K76</f>
         <v/>
       </c>
-      <c r="Y76">
+      <c r="X76" s="4" t="n"/>
+      <c r="Y76" s="5">
         <f>IF(TODAY()&lt;R76, 0, IF(TODAY()&gt;S76, T76, T76 * (TODAY()-R76)/(S76-R76+1)))</f>
         <v/>
       </c>
-      <c r="Z76">
-        <f>T76 * X76</f>
-        <v/>
-      </c>
-      <c r="AA76">
+      <c r="Z76" s="5">
+        <f>T76 * (X76/100)</f>
+        <v/>
+      </c>
+      <c r="AA76" s="5">
         <f>W76</f>
         <v/>
       </c>
-      <c r="AK76">
+      <c r="AJ76" s="4" t="n"/>
+      <c r="AK76" s="5">
         <f>IF(TODAY()&lt;AD76, 0, IF(TODAY()&gt;AE76, AF76, AF76 * (TODAY()-AD76)/(AE76-AD76+1)))</f>
         <v/>
       </c>
-      <c r="AL76">
-        <f>AF76 * AJ76</f>
-        <v/>
-      </c>
-      <c r="AM76">
+      <c r="AL76" s="5">
+        <f>AF76 * (AJ76/100)</f>
+        <v/>
+      </c>
+      <c r="AM76" s="5">
         <f>AI76</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="M77">
+      <c r="L77" s="4" t="n"/>
+      <c r="M77" s="5">
         <f>IF(TODAY()&lt;F77, 0, IF(TODAY()&gt;G77, H77, H77 * (TODAY()-F77)/(G77-F77+1)))</f>
         <v/>
       </c>
-      <c r="N77">
-        <f>H77 * L77</f>
-        <v/>
-      </c>
-      <c r="O77">
+      <c r="N77" s="5">
+        <f>H77 * (L77/100)</f>
+        <v/>
+      </c>
+      <c r="O77" s="5">
         <f>K77</f>
         <v/>
       </c>
-      <c r="Y77">
+      <c r="X77" s="4" t="n"/>
+      <c r="Y77" s="5">
         <f>IF(TODAY()&lt;R77, 0, IF(TODAY()&gt;S77, T77, T77 * (TODAY()-R77)/(S77-R77+1)))</f>
         <v/>
       </c>
-      <c r="Z77">
-        <f>T77 * X77</f>
-        <v/>
-      </c>
-      <c r="AA77">
+      <c r="Z77" s="5">
+        <f>T77 * (X77/100)</f>
+        <v/>
+      </c>
+      <c r="AA77" s="5">
         <f>W77</f>
         <v/>
       </c>
-      <c r="AK77">
+      <c r="AJ77" s="4" t="n"/>
+      <c r="AK77" s="5">
         <f>IF(TODAY()&lt;AD77, 0, IF(TODAY()&gt;AE77, AF77, AF77 * (TODAY()-AD77)/(AE77-AD77+1)))</f>
         <v/>
       </c>
-      <c r="AL77">
-        <f>AF77 * AJ77</f>
-        <v/>
-      </c>
-      <c r="AM77">
+      <c r="AL77" s="5">
+        <f>AF77 * (AJ77/100)</f>
+        <v/>
+      </c>
+      <c r="AM77" s="5">
         <f>AI77</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="M78">
+      <c r="L78" s="4" t="n"/>
+      <c r="M78" s="5">
         <f>IF(TODAY()&lt;F78, 0, IF(TODAY()&gt;G78, H78, H78 * (TODAY()-F78)/(G78-F78+1)))</f>
         <v/>
       </c>
-      <c r="N78">
-        <f>H78 * L78</f>
-        <v/>
-      </c>
-      <c r="O78">
+      <c r="N78" s="5">
+        <f>H78 * (L78/100)</f>
+        <v/>
+      </c>
+      <c r="O78" s="5">
         <f>K78</f>
         <v/>
       </c>
-      <c r="Y78">
+      <c r="X78" s="4" t="n"/>
+      <c r="Y78" s="5">
         <f>IF(TODAY()&lt;R78, 0, IF(TODAY()&gt;S78, T78, T78 * (TODAY()-R78)/(S78-R78+1)))</f>
         <v/>
       </c>
-      <c r="Z78">
-        <f>T78 * X78</f>
-        <v/>
-      </c>
-      <c r="AA78">
+      <c r="Z78" s="5">
+        <f>T78 * (X78/100)</f>
+        <v/>
+      </c>
+      <c r="AA78" s="5">
         <f>W78</f>
         <v/>
       </c>
-      <c r="AK78">
+      <c r="AJ78" s="4" t="n"/>
+      <c r="AK78" s="5">
         <f>IF(TODAY()&lt;AD78, 0, IF(TODAY()&gt;AE78, AF78, AF78 * (TODAY()-AD78)/(AE78-AD78+1)))</f>
         <v/>
       </c>
-      <c r="AL78">
-        <f>AF78 * AJ78</f>
-        <v/>
-      </c>
-      <c r="AM78">
+      <c r="AL78" s="5">
+        <f>AF78 * (AJ78/100)</f>
+        <v/>
+      </c>
+      <c r="AM78" s="5">
         <f>AI78</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="M79">
+      <c r="L79" s="4" t="n"/>
+      <c r="M79" s="5">
         <f>IF(TODAY()&lt;F79, 0, IF(TODAY()&gt;G79, H79, H79 * (TODAY()-F79)/(G79-F79+1)))</f>
         <v/>
       </c>
-      <c r="N79">
-        <f>H79 * L79</f>
-        <v/>
-      </c>
-      <c r="O79">
+      <c r="N79" s="5">
+        <f>H79 * (L79/100)</f>
+        <v/>
+      </c>
+      <c r="O79" s="5">
         <f>K79</f>
         <v/>
       </c>
-      <c r="Y79">
+      <c r="X79" s="4" t="n"/>
+      <c r="Y79" s="5">
         <f>IF(TODAY()&lt;R79, 0, IF(TODAY()&gt;S79, T79, T79 * (TODAY()-R79)/(S79-R79+1)))</f>
         <v/>
       </c>
-      <c r="Z79">
-        <f>T79 * X79</f>
-        <v/>
-      </c>
-      <c r="AA79">
+      <c r="Z79" s="5">
+        <f>T79 * (X79/100)</f>
+        <v/>
+      </c>
+      <c r="AA79" s="5">
         <f>W79</f>
         <v/>
       </c>
-      <c r="AK79">
+      <c r="AJ79" s="4" t="n"/>
+      <c r="AK79" s="5">
         <f>IF(TODAY()&lt;AD79, 0, IF(TODAY()&gt;AE79, AF79, AF79 * (TODAY()-AD79)/(AE79-AD79+1)))</f>
         <v/>
       </c>
-      <c r="AL79">
-        <f>AF79 * AJ79</f>
-        <v/>
-      </c>
-      <c r="AM79">
+      <c r="AL79" s="5">
+        <f>AF79 * (AJ79/100)</f>
+        <v/>
+      </c>
+      <c r="AM79" s="5">
         <f>AI79</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="M80">
+      <c r="L80" s="4" t="n"/>
+      <c r="M80" s="5">
         <f>IF(TODAY()&lt;F80, 0, IF(TODAY()&gt;G80, H80, H80 * (TODAY()-F80)/(G80-F80+1)))</f>
         <v/>
       </c>
-      <c r="N80">
-        <f>H80 * L80</f>
-        <v/>
-      </c>
-      <c r="O80">
+      <c r="N80" s="5">
+        <f>H80 * (L80/100)</f>
+        <v/>
+      </c>
+      <c r="O80" s="5">
         <f>K80</f>
         <v/>
       </c>
-      <c r="Y80">
+      <c r="X80" s="4" t="n"/>
+      <c r="Y80" s="5">
         <f>IF(TODAY()&lt;R80, 0, IF(TODAY()&gt;S80, T80, T80 * (TODAY()-R80)/(S80-R80+1)))</f>
         <v/>
       </c>
-      <c r="Z80">
-        <f>T80 * X80</f>
-        <v/>
-      </c>
-      <c r="AA80">
+      <c r="Z80" s="5">
+        <f>T80 * (X80/100)</f>
+        <v/>
+      </c>
+      <c r="AA80" s="5">
         <f>W80</f>
         <v/>
       </c>
-      <c r="AK80">
+      <c r="AJ80" s="4" t="n"/>
+      <c r="AK80" s="5">
         <f>IF(TODAY()&lt;AD80, 0, IF(TODAY()&gt;AE80, AF80, AF80 * (TODAY()-AD80)/(AE80-AD80+1)))</f>
         <v/>
       </c>
-      <c r="AL80">
-        <f>AF80 * AJ80</f>
-        <v/>
-      </c>
-      <c r="AM80">
+      <c r="AL80" s="5">
+        <f>AF80 * (AJ80/100)</f>
+        <v/>
+      </c>
+      <c r="AM80" s="5">
         <f>AI80</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="M81">
+      <c r="L81" s="4" t="n"/>
+      <c r="M81" s="5">
         <f>IF(TODAY()&lt;F81, 0, IF(TODAY()&gt;G81, H81, H81 * (TODAY()-F81)/(G81-F81+1)))</f>
         <v/>
       </c>
-      <c r="N81">
-        <f>H81 * L81</f>
-        <v/>
-      </c>
-      <c r="O81">
+      <c r="N81" s="5">
+        <f>H81 * (L81/100)</f>
+        <v/>
+      </c>
+      <c r="O81" s="5">
         <f>K81</f>
         <v/>
       </c>
-      <c r="Y81">
+      <c r="X81" s="4" t="n"/>
+      <c r="Y81" s="5">
         <f>IF(TODAY()&lt;R81, 0, IF(TODAY()&gt;S81, T81, T81 * (TODAY()-R81)/(S81-R81+1)))</f>
         <v/>
       </c>
-      <c r="Z81">
-        <f>T81 * X81</f>
-        <v/>
-      </c>
-      <c r="AA81">
+      <c r="Z81" s="5">
+        <f>T81 * (X81/100)</f>
+        <v/>
+      </c>
+      <c r="AA81" s="5">
         <f>W81</f>
         <v/>
       </c>
-      <c r="AK81">
+      <c r="AJ81" s="4" t="n"/>
+      <c r="AK81" s="5">
         <f>IF(TODAY()&lt;AD81, 0, IF(TODAY()&gt;AE81, AF81, AF81 * (TODAY()-AD81)/(AE81-AD81+1)))</f>
         <v/>
       </c>
-      <c r="AL81">
-        <f>AF81 * AJ81</f>
-        <v/>
-      </c>
-      <c r="AM81">
+      <c r="AL81" s="5">
+        <f>AF81 * (AJ81/100)</f>
+        <v/>
+      </c>
+      <c r="AM81" s="5">
         <f>AI81</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="M82">
+      <c r="L82" s="4" t="n"/>
+      <c r="M82" s="5">
         <f>IF(TODAY()&lt;F82, 0, IF(TODAY()&gt;G82, H82, H82 * (TODAY()-F82)/(G82-F82+1)))</f>
         <v/>
       </c>
-      <c r="N82">
-        <f>H82 * L82</f>
-        <v/>
-      </c>
-      <c r="O82">
+      <c r="N82" s="5">
+        <f>H82 * (L82/100)</f>
+        <v/>
+      </c>
+      <c r="O82" s="5">
         <f>K82</f>
         <v/>
       </c>
-      <c r="Y82">
+      <c r="X82" s="4" t="n"/>
+      <c r="Y82" s="5">
         <f>IF(TODAY()&lt;R82, 0, IF(TODAY()&gt;S82, T82, T82 * (TODAY()-R82)/(S82-R82+1)))</f>
         <v/>
       </c>
-      <c r="Z82">
-        <f>T82 * X82</f>
-        <v/>
-      </c>
-      <c r="AA82">
+      <c r="Z82" s="5">
+        <f>T82 * (X82/100)</f>
+        <v/>
+      </c>
+      <c r="AA82" s="5">
         <f>W82</f>
         <v/>
       </c>
-      <c r="AK82">
+      <c r="AJ82" s="4" t="n"/>
+      <c r="AK82" s="5">
         <f>IF(TODAY()&lt;AD82, 0, IF(TODAY()&gt;AE82, AF82, AF82 * (TODAY()-AD82)/(AE82-AD82+1)))</f>
         <v/>
       </c>
-      <c r="AL82">
-        <f>AF82 * AJ82</f>
-        <v/>
-      </c>
-      <c r="AM82">
+      <c r="AL82" s="5">
+        <f>AF82 * (AJ82/100)</f>
+        <v/>
+      </c>
+      <c r="AM82" s="5">
         <f>AI82</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="M83">
+      <c r="L83" s="4" t="n"/>
+      <c r="M83" s="5">
         <f>IF(TODAY()&lt;F83, 0, IF(TODAY()&gt;G83, H83, H83 * (TODAY()-F83)/(G83-F83+1)))</f>
         <v/>
       </c>
-      <c r="N83">
-        <f>H83 * L83</f>
-        <v/>
-      </c>
-      <c r="O83">
+      <c r="N83" s="5">
+        <f>H83 * (L83/100)</f>
+        <v/>
+      </c>
+      <c r="O83" s="5">
         <f>K83</f>
         <v/>
       </c>
-      <c r="Y83">
+      <c r="X83" s="4" t="n"/>
+      <c r="Y83" s="5">
         <f>IF(TODAY()&lt;R83, 0, IF(TODAY()&gt;S83, T83, T83 * (TODAY()-R83)/(S83-R83+1)))</f>
         <v/>
       </c>
-      <c r="Z83">
-        <f>T83 * X83</f>
-        <v/>
-      </c>
-      <c r="AA83">
+      <c r="Z83" s="5">
+        <f>T83 * (X83/100)</f>
+        <v/>
+      </c>
+      <c r="AA83" s="5">
         <f>W83</f>
         <v/>
       </c>
-      <c r="AK83">
+      <c r="AJ83" s="4" t="n"/>
+      <c r="AK83" s="5">
         <f>IF(TODAY()&lt;AD83, 0, IF(TODAY()&gt;AE83, AF83, AF83 * (TODAY()-AD83)/(AE83-AD83+1)))</f>
         <v/>
       </c>
-      <c r="AL83">
-        <f>AF83 * AJ83</f>
-        <v/>
-      </c>
-      <c r="AM83">
+      <c r="AL83" s="5">
+        <f>AF83 * (AJ83/100)</f>
+        <v/>
+      </c>
+      <c r="AM83" s="5">
         <f>AI83</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="M84">
+      <c r="L84" s="4" t="n"/>
+      <c r="M84" s="5">
         <f>IF(TODAY()&lt;F84, 0, IF(TODAY()&gt;G84, H84, H84 * (TODAY()-F84)/(G84-F84+1)))</f>
         <v/>
       </c>
-      <c r="N84">
-        <f>H84 * L84</f>
-        <v/>
-      </c>
-      <c r="O84">
+      <c r="N84" s="5">
+        <f>H84 * (L84/100)</f>
+        <v/>
+      </c>
+      <c r="O84" s="5">
         <f>K84</f>
         <v/>
       </c>
-      <c r="Y84">
+      <c r="X84" s="4" t="n"/>
+      <c r="Y84" s="5">
         <f>IF(TODAY()&lt;R84, 0, IF(TODAY()&gt;S84, T84, T84 * (TODAY()-R84)/(S84-R84+1)))</f>
         <v/>
       </c>
-      <c r="Z84">
-        <f>T84 * X84</f>
-        <v/>
-      </c>
-      <c r="AA84">
+      <c r="Z84" s="5">
+        <f>T84 * (X84/100)</f>
+        <v/>
+      </c>
+      <c r="AA84" s="5">
         <f>W84</f>
         <v/>
       </c>
-      <c r="AK84">
+      <c r="AJ84" s="4" t="n"/>
+      <c r="AK84" s="5">
         <f>IF(TODAY()&lt;AD84, 0, IF(TODAY()&gt;AE84, AF84, AF84 * (TODAY()-AD84)/(AE84-AD84+1)))</f>
         <v/>
       </c>
-      <c r="AL84">
-        <f>AF84 * AJ84</f>
-        <v/>
-      </c>
-      <c r="AM84">
+      <c r="AL84" s="5">
+        <f>AF84 * (AJ84/100)</f>
+        <v/>
+      </c>
+      <c r="AM84" s="5">
         <f>AI84</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="M85">
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="5">
         <f>IF(TODAY()&lt;F85, 0, IF(TODAY()&gt;G85, H85, H85 * (TODAY()-F85)/(G85-F85+1)))</f>
         <v/>
       </c>
-      <c r="N85">
-        <f>H85 * L85</f>
-        <v/>
-      </c>
-      <c r="O85">
+      <c r="N85" s="5">
+        <f>H85 * (L85/100)</f>
+        <v/>
+      </c>
+      <c r="O85" s="5">
         <f>K85</f>
         <v/>
       </c>
-      <c r="Y85">
+      <c r="X85" s="4" t="n"/>
+      <c r="Y85" s="5">
         <f>IF(TODAY()&lt;R85, 0, IF(TODAY()&gt;S85, T85, T85 * (TODAY()-R85)/(S85-R85+1)))</f>
         <v/>
       </c>
-      <c r="Z85">
-        <f>T85 * X85</f>
-        <v/>
-      </c>
-      <c r="AA85">
+      <c r="Z85" s="5">
+        <f>T85 * (X85/100)</f>
+        <v/>
+      </c>
+      <c r="AA85" s="5">
         <f>W85</f>
         <v/>
       </c>
-      <c r="AK85">
+      <c r="AJ85" s="4" t="n"/>
+      <c r="AK85" s="5">
         <f>IF(TODAY()&lt;AD85, 0, IF(TODAY()&gt;AE85, AF85, AF85 * (TODAY()-AD85)/(AE85-AD85+1)))</f>
         <v/>
       </c>
-      <c r="AL85">
-        <f>AF85 * AJ85</f>
-        <v/>
-      </c>
-      <c r="AM85">
+      <c r="AL85" s="5">
+        <f>AF85 * (AJ85/100)</f>
+        <v/>
+      </c>
+      <c r="AM85" s="5">
         <f>AI85</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="M86">
+      <c r="L86" s="4" t="n"/>
+      <c r="M86" s="5">
         <f>IF(TODAY()&lt;F86, 0, IF(TODAY()&gt;G86, H86, H86 * (TODAY()-F86)/(G86-F86+1)))</f>
         <v/>
       </c>
-      <c r="N86">
-        <f>H86 * L86</f>
-        <v/>
-      </c>
-      <c r="O86">
+      <c r="N86" s="5">
+        <f>H86 * (L86/100)</f>
+        <v/>
+      </c>
+      <c r="O86" s="5">
         <f>K86</f>
         <v/>
       </c>
-      <c r="Y86">
+      <c r="X86" s="4" t="n"/>
+      <c r="Y86" s="5">
         <f>IF(TODAY()&lt;R86, 0, IF(TODAY()&gt;S86, T86, T86 * (TODAY()-R86)/(S86-R86+1)))</f>
         <v/>
       </c>
-      <c r="Z86">
-        <f>T86 * X86</f>
-        <v/>
-      </c>
-      <c r="AA86">
+      <c r="Z86" s="5">
+        <f>T86 * (X86/100)</f>
+        <v/>
+      </c>
+      <c r="AA86" s="5">
         <f>W86</f>
         <v/>
       </c>
-      <c r="AK86">
+      <c r="AJ86" s="4" t="n"/>
+      <c r="AK86" s="5">
         <f>IF(TODAY()&lt;AD86, 0, IF(TODAY()&gt;AE86, AF86, AF86 * (TODAY()-AD86)/(AE86-AD86+1)))</f>
         <v/>
       </c>
-      <c r="AL86">
-        <f>AF86 * AJ86</f>
-        <v/>
-      </c>
-      <c r="AM86">
+      <c r="AL86" s="5">
+        <f>AF86 * (AJ86/100)</f>
+        <v/>
+      </c>
+      <c r="AM86" s="5">
         <f>AI86</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="M87">
+      <c r="L87" s="4" t="n"/>
+      <c r="M87" s="5">
         <f>IF(TODAY()&lt;F87, 0, IF(TODAY()&gt;G87, H87, H87 * (TODAY()-F87)/(G87-F87+1)))</f>
         <v/>
       </c>
-      <c r="N87">
-        <f>H87 * L87</f>
-        <v/>
-      </c>
-      <c r="O87">
+      <c r="N87" s="5">
+        <f>H87 * (L87/100)</f>
+        <v/>
+      </c>
+      <c r="O87" s="5">
         <f>K87</f>
         <v/>
       </c>
-      <c r="Y87">
+      <c r="X87" s="4" t="n"/>
+      <c r="Y87" s="5">
         <f>IF(TODAY()&lt;R87, 0, IF(TODAY()&gt;S87, T87, T87 * (TODAY()-R87)/(S87-R87+1)))</f>
         <v/>
       </c>
-      <c r="Z87">
-        <f>T87 * X87</f>
-        <v/>
-      </c>
-      <c r="AA87">
+      <c r="Z87" s="5">
+        <f>T87 * (X87/100)</f>
+        <v/>
+      </c>
+      <c r="AA87" s="5">
         <f>W87</f>
         <v/>
       </c>
-      <c r="AK87">
+      <c r="AJ87" s="4" t="n"/>
+      <c r="AK87" s="5">
         <f>IF(TODAY()&lt;AD87, 0, IF(TODAY()&gt;AE87, AF87, AF87 * (TODAY()-AD87)/(AE87-AD87+1)))</f>
         <v/>
       </c>
-      <c r="AL87">
-        <f>AF87 * AJ87</f>
-        <v/>
-      </c>
-      <c r="AM87">
+      <c r="AL87" s="5">
+        <f>AF87 * (AJ87/100)</f>
+        <v/>
+      </c>
+      <c r="AM87" s="5">
         <f>AI87</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="M88">
+      <c r="L88" s="4" t="n"/>
+      <c r="M88" s="5">
         <f>IF(TODAY()&lt;F88, 0, IF(TODAY()&gt;G88, H88, H88 * (TODAY()-F88)/(G88-F88+1)))</f>
         <v/>
       </c>
-      <c r="N88">
-        <f>H88 * L88</f>
-        <v/>
-      </c>
-      <c r="O88">
+      <c r="N88" s="5">
+        <f>H88 * (L88/100)</f>
+        <v/>
+      </c>
+      <c r="O88" s="5">
         <f>K88</f>
         <v/>
       </c>
-      <c r="Y88">
+      <c r="X88" s="4" t="n"/>
+      <c r="Y88" s="5">
         <f>IF(TODAY()&lt;R88, 0, IF(TODAY()&gt;S88, T88, T88 * (TODAY()-R88)/(S88-R88+1)))</f>
         <v/>
       </c>
-      <c r="Z88">
-        <f>T88 * X88</f>
-        <v/>
-      </c>
-      <c r="AA88">
+      <c r="Z88" s="5">
+        <f>T88 * (X88/100)</f>
+        <v/>
+      </c>
+      <c r="AA88" s="5">
         <f>W88</f>
         <v/>
       </c>
-      <c r="AK88">
+      <c r="AJ88" s="4" t="n"/>
+      <c r="AK88" s="5">
         <f>IF(TODAY()&lt;AD88, 0, IF(TODAY()&gt;AE88, AF88, AF88 * (TODAY()-AD88)/(AE88-AD88+1)))</f>
         <v/>
       </c>
-      <c r="AL88">
-        <f>AF88 * AJ88</f>
-        <v/>
-      </c>
-      <c r="AM88">
+      <c r="AL88" s="5">
+        <f>AF88 * (AJ88/100)</f>
+        <v/>
+      </c>
+      <c r="AM88" s="5">
         <f>AI88</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="M89">
+      <c r="L89" s="4" t="n"/>
+      <c r="M89" s="5">
         <f>IF(TODAY()&lt;F89, 0, IF(TODAY()&gt;G89, H89, H89 * (TODAY()-F89)/(G89-F89+1)))</f>
         <v/>
       </c>
-      <c r="N89">
-        <f>H89 * L89</f>
-        <v/>
-      </c>
-      <c r="O89">
+      <c r="N89" s="5">
+        <f>H89 * (L89/100)</f>
+        <v/>
+      </c>
+      <c r="O89" s="5">
         <f>K89</f>
         <v/>
       </c>
-      <c r="Y89">
+      <c r="X89" s="4" t="n"/>
+      <c r="Y89" s="5">
         <f>IF(TODAY()&lt;R89, 0, IF(TODAY()&gt;S89, T89, T89 * (TODAY()-R89)/(S89-R89+1)))</f>
         <v/>
       </c>
-      <c r="Z89">
-        <f>T89 * X89</f>
-        <v/>
-      </c>
-      <c r="AA89">
+      <c r="Z89" s="5">
+        <f>T89 * (X89/100)</f>
+        <v/>
+      </c>
+      <c r="AA89" s="5">
         <f>W89</f>
         <v/>
       </c>
-      <c r="AK89">
+      <c r="AJ89" s="4" t="n"/>
+      <c r="AK89" s="5">
         <f>IF(TODAY()&lt;AD89, 0, IF(TODAY()&gt;AE89, AF89, AF89 * (TODAY()-AD89)/(AE89-AD89+1)))</f>
         <v/>
       </c>
-      <c r="AL89">
-        <f>AF89 * AJ89</f>
-        <v/>
-      </c>
-      <c r="AM89">
+      <c r="AL89" s="5">
+        <f>AF89 * (AJ89/100)</f>
+        <v/>
+      </c>
+      <c r="AM89" s="5">
         <f>AI89</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="M90">
+      <c r="L90" s="4" t="n"/>
+      <c r="M90" s="5">
         <f>IF(TODAY()&lt;F90, 0, IF(TODAY()&gt;G90, H90, H90 * (TODAY()-F90)/(G90-F90+1)))</f>
         <v/>
       </c>
-      <c r="N90">
-        <f>H90 * L90</f>
-        <v/>
-      </c>
-      <c r="O90">
+      <c r="N90" s="5">
+        <f>H90 * (L90/100)</f>
+        <v/>
+      </c>
+      <c r="O90" s="5">
         <f>K90</f>
         <v/>
       </c>
-      <c r="Y90">
+      <c r="X90" s="4" t="n"/>
+      <c r="Y90" s="5">
         <f>IF(TODAY()&lt;R90, 0, IF(TODAY()&gt;S90, T90, T90 * (TODAY()-R90)/(S90-R90+1)))</f>
         <v/>
       </c>
-      <c r="Z90">
-        <f>T90 * X90</f>
-        <v/>
-      </c>
-      <c r="AA90">
+      <c r="Z90" s="5">
+        <f>T90 * (X90/100)</f>
+        <v/>
+      </c>
+      <c r="AA90" s="5">
         <f>W90</f>
         <v/>
       </c>
-      <c r="AK90">
+      <c r="AJ90" s="4" t="n"/>
+      <c r="AK90" s="5">
         <f>IF(TODAY()&lt;AD90, 0, IF(TODAY()&gt;AE90, AF90, AF90 * (TODAY()-AD90)/(AE90-AD90+1)))</f>
         <v/>
       </c>
-      <c r="AL90">
-        <f>AF90 * AJ90</f>
-        <v/>
-      </c>
-      <c r="AM90">
+      <c r="AL90" s="5">
+        <f>AF90 * (AJ90/100)</f>
+        <v/>
+      </c>
+      <c r="AM90" s="5">
         <f>AI90</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="M91">
+      <c r="L91" s="4" t="n"/>
+      <c r="M91" s="5">
         <f>IF(TODAY()&lt;F91, 0, IF(TODAY()&gt;G91, H91, H91 * (TODAY()-F91)/(G91-F91+1)))</f>
         <v/>
       </c>
-      <c r="N91">
-        <f>H91 * L91</f>
-        <v/>
-      </c>
-      <c r="O91">
+      <c r="N91" s="5">
+        <f>H91 * (L91/100)</f>
+        <v/>
+      </c>
+      <c r="O91" s="5">
         <f>K91</f>
         <v/>
       </c>
-      <c r="Y91">
+      <c r="X91" s="4" t="n"/>
+      <c r="Y91" s="5">
         <f>IF(TODAY()&lt;R91, 0, IF(TODAY()&gt;S91, T91, T91 * (TODAY()-R91)/(S91-R91+1)))</f>
         <v/>
       </c>
-      <c r="Z91">
-        <f>T91 * X91</f>
-        <v/>
-      </c>
-      <c r="AA91">
+      <c r="Z91" s="5">
+        <f>T91 * (X91/100)</f>
+        <v/>
+      </c>
+      <c r="AA91" s="5">
         <f>W91</f>
         <v/>
       </c>
-      <c r="AK91">
+      <c r="AJ91" s="4" t="n"/>
+      <c r="AK91" s="5">
         <f>IF(TODAY()&lt;AD91, 0, IF(TODAY()&gt;AE91, AF91, AF91 * (TODAY()-AD91)/(AE91-AD91+1)))</f>
         <v/>
       </c>
-      <c r="AL91">
-        <f>AF91 * AJ91</f>
-        <v/>
-      </c>
-      <c r="AM91">
+      <c r="AL91" s="5">
+        <f>AF91 * (AJ91/100)</f>
+        <v/>
+      </c>
+      <c r="AM91" s="5">
         <f>AI91</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="M92">
+      <c r="L92" s="4" t="n"/>
+      <c r="M92" s="5">
         <f>IF(TODAY()&lt;F92, 0, IF(TODAY()&gt;G92, H92, H92 * (TODAY()-F92)/(G92-F92+1)))</f>
         <v/>
       </c>
-      <c r="N92">
-        <f>H92 * L92</f>
-        <v/>
-      </c>
-      <c r="O92">
+      <c r="N92" s="5">
+        <f>H92 * (L92/100)</f>
+        <v/>
+      </c>
+      <c r="O92" s="5">
         <f>K92</f>
         <v/>
       </c>
-      <c r="Y92">
+      <c r="X92" s="4" t="n"/>
+      <c r="Y92" s="5">
         <f>IF(TODAY()&lt;R92, 0, IF(TODAY()&gt;S92, T92, T92 * (TODAY()-R92)/(S92-R92+1)))</f>
         <v/>
       </c>
-      <c r="Z92">
-        <f>T92 * X92</f>
-        <v/>
-      </c>
-      <c r="AA92">
+      <c r="Z92" s="5">
+        <f>T92 * (X92/100)</f>
+        <v/>
+      </c>
+      <c r="AA92" s="5">
         <f>W92</f>
         <v/>
       </c>
-      <c r="AK92">
+      <c r="AJ92" s="4" t="n"/>
+      <c r="AK92" s="5">
         <f>IF(TODAY()&lt;AD92, 0, IF(TODAY()&gt;AE92, AF92, AF92 * (TODAY()-AD92)/(AE92-AD92+1)))</f>
         <v/>
       </c>
-      <c r="AL92">
-        <f>AF92 * AJ92</f>
-        <v/>
-      </c>
-      <c r="AM92">
+      <c r="AL92" s="5">
+        <f>AF92 * (AJ92/100)</f>
+        <v/>
+      </c>
+      <c r="AM92" s="5">
         <f>AI92</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="M93">
+      <c r="L93" s="4" t="n"/>
+      <c r="M93" s="5">
         <f>IF(TODAY()&lt;F93, 0, IF(TODAY()&gt;G93, H93, H93 * (TODAY()-F93)/(G93-F93+1)))</f>
         <v/>
       </c>
-      <c r="N93">
-        <f>H93 * L93</f>
-        <v/>
-      </c>
-      <c r="O93">
+      <c r="N93" s="5">
+        <f>H93 * (L93/100)</f>
+        <v/>
+      </c>
+      <c r="O93" s="5">
         <f>K93</f>
         <v/>
       </c>
-      <c r="Y93">
+      <c r="X93" s="4" t="n"/>
+      <c r="Y93" s="5">
         <f>IF(TODAY()&lt;R93, 0, IF(TODAY()&gt;S93, T93, T93 * (TODAY()-R93)/(S93-R93+1)))</f>
         <v/>
       </c>
-      <c r="Z93">
-        <f>T93 * X93</f>
-        <v/>
-      </c>
-      <c r="AA93">
+      <c r="Z93" s="5">
+        <f>T93 * (X93/100)</f>
+        <v/>
+      </c>
+      <c r="AA93" s="5">
         <f>W93</f>
         <v/>
       </c>
-      <c r="AK93">
+      <c r="AJ93" s="4" t="n"/>
+      <c r="AK93" s="5">
         <f>IF(TODAY()&lt;AD93, 0, IF(TODAY()&gt;AE93, AF93, AF93 * (TODAY()-AD93)/(AE93-AD93+1)))</f>
         <v/>
       </c>
-      <c r="AL93">
-        <f>AF93 * AJ93</f>
-        <v/>
-      </c>
-      <c r="AM93">
+      <c r="AL93" s="5">
+        <f>AF93 * (AJ93/100)</f>
+        <v/>
+      </c>
+      <c r="AM93" s="5">
         <f>AI93</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="M94">
+      <c r="L94" s="4" t="n"/>
+      <c r="M94" s="5">
         <f>IF(TODAY()&lt;F94, 0, IF(TODAY()&gt;G94, H94, H94 * (TODAY()-F94)/(G94-F94+1)))</f>
         <v/>
       </c>
-      <c r="N94">
-        <f>H94 * L94</f>
-        <v/>
-      </c>
-      <c r="O94">
+      <c r="N94" s="5">
+        <f>H94 * (L94/100)</f>
+        <v/>
+      </c>
+      <c r="O94" s="5">
         <f>K94</f>
         <v/>
       </c>
-      <c r="Y94">
+      <c r="X94" s="4" t="n"/>
+      <c r="Y94" s="5">
         <f>IF(TODAY()&lt;R94, 0, IF(TODAY()&gt;S94, T94, T94 * (TODAY()-R94)/(S94-R94+1)))</f>
         <v/>
       </c>
-      <c r="Z94">
-        <f>T94 * X94</f>
-        <v/>
-      </c>
-      <c r="AA94">
+      <c r="Z94" s="5">
+        <f>T94 * (X94/100)</f>
+        <v/>
+      </c>
+      <c r="AA94" s="5">
         <f>W94</f>
         <v/>
       </c>
-      <c r="AK94">
+      <c r="AJ94" s="4" t="n"/>
+      <c r="AK94" s="5">
         <f>IF(TODAY()&lt;AD94, 0, IF(TODAY()&gt;AE94, AF94, AF94 * (TODAY()-AD94)/(AE94-AD94+1)))</f>
         <v/>
       </c>
-      <c r="AL94">
-        <f>AF94 * AJ94</f>
-        <v/>
-      </c>
-      <c r="AM94">
+      <c r="AL94" s="5">
+        <f>AF94 * (AJ94/100)</f>
+        <v/>
+      </c>
+      <c r="AM94" s="5">
         <f>AI94</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="M95">
+      <c r="L95" s="4" t="n"/>
+      <c r="M95" s="5">
         <f>IF(TODAY()&lt;F95, 0, IF(TODAY()&gt;G95, H95, H95 * (TODAY()-F95)/(G95-F95+1)))</f>
         <v/>
       </c>
-      <c r="N95">
-        <f>H95 * L95</f>
-        <v/>
-      </c>
-      <c r="O95">
+      <c r="N95" s="5">
+        <f>H95 * (L95/100)</f>
+        <v/>
+      </c>
+      <c r="O95" s="5">
         <f>K95</f>
         <v/>
       </c>
-      <c r="Y95">
+      <c r="X95" s="4" t="n"/>
+      <c r="Y95" s="5">
         <f>IF(TODAY()&lt;R95, 0, IF(TODAY()&gt;S95, T95, T95 * (TODAY()-R95)/(S95-R95+1)))</f>
         <v/>
       </c>
-      <c r="Z95">
-        <f>T95 * X95</f>
-        <v/>
-      </c>
-      <c r="AA95">
+      <c r="Z95" s="5">
+        <f>T95 * (X95/100)</f>
+        <v/>
+      </c>
+      <c r="AA95" s="5">
         <f>W95</f>
         <v/>
       </c>
-      <c r="AK95">
+      <c r="AJ95" s="4" t="n"/>
+      <c r="AK95" s="5">
         <f>IF(TODAY()&lt;AD95, 0, IF(TODAY()&gt;AE95, AF95, AF95 * (TODAY()-AD95)/(AE95-AD95+1)))</f>
         <v/>
       </c>
-      <c r="AL95">
-        <f>AF95 * AJ95</f>
-        <v/>
-      </c>
-      <c r="AM95">
+      <c r="AL95" s="5">
+        <f>AF95 * (AJ95/100)</f>
+        <v/>
+      </c>
+      <c r="AM95" s="5">
         <f>AI95</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="M96">
+      <c r="L96" s="4" t="n"/>
+      <c r="M96" s="5">
         <f>IF(TODAY()&lt;F96, 0, IF(TODAY()&gt;G96, H96, H96 * (TODAY()-F96)/(G96-F96+1)))</f>
         <v/>
       </c>
-      <c r="N96">
-        <f>H96 * L96</f>
-        <v/>
-      </c>
-      <c r="O96">
+      <c r="N96" s="5">
+        <f>H96 * (L96/100)</f>
+        <v/>
+      </c>
+      <c r="O96" s="5">
         <f>K96</f>
         <v/>
       </c>
-      <c r="Y96">
+      <c r="X96" s="4" t="n"/>
+      <c r="Y96" s="5">
         <f>IF(TODAY()&lt;R96, 0, IF(TODAY()&gt;S96, T96, T96 * (TODAY()-R96)/(S96-R96+1)))</f>
         <v/>
       </c>
-      <c r="Z96">
-        <f>T96 * X96</f>
-        <v/>
-      </c>
-      <c r="AA96">
+      <c r="Z96" s="5">
+        <f>T96 * (X96/100)</f>
+        <v/>
+      </c>
+      <c r="AA96" s="5">
         <f>W96</f>
         <v/>
       </c>
-      <c r="AK96">
+      <c r="AJ96" s="4" t="n"/>
+      <c r="AK96" s="5">
         <f>IF(TODAY()&lt;AD96, 0, IF(TODAY()&gt;AE96, AF96, AF96 * (TODAY()-AD96)/(AE96-AD96+1)))</f>
         <v/>
       </c>
-      <c r="AL96">
-        <f>AF96 * AJ96</f>
-        <v/>
-      </c>
-      <c r="AM96">
+      <c r="AL96" s="5">
+        <f>AF96 * (AJ96/100)</f>
+        <v/>
+      </c>
+      <c r="AM96" s="5">
         <f>AI96</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="M97">
+      <c r="L97" s="4" t="n"/>
+      <c r="M97" s="5">
         <f>IF(TODAY()&lt;F97, 0, IF(TODAY()&gt;G97, H97, H97 * (TODAY()-F97)/(G97-F97+1)))</f>
         <v/>
       </c>
-      <c r="N97">
-        <f>H97 * L97</f>
-        <v/>
-      </c>
-      <c r="O97">
+      <c r="N97" s="5">
+        <f>H97 * (L97/100)</f>
+        <v/>
+      </c>
+      <c r="O97" s="5">
         <f>K97</f>
         <v/>
       </c>
-      <c r="Y97">
+      <c r="X97" s="4" t="n"/>
+      <c r="Y97" s="5">
         <f>IF(TODAY()&lt;R97, 0, IF(TODAY()&gt;S97, T97, T97 * (TODAY()-R97)/(S97-R97+1)))</f>
         <v/>
       </c>
-      <c r="Z97">
-        <f>T97 * X97</f>
-        <v/>
-      </c>
-      <c r="AA97">
+      <c r="Z97" s="5">
+        <f>T97 * (X97/100)</f>
+        <v/>
+      </c>
+      <c r="AA97" s="5">
         <f>W97</f>
         <v/>
       </c>
-      <c r="AK97">
+      <c r="AJ97" s="4" t="n"/>
+      <c r="AK97" s="5">
         <f>IF(TODAY()&lt;AD97, 0, IF(TODAY()&gt;AE97, AF97, AF97 * (TODAY()-AD97)/(AE97-AD97+1)))</f>
         <v/>
       </c>
-      <c r="AL97">
-        <f>AF97 * AJ97</f>
-        <v/>
-      </c>
-      <c r="AM97">
+      <c r="AL97" s="5">
+        <f>AF97 * (AJ97/100)</f>
+        <v/>
+      </c>
+      <c r="AM97" s="5">
         <f>AI97</f>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="M98">
+      <c r="L98" s="4" t="n"/>
+      <c r="M98" s="5">
         <f>IF(TODAY()&lt;F98, 0, IF(TODAY()&gt;G98, H98, H98 * (TODAY()-F98)/(G98-F98+1)))</f>
         <v/>
       </c>
-      <c r="N98">
-        <f>H98 * L98</f>
-        <v/>
-      </c>
-      <c r="O98">
+      <c r="N98" s="5">
+        <f>H98 * (L98/100)</f>
+        <v/>
+      </c>
+      <c r="O98" s="5">
         <f>K98</f>
         <v/>
       </c>
-      <c r="Y98">
+      <c r="X98" s="4" t="n"/>
+      <c r="Y98" s="5">
         <f>IF(TODAY()&lt;R98, 0, IF(TODAY()&gt;S98, T98, T98 * (TODAY()-R98)/(S98-R98+1)))</f>
         <v/>
       </c>
-      <c r="Z98">
-        <f>T98 * X98</f>
-        <v/>
-      </c>
-      <c r="AA98">
+      <c r="Z98" s="5">
+        <f>T98 * (X98/100)</f>
+        <v/>
+      </c>
+      <c r="AA98" s="5">
         <f>W98</f>
         <v/>
       </c>
-      <c r="AK98">
+      <c r="AJ98" s="4" t="n"/>
+      <c r="AK98" s="5">
         <f>IF(TODAY()&lt;AD98, 0, IF(TODAY()&gt;AE98, AF98, AF98 * (TODAY()-AD98)/(AE98-AD98+1)))</f>
         <v/>
       </c>
-      <c r="AL98">
-        <f>AF98 * AJ98</f>
-        <v/>
-      </c>
-      <c r="AM98">
+      <c r="AL98" s="5">
+        <f>AF98 * (AJ98/100)</f>
+        <v/>
+      </c>
+      <c r="AM98" s="5">
         <f>AI98</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="M99">
+      <c r="L99" s="4" t="n"/>
+      <c r="M99" s="5">
         <f>IF(TODAY()&lt;F99, 0, IF(TODAY()&gt;G99, H99, H99 * (TODAY()-F99)/(G99-F99+1)))</f>
         <v/>
       </c>
-      <c r="N99">
-        <f>H99 * L99</f>
-        <v/>
-      </c>
-      <c r="O99">
+      <c r="N99" s="5">
+        <f>H99 * (L99/100)</f>
+        <v/>
+      </c>
+      <c r="O99" s="5">
         <f>K99</f>
         <v/>
       </c>
-      <c r="Y99">
+      <c r="X99" s="4" t="n"/>
+      <c r="Y99" s="5">
         <f>IF(TODAY()&lt;R99, 0, IF(TODAY()&gt;S99, T99, T99 * (TODAY()-R99)/(S99-R99+1)))</f>
         <v/>
       </c>
-      <c r="Z99">
-        <f>T99 * X99</f>
-        <v/>
-      </c>
-      <c r="AA99">
+      <c r="Z99" s="5">
+        <f>T99 * (X99/100)</f>
+        <v/>
+      </c>
+      <c r="AA99" s="5">
         <f>W99</f>
         <v/>
       </c>
-      <c r="AK99">
+      <c r="AJ99" s="4" t="n"/>
+      <c r="AK99" s="5">
         <f>IF(TODAY()&lt;AD99, 0, IF(TODAY()&gt;AE99, AF99, AF99 * (TODAY()-AD99)/(AE99-AD99+1)))</f>
         <v/>
       </c>
-      <c r="AL99">
-        <f>AF99 * AJ99</f>
-        <v/>
-      </c>
-      <c r="AM99">
+      <c r="AL99" s="5">
+        <f>AF99 * (AJ99/100)</f>
+        <v/>
+      </c>
+      <c r="AM99" s="5">
         <f>AI99</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="M100">
+      <c r="L100" s="4" t="n"/>
+      <c r="M100" s="5">
         <f>IF(TODAY()&lt;F100, 0, IF(TODAY()&gt;G100, H100, H100 * (TODAY()-F100)/(G100-F100+1)))</f>
         <v/>
       </c>
-      <c r="N100">
-        <f>H100 * L100</f>
-        <v/>
-      </c>
-      <c r="O100">
+      <c r="N100" s="5">
+        <f>H100 * (L100/100)</f>
+        <v/>
+      </c>
+      <c r="O100" s="5">
         <f>K100</f>
         <v/>
       </c>
-      <c r="Y100">
+      <c r="X100" s="4" t="n"/>
+      <c r="Y100" s="5">
         <f>IF(TODAY()&lt;R100, 0, IF(TODAY()&gt;S100, T100, T100 * (TODAY()-R100)/(S100-R100+1)))</f>
         <v/>
       </c>
-      <c r="Z100">
-        <f>T100 * X100</f>
-        <v/>
-      </c>
-      <c r="AA100">
+      <c r="Z100" s="5">
+        <f>T100 * (X100/100)</f>
+        <v/>
+      </c>
+      <c r="AA100" s="5">
         <f>W100</f>
         <v/>
       </c>
-      <c r="AK100">
+      <c r="AJ100" s="4" t="n"/>
+      <c r="AK100" s="5">
         <f>IF(TODAY()&lt;AD100, 0, IF(TODAY()&gt;AE100, AF100, AF100 * (TODAY()-AD100)/(AE100-AD100+1)))</f>
         <v/>
       </c>
-      <c r="AL100">
-        <f>AF100 * AJ100</f>
-        <v/>
-      </c>
-      <c r="AM100">
+      <c r="AL100" s="5">
+        <f>AF100 * (AJ100/100)</f>
+        <v/>
+      </c>
+      <c r="AM100" s="5">
         <f>AI100</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="M101">
+      <c r="L101" s="4" t="n"/>
+      <c r="M101" s="5">
         <f>IF(TODAY()&lt;F101, 0, IF(TODAY()&gt;G101, H101, H101 * (TODAY()-F101)/(G101-F101+1)))</f>
         <v/>
       </c>
-      <c r="N101">
-        <f>H101 * L101</f>
-        <v/>
-      </c>
-      <c r="O101">
+      <c r="N101" s="5">
+        <f>H101 * (L101/100)</f>
+        <v/>
+      </c>
+      <c r="O101" s="5">
         <f>K101</f>
         <v/>
       </c>
-      <c r="Y101">
+      <c r="X101" s="4" t="n"/>
+      <c r="Y101" s="5">
         <f>IF(TODAY()&lt;R101, 0, IF(TODAY()&gt;S101, T101, T101 * (TODAY()-R101)/(S101-R101+1)))</f>
         <v/>
       </c>
-      <c r="Z101">
-        <f>T101 * X101</f>
-        <v/>
-      </c>
-      <c r="AA101">
+      <c r="Z101" s="5">
+        <f>T101 * (X101/100)</f>
+        <v/>
+      </c>
+      <c r="AA101" s="5">
         <f>W101</f>
         <v/>
       </c>
-      <c r="AK101">
+      <c r="AJ101" s="4" t="n"/>
+      <c r="AK101" s="5">
         <f>IF(TODAY()&lt;AD101, 0, IF(TODAY()&gt;AE101, AF101, AF101 * (TODAY()-AD101)/(AE101-AD101+1)))</f>
         <v/>
       </c>
-      <c r="AL101">
-        <f>AF101 * AJ101</f>
-        <v/>
-      </c>
-      <c r="AM101">
+      <c r="AL101" s="5">
+        <f>AF101 * (AJ101/100)</f>
+        <v/>
+      </c>
+      <c r="AM101" s="5">
         <f>AI101</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="M102">
+      <c r="L102" s="4" t="n"/>
+      <c r="M102" s="5">
         <f>IF(TODAY()&lt;F102, 0, IF(TODAY()&gt;G102, H102, H102 * (TODAY()-F102)/(G102-F102+1)))</f>
         <v/>
       </c>
-      <c r="N102">
-        <f>H102 * L102</f>
-        <v/>
-      </c>
-      <c r="O102">
+      <c r="N102" s="5">
+        <f>H102 * (L102/100)</f>
+        <v/>
+      </c>
+      <c r="O102" s="5">
         <f>K102</f>
         <v/>
       </c>
-      <c r="Y102">
+      <c r="X102" s="4" t="n"/>
+      <c r="Y102" s="5">
         <f>IF(TODAY()&lt;R102, 0, IF(TODAY()&gt;S102, T102, T102 * (TODAY()-R102)/(S102-R102+1)))</f>
         <v/>
       </c>
-      <c r="Z102">
-        <f>T102 * X102</f>
-        <v/>
-      </c>
-      <c r="AA102">
+      <c r="Z102" s="5">
+        <f>T102 * (X102/100)</f>
+        <v/>
+      </c>
+      <c r="AA102" s="5">
         <f>W102</f>
         <v/>
       </c>
-      <c r="AK102">
+      <c r="AJ102" s="4" t="n"/>
+      <c r="AK102" s="5">
         <f>IF(TODAY()&lt;AD102, 0, IF(TODAY()&gt;AE102, AF102, AF102 * (TODAY()-AD102)/(AE102-AD102+1)))</f>
         <v/>
       </c>
-      <c r="AL102">
-        <f>AF102 * AJ102</f>
-        <v/>
-      </c>
-      <c r="AM102">
+      <c r="AL102" s="5">
+        <f>AF102 * (AJ102/100)</f>
+        <v/>
+      </c>
+      <c r="AM102" s="5">
         <f>AI102</f>
         <v/>
       </c>
@@ -4675,49 +4983,49 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>EVM指標集計</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>フェーズ</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>PV (計画値)</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>EV (出来高)</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>AC (実績コスト)</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>SV</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>SPI</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>CPI</t>
         </is>
@@ -4829,39 +5137,39 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>タスクメトリクス</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>フェーズ</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>総数</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>仕掛かり(予定)</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>仕掛かり(実績)</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>完了(予定)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>完了(実績)</t>
         </is>
@@ -4920,49 +5228,49 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>EVM指標集計</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>フェーズ</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>PV (計画値)</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>EV (出来高)</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>AC (実績コスト)</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>SV</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>SPI</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>CPI</t>
         </is>
@@ -5074,39 +5382,39 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>タスクメトリクス</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>フェーズ</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>総数</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>仕掛かり(予定)</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>仕掛かり(実績)</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>完了(予定)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>完了(実績)</t>
         </is>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -63,7 +63,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -71,25 +71,111 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -628,4315 +714,7051 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="D1" s="2" t="inlineStr">
+      <c r="A1" s="2" t="n"/>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>作成</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+      <c r="O1" s="4" t="n"/>
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>レビュー実施</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="Q1" s="3" t="n"/>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="T1" s="3" t="n"/>
+      <c r="U1" s="3" t="n"/>
+      <c r="V1" s="3" t="n"/>
+      <c r="W1" s="3" t="n"/>
+      <c r="X1" s="3" t="n"/>
+      <c r="Y1" s="3" t="n"/>
+      <c r="Z1" s="3" t="n"/>
+      <c r="AA1" s="4" t="n"/>
+      <c r="AB1" s="5" t="inlineStr">
         <is>
           <t>レビュー後修正</t>
         </is>
       </c>
+      <c r="AC1" s="3" t="n"/>
+      <c r="AD1" s="3" t="n"/>
+      <c r="AE1" s="3" t="n"/>
+      <c r="AF1" s="3" t="n"/>
+      <c r="AG1" s="3" t="n"/>
+      <c r="AH1" s="3" t="n"/>
+      <c r="AI1" s="3" t="n"/>
+      <c r="AJ1" s="3" t="n"/>
+      <c r="AK1" s="3" t="n"/>
+      <c r="AL1" s="3" t="n"/>
+      <c r="AM1" s="4" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>機能ID</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>機能名称</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>担当メンバー</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>チームリーダー</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>開始日予定</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>終了日予定</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>工数予定</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>開始日実績</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>終了日実績</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>工数実績</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>進捗率(%)</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>PV (計画値)</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="9" t="inlineStr">
         <is>
           <t>EV (出来高)</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" s="10" t="inlineStr">
         <is>
           <t>AC (実績コスト)</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" s="9" t="inlineStr">
         <is>
           <t>担当メンバー</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q2" s="9" t="inlineStr">
         <is>
           <t>チームリーダー</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" s="9" t="inlineStr">
         <is>
           <t>開始日予定</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="S2" s="9" t="inlineStr">
         <is>
           <t>終了日予定</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="T2" s="9" t="inlineStr">
         <is>
           <t>工数予定</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="U2" s="9" t="inlineStr">
         <is>
           <t>開始日実績</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V2" s="9" t="inlineStr">
         <is>
           <t>終了日実績</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="W2" s="9" t="inlineStr">
         <is>
           <t>工数実績</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="X2" s="9" t="inlineStr">
         <is>
           <t>進捗率(%)</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="Y2" s="9" t="inlineStr">
         <is>
           <t>PV (計画値)</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="Z2" s="9" t="inlineStr">
         <is>
           <t>EV (出来高)</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AA2" s="10" t="inlineStr">
         <is>
           <t>AC (実績コスト)</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AB2" s="9" t="inlineStr">
         <is>
           <t>担当メンバー</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AC2" s="9" t="inlineStr">
         <is>
           <t>チームリーダー</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr">
+      <c r="AD2" s="9" t="inlineStr">
         <is>
           <t>開始日予定</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AE2" s="9" t="inlineStr">
         <is>
           <t>終了日予定</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AF2" s="9" t="inlineStr">
         <is>
           <t>工数予定</t>
         </is>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AG2" s="9" t="inlineStr">
         <is>
           <t>開始日実績</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr">
+      <c r="AH2" s="9" t="inlineStr">
         <is>
           <t>終了日実績</t>
         </is>
       </c>
-      <c r="AI2" s="2" t="inlineStr">
+      <c r="AI2" s="9" t="inlineStr">
         <is>
           <t>工数実績</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AJ2" s="9" t="inlineStr">
         <is>
           <t>進捗率(%)</t>
         </is>
       </c>
-      <c r="AK2" s="2" t="inlineStr">
+      <c r="AK2" s="9" t="inlineStr">
         <is>
           <t>PV (計画値)</t>
         </is>
       </c>
-      <c r="AL2" s="2" t="inlineStr">
+      <c r="AL2" s="9" t="inlineStr">
         <is>
           <t>EV (出来高)</t>
         </is>
       </c>
-      <c r="AM2" s="2" t="inlineStr">
+      <c r="AM2" s="10" t="inlineStr">
         <is>
           <t>AC (実績コスト)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="L3" s="4" t="n"/>
-      <c r="M3" s="5">
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="12" t="n"/>
+      <c r="G3" s="12" t="n"/>
+      <c r="H3" s="12" t="n"/>
+      <c r="I3" s="12" t="n"/>
+      <c r="J3" s="12" t="n"/>
+      <c r="K3" s="12" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="15">
         <f>IF(TODAY()&lt;F3, 0, IF(TODAY()&gt;G3, H3, H3 * (TODAY()-F3)/(G3-F3+1)))</f>
         <v/>
       </c>
-      <c r="N3" s="5">
+      <c r="N3" s="15">
         <f>H3 * (L3/100)</f>
         <v/>
       </c>
-      <c r="O3" s="5">
+      <c r="O3" s="16">
         <f>K3</f>
         <v/>
       </c>
-      <c r="X3" s="4" t="n"/>
-      <c r="Y3" s="5">
+      <c r="P3" s="12" t="n"/>
+      <c r="Q3" s="12" t="n"/>
+      <c r="R3" s="12" t="n"/>
+      <c r="S3" s="12" t="n"/>
+      <c r="T3" s="12" t="n"/>
+      <c r="U3" s="12" t="n"/>
+      <c r="V3" s="12" t="n"/>
+      <c r="W3" s="12" t="n"/>
+      <c r="X3" s="14" t="n"/>
+      <c r="Y3" s="15">
         <f>IF(TODAY()&lt;R3, 0, IF(TODAY()&gt;S3, T3, T3 * (TODAY()-R3)/(S3-R3+1)))</f>
         <v/>
       </c>
-      <c r="Z3" s="5">
+      <c r="Z3" s="15">
         <f>T3 * (X3/100)</f>
         <v/>
       </c>
-      <c r="AA3" s="5">
+      <c r="AA3" s="16">
         <f>W3</f>
         <v/>
       </c>
-      <c r="AJ3" s="4" t="n"/>
-      <c r="AK3" s="5">
+      <c r="AB3" s="12" t="n"/>
+      <c r="AC3" s="12" t="n"/>
+      <c r="AD3" s="12" t="n"/>
+      <c r="AE3" s="12" t="n"/>
+      <c r="AF3" s="12" t="n"/>
+      <c r="AG3" s="12" t="n"/>
+      <c r="AH3" s="12" t="n"/>
+      <c r="AI3" s="12" t="n"/>
+      <c r="AJ3" s="14" t="n"/>
+      <c r="AK3" s="15">
         <f>IF(TODAY()&lt;AD3, 0, IF(TODAY()&gt;AE3, AF3, AF3 * (TODAY()-AD3)/(AE3-AD3+1)))</f>
         <v/>
       </c>
-      <c r="AL3" s="5">
+      <c r="AL3" s="15">
         <f>AF3 * (AJ3/100)</f>
         <v/>
       </c>
-      <c r="AM3" s="5">
+      <c r="AM3" s="16">
         <f>AI3</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="L4" s="4" t="n"/>
-      <c r="M4" s="5">
+      <c r="A4" s="11" t="n"/>
+      <c r="B4" s="12" t="n"/>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="12" t="n"/>
+      <c r="J4" s="12" t="n"/>
+      <c r="K4" s="12" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="15">
         <f>IF(TODAY()&lt;F4, 0, IF(TODAY()&gt;G4, H4, H4 * (TODAY()-F4)/(G4-F4+1)))</f>
         <v/>
       </c>
-      <c r="N4" s="5">
+      <c r="N4" s="15">
         <f>H4 * (L4/100)</f>
         <v/>
       </c>
-      <c r="O4" s="5">
+      <c r="O4" s="16">
         <f>K4</f>
         <v/>
       </c>
-      <c r="X4" s="4" t="n"/>
-      <c r="Y4" s="5">
+      <c r="P4" s="12" t="n"/>
+      <c r="Q4" s="12" t="n"/>
+      <c r="R4" s="12" t="n"/>
+      <c r="S4" s="12" t="n"/>
+      <c r="T4" s="12" t="n"/>
+      <c r="U4" s="12" t="n"/>
+      <c r="V4" s="12" t="n"/>
+      <c r="W4" s="12" t="n"/>
+      <c r="X4" s="14" t="n"/>
+      <c r="Y4" s="15">
         <f>IF(TODAY()&lt;R4, 0, IF(TODAY()&gt;S4, T4, T4 * (TODAY()-R4)/(S4-R4+1)))</f>
         <v/>
       </c>
-      <c r="Z4" s="5">
+      <c r="Z4" s="15">
         <f>T4 * (X4/100)</f>
         <v/>
       </c>
-      <c r="AA4" s="5">
+      <c r="AA4" s="16">
         <f>W4</f>
         <v/>
       </c>
-      <c r="AJ4" s="4" t="n"/>
-      <c r="AK4" s="5">
+      <c r="AB4" s="12" t="n"/>
+      <c r="AC4" s="12" t="n"/>
+      <c r="AD4" s="12" t="n"/>
+      <c r="AE4" s="12" t="n"/>
+      <c r="AF4" s="12" t="n"/>
+      <c r="AG4" s="12" t="n"/>
+      <c r="AH4" s="12" t="n"/>
+      <c r="AI4" s="12" t="n"/>
+      <c r="AJ4" s="14" t="n"/>
+      <c r="AK4" s="15">
         <f>IF(TODAY()&lt;AD4, 0, IF(TODAY()&gt;AE4, AF4, AF4 * (TODAY()-AD4)/(AE4-AD4+1)))</f>
         <v/>
       </c>
-      <c r="AL4" s="5">
+      <c r="AL4" s="15">
         <f>AF4 * (AJ4/100)</f>
         <v/>
       </c>
-      <c r="AM4" s="5">
+      <c r="AM4" s="16">
         <f>AI4</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="5">
+      <c r="A5" s="11" t="n"/>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="12" t="n"/>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="15">
         <f>IF(TODAY()&lt;F5, 0, IF(TODAY()&gt;G5, H5, H5 * (TODAY()-F5)/(G5-F5+1)))</f>
         <v/>
       </c>
-      <c r="N5" s="5">
+      <c r="N5" s="15">
         <f>H5 * (L5/100)</f>
         <v/>
       </c>
-      <c r="O5" s="5">
+      <c r="O5" s="16">
         <f>K5</f>
         <v/>
       </c>
-      <c r="X5" s="4" t="n"/>
-      <c r="Y5" s="5">
+      <c r="P5" s="12" t="n"/>
+      <c r="Q5" s="12" t="n"/>
+      <c r="R5" s="12" t="n"/>
+      <c r="S5" s="12" t="n"/>
+      <c r="T5" s="12" t="n"/>
+      <c r="U5" s="12" t="n"/>
+      <c r="V5" s="12" t="n"/>
+      <c r="W5" s="12" t="n"/>
+      <c r="X5" s="14" t="n"/>
+      <c r="Y5" s="15">
         <f>IF(TODAY()&lt;R5, 0, IF(TODAY()&gt;S5, T5, T5 * (TODAY()-R5)/(S5-R5+1)))</f>
         <v/>
       </c>
-      <c r="Z5" s="5">
+      <c r="Z5" s="15">
         <f>T5 * (X5/100)</f>
         <v/>
       </c>
-      <c r="AA5" s="5">
+      <c r="AA5" s="16">
         <f>W5</f>
         <v/>
       </c>
-      <c r="AJ5" s="4" t="n"/>
-      <c r="AK5" s="5">
+      <c r="AB5" s="12" t="n"/>
+      <c r="AC5" s="12" t="n"/>
+      <c r="AD5" s="12" t="n"/>
+      <c r="AE5" s="12" t="n"/>
+      <c r="AF5" s="12" t="n"/>
+      <c r="AG5" s="12" t="n"/>
+      <c r="AH5" s="12" t="n"/>
+      <c r="AI5" s="12" t="n"/>
+      <c r="AJ5" s="14" t="n"/>
+      <c r="AK5" s="15">
         <f>IF(TODAY()&lt;AD5, 0, IF(TODAY()&gt;AE5, AF5, AF5 * (TODAY()-AD5)/(AE5-AD5+1)))</f>
         <v/>
       </c>
-      <c r="AL5" s="5">
+      <c r="AL5" s="15">
         <f>AF5 * (AJ5/100)</f>
         <v/>
       </c>
-      <c r="AM5" s="5">
+      <c r="AM5" s="16">
         <f>AI5</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="5">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="15">
         <f>IF(TODAY()&lt;F6, 0, IF(TODAY()&gt;G6, H6, H6 * (TODAY()-F6)/(G6-F6+1)))</f>
         <v/>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="15">
         <f>H6 * (L6/100)</f>
         <v/>
       </c>
-      <c r="O6" s="5">
+      <c r="O6" s="16">
         <f>K6</f>
         <v/>
       </c>
-      <c r="X6" s="4" t="n"/>
-      <c r="Y6" s="5">
+      <c r="P6" s="12" t="n"/>
+      <c r="Q6" s="12" t="n"/>
+      <c r="R6" s="12" t="n"/>
+      <c r="S6" s="12" t="n"/>
+      <c r="T6" s="12" t="n"/>
+      <c r="U6" s="12" t="n"/>
+      <c r="V6" s="12" t="n"/>
+      <c r="W6" s="12" t="n"/>
+      <c r="X6" s="14" t="n"/>
+      <c r="Y6" s="15">
         <f>IF(TODAY()&lt;R6, 0, IF(TODAY()&gt;S6, T6, T6 * (TODAY()-R6)/(S6-R6+1)))</f>
         <v/>
       </c>
-      <c r="Z6" s="5">
+      <c r="Z6" s="15">
         <f>T6 * (X6/100)</f>
         <v/>
       </c>
-      <c r="AA6" s="5">
+      <c r="AA6" s="16">
         <f>W6</f>
         <v/>
       </c>
-      <c r="AJ6" s="4" t="n"/>
-      <c r="AK6" s="5">
+      <c r="AB6" s="12" t="n"/>
+      <c r="AC6" s="12" t="n"/>
+      <c r="AD6" s="12" t="n"/>
+      <c r="AE6" s="12" t="n"/>
+      <c r="AF6" s="12" t="n"/>
+      <c r="AG6" s="12" t="n"/>
+      <c r="AH6" s="12" t="n"/>
+      <c r="AI6" s="12" t="n"/>
+      <c r="AJ6" s="14" t="n"/>
+      <c r="AK6" s="15">
         <f>IF(TODAY()&lt;AD6, 0, IF(TODAY()&gt;AE6, AF6, AF6 * (TODAY()-AD6)/(AE6-AD6+1)))</f>
         <v/>
       </c>
-      <c r="AL6" s="5">
+      <c r="AL6" s="15">
         <f>AF6 * (AJ6/100)</f>
         <v/>
       </c>
-      <c r="AM6" s="5">
+      <c r="AM6" s="16">
         <f>AI6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="5">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="12" t="n"/>
+      <c r="I7" s="12" t="n"/>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="14" t="n"/>
+      <c r="M7" s="15">
         <f>IF(TODAY()&lt;F7, 0, IF(TODAY()&gt;G7, H7, H7 * (TODAY()-F7)/(G7-F7+1)))</f>
         <v/>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="15">
         <f>H7 * (L7/100)</f>
         <v/>
       </c>
-      <c r="O7" s="5">
+      <c r="O7" s="16">
         <f>K7</f>
         <v/>
       </c>
-      <c r="X7" s="4" t="n"/>
-      <c r="Y7" s="5">
+      <c r="P7" s="12" t="n"/>
+      <c r="Q7" s="12" t="n"/>
+      <c r="R7" s="12" t="n"/>
+      <c r="S7" s="12" t="n"/>
+      <c r="T7" s="12" t="n"/>
+      <c r="U7" s="12" t="n"/>
+      <c r="V7" s="12" t="n"/>
+      <c r="W7" s="12" t="n"/>
+      <c r="X7" s="14" t="n"/>
+      <c r="Y7" s="15">
         <f>IF(TODAY()&lt;R7, 0, IF(TODAY()&gt;S7, T7, T7 * (TODAY()-R7)/(S7-R7+1)))</f>
         <v/>
       </c>
-      <c r="Z7" s="5">
+      <c r="Z7" s="15">
         <f>T7 * (X7/100)</f>
         <v/>
       </c>
-      <c r="AA7" s="5">
+      <c r="AA7" s="16">
         <f>W7</f>
         <v/>
       </c>
-      <c r="AJ7" s="4" t="n"/>
-      <c r="AK7" s="5">
+      <c r="AB7" s="12" t="n"/>
+      <c r="AC7" s="12" t="n"/>
+      <c r="AD7" s="12" t="n"/>
+      <c r="AE7" s="12" t="n"/>
+      <c r="AF7" s="12" t="n"/>
+      <c r="AG7" s="12" t="n"/>
+      <c r="AH7" s="12" t="n"/>
+      <c r="AI7" s="12" t="n"/>
+      <c r="AJ7" s="14" t="n"/>
+      <c r="AK7" s="15">
         <f>IF(TODAY()&lt;AD7, 0, IF(TODAY()&gt;AE7, AF7, AF7 * (TODAY()-AD7)/(AE7-AD7+1)))</f>
         <v/>
       </c>
-      <c r="AL7" s="5">
+      <c r="AL7" s="15">
         <f>AF7 * (AJ7/100)</f>
         <v/>
       </c>
-      <c r="AM7" s="5">
+      <c r="AM7" s="16">
         <f>AI7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="5">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="12" t="n"/>
+      <c r="H8" s="12" t="n"/>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="14" t="n"/>
+      <c r="M8" s="15">
         <f>IF(TODAY()&lt;F8, 0, IF(TODAY()&gt;G8, H8, H8 * (TODAY()-F8)/(G8-F8+1)))</f>
         <v/>
       </c>
-      <c r="N8" s="5">
+      <c r="N8" s="15">
         <f>H8 * (L8/100)</f>
         <v/>
       </c>
-      <c r="O8" s="5">
+      <c r="O8" s="16">
         <f>K8</f>
         <v/>
       </c>
-      <c r="X8" s="4" t="n"/>
-      <c r="Y8" s="5">
+      <c r="P8" s="12" t="n"/>
+      <c r="Q8" s="12" t="n"/>
+      <c r="R8" s="12" t="n"/>
+      <c r="S8" s="12" t="n"/>
+      <c r="T8" s="12" t="n"/>
+      <c r="U8" s="12" t="n"/>
+      <c r="V8" s="12" t="n"/>
+      <c r="W8" s="12" t="n"/>
+      <c r="X8" s="14" t="n"/>
+      <c r="Y8" s="15">
         <f>IF(TODAY()&lt;R8, 0, IF(TODAY()&gt;S8, T8, T8 * (TODAY()-R8)/(S8-R8+1)))</f>
         <v/>
       </c>
-      <c r="Z8" s="5">
+      <c r="Z8" s="15">
         <f>T8 * (X8/100)</f>
         <v/>
       </c>
-      <c r="AA8" s="5">
+      <c r="AA8" s="16">
         <f>W8</f>
         <v/>
       </c>
-      <c r="AJ8" s="4" t="n"/>
-      <c r="AK8" s="5">
+      <c r="AB8" s="12" t="n"/>
+      <c r="AC8" s="12" t="n"/>
+      <c r="AD8" s="12" t="n"/>
+      <c r="AE8" s="12" t="n"/>
+      <c r="AF8" s="12" t="n"/>
+      <c r="AG8" s="12" t="n"/>
+      <c r="AH8" s="12" t="n"/>
+      <c r="AI8" s="12" t="n"/>
+      <c r="AJ8" s="14" t="n"/>
+      <c r="AK8" s="15">
         <f>IF(TODAY()&lt;AD8, 0, IF(TODAY()&gt;AE8, AF8, AF8 * (TODAY()-AD8)/(AE8-AD8+1)))</f>
         <v/>
       </c>
-      <c r="AL8" s="5">
+      <c r="AL8" s="15">
         <f>AF8 * (AJ8/100)</f>
         <v/>
       </c>
-      <c r="AM8" s="5">
+      <c r="AM8" s="16">
         <f>AI8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="5">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="14" t="n"/>
+      <c r="M9" s="15">
         <f>IF(TODAY()&lt;F9, 0, IF(TODAY()&gt;G9, H9, H9 * (TODAY()-F9)/(G9-F9+1)))</f>
         <v/>
       </c>
-      <c r="N9" s="5">
+      <c r="N9" s="15">
         <f>H9 * (L9/100)</f>
         <v/>
       </c>
-      <c r="O9" s="5">
+      <c r="O9" s="16">
         <f>K9</f>
         <v/>
       </c>
-      <c r="X9" s="4" t="n"/>
-      <c r="Y9" s="5">
+      <c r="P9" s="12" t="n"/>
+      <c r="Q9" s="12" t="n"/>
+      <c r="R9" s="12" t="n"/>
+      <c r="S9" s="12" t="n"/>
+      <c r="T9" s="12" t="n"/>
+      <c r="U9" s="12" t="n"/>
+      <c r="V9" s="12" t="n"/>
+      <c r="W9" s="12" t="n"/>
+      <c r="X9" s="14" t="n"/>
+      <c r="Y9" s="15">
         <f>IF(TODAY()&lt;R9, 0, IF(TODAY()&gt;S9, T9, T9 * (TODAY()-R9)/(S9-R9+1)))</f>
         <v/>
       </c>
-      <c r="Z9" s="5">
+      <c r="Z9" s="15">
         <f>T9 * (X9/100)</f>
         <v/>
       </c>
-      <c r="AA9" s="5">
+      <c r="AA9" s="16">
         <f>W9</f>
         <v/>
       </c>
-      <c r="AJ9" s="4" t="n"/>
-      <c r="AK9" s="5">
+      <c r="AB9" s="12" t="n"/>
+      <c r="AC9" s="12" t="n"/>
+      <c r="AD9" s="12" t="n"/>
+      <c r="AE9" s="12" t="n"/>
+      <c r="AF9" s="12" t="n"/>
+      <c r="AG9" s="12" t="n"/>
+      <c r="AH9" s="12" t="n"/>
+      <c r="AI9" s="12" t="n"/>
+      <c r="AJ9" s="14" t="n"/>
+      <c r="AK9" s="15">
         <f>IF(TODAY()&lt;AD9, 0, IF(TODAY()&gt;AE9, AF9, AF9 * (TODAY()-AD9)/(AE9-AD9+1)))</f>
         <v/>
       </c>
-      <c r="AL9" s="5">
+      <c r="AL9" s="15">
         <f>AF9 * (AJ9/100)</f>
         <v/>
       </c>
-      <c r="AM9" s="5">
+      <c r="AM9" s="16">
         <f>AI9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="5">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="14" t="n"/>
+      <c r="M10" s="15">
         <f>IF(TODAY()&lt;F10, 0, IF(TODAY()&gt;G10, H10, H10 * (TODAY()-F10)/(G10-F10+1)))</f>
         <v/>
       </c>
-      <c r="N10" s="5">
+      <c r="N10" s="15">
         <f>H10 * (L10/100)</f>
         <v/>
       </c>
-      <c r="O10" s="5">
+      <c r="O10" s="16">
         <f>K10</f>
         <v/>
       </c>
-      <c r="X10" s="4" t="n"/>
-      <c r="Y10" s="5">
+      <c r="P10" s="12" t="n"/>
+      <c r="Q10" s="12" t="n"/>
+      <c r="R10" s="12" t="n"/>
+      <c r="S10" s="12" t="n"/>
+      <c r="T10" s="12" t="n"/>
+      <c r="U10" s="12" t="n"/>
+      <c r="V10" s="12" t="n"/>
+      <c r="W10" s="12" t="n"/>
+      <c r="X10" s="14" t="n"/>
+      <c r="Y10" s="15">
         <f>IF(TODAY()&lt;R10, 0, IF(TODAY()&gt;S10, T10, T10 * (TODAY()-R10)/(S10-R10+1)))</f>
         <v/>
       </c>
-      <c r="Z10" s="5">
+      <c r="Z10" s="15">
         <f>T10 * (X10/100)</f>
         <v/>
       </c>
-      <c r="AA10" s="5">
+      <c r="AA10" s="16">
         <f>W10</f>
         <v/>
       </c>
-      <c r="AJ10" s="4" t="n"/>
-      <c r="AK10" s="5">
+      <c r="AB10" s="12" t="n"/>
+      <c r="AC10" s="12" t="n"/>
+      <c r="AD10" s="12" t="n"/>
+      <c r="AE10" s="12" t="n"/>
+      <c r="AF10" s="12" t="n"/>
+      <c r="AG10" s="12" t="n"/>
+      <c r="AH10" s="12" t="n"/>
+      <c r="AI10" s="12" t="n"/>
+      <c r="AJ10" s="14" t="n"/>
+      <c r="AK10" s="15">
         <f>IF(TODAY()&lt;AD10, 0, IF(TODAY()&gt;AE10, AF10, AF10 * (TODAY()-AD10)/(AE10-AD10+1)))</f>
         <v/>
       </c>
-      <c r="AL10" s="5">
+      <c r="AL10" s="15">
         <f>AF10 * (AJ10/100)</f>
         <v/>
       </c>
-      <c r="AM10" s="5">
+      <c r="AM10" s="16">
         <f>AI10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="5">
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="15">
         <f>IF(TODAY()&lt;F11, 0, IF(TODAY()&gt;G11, H11, H11 * (TODAY()-F11)/(G11-F11+1)))</f>
         <v/>
       </c>
-      <c r="N11" s="5">
+      <c r="N11" s="15">
         <f>H11 * (L11/100)</f>
         <v/>
       </c>
-      <c r="O11" s="5">
+      <c r="O11" s="16">
         <f>K11</f>
         <v/>
       </c>
-      <c r="X11" s="4" t="n"/>
-      <c r="Y11" s="5">
+      <c r="P11" s="12" t="n"/>
+      <c r="Q11" s="12" t="n"/>
+      <c r="R11" s="12" t="n"/>
+      <c r="S11" s="12" t="n"/>
+      <c r="T11" s="12" t="n"/>
+      <c r="U11" s="12" t="n"/>
+      <c r="V11" s="12" t="n"/>
+      <c r="W11" s="12" t="n"/>
+      <c r="X11" s="14" t="n"/>
+      <c r="Y11" s="15">
         <f>IF(TODAY()&lt;R11, 0, IF(TODAY()&gt;S11, T11, T11 * (TODAY()-R11)/(S11-R11+1)))</f>
         <v/>
       </c>
-      <c r="Z11" s="5">
+      <c r="Z11" s="15">
         <f>T11 * (X11/100)</f>
         <v/>
       </c>
-      <c r="AA11" s="5">
+      <c r="AA11" s="16">
         <f>W11</f>
         <v/>
       </c>
-      <c r="AJ11" s="4" t="n"/>
-      <c r="AK11" s="5">
+      <c r="AB11" s="12" t="n"/>
+      <c r="AC11" s="12" t="n"/>
+      <c r="AD11" s="12" t="n"/>
+      <c r="AE11" s="12" t="n"/>
+      <c r="AF11" s="12" t="n"/>
+      <c r="AG11" s="12" t="n"/>
+      <c r="AH11" s="12" t="n"/>
+      <c r="AI11" s="12" t="n"/>
+      <c r="AJ11" s="14" t="n"/>
+      <c r="AK11" s="15">
         <f>IF(TODAY()&lt;AD11, 0, IF(TODAY()&gt;AE11, AF11, AF11 * (TODAY()-AD11)/(AE11-AD11+1)))</f>
         <v/>
       </c>
-      <c r="AL11" s="5">
+      <c r="AL11" s="15">
         <f>AF11 * (AJ11/100)</f>
         <v/>
       </c>
-      <c r="AM11" s="5">
+      <c r="AM11" s="16">
         <f>AI11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="5">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="14" t="n"/>
+      <c r="M12" s="15">
         <f>IF(TODAY()&lt;F12, 0, IF(TODAY()&gt;G12, H12, H12 * (TODAY()-F12)/(G12-F12+1)))</f>
         <v/>
       </c>
-      <c r="N12" s="5">
+      <c r="N12" s="15">
         <f>H12 * (L12/100)</f>
         <v/>
       </c>
-      <c r="O12" s="5">
+      <c r="O12" s="16">
         <f>K12</f>
         <v/>
       </c>
-      <c r="X12" s="4" t="n"/>
-      <c r="Y12" s="5">
+      <c r="P12" s="12" t="n"/>
+      <c r="Q12" s="12" t="n"/>
+      <c r="R12" s="12" t="n"/>
+      <c r="S12" s="12" t="n"/>
+      <c r="T12" s="12" t="n"/>
+      <c r="U12" s="12" t="n"/>
+      <c r="V12" s="12" t="n"/>
+      <c r="W12" s="12" t="n"/>
+      <c r="X12" s="14" t="n"/>
+      <c r="Y12" s="15">
         <f>IF(TODAY()&lt;R12, 0, IF(TODAY()&gt;S12, T12, T12 * (TODAY()-R12)/(S12-R12+1)))</f>
         <v/>
       </c>
-      <c r="Z12" s="5">
+      <c r="Z12" s="15">
         <f>T12 * (X12/100)</f>
         <v/>
       </c>
-      <c r="AA12" s="5">
+      <c r="AA12" s="16">
         <f>W12</f>
         <v/>
       </c>
-      <c r="AJ12" s="4" t="n"/>
-      <c r="AK12" s="5">
+      <c r="AB12" s="12" t="n"/>
+      <c r="AC12" s="12" t="n"/>
+      <c r="AD12" s="12" t="n"/>
+      <c r="AE12" s="12" t="n"/>
+      <c r="AF12" s="12" t="n"/>
+      <c r="AG12" s="12" t="n"/>
+      <c r="AH12" s="12" t="n"/>
+      <c r="AI12" s="12" t="n"/>
+      <c r="AJ12" s="14" t="n"/>
+      <c r="AK12" s="15">
         <f>IF(TODAY()&lt;AD12, 0, IF(TODAY()&gt;AE12, AF12, AF12 * (TODAY()-AD12)/(AE12-AD12+1)))</f>
         <v/>
       </c>
-      <c r="AL12" s="5">
+      <c r="AL12" s="15">
         <f>AF12 * (AJ12/100)</f>
         <v/>
       </c>
-      <c r="AM12" s="5">
+      <c r="AM12" s="16">
         <f>AI12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="5">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="14" t="n"/>
+      <c r="M13" s="15">
         <f>IF(TODAY()&lt;F13, 0, IF(TODAY()&gt;G13, H13, H13 * (TODAY()-F13)/(G13-F13+1)))</f>
         <v/>
       </c>
-      <c r="N13" s="5">
+      <c r="N13" s="15">
         <f>H13 * (L13/100)</f>
         <v/>
       </c>
-      <c r="O13" s="5">
+      <c r="O13" s="16">
         <f>K13</f>
         <v/>
       </c>
-      <c r="X13" s="4" t="n"/>
-      <c r="Y13" s="5">
+      <c r="P13" s="12" t="n"/>
+      <c r="Q13" s="12" t="n"/>
+      <c r="R13" s="12" t="n"/>
+      <c r="S13" s="12" t="n"/>
+      <c r="T13" s="12" t="n"/>
+      <c r="U13" s="12" t="n"/>
+      <c r="V13" s="12" t="n"/>
+      <c r="W13" s="12" t="n"/>
+      <c r="X13" s="14" t="n"/>
+      <c r="Y13" s="15">
         <f>IF(TODAY()&lt;R13, 0, IF(TODAY()&gt;S13, T13, T13 * (TODAY()-R13)/(S13-R13+1)))</f>
         <v/>
       </c>
-      <c r="Z13" s="5">
+      <c r="Z13" s="15">
         <f>T13 * (X13/100)</f>
         <v/>
       </c>
-      <c r="AA13" s="5">
+      <c r="AA13" s="16">
         <f>W13</f>
         <v/>
       </c>
-      <c r="AJ13" s="4" t="n"/>
-      <c r="AK13" s="5">
+      <c r="AB13" s="12" t="n"/>
+      <c r="AC13" s="12" t="n"/>
+      <c r="AD13" s="12" t="n"/>
+      <c r="AE13" s="12" t="n"/>
+      <c r="AF13" s="12" t="n"/>
+      <c r="AG13" s="12" t="n"/>
+      <c r="AH13" s="12" t="n"/>
+      <c r="AI13" s="12" t="n"/>
+      <c r="AJ13" s="14" t="n"/>
+      <c r="AK13" s="15">
         <f>IF(TODAY()&lt;AD13, 0, IF(TODAY()&gt;AE13, AF13, AF13 * (TODAY()-AD13)/(AE13-AD13+1)))</f>
         <v/>
       </c>
-      <c r="AL13" s="5">
+      <c r="AL13" s="15">
         <f>AF13 * (AJ13/100)</f>
         <v/>
       </c>
-      <c r="AM13" s="5">
+      <c r="AM13" s="16">
         <f>AI13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="5">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="14" t="n"/>
+      <c r="M14" s="15">
         <f>IF(TODAY()&lt;F14, 0, IF(TODAY()&gt;G14, H14, H14 * (TODAY()-F14)/(G14-F14+1)))</f>
         <v/>
       </c>
-      <c r="N14" s="5">
+      <c r="N14" s="15">
         <f>H14 * (L14/100)</f>
         <v/>
       </c>
-      <c r="O14" s="5">
+      <c r="O14" s="16">
         <f>K14</f>
         <v/>
       </c>
-      <c r="X14" s="4" t="n"/>
-      <c r="Y14" s="5">
+      <c r="P14" s="12" t="n"/>
+      <c r="Q14" s="12" t="n"/>
+      <c r="R14" s="12" t="n"/>
+      <c r="S14" s="12" t="n"/>
+      <c r="T14" s="12" t="n"/>
+      <c r="U14" s="12" t="n"/>
+      <c r="V14" s="12" t="n"/>
+      <c r="W14" s="12" t="n"/>
+      <c r="X14" s="14" t="n"/>
+      <c r="Y14" s="15">
         <f>IF(TODAY()&lt;R14, 0, IF(TODAY()&gt;S14, T14, T14 * (TODAY()-R14)/(S14-R14+1)))</f>
         <v/>
       </c>
-      <c r="Z14" s="5">
+      <c r="Z14" s="15">
         <f>T14 * (X14/100)</f>
         <v/>
       </c>
-      <c r="AA14" s="5">
+      <c r="AA14" s="16">
         <f>W14</f>
         <v/>
       </c>
-      <c r="AJ14" s="4" t="n"/>
-      <c r="AK14" s="5">
+      <c r="AB14" s="12" t="n"/>
+      <c r="AC14" s="12" t="n"/>
+      <c r="AD14" s="12" t="n"/>
+      <c r="AE14" s="12" t="n"/>
+      <c r="AF14" s="12" t="n"/>
+      <c r="AG14" s="12" t="n"/>
+      <c r="AH14" s="12" t="n"/>
+      <c r="AI14" s="12" t="n"/>
+      <c r="AJ14" s="14" t="n"/>
+      <c r="AK14" s="15">
         <f>IF(TODAY()&lt;AD14, 0, IF(TODAY()&gt;AE14, AF14, AF14 * (TODAY()-AD14)/(AE14-AD14+1)))</f>
         <v/>
       </c>
-      <c r="AL14" s="5">
+      <c r="AL14" s="15">
         <f>AF14 * (AJ14/100)</f>
         <v/>
       </c>
-      <c r="AM14" s="5">
+      <c r="AM14" s="16">
         <f>AI14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="5">
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="14" t="n"/>
+      <c r="M15" s="15">
         <f>IF(TODAY()&lt;F15, 0, IF(TODAY()&gt;G15, H15, H15 * (TODAY()-F15)/(G15-F15+1)))</f>
         <v/>
       </c>
-      <c r="N15" s="5">
+      <c r="N15" s="15">
         <f>H15 * (L15/100)</f>
         <v/>
       </c>
-      <c r="O15" s="5">
+      <c r="O15" s="16">
         <f>K15</f>
         <v/>
       </c>
-      <c r="X15" s="4" t="n"/>
-      <c r="Y15" s="5">
+      <c r="P15" s="12" t="n"/>
+      <c r="Q15" s="12" t="n"/>
+      <c r="R15" s="12" t="n"/>
+      <c r="S15" s="12" t="n"/>
+      <c r="T15" s="12" t="n"/>
+      <c r="U15" s="12" t="n"/>
+      <c r="V15" s="12" t="n"/>
+      <c r="W15" s="12" t="n"/>
+      <c r="X15" s="14" t="n"/>
+      <c r="Y15" s="15">
         <f>IF(TODAY()&lt;R15, 0, IF(TODAY()&gt;S15, T15, T15 * (TODAY()-R15)/(S15-R15+1)))</f>
         <v/>
       </c>
-      <c r="Z15" s="5">
+      <c r="Z15" s="15">
         <f>T15 * (X15/100)</f>
         <v/>
       </c>
-      <c r="AA15" s="5">
+      <c r="AA15" s="16">
         <f>W15</f>
         <v/>
       </c>
-      <c r="AJ15" s="4" t="n"/>
-      <c r="AK15" s="5">
+      <c r="AB15" s="12" t="n"/>
+      <c r="AC15" s="12" t="n"/>
+      <c r="AD15" s="12" t="n"/>
+      <c r="AE15" s="12" t="n"/>
+      <c r="AF15" s="12" t="n"/>
+      <c r="AG15" s="12" t="n"/>
+      <c r="AH15" s="12" t="n"/>
+      <c r="AI15" s="12" t="n"/>
+      <c r="AJ15" s="14" t="n"/>
+      <c r="AK15" s="15">
         <f>IF(TODAY()&lt;AD15, 0, IF(TODAY()&gt;AE15, AF15, AF15 * (TODAY()-AD15)/(AE15-AD15+1)))</f>
         <v/>
       </c>
-      <c r="AL15" s="5">
+      <c r="AL15" s="15">
         <f>AF15 * (AJ15/100)</f>
         <v/>
       </c>
-      <c r="AM15" s="5">
+      <c r="AM15" s="16">
         <f>AI15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="5">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="15">
         <f>IF(TODAY()&lt;F16, 0, IF(TODAY()&gt;G16, H16, H16 * (TODAY()-F16)/(G16-F16+1)))</f>
         <v/>
       </c>
-      <c r="N16" s="5">
+      <c r="N16" s="15">
         <f>H16 * (L16/100)</f>
         <v/>
       </c>
-      <c r="O16" s="5">
+      <c r="O16" s="16">
         <f>K16</f>
         <v/>
       </c>
-      <c r="X16" s="4" t="n"/>
-      <c r="Y16" s="5">
+      <c r="P16" s="12" t="n"/>
+      <c r="Q16" s="12" t="n"/>
+      <c r="R16" s="12" t="n"/>
+      <c r="S16" s="12" t="n"/>
+      <c r="T16" s="12" t="n"/>
+      <c r="U16" s="12" t="n"/>
+      <c r="V16" s="12" t="n"/>
+      <c r="W16" s="12" t="n"/>
+      <c r="X16" s="14" t="n"/>
+      <c r="Y16" s="15">
         <f>IF(TODAY()&lt;R16, 0, IF(TODAY()&gt;S16, T16, T16 * (TODAY()-R16)/(S16-R16+1)))</f>
         <v/>
       </c>
-      <c r="Z16" s="5">
+      <c r="Z16" s="15">
         <f>T16 * (X16/100)</f>
         <v/>
       </c>
-      <c r="AA16" s="5">
+      <c r="AA16" s="16">
         <f>W16</f>
         <v/>
       </c>
-      <c r="AJ16" s="4" t="n"/>
-      <c r="AK16" s="5">
+      <c r="AB16" s="12" t="n"/>
+      <c r="AC16" s="12" t="n"/>
+      <c r="AD16" s="12" t="n"/>
+      <c r="AE16" s="12" t="n"/>
+      <c r="AF16" s="12" t="n"/>
+      <c r="AG16" s="12" t="n"/>
+      <c r="AH16" s="12" t="n"/>
+      <c r="AI16" s="12" t="n"/>
+      <c r="AJ16" s="14" t="n"/>
+      <c r="AK16" s="15">
         <f>IF(TODAY()&lt;AD16, 0, IF(TODAY()&gt;AE16, AF16, AF16 * (TODAY()-AD16)/(AE16-AD16+1)))</f>
         <v/>
       </c>
-      <c r="AL16" s="5">
+      <c r="AL16" s="15">
         <f>AF16 * (AJ16/100)</f>
         <v/>
       </c>
-      <c r="AM16" s="5">
+      <c r="AM16" s="16">
         <f>AI16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="L17" s="4" t="n"/>
-      <c r="M17" s="5">
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="15">
         <f>IF(TODAY()&lt;F17, 0, IF(TODAY()&gt;G17, H17, H17 * (TODAY()-F17)/(G17-F17+1)))</f>
         <v/>
       </c>
-      <c r="N17" s="5">
+      <c r="N17" s="15">
         <f>H17 * (L17/100)</f>
         <v/>
       </c>
-      <c r="O17" s="5">
+      <c r="O17" s="16">
         <f>K17</f>
         <v/>
       </c>
-      <c r="X17" s="4" t="n"/>
-      <c r="Y17" s="5">
+      <c r="P17" s="12" t="n"/>
+      <c r="Q17" s="12" t="n"/>
+      <c r="R17" s="12" t="n"/>
+      <c r="S17" s="12" t="n"/>
+      <c r="T17" s="12" t="n"/>
+      <c r="U17" s="12" t="n"/>
+      <c r="V17" s="12" t="n"/>
+      <c r="W17" s="12" t="n"/>
+      <c r="X17" s="14" t="n"/>
+      <c r="Y17" s="15">
         <f>IF(TODAY()&lt;R17, 0, IF(TODAY()&gt;S17, T17, T17 * (TODAY()-R17)/(S17-R17+1)))</f>
         <v/>
       </c>
-      <c r="Z17" s="5">
+      <c r="Z17" s="15">
         <f>T17 * (X17/100)</f>
         <v/>
       </c>
-      <c r="AA17" s="5">
+      <c r="AA17" s="16">
         <f>W17</f>
         <v/>
       </c>
-      <c r="AJ17" s="4" t="n"/>
-      <c r="AK17" s="5">
+      <c r="AB17" s="12" t="n"/>
+      <c r="AC17" s="12" t="n"/>
+      <c r="AD17" s="12" t="n"/>
+      <c r="AE17" s="12" t="n"/>
+      <c r="AF17" s="12" t="n"/>
+      <c r="AG17" s="12" t="n"/>
+      <c r="AH17" s="12" t="n"/>
+      <c r="AI17" s="12" t="n"/>
+      <c r="AJ17" s="14" t="n"/>
+      <c r="AK17" s="15">
         <f>IF(TODAY()&lt;AD17, 0, IF(TODAY()&gt;AE17, AF17, AF17 * (TODAY()-AD17)/(AE17-AD17+1)))</f>
         <v/>
       </c>
-      <c r="AL17" s="5">
+      <c r="AL17" s="15">
         <f>AF17 * (AJ17/100)</f>
         <v/>
       </c>
-      <c r="AM17" s="5">
+      <c r="AM17" s="16">
         <f>AI17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="L18" s="4" t="n"/>
-      <c r="M18" s="5">
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="15">
         <f>IF(TODAY()&lt;F18, 0, IF(TODAY()&gt;G18, H18, H18 * (TODAY()-F18)/(G18-F18+1)))</f>
         <v/>
       </c>
-      <c r="N18" s="5">
+      <c r="N18" s="15">
         <f>H18 * (L18/100)</f>
         <v/>
       </c>
-      <c r="O18" s="5">
+      <c r="O18" s="16">
         <f>K18</f>
         <v/>
       </c>
-      <c r="X18" s="4" t="n"/>
-      <c r="Y18" s="5">
+      <c r="P18" s="12" t="n"/>
+      <c r="Q18" s="12" t="n"/>
+      <c r="R18" s="12" t="n"/>
+      <c r="S18" s="12" t="n"/>
+      <c r="T18" s="12" t="n"/>
+      <c r="U18" s="12" t="n"/>
+      <c r="V18" s="12" t="n"/>
+      <c r="W18" s="12" t="n"/>
+      <c r="X18" s="14" t="n"/>
+      <c r="Y18" s="15">
         <f>IF(TODAY()&lt;R18, 0, IF(TODAY()&gt;S18, T18, T18 * (TODAY()-R18)/(S18-R18+1)))</f>
         <v/>
       </c>
-      <c r="Z18" s="5">
+      <c r="Z18" s="15">
         <f>T18 * (X18/100)</f>
         <v/>
       </c>
-      <c r="AA18" s="5">
+      <c r="AA18" s="16">
         <f>W18</f>
         <v/>
       </c>
-      <c r="AJ18" s="4" t="n"/>
-      <c r="AK18" s="5">
+      <c r="AB18" s="12" t="n"/>
+      <c r="AC18" s="12" t="n"/>
+      <c r="AD18" s="12" t="n"/>
+      <c r="AE18" s="12" t="n"/>
+      <c r="AF18" s="12" t="n"/>
+      <c r="AG18" s="12" t="n"/>
+      <c r="AH18" s="12" t="n"/>
+      <c r="AI18" s="12" t="n"/>
+      <c r="AJ18" s="14" t="n"/>
+      <c r="AK18" s="15">
         <f>IF(TODAY()&lt;AD18, 0, IF(TODAY()&gt;AE18, AF18, AF18 * (TODAY()-AD18)/(AE18-AD18+1)))</f>
         <v/>
       </c>
-      <c r="AL18" s="5">
+      <c r="AL18" s="15">
         <f>AF18 * (AJ18/100)</f>
         <v/>
       </c>
-      <c r="AM18" s="5">
+      <c r="AM18" s="16">
         <f>AI18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="L19" s="4" t="n"/>
-      <c r="M19" s="5">
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="14" t="n"/>
+      <c r="M19" s="15">
         <f>IF(TODAY()&lt;F19, 0, IF(TODAY()&gt;G19, H19, H19 * (TODAY()-F19)/(G19-F19+1)))</f>
         <v/>
       </c>
-      <c r="N19" s="5">
+      <c r="N19" s="15">
         <f>H19 * (L19/100)</f>
         <v/>
       </c>
-      <c r="O19" s="5">
+      <c r="O19" s="16">
         <f>K19</f>
         <v/>
       </c>
-      <c r="X19" s="4" t="n"/>
-      <c r="Y19" s="5">
+      <c r="P19" s="12" t="n"/>
+      <c r="Q19" s="12" t="n"/>
+      <c r="R19" s="12" t="n"/>
+      <c r="S19" s="12" t="n"/>
+      <c r="T19" s="12" t="n"/>
+      <c r="U19" s="12" t="n"/>
+      <c r="V19" s="12" t="n"/>
+      <c r="W19" s="12" t="n"/>
+      <c r="X19" s="14" t="n"/>
+      <c r="Y19" s="15">
         <f>IF(TODAY()&lt;R19, 0, IF(TODAY()&gt;S19, T19, T19 * (TODAY()-R19)/(S19-R19+1)))</f>
         <v/>
       </c>
-      <c r="Z19" s="5">
+      <c r="Z19" s="15">
         <f>T19 * (X19/100)</f>
         <v/>
       </c>
-      <c r="AA19" s="5">
+      <c r="AA19" s="16">
         <f>W19</f>
         <v/>
       </c>
-      <c r="AJ19" s="4" t="n"/>
-      <c r="AK19" s="5">
+      <c r="AB19" s="12" t="n"/>
+      <c r="AC19" s="12" t="n"/>
+      <c r="AD19" s="12" t="n"/>
+      <c r="AE19" s="12" t="n"/>
+      <c r="AF19" s="12" t="n"/>
+      <c r="AG19" s="12" t="n"/>
+      <c r="AH19" s="12" t="n"/>
+      <c r="AI19" s="12" t="n"/>
+      <c r="AJ19" s="14" t="n"/>
+      <c r="AK19" s="15">
         <f>IF(TODAY()&lt;AD19, 0, IF(TODAY()&gt;AE19, AF19, AF19 * (TODAY()-AD19)/(AE19-AD19+1)))</f>
         <v/>
       </c>
-      <c r="AL19" s="5">
+      <c r="AL19" s="15">
         <f>AF19 * (AJ19/100)</f>
         <v/>
       </c>
-      <c r="AM19" s="5">
+      <c r="AM19" s="16">
         <f>AI19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="5">
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="14" t="n"/>
+      <c r="M20" s="15">
         <f>IF(TODAY()&lt;F20, 0, IF(TODAY()&gt;G20, H20, H20 * (TODAY()-F20)/(G20-F20+1)))</f>
         <v/>
       </c>
-      <c r="N20" s="5">
+      <c r="N20" s="15">
         <f>H20 * (L20/100)</f>
         <v/>
       </c>
-      <c r="O20" s="5">
+      <c r="O20" s="16">
         <f>K20</f>
         <v/>
       </c>
-      <c r="X20" s="4" t="n"/>
-      <c r="Y20" s="5">
+      <c r="P20" s="12" t="n"/>
+      <c r="Q20" s="12" t="n"/>
+      <c r="R20" s="12" t="n"/>
+      <c r="S20" s="12" t="n"/>
+      <c r="T20" s="12" t="n"/>
+      <c r="U20" s="12" t="n"/>
+      <c r="V20" s="12" t="n"/>
+      <c r="W20" s="12" t="n"/>
+      <c r="X20" s="14" t="n"/>
+      <c r="Y20" s="15">
         <f>IF(TODAY()&lt;R20, 0, IF(TODAY()&gt;S20, T20, T20 * (TODAY()-R20)/(S20-R20+1)))</f>
         <v/>
       </c>
-      <c r="Z20" s="5">
+      <c r="Z20" s="15">
         <f>T20 * (X20/100)</f>
         <v/>
       </c>
-      <c r="AA20" s="5">
+      <c r="AA20" s="16">
         <f>W20</f>
         <v/>
       </c>
-      <c r="AJ20" s="4" t="n"/>
-      <c r="AK20" s="5">
+      <c r="AB20" s="12" t="n"/>
+      <c r="AC20" s="12" t="n"/>
+      <c r="AD20" s="12" t="n"/>
+      <c r="AE20" s="12" t="n"/>
+      <c r="AF20" s="12" t="n"/>
+      <c r="AG20" s="12" t="n"/>
+      <c r="AH20" s="12" t="n"/>
+      <c r="AI20" s="12" t="n"/>
+      <c r="AJ20" s="14" t="n"/>
+      <c r="AK20" s="15">
         <f>IF(TODAY()&lt;AD20, 0, IF(TODAY()&gt;AE20, AF20, AF20 * (TODAY()-AD20)/(AE20-AD20+1)))</f>
         <v/>
       </c>
-      <c r="AL20" s="5">
+      <c r="AL20" s="15">
         <f>AF20 * (AJ20/100)</f>
         <v/>
       </c>
-      <c r="AM20" s="5">
+      <c r="AM20" s="16">
         <f>AI20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="L21" s="4" t="n"/>
-      <c r="M21" s="5">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="14" t="n"/>
+      <c r="M21" s="15">
         <f>IF(TODAY()&lt;F21, 0, IF(TODAY()&gt;G21, H21, H21 * (TODAY()-F21)/(G21-F21+1)))</f>
         <v/>
       </c>
-      <c r="N21" s="5">
+      <c r="N21" s="15">
         <f>H21 * (L21/100)</f>
         <v/>
       </c>
-      <c r="O21" s="5">
+      <c r="O21" s="16">
         <f>K21</f>
         <v/>
       </c>
-      <c r="X21" s="4" t="n"/>
-      <c r="Y21" s="5">
+      <c r="P21" s="12" t="n"/>
+      <c r="Q21" s="12" t="n"/>
+      <c r="R21" s="12" t="n"/>
+      <c r="S21" s="12" t="n"/>
+      <c r="T21" s="12" t="n"/>
+      <c r="U21" s="12" t="n"/>
+      <c r="V21" s="12" t="n"/>
+      <c r="W21" s="12" t="n"/>
+      <c r="X21" s="14" t="n"/>
+      <c r="Y21" s="15">
         <f>IF(TODAY()&lt;R21, 0, IF(TODAY()&gt;S21, T21, T21 * (TODAY()-R21)/(S21-R21+1)))</f>
         <v/>
       </c>
-      <c r="Z21" s="5">
+      <c r="Z21" s="15">
         <f>T21 * (X21/100)</f>
         <v/>
       </c>
-      <c r="AA21" s="5">
+      <c r="AA21" s="16">
         <f>W21</f>
         <v/>
       </c>
-      <c r="AJ21" s="4" t="n"/>
-      <c r="AK21" s="5">
+      <c r="AB21" s="12" t="n"/>
+      <c r="AC21" s="12" t="n"/>
+      <c r="AD21" s="12" t="n"/>
+      <c r="AE21" s="12" t="n"/>
+      <c r="AF21" s="12" t="n"/>
+      <c r="AG21" s="12" t="n"/>
+      <c r="AH21" s="12" t="n"/>
+      <c r="AI21" s="12" t="n"/>
+      <c r="AJ21" s="14" t="n"/>
+      <c r="AK21" s="15">
         <f>IF(TODAY()&lt;AD21, 0, IF(TODAY()&gt;AE21, AF21, AF21 * (TODAY()-AD21)/(AE21-AD21+1)))</f>
         <v/>
       </c>
-      <c r="AL21" s="5">
+      <c r="AL21" s="15">
         <f>AF21 * (AJ21/100)</f>
         <v/>
       </c>
-      <c r="AM21" s="5">
+      <c r="AM21" s="16">
         <f>AI21</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="L22" s="4" t="n"/>
-      <c r="M22" s="5">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="14" t="n"/>
+      <c r="M22" s="15">
         <f>IF(TODAY()&lt;F22, 0, IF(TODAY()&gt;G22, H22, H22 * (TODAY()-F22)/(G22-F22+1)))</f>
         <v/>
       </c>
-      <c r="N22" s="5">
+      <c r="N22" s="15">
         <f>H22 * (L22/100)</f>
         <v/>
       </c>
-      <c r="O22" s="5">
+      <c r="O22" s="16">
         <f>K22</f>
         <v/>
       </c>
-      <c r="X22" s="4" t="n"/>
-      <c r="Y22" s="5">
+      <c r="P22" s="12" t="n"/>
+      <c r="Q22" s="12" t="n"/>
+      <c r="R22" s="12" t="n"/>
+      <c r="S22" s="12" t="n"/>
+      <c r="T22" s="12" t="n"/>
+      <c r="U22" s="12" t="n"/>
+      <c r="V22" s="12" t="n"/>
+      <c r="W22" s="12" t="n"/>
+      <c r="X22" s="14" t="n"/>
+      <c r="Y22" s="15">
         <f>IF(TODAY()&lt;R22, 0, IF(TODAY()&gt;S22, T22, T22 * (TODAY()-R22)/(S22-R22+1)))</f>
         <v/>
       </c>
-      <c r="Z22" s="5">
+      <c r="Z22" s="15">
         <f>T22 * (X22/100)</f>
         <v/>
       </c>
-      <c r="AA22" s="5">
+      <c r="AA22" s="16">
         <f>W22</f>
         <v/>
       </c>
-      <c r="AJ22" s="4" t="n"/>
-      <c r="AK22" s="5">
+      <c r="AB22" s="12" t="n"/>
+      <c r="AC22" s="12" t="n"/>
+      <c r="AD22" s="12" t="n"/>
+      <c r="AE22" s="12" t="n"/>
+      <c r="AF22" s="12" t="n"/>
+      <c r="AG22" s="12" t="n"/>
+      <c r="AH22" s="12" t="n"/>
+      <c r="AI22" s="12" t="n"/>
+      <c r="AJ22" s="14" t="n"/>
+      <c r="AK22" s="15">
         <f>IF(TODAY()&lt;AD22, 0, IF(TODAY()&gt;AE22, AF22, AF22 * (TODAY()-AD22)/(AE22-AD22+1)))</f>
         <v/>
       </c>
-      <c r="AL22" s="5">
+      <c r="AL22" s="15">
         <f>AF22 * (AJ22/100)</f>
         <v/>
       </c>
-      <c r="AM22" s="5">
+      <c r="AM22" s="16">
         <f>AI22</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="5">
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="14" t="n"/>
+      <c r="M23" s="15">
         <f>IF(TODAY()&lt;F23, 0, IF(TODAY()&gt;G23, H23, H23 * (TODAY()-F23)/(G23-F23+1)))</f>
         <v/>
       </c>
-      <c r="N23" s="5">
+      <c r="N23" s="15">
         <f>H23 * (L23/100)</f>
         <v/>
       </c>
-      <c r="O23" s="5">
+      <c r="O23" s="16">
         <f>K23</f>
         <v/>
       </c>
-      <c r="X23" s="4" t="n"/>
-      <c r="Y23" s="5">
+      <c r="P23" s="12" t="n"/>
+      <c r="Q23" s="12" t="n"/>
+      <c r="R23" s="12" t="n"/>
+      <c r="S23" s="12" t="n"/>
+      <c r="T23" s="12" t="n"/>
+      <c r="U23" s="12" t="n"/>
+      <c r="V23" s="12" t="n"/>
+      <c r="W23" s="12" t="n"/>
+      <c r="X23" s="14" t="n"/>
+      <c r="Y23" s="15">
         <f>IF(TODAY()&lt;R23, 0, IF(TODAY()&gt;S23, T23, T23 * (TODAY()-R23)/(S23-R23+1)))</f>
         <v/>
       </c>
-      <c r="Z23" s="5">
+      <c r="Z23" s="15">
         <f>T23 * (X23/100)</f>
         <v/>
       </c>
-      <c r="AA23" s="5">
+      <c r="AA23" s="16">
         <f>W23</f>
         <v/>
       </c>
-      <c r="AJ23" s="4" t="n"/>
-      <c r="AK23" s="5">
+      <c r="AB23" s="12" t="n"/>
+      <c r="AC23" s="12" t="n"/>
+      <c r="AD23" s="12" t="n"/>
+      <c r="AE23" s="12" t="n"/>
+      <c r="AF23" s="12" t="n"/>
+      <c r="AG23" s="12" t="n"/>
+      <c r="AH23" s="12" t="n"/>
+      <c r="AI23" s="12" t="n"/>
+      <c r="AJ23" s="14" t="n"/>
+      <c r="AK23" s="15">
         <f>IF(TODAY()&lt;AD23, 0, IF(TODAY()&gt;AE23, AF23, AF23 * (TODAY()-AD23)/(AE23-AD23+1)))</f>
         <v/>
       </c>
-      <c r="AL23" s="5">
+      <c r="AL23" s="15">
         <f>AF23 * (AJ23/100)</f>
         <v/>
       </c>
-      <c r="AM23" s="5">
+      <c r="AM23" s="16">
         <f>AI23</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="L24" s="4" t="n"/>
-      <c r="M24" s="5">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="14" t="n"/>
+      <c r="M24" s="15">
         <f>IF(TODAY()&lt;F24, 0, IF(TODAY()&gt;G24, H24, H24 * (TODAY()-F24)/(G24-F24+1)))</f>
         <v/>
       </c>
-      <c r="N24" s="5">
+      <c r="N24" s="15">
         <f>H24 * (L24/100)</f>
         <v/>
       </c>
-      <c r="O24" s="5">
+      <c r="O24" s="16">
         <f>K24</f>
         <v/>
       </c>
-      <c r="X24" s="4" t="n"/>
-      <c r="Y24" s="5">
+      <c r="P24" s="12" t="n"/>
+      <c r="Q24" s="12" t="n"/>
+      <c r="R24" s="12" t="n"/>
+      <c r="S24" s="12" t="n"/>
+      <c r="T24" s="12" t="n"/>
+      <c r="U24" s="12" t="n"/>
+      <c r="V24" s="12" t="n"/>
+      <c r="W24" s="12" t="n"/>
+      <c r="X24" s="14" t="n"/>
+      <c r="Y24" s="15">
         <f>IF(TODAY()&lt;R24, 0, IF(TODAY()&gt;S24, T24, T24 * (TODAY()-R24)/(S24-R24+1)))</f>
         <v/>
       </c>
-      <c r="Z24" s="5">
+      <c r="Z24" s="15">
         <f>T24 * (X24/100)</f>
         <v/>
       </c>
-      <c r="AA24" s="5">
+      <c r="AA24" s="16">
         <f>W24</f>
         <v/>
       </c>
-      <c r="AJ24" s="4" t="n"/>
-      <c r="AK24" s="5">
+      <c r="AB24" s="12" t="n"/>
+      <c r="AC24" s="12" t="n"/>
+      <c r="AD24" s="12" t="n"/>
+      <c r="AE24" s="12" t="n"/>
+      <c r="AF24" s="12" t="n"/>
+      <c r="AG24" s="12" t="n"/>
+      <c r="AH24" s="12" t="n"/>
+      <c r="AI24" s="12" t="n"/>
+      <c r="AJ24" s="14" t="n"/>
+      <c r="AK24" s="15">
         <f>IF(TODAY()&lt;AD24, 0, IF(TODAY()&gt;AE24, AF24, AF24 * (TODAY()-AD24)/(AE24-AD24+1)))</f>
         <v/>
       </c>
-      <c r="AL24" s="5">
+      <c r="AL24" s="15">
         <f>AF24 * (AJ24/100)</f>
         <v/>
       </c>
-      <c r="AM24" s="5">
+      <c r="AM24" s="16">
         <f>AI24</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="5">
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="14" t="n"/>
+      <c r="M25" s="15">
         <f>IF(TODAY()&lt;F25, 0, IF(TODAY()&gt;G25, H25, H25 * (TODAY()-F25)/(G25-F25+1)))</f>
         <v/>
       </c>
-      <c r="N25" s="5">
+      <c r="N25" s="15">
         <f>H25 * (L25/100)</f>
         <v/>
       </c>
-      <c r="O25" s="5">
+      <c r="O25" s="16">
         <f>K25</f>
         <v/>
       </c>
-      <c r="X25" s="4" t="n"/>
-      <c r="Y25" s="5">
+      <c r="P25" s="12" t="n"/>
+      <c r="Q25" s="12" t="n"/>
+      <c r="R25" s="12" t="n"/>
+      <c r="S25" s="12" t="n"/>
+      <c r="T25" s="12" t="n"/>
+      <c r="U25" s="12" t="n"/>
+      <c r="V25" s="12" t="n"/>
+      <c r="W25" s="12" t="n"/>
+      <c r="X25" s="14" t="n"/>
+      <c r="Y25" s="15">
         <f>IF(TODAY()&lt;R25, 0, IF(TODAY()&gt;S25, T25, T25 * (TODAY()-R25)/(S25-R25+1)))</f>
         <v/>
       </c>
-      <c r="Z25" s="5">
+      <c r="Z25" s="15">
         <f>T25 * (X25/100)</f>
         <v/>
       </c>
-      <c r="AA25" s="5">
+      <c r="AA25" s="16">
         <f>W25</f>
         <v/>
       </c>
-      <c r="AJ25" s="4" t="n"/>
-      <c r="AK25" s="5">
+      <c r="AB25" s="12" t="n"/>
+      <c r="AC25" s="12" t="n"/>
+      <c r="AD25" s="12" t="n"/>
+      <c r="AE25" s="12" t="n"/>
+      <c r="AF25" s="12" t="n"/>
+      <c r="AG25" s="12" t="n"/>
+      <c r="AH25" s="12" t="n"/>
+      <c r="AI25" s="12" t="n"/>
+      <c r="AJ25" s="14" t="n"/>
+      <c r="AK25" s="15">
         <f>IF(TODAY()&lt;AD25, 0, IF(TODAY()&gt;AE25, AF25, AF25 * (TODAY()-AD25)/(AE25-AD25+1)))</f>
         <v/>
       </c>
-      <c r="AL25" s="5">
+      <c r="AL25" s="15">
         <f>AF25 * (AJ25/100)</f>
         <v/>
       </c>
-      <c r="AM25" s="5">
+      <c r="AM25" s="16">
         <f>AI25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="L26" s="4" t="n"/>
-      <c r="M26" s="5">
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="14" t="n"/>
+      <c r="M26" s="15">
         <f>IF(TODAY()&lt;F26, 0, IF(TODAY()&gt;G26, H26, H26 * (TODAY()-F26)/(G26-F26+1)))</f>
         <v/>
       </c>
-      <c r="N26" s="5">
+      <c r="N26" s="15">
         <f>H26 * (L26/100)</f>
         <v/>
       </c>
-      <c r="O26" s="5">
+      <c r="O26" s="16">
         <f>K26</f>
         <v/>
       </c>
-      <c r="X26" s="4" t="n"/>
-      <c r="Y26" s="5">
+      <c r="P26" s="12" t="n"/>
+      <c r="Q26" s="12" t="n"/>
+      <c r="R26" s="12" t="n"/>
+      <c r="S26" s="12" t="n"/>
+      <c r="T26" s="12" t="n"/>
+      <c r="U26" s="12" t="n"/>
+      <c r="V26" s="12" t="n"/>
+      <c r="W26" s="12" t="n"/>
+      <c r="X26" s="14" t="n"/>
+      <c r="Y26" s="15">
         <f>IF(TODAY()&lt;R26, 0, IF(TODAY()&gt;S26, T26, T26 * (TODAY()-R26)/(S26-R26+1)))</f>
         <v/>
       </c>
-      <c r="Z26" s="5">
+      <c r="Z26" s="15">
         <f>T26 * (X26/100)</f>
         <v/>
       </c>
-      <c r="AA26" s="5">
+      <c r="AA26" s="16">
         <f>W26</f>
         <v/>
       </c>
-      <c r="AJ26" s="4" t="n"/>
-      <c r="AK26" s="5">
+      <c r="AB26" s="12" t="n"/>
+      <c r="AC26" s="12" t="n"/>
+      <c r="AD26" s="12" t="n"/>
+      <c r="AE26" s="12" t="n"/>
+      <c r="AF26" s="12" t="n"/>
+      <c r="AG26" s="12" t="n"/>
+      <c r="AH26" s="12" t="n"/>
+      <c r="AI26" s="12" t="n"/>
+      <c r="AJ26" s="14" t="n"/>
+      <c r="AK26" s="15">
         <f>IF(TODAY()&lt;AD26, 0, IF(TODAY()&gt;AE26, AF26, AF26 * (TODAY()-AD26)/(AE26-AD26+1)))</f>
         <v/>
       </c>
-      <c r="AL26" s="5">
+      <c r="AL26" s="15">
         <f>AF26 * (AJ26/100)</f>
         <v/>
       </c>
-      <c r="AM26" s="5">
+      <c r="AM26" s="16">
         <f>AI26</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="L27" s="4" t="n"/>
-      <c r="M27" s="5">
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="14" t="n"/>
+      <c r="M27" s="15">
         <f>IF(TODAY()&lt;F27, 0, IF(TODAY()&gt;G27, H27, H27 * (TODAY()-F27)/(G27-F27+1)))</f>
         <v/>
       </c>
-      <c r="N27" s="5">
+      <c r="N27" s="15">
         <f>H27 * (L27/100)</f>
         <v/>
       </c>
-      <c r="O27" s="5">
+      <c r="O27" s="16">
         <f>K27</f>
         <v/>
       </c>
-      <c r="X27" s="4" t="n"/>
-      <c r="Y27" s="5">
+      <c r="P27" s="12" t="n"/>
+      <c r="Q27" s="12" t="n"/>
+      <c r="R27" s="12" t="n"/>
+      <c r="S27" s="12" t="n"/>
+      <c r="T27" s="12" t="n"/>
+      <c r="U27" s="12" t="n"/>
+      <c r="V27" s="12" t="n"/>
+      <c r="W27" s="12" t="n"/>
+      <c r="X27" s="14" t="n"/>
+      <c r="Y27" s="15">
         <f>IF(TODAY()&lt;R27, 0, IF(TODAY()&gt;S27, T27, T27 * (TODAY()-R27)/(S27-R27+1)))</f>
         <v/>
       </c>
-      <c r="Z27" s="5">
+      <c r="Z27" s="15">
         <f>T27 * (X27/100)</f>
         <v/>
       </c>
-      <c r="AA27" s="5">
+      <c r="AA27" s="16">
         <f>W27</f>
         <v/>
       </c>
-      <c r="AJ27" s="4" t="n"/>
-      <c r="AK27" s="5">
+      <c r="AB27" s="12" t="n"/>
+      <c r="AC27" s="12" t="n"/>
+      <c r="AD27" s="12" t="n"/>
+      <c r="AE27" s="12" t="n"/>
+      <c r="AF27" s="12" t="n"/>
+      <c r="AG27" s="12" t="n"/>
+      <c r="AH27" s="12" t="n"/>
+      <c r="AI27" s="12" t="n"/>
+      <c r="AJ27" s="14" t="n"/>
+      <c r="AK27" s="15">
         <f>IF(TODAY()&lt;AD27, 0, IF(TODAY()&gt;AE27, AF27, AF27 * (TODAY()-AD27)/(AE27-AD27+1)))</f>
         <v/>
       </c>
-      <c r="AL27" s="5">
+      <c r="AL27" s="15">
         <f>AF27 * (AJ27/100)</f>
         <v/>
       </c>
-      <c r="AM27" s="5">
+      <c r="AM27" s="16">
         <f>AI27</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="L28" s="4" t="n"/>
-      <c r="M28" s="5">
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="12" t="n"/>
+      <c r="G28" s="12" t="n"/>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="14" t="n"/>
+      <c r="M28" s="15">
         <f>IF(TODAY()&lt;F28, 0, IF(TODAY()&gt;G28, H28, H28 * (TODAY()-F28)/(G28-F28+1)))</f>
         <v/>
       </c>
-      <c r="N28" s="5">
+      <c r="N28" s="15">
         <f>H28 * (L28/100)</f>
         <v/>
       </c>
-      <c r="O28" s="5">
+      <c r="O28" s="16">
         <f>K28</f>
         <v/>
       </c>
-      <c r="X28" s="4" t="n"/>
-      <c r="Y28" s="5">
+      <c r="P28" s="12" t="n"/>
+      <c r="Q28" s="12" t="n"/>
+      <c r="R28" s="12" t="n"/>
+      <c r="S28" s="12" t="n"/>
+      <c r="T28" s="12" t="n"/>
+      <c r="U28" s="12" t="n"/>
+      <c r="V28" s="12" t="n"/>
+      <c r="W28" s="12" t="n"/>
+      <c r="X28" s="14" t="n"/>
+      <c r="Y28" s="15">
         <f>IF(TODAY()&lt;R28, 0, IF(TODAY()&gt;S28, T28, T28 * (TODAY()-R28)/(S28-R28+1)))</f>
         <v/>
       </c>
-      <c r="Z28" s="5">
+      <c r="Z28" s="15">
         <f>T28 * (X28/100)</f>
         <v/>
       </c>
-      <c r="AA28" s="5">
+      <c r="AA28" s="16">
         <f>W28</f>
         <v/>
       </c>
-      <c r="AJ28" s="4" t="n"/>
-      <c r="AK28" s="5">
+      <c r="AB28" s="12" t="n"/>
+      <c r="AC28" s="12" t="n"/>
+      <c r="AD28" s="12" t="n"/>
+      <c r="AE28" s="12" t="n"/>
+      <c r="AF28" s="12" t="n"/>
+      <c r="AG28" s="12" t="n"/>
+      <c r="AH28" s="12" t="n"/>
+      <c r="AI28" s="12" t="n"/>
+      <c r="AJ28" s="14" t="n"/>
+      <c r="AK28" s="15">
         <f>IF(TODAY()&lt;AD28, 0, IF(TODAY()&gt;AE28, AF28, AF28 * (TODAY()-AD28)/(AE28-AD28+1)))</f>
         <v/>
       </c>
-      <c r="AL28" s="5">
+      <c r="AL28" s="15">
         <f>AF28 * (AJ28/100)</f>
         <v/>
       </c>
-      <c r="AM28" s="5">
+      <c r="AM28" s="16">
         <f>AI28</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="L29" s="4" t="n"/>
-      <c r="M29" s="5">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="14" t="n"/>
+      <c r="M29" s="15">
         <f>IF(TODAY()&lt;F29, 0, IF(TODAY()&gt;G29, H29, H29 * (TODAY()-F29)/(G29-F29+1)))</f>
         <v/>
       </c>
-      <c r="N29" s="5">
+      <c r="N29" s="15">
         <f>H29 * (L29/100)</f>
         <v/>
       </c>
-      <c r="O29" s="5">
+      <c r="O29" s="16">
         <f>K29</f>
         <v/>
       </c>
-      <c r="X29" s="4" t="n"/>
-      <c r="Y29" s="5">
+      <c r="P29" s="12" t="n"/>
+      <c r="Q29" s="12" t="n"/>
+      <c r="R29" s="12" t="n"/>
+      <c r="S29" s="12" t="n"/>
+      <c r="T29" s="12" t="n"/>
+      <c r="U29" s="12" t="n"/>
+      <c r="V29" s="12" t="n"/>
+      <c r="W29" s="12" t="n"/>
+      <c r="X29" s="14" t="n"/>
+      <c r="Y29" s="15">
         <f>IF(TODAY()&lt;R29, 0, IF(TODAY()&gt;S29, T29, T29 * (TODAY()-R29)/(S29-R29+1)))</f>
         <v/>
       </c>
-      <c r="Z29" s="5">
+      <c r="Z29" s="15">
         <f>T29 * (X29/100)</f>
         <v/>
       </c>
-      <c r="AA29" s="5">
+      <c r="AA29" s="16">
         <f>W29</f>
         <v/>
       </c>
-      <c r="AJ29" s="4" t="n"/>
-      <c r="AK29" s="5">
+      <c r="AB29" s="12" t="n"/>
+      <c r="AC29" s="12" t="n"/>
+      <c r="AD29" s="12" t="n"/>
+      <c r="AE29" s="12" t="n"/>
+      <c r="AF29" s="12" t="n"/>
+      <c r="AG29" s="12" t="n"/>
+      <c r="AH29" s="12" t="n"/>
+      <c r="AI29" s="12" t="n"/>
+      <c r="AJ29" s="14" t="n"/>
+      <c r="AK29" s="15">
         <f>IF(TODAY()&lt;AD29, 0, IF(TODAY()&gt;AE29, AF29, AF29 * (TODAY()-AD29)/(AE29-AD29+1)))</f>
         <v/>
       </c>
-      <c r="AL29" s="5">
+      <c r="AL29" s="15">
         <f>AF29 * (AJ29/100)</f>
         <v/>
       </c>
-      <c r="AM29" s="5">
+      <c r="AM29" s="16">
         <f>AI29</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="L30" s="4" t="n"/>
-      <c r="M30" s="5">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="14" t="n"/>
+      <c r="M30" s="15">
         <f>IF(TODAY()&lt;F30, 0, IF(TODAY()&gt;G30, H30, H30 * (TODAY()-F30)/(G30-F30+1)))</f>
         <v/>
       </c>
-      <c r="N30" s="5">
+      <c r="N30" s="15">
         <f>H30 * (L30/100)</f>
         <v/>
       </c>
-      <c r="O30" s="5">
+      <c r="O30" s="16">
         <f>K30</f>
         <v/>
       </c>
-      <c r="X30" s="4" t="n"/>
-      <c r="Y30" s="5">
+      <c r="P30" s="12" t="n"/>
+      <c r="Q30" s="12" t="n"/>
+      <c r="R30" s="12" t="n"/>
+      <c r="S30" s="12" t="n"/>
+      <c r="T30" s="12" t="n"/>
+      <c r="U30" s="12" t="n"/>
+      <c r="V30" s="12" t="n"/>
+      <c r="W30" s="12" t="n"/>
+      <c r="X30" s="14" t="n"/>
+      <c r="Y30" s="15">
         <f>IF(TODAY()&lt;R30, 0, IF(TODAY()&gt;S30, T30, T30 * (TODAY()-R30)/(S30-R30+1)))</f>
         <v/>
       </c>
-      <c r="Z30" s="5">
+      <c r="Z30" s="15">
         <f>T30 * (X30/100)</f>
         <v/>
       </c>
-      <c r="AA30" s="5">
+      <c r="AA30" s="16">
         <f>W30</f>
         <v/>
       </c>
-      <c r="AJ30" s="4" t="n"/>
-      <c r="AK30" s="5">
+      <c r="AB30" s="12" t="n"/>
+      <c r="AC30" s="12" t="n"/>
+      <c r="AD30" s="12" t="n"/>
+      <c r="AE30" s="12" t="n"/>
+      <c r="AF30" s="12" t="n"/>
+      <c r="AG30" s="12" t="n"/>
+      <c r="AH30" s="12" t="n"/>
+      <c r="AI30" s="12" t="n"/>
+      <c r="AJ30" s="14" t="n"/>
+      <c r="AK30" s="15">
         <f>IF(TODAY()&lt;AD30, 0, IF(TODAY()&gt;AE30, AF30, AF30 * (TODAY()-AD30)/(AE30-AD30+1)))</f>
         <v/>
       </c>
-      <c r="AL30" s="5">
+      <c r="AL30" s="15">
         <f>AF30 * (AJ30/100)</f>
         <v/>
       </c>
-      <c r="AM30" s="5">
+      <c r="AM30" s="16">
         <f>AI30</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="L31" s="4" t="n"/>
-      <c r="M31" s="5">
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="14" t="n"/>
+      <c r="M31" s="15">
         <f>IF(TODAY()&lt;F31, 0, IF(TODAY()&gt;G31, H31, H31 * (TODAY()-F31)/(G31-F31+1)))</f>
         <v/>
       </c>
-      <c r="N31" s="5">
+      <c r="N31" s="15">
         <f>H31 * (L31/100)</f>
         <v/>
       </c>
-      <c r="O31" s="5">
+      <c r="O31" s="16">
         <f>K31</f>
         <v/>
       </c>
-      <c r="X31" s="4" t="n"/>
-      <c r="Y31" s="5">
+      <c r="P31" s="12" t="n"/>
+      <c r="Q31" s="12" t="n"/>
+      <c r="R31" s="12" t="n"/>
+      <c r="S31" s="12" t="n"/>
+      <c r="T31" s="12" t="n"/>
+      <c r="U31" s="12" t="n"/>
+      <c r="V31" s="12" t="n"/>
+      <c r="W31" s="12" t="n"/>
+      <c r="X31" s="14" t="n"/>
+      <c r="Y31" s="15">
         <f>IF(TODAY()&lt;R31, 0, IF(TODAY()&gt;S31, T31, T31 * (TODAY()-R31)/(S31-R31+1)))</f>
         <v/>
       </c>
-      <c r="Z31" s="5">
+      <c r="Z31" s="15">
         <f>T31 * (X31/100)</f>
         <v/>
       </c>
-      <c r="AA31" s="5">
+      <c r="AA31" s="16">
         <f>W31</f>
         <v/>
       </c>
-      <c r="AJ31" s="4" t="n"/>
-      <c r="AK31" s="5">
+      <c r="AB31" s="12" t="n"/>
+      <c r="AC31" s="12" t="n"/>
+      <c r="AD31" s="12" t="n"/>
+      <c r="AE31" s="12" t="n"/>
+      <c r="AF31" s="12" t="n"/>
+      <c r="AG31" s="12" t="n"/>
+      <c r="AH31" s="12" t="n"/>
+      <c r="AI31" s="12" t="n"/>
+      <c r="AJ31" s="14" t="n"/>
+      <c r="AK31" s="15">
         <f>IF(TODAY()&lt;AD31, 0, IF(TODAY()&gt;AE31, AF31, AF31 * (TODAY()-AD31)/(AE31-AD31+1)))</f>
         <v/>
       </c>
-      <c r="AL31" s="5">
+      <c r="AL31" s="15">
         <f>AF31 * (AJ31/100)</f>
         <v/>
       </c>
-      <c r="AM31" s="5">
+      <c r="AM31" s="16">
         <f>AI31</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="L32" s="4" t="n"/>
-      <c r="M32" s="5">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="14" t="n"/>
+      <c r="M32" s="15">
         <f>IF(TODAY()&lt;F32, 0, IF(TODAY()&gt;G32, H32, H32 * (TODAY()-F32)/(G32-F32+1)))</f>
         <v/>
       </c>
-      <c r="N32" s="5">
+      <c r="N32" s="15">
         <f>H32 * (L32/100)</f>
         <v/>
       </c>
-      <c r="O32" s="5">
+      <c r="O32" s="16">
         <f>K32</f>
         <v/>
       </c>
-      <c r="X32" s="4" t="n"/>
-      <c r="Y32" s="5">
+      <c r="P32" s="12" t="n"/>
+      <c r="Q32" s="12" t="n"/>
+      <c r="R32" s="12" t="n"/>
+      <c r="S32" s="12" t="n"/>
+      <c r="T32" s="12" t="n"/>
+      <c r="U32" s="12" t="n"/>
+      <c r="V32" s="12" t="n"/>
+      <c r="W32" s="12" t="n"/>
+      <c r="X32" s="14" t="n"/>
+      <c r="Y32" s="15">
         <f>IF(TODAY()&lt;R32, 0, IF(TODAY()&gt;S32, T32, T32 * (TODAY()-R32)/(S32-R32+1)))</f>
         <v/>
       </c>
-      <c r="Z32" s="5">
+      <c r="Z32" s="15">
         <f>T32 * (X32/100)</f>
         <v/>
       </c>
-      <c r="AA32" s="5">
+      <c r="AA32" s="16">
         <f>W32</f>
         <v/>
       </c>
-      <c r="AJ32" s="4" t="n"/>
-      <c r="AK32" s="5">
+      <c r="AB32" s="12" t="n"/>
+      <c r="AC32" s="12" t="n"/>
+      <c r="AD32" s="12" t="n"/>
+      <c r="AE32" s="12" t="n"/>
+      <c r="AF32" s="12" t="n"/>
+      <c r="AG32" s="12" t="n"/>
+      <c r="AH32" s="12" t="n"/>
+      <c r="AI32" s="12" t="n"/>
+      <c r="AJ32" s="14" t="n"/>
+      <c r="AK32" s="15">
         <f>IF(TODAY()&lt;AD32, 0, IF(TODAY()&gt;AE32, AF32, AF32 * (TODAY()-AD32)/(AE32-AD32+1)))</f>
         <v/>
       </c>
-      <c r="AL32" s="5">
+      <c r="AL32" s="15">
         <f>AF32 * (AJ32/100)</f>
         <v/>
       </c>
-      <c r="AM32" s="5">
+      <c r="AM32" s="16">
         <f>AI32</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="L33" s="4" t="n"/>
-      <c r="M33" s="5">
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="13" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="14" t="n"/>
+      <c r="M33" s="15">
         <f>IF(TODAY()&lt;F33, 0, IF(TODAY()&gt;G33, H33, H33 * (TODAY()-F33)/(G33-F33+1)))</f>
         <v/>
       </c>
-      <c r="N33" s="5">
+      <c r="N33" s="15">
         <f>H33 * (L33/100)</f>
         <v/>
       </c>
-      <c r="O33" s="5">
+      <c r="O33" s="16">
         <f>K33</f>
         <v/>
       </c>
-      <c r="X33" s="4" t="n"/>
-      <c r="Y33" s="5">
+      <c r="P33" s="12" t="n"/>
+      <c r="Q33" s="12" t="n"/>
+      <c r="R33" s="12" t="n"/>
+      <c r="S33" s="12" t="n"/>
+      <c r="T33" s="12" t="n"/>
+      <c r="U33" s="12" t="n"/>
+      <c r="V33" s="12" t="n"/>
+      <c r="W33" s="12" t="n"/>
+      <c r="X33" s="14" t="n"/>
+      <c r="Y33" s="15">
         <f>IF(TODAY()&lt;R33, 0, IF(TODAY()&gt;S33, T33, T33 * (TODAY()-R33)/(S33-R33+1)))</f>
         <v/>
       </c>
-      <c r="Z33" s="5">
+      <c r="Z33" s="15">
         <f>T33 * (X33/100)</f>
         <v/>
       </c>
-      <c r="AA33" s="5">
+      <c r="AA33" s="16">
         <f>W33</f>
         <v/>
       </c>
-      <c r="AJ33" s="4" t="n"/>
-      <c r="AK33" s="5">
+      <c r="AB33" s="12" t="n"/>
+      <c r="AC33" s="12" t="n"/>
+      <c r="AD33" s="12" t="n"/>
+      <c r="AE33" s="12" t="n"/>
+      <c r="AF33" s="12" t="n"/>
+      <c r="AG33" s="12" t="n"/>
+      <c r="AH33" s="12" t="n"/>
+      <c r="AI33" s="12" t="n"/>
+      <c r="AJ33" s="14" t="n"/>
+      <c r="AK33" s="15">
         <f>IF(TODAY()&lt;AD33, 0, IF(TODAY()&gt;AE33, AF33, AF33 * (TODAY()-AD33)/(AE33-AD33+1)))</f>
         <v/>
       </c>
-      <c r="AL33" s="5">
+      <c r="AL33" s="15">
         <f>AF33 * (AJ33/100)</f>
         <v/>
       </c>
-      <c r="AM33" s="5">
+      <c r="AM33" s="16">
         <f>AI33</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="L34" s="4" t="n"/>
-      <c r="M34" s="5">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="13" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="12" t="n"/>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="12" t="n"/>
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="14" t="n"/>
+      <c r="M34" s="15">
         <f>IF(TODAY()&lt;F34, 0, IF(TODAY()&gt;G34, H34, H34 * (TODAY()-F34)/(G34-F34+1)))</f>
         <v/>
       </c>
-      <c r="N34" s="5">
+      <c r="N34" s="15">
         <f>H34 * (L34/100)</f>
         <v/>
       </c>
-      <c r="O34" s="5">
+      <c r="O34" s="16">
         <f>K34</f>
         <v/>
       </c>
-      <c r="X34" s="4" t="n"/>
-      <c r="Y34" s="5">
+      <c r="P34" s="12" t="n"/>
+      <c r="Q34" s="12" t="n"/>
+      <c r="R34" s="12" t="n"/>
+      <c r="S34" s="12" t="n"/>
+      <c r="T34" s="12" t="n"/>
+      <c r="U34" s="12" t="n"/>
+      <c r="V34" s="12" t="n"/>
+      <c r="W34" s="12" t="n"/>
+      <c r="X34" s="14" t="n"/>
+      <c r="Y34" s="15">
         <f>IF(TODAY()&lt;R34, 0, IF(TODAY()&gt;S34, T34, T34 * (TODAY()-R34)/(S34-R34+1)))</f>
         <v/>
       </c>
-      <c r="Z34" s="5">
+      <c r="Z34" s="15">
         <f>T34 * (X34/100)</f>
         <v/>
       </c>
-      <c r="AA34" s="5">
+      <c r="AA34" s="16">
         <f>W34</f>
         <v/>
       </c>
-      <c r="AJ34" s="4" t="n"/>
-      <c r="AK34" s="5">
+      <c r="AB34" s="12" t="n"/>
+      <c r="AC34" s="12" t="n"/>
+      <c r="AD34" s="12" t="n"/>
+      <c r="AE34" s="12" t="n"/>
+      <c r="AF34" s="12" t="n"/>
+      <c r="AG34" s="12" t="n"/>
+      <c r="AH34" s="12" t="n"/>
+      <c r="AI34" s="12" t="n"/>
+      <c r="AJ34" s="14" t="n"/>
+      <c r="AK34" s="15">
         <f>IF(TODAY()&lt;AD34, 0, IF(TODAY()&gt;AE34, AF34, AF34 * (TODAY()-AD34)/(AE34-AD34+1)))</f>
         <v/>
       </c>
-      <c r="AL34" s="5">
+      <c r="AL34" s="15">
         <f>AF34 * (AJ34/100)</f>
         <v/>
       </c>
-      <c r="AM34" s="5">
+      <c r="AM34" s="16">
         <f>AI34</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="L35" s="4" t="n"/>
-      <c r="M35" s="5">
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="13" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="12" t="n"/>
+      <c r="K35" s="12" t="n"/>
+      <c r="L35" s="14" t="n"/>
+      <c r="M35" s="15">
         <f>IF(TODAY()&lt;F35, 0, IF(TODAY()&gt;G35, H35, H35 * (TODAY()-F35)/(G35-F35+1)))</f>
         <v/>
       </c>
-      <c r="N35" s="5">
+      <c r="N35" s="15">
         <f>H35 * (L35/100)</f>
         <v/>
       </c>
-      <c r="O35" s="5">
+      <c r="O35" s="16">
         <f>K35</f>
         <v/>
       </c>
-      <c r="X35" s="4" t="n"/>
-      <c r="Y35" s="5">
+      <c r="P35" s="12" t="n"/>
+      <c r="Q35" s="12" t="n"/>
+      <c r="R35" s="12" t="n"/>
+      <c r="S35" s="12" t="n"/>
+      <c r="T35" s="12" t="n"/>
+      <c r="U35" s="12" t="n"/>
+      <c r="V35" s="12" t="n"/>
+      <c r="W35" s="12" t="n"/>
+      <c r="X35" s="14" t="n"/>
+      <c r="Y35" s="15">
         <f>IF(TODAY()&lt;R35, 0, IF(TODAY()&gt;S35, T35, T35 * (TODAY()-R35)/(S35-R35+1)))</f>
         <v/>
       </c>
-      <c r="Z35" s="5">
+      <c r="Z35" s="15">
         <f>T35 * (X35/100)</f>
         <v/>
       </c>
-      <c r="AA35" s="5">
+      <c r="AA35" s="16">
         <f>W35</f>
         <v/>
       </c>
-      <c r="AJ35" s="4" t="n"/>
-      <c r="AK35" s="5">
+      <c r="AB35" s="12" t="n"/>
+      <c r="AC35" s="12" t="n"/>
+      <c r="AD35" s="12" t="n"/>
+      <c r="AE35" s="12" t="n"/>
+      <c r="AF35" s="12" t="n"/>
+      <c r="AG35" s="12" t="n"/>
+      <c r="AH35" s="12" t="n"/>
+      <c r="AI35" s="12" t="n"/>
+      <c r="AJ35" s="14" t="n"/>
+      <c r="AK35" s="15">
         <f>IF(TODAY()&lt;AD35, 0, IF(TODAY()&gt;AE35, AF35, AF35 * (TODAY()-AD35)/(AE35-AD35+1)))</f>
         <v/>
       </c>
-      <c r="AL35" s="5">
+      <c r="AL35" s="15">
         <f>AF35 * (AJ35/100)</f>
         <v/>
       </c>
-      <c r="AM35" s="5">
+      <c r="AM35" s="16">
         <f>AI35</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="L36" s="4" t="n"/>
-      <c r="M36" s="5">
+      <c r="A36" s="11" t="n"/>
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="13" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="12" t="n"/>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="14" t="n"/>
+      <c r="M36" s="15">
         <f>IF(TODAY()&lt;F36, 0, IF(TODAY()&gt;G36, H36, H36 * (TODAY()-F36)/(G36-F36+1)))</f>
         <v/>
       </c>
-      <c r="N36" s="5">
+      <c r="N36" s="15">
         <f>H36 * (L36/100)</f>
         <v/>
       </c>
-      <c r="O36" s="5">
+      <c r="O36" s="16">
         <f>K36</f>
         <v/>
       </c>
-      <c r="X36" s="4" t="n"/>
-      <c r="Y36" s="5">
+      <c r="P36" s="12" t="n"/>
+      <c r="Q36" s="12" t="n"/>
+      <c r="R36" s="12" t="n"/>
+      <c r="S36" s="12" t="n"/>
+      <c r="T36" s="12" t="n"/>
+      <c r="U36" s="12" t="n"/>
+      <c r="V36" s="12" t="n"/>
+      <c r="W36" s="12" t="n"/>
+      <c r="X36" s="14" t="n"/>
+      <c r="Y36" s="15">
         <f>IF(TODAY()&lt;R36, 0, IF(TODAY()&gt;S36, T36, T36 * (TODAY()-R36)/(S36-R36+1)))</f>
         <v/>
       </c>
-      <c r="Z36" s="5">
+      <c r="Z36" s="15">
         <f>T36 * (X36/100)</f>
         <v/>
       </c>
-      <c r="AA36" s="5">
+      <c r="AA36" s="16">
         <f>W36</f>
         <v/>
       </c>
-      <c r="AJ36" s="4" t="n"/>
-      <c r="AK36" s="5">
+      <c r="AB36" s="12" t="n"/>
+      <c r="AC36" s="12" t="n"/>
+      <c r="AD36" s="12" t="n"/>
+      <c r="AE36" s="12" t="n"/>
+      <c r="AF36" s="12" t="n"/>
+      <c r="AG36" s="12" t="n"/>
+      <c r="AH36" s="12" t="n"/>
+      <c r="AI36" s="12" t="n"/>
+      <c r="AJ36" s="14" t="n"/>
+      <c r="AK36" s="15">
         <f>IF(TODAY()&lt;AD36, 0, IF(TODAY()&gt;AE36, AF36, AF36 * (TODAY()-AD36)/(AE36-AD36+1)))</f>
         <v/>
       </c>
-      <c r="AL36" s="5">
+      <c r="AL36" s="15">
         <f>AF36 * (AJ36/100)</f>
         <v/>
       </c>
-      <c r="AM36" s="5">
+      <c r="AM36" s="16">
         <f>AI36</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="L37" s="4" t="n"/>
-      <c r="M37" s="5">
+      <c r="A37" s="11" t="n"/>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="13" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="12" t="n"/>
+      <c r="K37" s="12" t="n"/>
+      <c r="L37" s="14" t="n"/>
+      <c r="M37" s="15">
         <f>IF(TODAY()&lt;F37, 0, IF(TODAY()&gt;G37, H37, H37 * (TODAY()-F37)/(G37-F37+1)))</f>
         <v/>
       </c>
-      <c r="N37" s="5">
+      <c r="N37" s="15">
         <f>H37 * (L37/100)</f>
         <v/>
       </c>
-      <c r="O37" s="5">
+      <c r="O37" s="16">
         <f>K37</f>
         <v/>
       </c>
-      <c r="X37" s="4" t="n"/>
-      <c r="Y37" s="5">
+      <c r="P37" s="12" t="n"/>
+      <c r="Q37" s="12" t="n"/>
+      <c r="R37" s="12" t="n"/>
+      <c r="S37" s="12" t="n"/>
+      <c r="T37" s="12" t="n"/>
+      <c r="U37" s="12" t="n"/>
+      <c r="V37" s="12" t="n"/>
+      <c r="W37" s="12" t="n"/>
+      <c r="X37" s="14" t="n"/>
+      <c r="Y37" s="15">
         <f>IF(TODAY()&lt;R37, 0, IF(TODAY()&gt;S37, T37, T37 * (TODAY()-R37)/(S37-R37+1)))</f>
         <v/>
       </c>
-      <c r="Z37" s="5">
+      <c r="Z37" s="15">
         <f>T37 * (X37/100)</f>
         <v/>
       </c>
-      <c r="AA37" s="5">
+      <c r="AA37" s="16">
         <f>W37</f>
         <v/>
       </c>
-      <c r="AJ37" s="4" t="n"/>
-      <c r="AK37" s="5">
+      <c r="AB37" s="12" t="n"/>
+      <c r="AC37" s="12" t="n"/>
+      <c r="AD37" s="12" t="n"/>
+      <c r="AE37" s="12" t="n"/>
+      <c r="AF37" s="12" t="n"/>
+      <c r="AG37" s="12" t="n"/>
+      <c r="AH37" s="12" t="n"/>
+      <c r="AI37" s="12" t="n"/>
+      <c r="AJ37" s="14" t="n"/>
+      <c r="AK37" s="15">
         <f>IF(TODAY()&lt;AD37, 0, IF(TODAY()&gt;AE37, AF37, AF37 * (TODAY()-AD37)/(AE37-AD37+1)))</f>
         <v/>
       </c>
-      <c r="AL37" s="5">
+      <c r="AL37" s="15">
         <f>AF37 * (AJ37/100)</f>
         <v/>
       </c>
-      <c r="AM37" s="5">
+      <c r="AM37" s="16">
         <f>AI37</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="L38" s="4" t="n"/>
-      <c r="M38" s="5">
+      <c r="A38" s="11" t="n"/>
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="13" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="12" t="n"/>
+      <c r="G38" s="12" t="n"/>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="12" t="n"/>
+      <c r="J38" s="12" t="n"/>
+      <c r="K38" s="12" t="n"/>
+      <c r="L38" s="14" t="n"/>
+      <c r="M38" s="15">
         <f>IF(TODAY()&lt;F38, 0, IF(TODAY()&gt;G38, H38, H38 * (TODAY()-F38)/(G38-F38+1)))</f>
         <v/>
       </c>
-      <c r="N38" s="5">
+      <c r="N38" s="15">
         <f>H38 * (L38/100)</f>
         <v/>
       </c>
-      <c r="O38" s="5">
+      <c r="O38" s="16">
         <f>K38</f>
         <v/>
       </c>
-      <c r="X38" s="4" t="n"/>
-      <c r="Y38" s="5">
+      <c r="P38" s="12" t="n"/>
+      <c r="Q38" s="12" t="n"/>
+      <c r="R38" s="12" t="n"/>
+      <c r="S38" s="12" t="n"/>
+      <c r="T38" s="12" t="n"/>
+      <c r="U38" s="12" t="n"/>
+      <c r="V38" s="12" t="n"/>
+      <c r="W38" s="12" t="n"/>
+      <c r="X38" s="14" t="n"/>
+      <c r="Y38" s="15">
         <f>IF(TODAY()&lt;R38, 0, IF(TODAY()&gt;S38, T38, T38 * (TODAY()-R38)/(S38-R38+1)))</f>
         <v/>
       </c>
-      <c r="Z38" s="5">
+      <c r="Z38" s="15">
         <f>T38 * (X38/100)</f>
         <v/>
       </c>
-      <c r="AA38" s="5">
+      <c r="AA38" s="16">
         <f>W38</f>
         <v/>
       </c>
-      <c r="AJ38" s="4" t="n"/>
-      <c r="AK38" s="5">
+      <c r="AB38" s="12" t="n"/>
+      <c r="AC38" s="12" t="n"/>
+      <c r="AD38" s="12" t="n"/>
+      <c r="AE38" s="12" t="n"/>
+      <c r="AF38" s="12" t="n"/>
+      <c r="AG38" s="12" t="n"/>
+      <c r="AH38" s="12" t="n"/>
+      <c r="AI38" s="12" t="n"/>
+      <c r="AJ38" s="14" t="n"/>
+      <c r="AK38" s="15">
         <f>IF(TODAY()&lt;AD38, 0, IF(TODAY()&gt;AE38, AF38, AF38 * (TODAY()-AD38)/(AE38-AD38+1)))</f>
         <v/>
       </c>
-      <c r="AL38" s="5">
+      <c r="AL38" s="15">
         <f>AF38 * (AJ38/100)</f>
         <v/>
       </c>
-      <c r="AM38" s="5">
+      <c r="AM38" s="16">
         <f>AI38</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="L39" s="4" t="n"/>
-      <c r="M39" s="5">
+      <c r="A39" s="11" t="n"/>
+      <c r="B39" s="12" t="n"/>
+      <c r="C39" s="13" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="12" t="n"/>
+      <c r="G39" s="12" t="n"/>
+      <c r="H39" s="12" t="n"/>
+      <c r="I39" s="12" t="n"/>
+      <c r="J39" s="12" t="n"/>
+      <c r="K39" s="12" t="n"/>
+      <c r="L39" s="14" t="n"/>
+      <c r="M39" s="15">
         <f>IF(TODAY()&lt;F39, 0, IF(TODAY()&gt;G39, H39, H39 * (TODAY()-F39)/(G39-F39+1)))</f>
         <v/>
       </c>
-      <c r="N39" s="5">
+      <c r="N39" s="15">
         <f>H39 * (L39/100)</f>
         <v/>
       </c>
-      <c r="O39" s="5">
+      <c r="O39" s="16">
         <f>K39</f>
         <v/>
       </c>
-      <c r="X39" s="4" t="n"/>
-      <c r="Y39" s="5">
+      <c r="P39" s="12" t="n"/>
+      <c r="Q39" s="12" t="n"/>
+      <c r="R39" s="12" t="n"/>
+      <c r="S39" s="12" t="n"/>
+      <c r="T39" s="12" t="n"/>
+      <c r="U39" s="12" t="n"/>
+      <c r="V39" s="12" t="n"/>
+      <c r="W39" s="12" t="n"/>
+      <c r="X39" s="14" t="n"/>
+      <c r="Y39" s="15">
         <f>IF(TODAY()&lt;R39, 0, IF(TODAY()&gt;S39, T39, T39 * (TODAY()-R39)/(S39-R39+1)))</f>
         <v/>
       </c>
-      <c r="Z39" s="5">
+      <c r="Z39" s="15">
         <f>T39 * (X39/100)</f>
         <v/>
       </c>
-      <c r="AA39" s="5">
+      <c r="AA39" s="16">
         <f>W39</f>
         <v/>
       </c>
-      <c r="AJ39" s="4" t="n"/>
-      <c r="AK39" s="5">
+      <c r="AB39" s="12" t="n"/>
+      <c r="AC39" s="12" t="n"/>
+      <c r="AD39" s="12" t="n"/>
+      <c r="AE39" s="12" t="n"/>
+      <c r="AF39" s="12" t="n"/>
+      <c r="AG39" s="12" t="n"/>
+      <c r="AH39" s="12" t="n"/>
+      <c r="AI39" s="12" t="n"/>
+      <c r="AJ39" s="14" t="n"/>
+      <c r="AK39" s="15">
         <f>IF(TODAY()&lt;AD39, 0, IF(TODAY()&gt;AE39, AF39, AF39 * (TODAY()-AD39)/(AE39-AD39+1)))</f>
         <v/>
       </c>
-      <c r="AL39" s="5">
+      <c r="AL39" s="15">
         <f>AF39 * (AJ39/100)</f>
         <v/>
       </c>
-      <c r="AM39" s="5">
+      <c r="AM39" s="16">
         <f>AI39</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="L40" s="4" t="n"/>
-      <c r="M40" s="5">
+      <c r="A40" s="11" t="n"/>
+      <c r="B40" s="12" t="n"/>
+      <c r="C40" s="13" t="n"/>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="12" t="n"/>
+      <c r="G40" s="12" t="n"/>
+      <c r="H40" s="12" t="n"/>
+      <c r="I40" s="12" t="n"/>
+      <c r="J40" s="12" t="n"/>
+      <c r="K40" s="12" t="n"/>
+      <c r="L40" s="14" t="n"/>
+      <c r="M40" s="15">
         <f>IF(TODAY()&lt;F40, 0, IF(TODAY()&gt;G40, H40, H40 * (TODAY()-F40)/(G40-F40+1)))</f>
         <v/>
       </c>
-      <c r="N40" s="5">
+      <c r="N40" s="15">
         <f>H40 * (L40/100)</f>
         <v/>
       </c>
-      <c r="O40" s="5">
+      <c r="O40" s="16">
         <f>K40</f>
         <v/>
       </c>
-      <c r="X40" s="4" t="n"/>
-      <c r="Y40" s="5">
+      <c r="P40" s="12" t="n"/>
+      <c r="Q40" s="12" t="n"/>
+      <c r="R40" s="12" t="n"/>
+      <c r="S40" s="12" t="n"/>
+      <c r="T40" s="12" t="n"/>
+      <c r="U40" s="12" t="n"/>
+      <c r="V40" s="12" t="n"/>
+      <c r="W40" s="12" t="n"/>
+      <c r="X40" s="14" t="n"/>
+      <c r="Y40" s="15">
         <f>IF(TODAY()&lt;R40, 0, IF(TODAY()&gt;S40, T40, T40 * (TODAY()-R40)/(S40-R40+1)))</f>
         <v/>
       </c>
-      <c r="Z40" s="5">
+      <c r="Z40" s="15">
         <f>T40 * (X40/100)</f>
         <v/>
       </c>
-      <c r="AA40" s="5">
+      <c r="AA40" s="16">
         <f>W40</f>
         <v/>
       </c>
-      <c r="AJ40" s="4" t="n"/>
-      <c r="AK40" s="5">
+      <c r="AB40" s="12" t="n"/>
+      <c r="AC40" s="12" t="n"/>
+      <c r="AD40" s="12" t="n"/>
+      <c r="AE40" s="12" t="n"/>
+      <c r="AF40" s="12" t="n"/>
+      <c r="AG40" s="12" t="n"/>
+      <c r="AH40" s="12" t="n"/>
+      <c r="AI40" s="12" t="n"/>
+      <c r="AJ40" s="14" t="n"/>
+      <c r="AK40" s="15">
         <f>IF(TODAY()&lt;AD40, 0, IF(TODAY()&gt;AE40, AF40, AF40 * (TODAY()-AD40)/(AE40-AD40+1)))</f>
         <v/>
       </c>
-      <c r="AL40" s="5">
+      <c r="AL40" s="15">
         <f>AF40 * (AJ40/100)</f>
         <v/>
       </c>
-      <c r="AM40" s="5">
+      <c r="AM40" s="16">
         <f>AI40</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="L41" s="4" t="n"/>
-      <c r="M41" s="5">
+      <c r="A41" s="11" t="n"/>
+      <c r="B41" s="12" t="n"/>
+      <c r="C41" s="13" t="n"/>
+      <c r="D41" s="12" t="n"/>
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="12" t="n"/>
+      <c r="G41" s="12" t="n"/>
+      <c r="H41" s="12" t="n"/>
+      <c r="I41" s="12" t="n"/>
+      <c r="J41" s="12" t="n"/>
+      <c r="K41" s="12" t="n"/>
+      <c r="L41" s="14" t="n"/>
+      <c r="M41" s="15">
         <f>IF(TODAY()&lt;F41, 0, IF(TODAY()&gt;G41, H41, H41 * (TODAY()-F41)/(G41-F41+1)))</f>
         <v/>
       </c>
-      <c r="N41" s="5">
+      <c r="N41" s="15">
         <f>H41 * (L41/100)</f>
         <v/>
       </c>
-      <c r="O41" s="5">
+      <c r="O41" s="16">
         <f>K41</f>
         <v/>
       </c>
-      <c r="X41" s="4" t="n"/>
-      <c r="Y41" s="5">
+      <c r="P41" s="12" t="n"/>
+      <c r="Q41" s="12" t="n"/>
+      <c r="R41" s="12" t="n"/>
+      <c r="S41" s="12" t="n"/>
+      <c r="T41" s="12" t="n"/>
+      <c r="U41" s="12" t="n"/>
+      <c r="V41" s="12" t="n"/>
+      <c r="W41" s="12" t="n"/>
+      <c r="X41" s="14" t="n"/>
+      <c r="Y41" s="15">
         <f>IF(TODAY()&lt;R41, 0, IF(TODAY()&gt;S41, T41, T41 * (TODAY()-R41)/(S41-R41+1)))</f>
         <v/>
       </c>
-      <c r="Z41" s="5">
+      <c r="Z41" s="15">
         <f>T41 * (X41/100)</f>
         <v/>
       </c>
-      <c r="AA41" s="5">
+      <c r="AA41" s="16">
         <f>W41</f>
         <v/>
       </c>
-      <c r="AJ41" s="4" t="n"/>
-      <c r="AK41" s="5">
+      <c r="AB41" s="12" t="n"/>
+      <c r="AC41" s="12" t="n"/>
+      <c r="AD41" s="12" t="n"/>
+      <c r="AE41" s="12" t="n"/>
+      <c r="AF41" s="12" t="n"/>
+      <c r="AG41" s="12" t="n"/>
+      <c r="AH41" s="12" t="n"/>
+      <c r="AI41" s="12" t="n"/>
+      <c r="AJ41" s="14" t="n"/>
+      <c r="AK41" s="15">
         <f>IF(TODAY()&lt;AD41, 0, IF(TODAY()&gt;AE41, AF41, AF41 * (TODAY()-AD41)/(AE41-AD41+1)))</f>
         <v/>
       </c>
-      <c r="AL41" s="5">
+      <c r="AL41" s="15">
         <f>AF41 * (AJ41/100)</f>
         <v/>
       </c>
-      <c r="AM41" s="5">
+      <c r="AM41" s="16">
         <f>AI41</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="L42" s="4" t="n"/>
-      <c r="M42" s="5">
+      <c r="A42" s="11" t="n"/>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="13" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="12" t="n"/>
+      <c r="H42" s="12" t="n"/>
+      <c r="I42" s="12" t="n"/>
+      <c r="J42" s="12" t="n"/>
+      <c r="K42" s="12" t="n"/>
+      <c r="L42" s="14" t="n"/>
+      <c r="M42" s="15">
         <f>IF(TODAY()&lt;F42, 0, IF(TODAY()&gt;G42, H42, H42 * (TODAY()-F42)/(G42-F42+1)))</f>
         <v/>
       </c>
-      <c r="N42" s="5">
+      <c r="N42" s="15">
         <f>H42 * (L42/100)</f>
         <v/>
       </c>
-      <c r="O42" s="5">
+      <c r="O42" s="16">
         <f>K42</f>
         <v/>
       </c>
-      <c r="X42" s="4" t="n"/>
-      <c r="Y42" s="5">
+      <c r="P42" s="12" t="n"/>
+      <c r="Q42" s="12" t="n"/>
+      <c r="R42" s="12" t="n"/>
+      <c r="S42" s="12" t="n"/>
+      <c r="T42" s="12" t="n"/>
+      <c r="U42" s="12" t="n"/>
+      <c r="V42" s="12" t="n"/>
+      <c r="W42" s="12" t="n"/>
+      <c r="X42" s="14" t="n"/>
+      <c r="Y42" s="15">
         <f>IF(TODAY()&lt;R42, 0, IF(TODAY()&gt;S42, T42, T42 * (TODAY()-R42)/(S42-R42+1)))</f>
         <v/>
       </c>
-      <c r="Z42" s="5">
+      <c r="Z42" s="15">
         <f>T42 * (X42/100)</f>
         <v/>
       </c>
-      <c r="AA42" s="5">
+      <c r="AA42" s="16">
         <f>W42</f>
         <v/>
       </c>
-      <c r="AJ42" s="4" t="n"/>
-      <c r="AK42" s="5">
+      <c r="AB42" s="12" t="n"/>
+      <c r="AC42" s="12" t="n"/>
+      <c r="AD42" s="12" t="n"/>
+      <c r="AE42" s="12" t="n"/>
+      <c r="AF42" s="12" t="n"/>
+      <c r="AG42" s="12" t="n"/>
+      <c r="AH42" s="12" t="n"/>
+      <c r="AI42" s="12" t="n"/>
+      <c r="AJ42" s="14" t="n"/>
+      <c r="AK42" s="15">
         <f>IF(TODAY()&lt;AD42, 0, IF(TODAY()&gt;AE42, AF42, AF42 * (TODAY()-AD42)/(AE42-AD42+1)))</f>
         <v/>
       </c>
-      <c r="AL42" s="5">
+      <c r="AL42" s="15">
         <f>AF42 * (AJ42/100)</f>
         <v/>
       </c>
-      <c r="AM42" s="5">
+      <c r="AM42" s="16">
         <f>AI42</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="L43" s="4" t="n"/>
-      <c r="M43" s="5">
+      <c r="A43" s="11" t="n"/>
+      <c r="B43" s="12" t="n"/>
+      <c r="C43" s="13" t="n"/>
+      <c r="D43" s="12" t="n"/>
+      <c r="E43" s="12" t="n"/>
+      <c r="F43" s="12" t="n"/>
+      <c r="G43" s="12" t="n"/>
+      <c r="H43" s="12" t="n"/>
+      <c r="I43" s="12" t="n"/>
+      <c r="J43" s="12" t="n"/>
+      <c r="K43" s="12" t="n"/>
+      <c r="L43" s="14" t="n"/>
+      <c r="M43" s="15">
         <f>IF(TODAY()&lt;F43, 0, IF(TODAY()&gt;G43, H43, H43 * (TODAY()-F43)/(G43-F43+1)))</f>
         <v/>
       </c>
-      <c r="N43" s="5">
+      <c r="N43" s="15">
         <f>H43 * (L43/100)</f>
         <v/>
       </c>
-      <c r="O43" s="5">
+      <c r="O43" s="16">
         <f>K43</f>
         <v/>
       </c>
-      <c r="X43" s="4" t="n"/>
-      <c r="Y43" s="5">
+      <c r="P43" s="12" t="n"/>
+      <c r="Q43" s="12" t="n"/>
+      <c r="R43" s="12" t="n"/>
+      <c r="S43" s="12" t="n"/>
+      <c r="T43" s="12" t="n"/>
+      <c r="U43" s="12" t="n"/>
+      <c r="V43" s="12" t="n"/>
+      <c r="W43" s="12" t="n"/>
+      <c r="X43" s="14" t="n"/>
+      <c r="Y43" s="15">
         <f>IF(TODAY()&lt;R43, 0, IF(TODAY()&gt;S43, T43, T43 * (TODAY()-R43)/(S43-R43+1)))</f>
         <v/>
       </c>
-      <c r="Z43" s="5">
+      <c r="Z43" s="15">
         <f>T43 * (X43/100)</f>
         <v/>
       </c>
-      <c r="AA43" s="5">
+      <c r="AA43" s="16">
         <f>W43</f>
         <v/>
       </c>
-      <c r="AJ43" s="4" t="n"/>
-      <c r="AK43" s="5">
+      <c r="AB43" s="12" t="n"/>
+      <c r="AC43" s="12" t="n"/>
+      <c r="AD43" s="12" t="n"/>
+      <c r="AE43" s="12" t="n"/>
+      <c r="AF43" s="12" t="n"/>
+      <c r="AG43" s="12" t="n"/>
+      <c r="AH43" s="12" t="n"/>
+      <c r="AI43" s="12" t="n"/>
+      <c r="AJ43" s="14" t="n"/>
+      <c r="AK43" s="15">
         <f>IF(TODAY()&lt;AD43, 0, IF(TODAY()&gt;AE43, AF43, AF43 * (TODAY()-AD43)/(AE43-AD43+1)))</f>
         <v/>
       </c>
-      <c r="AL43" s="5">
+      <c r="AL43" s="15">
         <f>AF43 * (AJ43/100)</f>
         <v/>
       </c>
-      <c r="AM43" s="5">
+      <c r="AM43" s="16">
         <f>AI43</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="L44" s="4" t="n"/>
-      <c r="M44" s="5">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="12" t="n"/>
+      <c r="C44" s="13" t="n"/>
+      <c r="D44" s="12" t="n"/>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="12" t="n"/>
+      <c r="G44" s="12" t="n"/>
+      <c r="H44" s="12" t="n"/>
+      <c r="I44" s="12" t="n"/>
+      <c r="J44" s="12" t="n"/>
+      <c r="K44" s="12" t="n"/>
+      <c r="L44" s="14" t="n"/>
+      <c r="M44" s="15">
         <f>IF(TODAY()&lt;F44, 0, IF(TODAY()&gt;G44, H44, H44 * (TODAY()-F44)/(G44-F44+1)))</f>
         <v/>
       </c>
-      <c r="N44" s="5">
+      <c r="N44" s="15">
         <f>H44 * (L44/100)</f>
         <v/>
       </c>
-      <c r="O44" s="5">
+      <c r="O44" s="16">
         <f>K44</f>
         <v/>
       </c>
-      <c r="X44" s="4" t="n"/>
-      <c r="Y44" s="5">
+      <c r="P44" s="12" t="n"/>
+      <c r="Q44" s="12" t="n"/>
+      <c r="R44" s="12" t="n"/>
+      <c r="S44" s="12" t="n"/>
+      <c r="T44" s="12" t="n"/>
+      <c r="U44" s="12" t="n"/>
+      <c r="V44" s="12" t="n"/>
+      <c r="W44" s="12" t="n"/>
+      <c r="X44" s="14" t="n"/>
+      <c r="Y44" s="15">
         <f>IF(TODAY()&lt;R44, 0, IF(TODAY()&gt;S44, T44, T44 * (TODAY()-R44)/(S44-R44+1)))</f>
         <v/>
       </c>
-      <c r="Z44" s="5">
+      <c r="Z44" s="15">
         <f>T44 * (X44/100)</f>
         <v/>
       </c>
-      <c r="AA44" s="5">
+      <c r="AA44" s="16">
         <f>W44</f>
         <v/>
       </c>
-      <c r="AJ44" s="4" t="n"/>
-      <c r="AK44" s="5">
+      <c r="AB44" s="12" t="n"/>
+      <c r="AC44" s="12" t="n"/>
+      <c r="AD44" s="12" t="n"/>
+      <c r="AE44" s="12" t="n"/>
+      <c r="AF44" s="12" t="n"/>
+      <c r="AG44" s="12" t="n"/>
+      <c r="AH44" s="12" t="n"/>
+      <c r="AI44" s="12" t="n"/>
+      <c r="AJ44" s="14" t="n"/>
+      <c r="AK44" s="15">
         <f>IF(TODAY()&lt;AD44, 0, IF(TODAY()&gt;AE44, AF44, AF44 * (TODAY()-AD44)/(AE44-AD44+1)))</f>
         <v/>
       </c>
-      <c r="AL44" s="5">
+      <c r="AL44" s="15">
         <f>AF44 * (AJ44/100)</f>
         <v/>
       </c>
-      <c r="AM44" s="5">
+      <c r="AM44" s="16">
         <f>AI44</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="L45" s="4" t="n"/>
-      <c r="M45" s="5">
+      <c r="A45" s="11" t="n"/>
+      <c r="B45" s="12" t="n"/>
+      <c r="C45" s="13" t="n"/>
+      <c r="D45" s="12" t="n"/>
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="12" t="n"/>
+      <c r="G45" s="12" t="n"/>
+      <c r="H45" s="12" t="n"/>
+      <c r="I45" s="12" t="n"/>
+      <c r="J45" s="12" t="n"/>
+      <c r="K45" s="12" t="n"/>
+      <c r="L45" s="14" t="n"/>
+      <c r="M45" s="15">
         <f>IF(TODAY()&lt;F45, 0, IF(TODAY()&gt;G45, H45, H45 * (TODAY()-F45)/(G45-F45+1)))</f>
         <v/>
       </c>
-      <c r="N45" s="5">
+      <c r="N45" s="15">
         <f>H45 * (L45/100)</f>
         <v/>
       </c>
-      <c r="O45" s="5">
+      <c r="O45" s="16">
         <f>K45</f>
         <v/>
       </c>
-      <c r="X45" s="4" t="n"/>
-      <c r="Y45" s="5">
+      <c r="P45" s="12" t="n"/>
+      <c r="Q45" s="12" t="n"/>
+      <c r="R45" s="12" t="n"/>
+      <c r="S45" s="12" t="n"/>
+      <c r="T45" s="12" t="n"/>
+      <c r="U45" s="12" t="n"/>
+      <c r="V45" s="12" t="n"/>
+      <c r="W45" s="12" t="n"/>
+      <c r="X45" s="14" t="n"/>
+      <c r="Y45" s="15">
         <f>IF(TODAY()&lt;R45, 0, IF(TODAY()&gt;S45, T45, T45 * (TODAY()-R45)/(S45-R45+1)))</f>
         <v/>
       </c>
-      <c r="Z45" s="5">
+      <c r="Z45" s="15">
         <f>T45 * (X45/100)</f>
         <v/>
       </c>
-      <c r="AA45" s="5">
+      <c r="AA45" s="16">
         <f>W45</f>
         <v/>
       </c>
-      <c r="AJ45" s="4" t="n"/>
-      <c r="AK45" s="5">
+      <c r="AB45" s="12" t="n"/>
+      <c r="AC45" s="12" t="n"/>
+      <c r="AD45" s="12" t="n"/>
+      <c r="AE45" s="12" t="n"/>
+      <c r="AF45" s="12" t="n"/>
+      <c r="AG45" s="12" t="n"/>
+      <c r="AH45" s="12" t="n"/>
+      <c r="AI45" s="12" t="n"/>
+      <c r="AJ45" s="14" t="n"/>
+      <c r="AK45" s="15">
         <f>IF(TODAY()&lt;AD45, 0, IF(TODAY()&gt;AE45, AF45, AF45 * (TODAY()-AD45)/(AE45-AD45+1)))</f>
         <v/>
       </c>
-      <c r="AL45" s="5">
+      <c r="AL45" s="15">
         <f>AF45 * (AJ45/100)</f>
         <v/>
       </c>
-      <c r="AM45" s="5">
+      <c r="AM45" s="16">
         <f>AI45</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="L46" s="4" t="n"/>
-      <c r="M46" s="5">
+      <c r="A46" s="11" t="n"/>
+      <c r="B46" s="12" t="n"/>
+      <c r="C46" s="13" t="n"/>
+      <c r="D46" s="12" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="12" t="n"/>
+      <c r="G46" s="12" t="n"/>
+      <c r="H46" s="12" t="n"/>
+      <c r="I46" s="12" t="n"/>
+      <c r="J46" s="12" t="n"/>
+      <c r="K46" s="12" t="n"/>
+      <c r="L46" s="14" t="n"/>
+      <c r="M46" s="15">
         <f>IF(TODAY()&lt;F46, 0, IF(TODAY()&gt;G46, H46, H46 * (TODAY()-F46)/(G46-F46+1)))</f>
         <v/>
       </c>
-      <c r="N46" s="5">
+      <c r="N46" s="15">
         <f>H46 * (L46/100)</f>
         <v/>
       </c>
-      <c r="O46" s="5">
+      <c r="O46" s="16">
         <f>K46</f>
         <v/>
       </c>
-      <c r="X46" s="4" t="n"/>
-      <c r="Y46" s="5">
+      <c r="P46" s="12" t="n"/>
+      <c r="Q46" s="12" t="n"/>
+      <c r="R46" s="12" t="n"/>
+      <c r="S46" s="12" t="n"/>
+      <c r="T46" s="12" t="n"/>
+      <c r="U46" s="12" t="n"/>
+      <c r="V46" s="12" t="n"/>
+      <c r="W46" s="12" t="n"/>
+      <c r="X46" s="14" t="n"/>
+      <c r="Y46" s="15">
         <f>IF(TODAY()&lt;R46, 0, IF(TODAY()&gt;S46, T46, T46 * (TODAY()-R46)/(S46-R46+1)))</f>
         <v/>
       </c>
-      <c r="Z46" s="5">
+      <c r="Z46" s="15">
         <f>T46 * (X46/100)</f>
         <v/>
       </c>
-      <c r="AA46" s="5">
+      <c r="AA46" s="16">
         <f>W46</f>
         <v/>
       </c>
-      <c r="AJ46" s="4" t="n"/>
-      <c r="AK46" s="5">
+      <c r="AB46" s="12" t="n"/>
+      <c r="AC46" s="12" t="n"/>
+      <c r="AD46" s="12" t="n"/>
+      <c r="AE46" s="12" t="n"/>
+      <c r="AF46" s="12" t="n"/>
+      <c r="AG46" s="12" t="n"/>
+      <c r="AH46" s="12" t="n"/>
+      <c r="AI46" s="12" t="n"/>
+      <c r="AJ46" s="14" t="n"/>
+      <c r="AK46" s="15">
         <f>IF(TODAY()&lt;AD46, 0, IF(TODAY()&gt;AE46, AF46, AF46 * (TODAY()-AD46)/(AE46-AD46+1)))</f>
         <v/>
       </c>
-      <c r="AL46" s="5">
+      <c r="AL46" s="15">
         <f>AF46 * (AJ46/100)</f>
         <v/>
       </c>
-      <c r="AM46" s="5">
+      <c r="AM46" s="16">
         <f>AI46</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="L47" s="4" t="n"/>
-      <c r="M47" s="5">
+      <c r="A47" s="11" t="n"/>
+      <c r="B47" s="12" t="n"/>
+      <c r="C47" s="13" t="n"/>
+      <c r="D47" s="12" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="12" t="n"/>
+      <c r="G47" s="12" t="n"/>
+      <c r="H47" s="12" t="n"/>
+      <c r="I47" s="12" t="n"/>
+      <c r="J47" s="12" t="n"/>
+      <c r="K47" s="12" t="n"/>
+      <c r="L47" s="14" t="n"/>
+      <c r="M47" s="15">
         <f>IF(TODAY()&lt;F47, 0, IF(TODAY()&gt;G47, H47, H47 * (TODAY()-F47)/(G47-F47+1)))</f>
         <v/>
       </c>
-      <c r="N47" s="5">
+      <c r="N47" s="15">
         <f>H47 * (L47/100)</f>
         <v/>
       </c>
-      <c r="O47" s="5">
+      <c r="O47" s="16">
         <f>K47</f>
         <v/>
       </c>
-      <c r="X47" s="4" t="n"/>
-      <c r="Y47" s="5">
+      <c r="P47" s="12" t="n"/>
+      <c r="Q47" s="12" t="n"/>
+      <c r="R47" s="12" t="n"/>
+      <c r="S47" s="12" t="n"/>
+      <c r="T47" s="12" t="n"/>
+      <c r="U47" s="12" t="n"/>
+      <c r="V47" s="12" t="n"/>
+      <c r="W47" s="12" t="n"/>
+      <c r="X47" s="14" t="n"/>
+      <c r="Y47" s="15">
         <f>IF(TODAY()&lt;R47, 0, IF(TODAY()&gt;S47, T47, T47 * (TODAY()-R47)/(S47-R47+1)))</f>
         <v/>
       </c>
-      <c r="Z47" s="5">
+      <c r="Z47" s="15">
         <f>T47 * (X47/100)</f>
         <v/>
       </c>
-      <c r="AA47" s="5">
+      <c r="AA47" s="16">
         <f>W47</f>
         <v/>
       </c>
-      <c r="AJ47" s="4" t="n"/>
-      <c r="AK47" s="5">
+      <c r="AB47" s="12" t="n"/>
+      <c r="AC47" s="12" t="n"/>
+      <c r="AD47" s="12" t="n"/>
+      <c r="AE47" s="12" t="n"/>
+      <c r="AF47" s="12" t="n"/>
+      <c r="AG47" s="12" t="n"/>
+      <c r="AH47" s="12" t="n"/>
+      <c r="AI47" s="12" t="n"/>
+      <c r="AJ47" s="14" t="n"/>
+      <c r="AK47" s="15">
         <f>IF(TODAY()&lt;AD47, 0, IF(TODAY()&gt;AE47, AF47, AF47 * (TODAY()-AD47)/(AE47-AD47+1)))</f>
         <v/>
       </c>
-      <c r="AL47" s="5">
+      <c r="AL47" s="15">
         <f>AF47 * (AJ47/100)</f>
         <v/>
       </c>
-      <c r="AM47" s="5">
+      <c r="AM47" s="16">
         <f>AI47</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="L48" s="4" t="n"/>
-      <c r="M48" s="5">
+      <c r="A48" s="11" t="n"/>
+      <c r="B48" s="12" t="n"/>
+      <c r="C48" s="13" t="n"/>
+      <c r="D48" s="12" t="n"/>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="12" t="n"/>
+      <c r="G48" s="12" t="n"/>
+      <c r="H48" s="12" t="n"/>
+      <c r="I48" s="12" t="n"/>
+      <c r="J48" s="12" t="n"/>
+      <c r="K48" s="12" t="n"/>
+      <c r="L48" s="14" t="n"/>
+      <c r="M48" s="15">
         <f>IF(TODAY()&lt;F48, 0, IF(TODAY()&gt;G48, H48, H48 * (TODAY()-F48)/(G48-F48+1)))</f>
         <v/>
       </c>
-      <c r="N48" s="5">
+      <c r="N48" s="15">
         <f>H48 * (L48/100)</f>
         <v/>
       </c>
-      <c r="O48" s="5">
+      <c r="O48" s="16">
         <f>K48</f>
         <v/>
       </c>
-      <c r="X48" s="4" t="n"/>
-      <c r="Y48" s="5">
+      <c r="P48" s="12" t="n"/>
+      <c r="Q48" s="12" t="n"/>
+      <c r="R48" s="12" t="n"/>
+      <c r="S48" s="12" t="n"/>
+      <c r="T48" s="12" t="n"/>
+      <c r="U48" s="12" t="n"/>
+      <c r="V48" s="12" t="n"/>
+      <c r="W48" s="12" t="n"/>
+      <c r="X48" s="14" t="n"/>
+      <c r="Y48" s="15">
         <f>IF(TODAY()&lt;R48, 0, IF(TODAY()&gt;S48, T48, T48 * (TODAY()-R48)/(S48-R48+1)))</f>
         <v/>
       </c>
-      <c r="Z48" s="5">
+      <c r="Z48" s="15">
         <f>T48 * (X48/100)</f>
         <v/>
       </c>
-      <c r="AA48" s="5">
+      <c r="AA48" s="16">
         <f>W48</f>
         <v/>
       </c>
-      <c r="AJ48" s="4" t="n"/>
-      <c r="AK48" s="5">
+      <c r="AB48" s="12" t="n"/>
+      <c r="AC48" s="12" t="n"/>
+      <c r="AD48" s="12" t="n"/>
+      <c r="AE48" s="12" t="n"/>
+      <c r="AF48" s="12" t="n"/>
+      <c r="AG48" s="12" t="n"/>
+      <c r="AH48" s="12" t="n"/>
+      <c r="AI48" s="12" t="n"/>
+      <c r="AJ48" s="14" t="n"/>
+      <c r="AK48" s="15">
         <f>IF(TODAY()&lt;AD48, 0, IF(TODAY()&gt;AE48, AF48, AF48 * (TODAY()-AD48)/(AE48-AD48+1)))</f>
         <v/>
       </c>
-      <c r="AL48" s="5">
+      <c r="AL48" s="15">
         <f>AF48 * (AJ48/100)</f>
         <v/>
       </c>
-      <c r="AM48" s="5">
+      <c r="AM48" s="16">
         <f>AI48</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="L49" s="4" t="n"/>
-      <c r="M49" s="5">
+      <c r="A49" s="11" t="n"/>
+      <c r="B49" s="12" t="n"/>
+      <c r="C49" s="13" t="n"/>
+      <c r="D49" s="12" t="n"/>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="12" t="n"/>
+      <c r="G49" s="12" t="n"/>
+      <c r="H49" s="12" t="n"/>
+      <c r="I49" s="12" t="n"/>
+      <c r="J49" s="12" t="n"/>
+      <c r="K49" s="12" t="n"/>
+      <c r="L49" s="14" t="n"/>
+      <c r="M49" s="15">
         <f>IF(TODAY()&lt;F49, 0, IF(TODAY()&gt;G49, H49, H49 * (TODAY()-F49)/(G49-F49+1)))</f>
         <v/>
       </c>
-      <c r="N49" s="5">
+      <c r="N49" s="15">
         <f>H49 * (L49/100)</f>
         <v/>
       </c>
-      <c r="O49" s="5">
+      <c r="O49" s="16">
         <f>K49</f>
         <v/>
       </c>
-      <c r="X49" s="4" t="n"/>
-      <c r="Y49" s="5">
+      <c r="P49" s="12" t="n"/>
+      <c r="Q49" s="12" t="n"/>
+      <c r="R49" s="12" t="n"/>
+      <c r="S49" s="12" t="n"/>
+      <c r="T49" s="12" t="n"/>
+      <c r="U49" s="12" t="n"/>
+      <c r="V49" s="12" t="n"/>
+      <c r="W49" s="12" t="n"/>
+      <c r="X49" s="14" t="n"/>
+      <c r="Y49" s="15">
         <f>IF(TODAY()&lt;R49, 0, IF(TODAY()&gt;S49, T49, T49 * (TODAY()-R49)/(S49-R49+1)))</f>
         <v/>
       </c>
-      <c r="Z49" s="5">
+      <c r="Z49" s="15">
         <f>T49 * (X49/100)</f>
         <v/>
       </c>
-      <c r="AA49" s="5">
+      <c r="AA49" s="16">
         <f>W49</f>
         <v/>
       </c>
-      <c r="AJ49" s="4" t="n"/>
-      <c r="AK49" s="5">
+      <c r="AB49" s="12" t="n"/>
+      <c r="AC49" s="12" t="n"/>
+      <c r="AD49" s="12" t="n"/>
+      <c r="AE49" s="12" t="n"/>
+      <c r="AF49" s="12" t="n"/>
+      <c r="AG49" s="12" t="n"/>
+      <c r="AH49" s="12" t="n"/>
+      <c r="AI49" s="12" t="n"/>
+      <c r="AJ49" s="14" t="n"/>
+      <c r="AK49" s="15">
         <f>IF(TODAY()&lt;AD49, 0, IF(TODAY()&gt;AE49, AF49, AF49 * (TODAY()-AD49)/(AE49-AD49+1)))</f>
         <v/>
       </c>
-      <c r="AL49" s="5">
+      <c r="AL49" s="15">
         <f>AF49 * (AJ49/100)</f>
         <v/>
       </c>
-      <c r="AM49" s="5">
+      <c r="AM49" s="16">
         <f>AI49</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="L50" s="4" t="n"/>
-      <c r="M50" s="5">
+      <c r="A50" s="11" t="n"/>
+      <c r="B50" s="12" t="n"/>
+      <c r="C50" s="13" t="n"/>
+      <c r="D50" s="12" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="12" t="n"/>
+      <c r="G50" s="12" t="n"/>
+      <c r="H50" s="12" t="n"/>
+      <c r="I50" s="12" t="n"/>
+      <c r="J50" s="12" t="n"/>
+      <c r="K50" s="12" t="n"/>
+      <c r="L50" s="14" t="n"/>
+      <c r="M50" s="15">
         <f>IF(TODAY()&lt;F50, 0, IF(TODAY()&gt;G50, H50, H50 * (TODAY()-F50)/(G50-F50+1)))</f>
         <v/>
       </c>
-      <c r="N50" s="5">
+      <c r="N50" s="15">
         <f>H50 * (L50/100)</f>
         <v/>
       </c>
-      <c r="O50" s="5">
+      <c r="O50" s="16">
         <f>K50</f>
         <v/>
       </c>
-      <c r="X50" s="4" t="n"/>
-      <c r="Y50" s="5">
+      <c r="P50" s="12" t="n"/>
+      <c r="Q50" s="12" t="n"/>
+      <c r="R50" s="12" t="n"/>
+      <c r="S50" s="12" t="n"/>
+      <c r="T50" s="12" t="n"/>
+      <c r="U50" s="12" t="n"/>
+      <c r="V50" s="12" t="n"/>
+      <c r="W50" s="12" t="n"/>
+      <c r="X50" s="14" t="n"/>
+      <c r="Y50" s="15">
         <f>IF(TODAY()&lt;R50, 0, IF(TODAY()&gt;S50, T50, T50 * (TODAY()-R50)/(S50-R50+1)))</f>
         <v/>
       </c>
-      <c r="Z50" s="5">
+      <c r="Z50" s="15">
         <f>T50 * (X50/100)</f>
         <v/>
       </c>
-      <c r="AA50" s="5">
+      <c r="AA50" s="16">
         <f>W50</f>
         <v/>
       </c>
-      <c r="AJ50" s="4" t="n"/>
-      <c r="AK50" s="5">
+      <c r="AB50" s="12" t="n"/>
+      <c r="AC50" s="12" t="n"/>
+      <c r="AD50" s="12" t="n"/>
+      <c r="AE50" s="12" t="n"/>
+      <c r="AF50" s="12" t="n"/>
+      <c r="AG50" s="12" t="n"/>
+      <c r="AH50" s="12" t="n"/>
+      <c r="AI50" s="12" t="n"/>
+      <c r="AJ50" s="14" t="n"/>
+      <c r="AK50" s="15">
         <f>IF(TODAY()&lt;AD50, 0, IF(TODAY()&gt;AE50, AF50, AF50 * (TODAY()-AD50)/(AE50-AD50+1)))</f>
         <v/>
       </c>
-      <c r="AL50" s="5">
+      <c r="AL50" s="15">
         <f>AF50 * (AJ50/100)</f>
         <v/>
       </c>
-      <c r="AM50" s="5">
+      <c r="AM50" s="16">
         <f>AI50</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="L51" s="4" t="n"/>
-      <c r="M51" s="5">
+      <c r="A51" s="11" t="n"/>
+      <c r="B51" s="12" t="n"/>
+      <c r="C51" s="13" t="n"/>
+      <c r="D51" s="12" t="n"/>
+      <c r="E51" s="12" t="n"/>
+      <c r="F51" s="12" t="n"/>
+      <c r="G51" s="12" t="n"/>
+      <c r="H51" s="12" t="n"/>
+      <c r="I51" s="12" t="n"/>
+      <c r="J51" s="12" t="n"/>
+      <c r="K51" s="12" t="n"/>
+      <c r="L51" s="14" t="n"/>
+      <c r="M51" s="15">
         <f>IF(TODAY()&lt;F51, 0, IF(TODAY()&gt;G51, H51, H51 * (TODAY()-F51)/(G51-F51+1)))</f>
         <v/>
       </c>
-      <c r="N51" s="5">
+      <c r="N51" s="15">
         <f>H51 * (L51/100)</f>
         <v/>
       </c>
-      <c r="O51" s="5">
+      <c r="O51" s="16">
         <f>K51</f>
         <v/>
       </c>
-      <c r="X51" s="4" t="n"/>
-      <c r="Y51" s="5">
+      <c r="P51" s="12" t="n"/>
+      <c r="Q51" s="12" t="n"/>
+      <c r="R51" s="12" t="n"/>
+      <c r="S51" s="12" t="n"/>
+      <c r="T51" s="12" t="n"/>
+      <c r="U51" s="12" t="n"/>
+      <c r="V51" s="12" t="n"/>
+      <c r="W51" s="12" t="n"/>
+      <c r="X51" s="14" t="n"/>
+      <c r="Y51" s="15">
         <f>IF(TODAY()&lt;R51, 0, IF(TODAY()&gt;S51, T51, T51 * (TODAY()-R51)/(S51-R51+1)))</f>
         <v/>
       </c>
-      <c r="Z51" s="5">
+      <c r="Z51" s="15">
         <f>T51 * (X51/100)</f>
         <v/>
       </c>
-      <c r="AA51" s="5">
+      <c r="AA51" s="16">
         <f>W51</f>
         <v/>
       </c>
-      <c r="AJ51" s="4" t="n"/>
-      <c r="AK51" s="5">
+      <c r="AB51" s="12" t="n"/>
+      <c r="AC51" s="12" t="n"/>
+      <c r="AD51" s="12" t="n"/>
+      <c r="AE51" s="12" t="n"/>
+      <c r="AF51" s="12" t="n"/>
+      <c r="AG51" s="12" t="n"/>
+      <c r="AH51" s="12" t="n"/>
+      <c r="AI51" s="12" t="n"/>
+      <c r="AJ51" s="14" t="n"/>
+      <c r="AK51" s="15">
         <f>IF(TODAY()&lt;AD51, 0, IF(TODAY()&gt;AE51, AF51, AF51 * (TODAY()-AD51)/(AE51-AD51+1)))</f>
         <v/>
       </c>
-      <c r="AL51" s="5">
+      <c r="AL51" s="15">
         <f>AF51 * (AJ51/100)</f>
         <v/>
       </c>
-      <c r="AM51" s="5">
+      <c r="AM51" s="16">
         <f>AI51</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="L52" s="4" t="n"/>
-      <c r="M52" s="5">
+      <c r="A52" s="11" t="n"/>
+      <c r="B52" s="12" t="n"/>
+      <c r="C52" s="13" t="n"/>
+      <c r="D52" s="12" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="12" t="n"/>
+      <c r="G52" s="12" t="n"/>
+      <c r="H52" s="12" t="n"/>
+      <c r="I52" s="12" t="n"/>
+      <c r="J52" s="12" t="n"/>
+      <c r="K52" s="12" t="n"/>
+      <c r="L52" s="14" t="n"/>
+      <c r="M52" s="15">
         <f>IF(TODAY()&lt;F52, 0, IF(TODAY()&gt;G52, H52, H52 * (TODAY()-F52)/(G52-F52+1)))</f>
         <v/>
       </c>
-      <c r="N52" s="5">
+      <c r="N52" s="15">
         <f>H52 * (L52/100)</f>
         <v/>
       </c>
-      <c r="O52" s="5">
+      <c r="O52" s="16">
         <f>K52</f>
         <v/>
       </c>
-      <c r="X52" s="4" t="n"/>
-      <c r="Y52" s="5">
+      <c r="P52" s="12" t="n"/>
+      <c r="Q52" s="12" t="n"/>
+      <c r="R52" s="12" t="n"/>
+      <c r="S52" s="12" t="n"/>
+      <c r="T52" s="12" t="n"/>
+      <c r="U52" s="12" t="n"/>
+      <c r="V52" s="12" t="n"/>
+      <c r="W52" s="12" t="n"/>
+      <c r="X52" s="14" t="n"/>
+      <c r="Y52" s="15">
         <f>IF(TODAY()&lt;R52, 0, IF(TODAY()&gt;S52, T52, T52 * (TODAY()-R52)/(S52-R52+1)))</f>
         <v/>
       </c>
-      <c r="Z52" s="5">
+      <c r="Z52" s="15">
         <f>T52 * (X52/100)</f>
         <v/>
       </c>
-      <c r="AA52" s="5">
+      <c r="AA52" s="16">
         <f>W52</f>
         <v/>
       </c>
-      <c r="AJ52" s="4" t="n"/>
-      <c r="AK52" s="5">
+      <c r="AB52" s="12" t="n"/>
+      <c r="AC52" s="12" t="n"/>
+      <c r="AD52" s="12" t="n"/>
+      <c r="AE52" s="12" t="n"/>
+      <c r="AF52" s="12" t="n"/>
+      <c r="AG52" s="12" t="n"/>
+      <c r="AH52" s="12" t="n"/>
+      <c r="AI52" s="12" t="n"/>
+      <c r="AJ52" s="14" t="n"/>
+      <c r="AK52" s="15">
         <f>IF(TODAY()&lt;AD52, 0, IF(TODAY()&gt;AE52, AF52, AF52 * (TODAY()-AD52)/(AE52-AD52+1)))</f>
         <v/>
       </c>
-      <c r="AL52" s="5">
+      <c r="AL52" s="15">
         <f>AF52 * (AJ52/100)</f>
         <v/>
       </c>
-      <c r="AM52" s="5">
+      <c r="AM52" s="16">
         <f>AI52</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="L53" s="4" t="n"/>
-      <c r="M53" s="5">
+      <c r="A53" s="11" t="n"/>
+      <c r="B53" s="12" t="n"/>
+      <c r="C53" s="13" t="n"/>
+      <c r="D53" s="12" t="n"/>
+      <c r="E53" s="12" t="n"/>
+      <c r="F53" s="12" t="n"/>
+      <c r="G53" s="12" t="n"/>
+      <c r="H53" s="12" t="n"/>
+      <c r="I53" s="12" t="n"/>
+      <c r="J53" s="12" t="n"/>
+      <c r="K53" s="12" t="n"/>
+      <c r="L53" s="14" t="n"/>
+      <c r="M53" s="15">
         <f>IF(TODAY()&lt;F53, 0, IF(TODAY()&gt;G53, H53, H53 * (TODAY()-F53)/(G53-F53+1)))</f>
         <v/>
       </c>
-      <c r="N53" s="5">
+      <c r="N53" s="15">
         <f>H53 * (L53/100)</f>
         <v/>
       </c>
-      <c r="O53" s="5">
+      <c r="O53" s="16">
         <f>K53</f>
         <v/>
       </c>
-      <c r="X53" s="4" t="n"/>
-      <c r="Y53" s="5">
+      <c r="P53" s="12" t="n"/>
+      <c r="Q53" s="12" t="n"/>
+      <c r="R53" s="12" t="n"/>
+      <c r="S53" s="12" t="n"/>
+      <c r="T53" s="12" t="n"/>
+      <c r="U53" s="12" t="n"/>
+      <c r="V53" s="12" t="n"/>
+      <c r="W53" s="12" t="n"/>
+      <c r="X53" s="14" t="n"/>
+      <c r="Y53" s="15">
         <f>IF(TODAY()&lt;R53, 0, IF(TODAY()&gt;S53, T53, T53 * (TODAY()-R53)/(S53-R53+1)))</f>
         <v/>
       </c>
-      <c r="Z53" s="5">
+      <c r="Z53" s="15">
         <f>T53 * (X53/100)</f>
         <v/>
       </c>
-      <c r="AA53" s="5">
+      <c r="AA53" s="16">
         <f>W53</f>
         <v/>
       </c>
-      <c r="AJ53" s="4" t="n"/>
-      <c r="AK53" s="5">
+      <c r="AB53" s="12" t="n"/>
+      <c r="AC53" s="12" t="n"/>
+      <c r="AD53" s="12" t="n"/>
+      <c r="AE53" s="12" t="n"/>
+      <c r="AF53" s="12" t="n"/>
+      <c r="AG53" s="12" t="n"/>
+      <c r="AH53" s="12" t="n"/>
+      <c r="AI53" s="12" t="n"/>
+      <c r="AJ53" s="14" t="n"/>
+      <c r="AK53" s="15">
         <f>IF(TODAY()&lt;AD53, 0, IF(TODAY()&gt;AE53, AF53, AF53 * (TODAY()-AD53)/(AE53-AD53+1)))</f>
         <v/>
       </c>
-      <c r="AL53" s="5">
+      <c r="AL53" s="15">
         <f>AF53 * (AJ53/100)</f>
         <v/>
       </c>
-      <c r="AM53" s="5">
+      <c r="AM53" s="16">
         <f>AI53</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="L54" s="4" t="n"/>
-      <c r="M54" s="5">
+      <c r="A54" s="11" t="n"/>
+      <c r="B54" s="12" t="n"/>
+      <c r="C54" s="13" t="n"/>
+      <c r="D54" s="12" t="n"/>
+      <c r="E54" s="12" t="n"/>
+      <c r="F54" s="12" t="n"/>
+      <c r="G54" s="12" t="n"/>
+      <c r="H54" s="12" t="n"/>
+      <c r="I54" s="12" t="n"/>
+      <c r="J54" s="12" t="n"/>
+      <c r="K54" s="12" t="n"/>
+      <c r="L54" s="14" t="n"/>
+      <c r="M54" s="15">
         <f>IF(TODAY()&lt;F54, 0, IF(TODAY()&gt;G54, H54, H54 * (TODAY()-F54)/(G54-F54+1)))</f>
         <v/>
       </c>
-      <c r="N54" s="5">
+      <c r="N54" s="15">
         <f>H54 * (L54/100)</f>
         <v/>
       </c>
-      <c r="O54" s="5">
+      <c r="O54" s="16">
         <f>K54</f>
         <v/>
       </c>
-      <c r="X54" s="4" t="n"/>
-      <c r="Y54" s="5">
+      <c r="P54" s="12" t="n"/>
+      <c r="Q54" s="12" t="n"/>
+      <c r="R54" s="12" t="n"/>
+      <c r="S54" s="12" t="n"/>
+      <c r="T54" s="12" t="n"/>
+      <c r="U54" s="12" t="n"/>
+      <c r="V54" s="12" t="n"/>
+      <c r="W54" s="12" t="n"/>
+      <c r="X54" s="14" t="n"/>
+      <c r="Y54" s="15">
         <f>IF(TODAY()&lt;R54, 0, IF(TODAY()&gt;S54, T54, T54 * (TODAY()-R54)/(S54-R54+1)))</f>
         <v/>
       </c>
-      <c r="Z54" s="5">
+      <c r="Z54" s="15">
         <f>T54 * (X54/100)</f>
         <v/>
       </c>
-      <c r="AA54" s="5">
+      <c r="AA54" s="16">
         <f>W54</f>
         <v/>
       </c>
-      <c r="AJ54" s="4" t="n"/>
-      <c r="AK54" s="5">
+      <c r="AB54" s="12" t="n"/>
+      <c r="AC54" s="12" t="n"/>
+      <c r="AD54" s="12" t="n"/>
+      <c r="AE54" s="12" t="n"/>
+      <c r="AF54" s="12" t="n"/>
+      <c r="AG54" s="12" t="n"/>
+      <c r="AH54" s="12" t="n"/>
+      <c r="AI54" s="12" t="n"/>
+      <c r="AJ54" s="14" t="n"/>
+      <c r="AK54" s="15">
         <f>IF(TODAY()&lt;AD54, 0, IF(TODAY()&gt;AE54, AF54, AF54 * (TODAY()-AD54)/(AE54-AD54+1)))</f>
         <v/>
       </c>
-      <c r="AL54" s="5">
+      <c r="AL54" s="15">
         <f>AF54 * (AJ54/100)</f>
         <v/>
       </c>
-      <c r="AM54" s="5">
+      <c r="AM54" s="16">
         <f>AI54</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="L55" s="4" t="n"/>
-      <c r="M55" s="5">
+      <c r="A55" s="11" t="n"/>
+      <c r="B55" s="12" t="n"/>
+      <c r="C55" s="13" t="n"/>
+      <c r="D55" s="12" t="n"/>
+      <c r="E55" s="12" t="n"/>
+      <c r="F55" s="12" t="n"/>
+      <c r="G55" s="12" t="n"/>
+      <c r="H55" s="12" t="n"/>
+      <c r="I55" s="12" t="n"/>
+      <c r="J55" s="12" t="n"/>
+      <c r="K55" s="12" t="n"/>
+      <c r="L55" s="14" t="n"/>
+      <c r="M55" s="15">
         <f>IF(TODAY()&lt;F55, 0, IF(TODAY()&gt;G55, H55, H55 * (TODAY()-F55)/(G55-F55+1)))</f>
         <v/>
       </c>
-      <c r="N55" s="5">
+      <c r="N55" s="15">
         <f>H55 * (L55/100)</f>
         <v/>
       </c>
-      <c r="O55" s="5">
+      <c r="O55" s="16">
         <f>K55</f>
         <v/>
       </c>
-      <c r="X55" s="4" t="n"/>
-      <c r="Y55" s="5">
+      <c r="P55" s="12" t="n"/>
+      <c r="Q55" s="12" t="n"/>
+      <c r="R55" s="12" t="n"/>
+      <c r="S55" s="12" t="n"/>
+      <c r="T55" s="12" t="n"/>
+      <c r="U55" s="12" t="n"/>
+      <c r="V55" s="12" t="n"/>
+      <c r="W55" s="12" t="n"/>
+      <c r="X55" s="14" t="n"/>
+      <c r="Y55" s="15">
         <f>IF(TODAY()&lt;R55, 0, IF(TODAY()&gt;S55, T55, T55 * (TODAY()-R55)/(S55-R55+1)))</f>
         <v/>
       </c>
-      <c r="Z55" s="5">
+      <c r="Z55" s="15">
         <f>T55 * (X55/100)</f>
         <v/>
       </c>
-      <c r="AA55" s="5">
+      <c r="AA55" s="16">
         <f>W55</f>
         <v/>
       </c>
-      <c r="AJ55" s="4" t="n"/>
-      <c r="AK55" s="5">
+      <c r="AB55" s="12" t="n"/>
+      <c r="AC55" s="12" t="n"/>
+      <c r="AD55" s="12" t="n"/>
+      <c r="AE55" s="12" t="n"/>
+      <c r="AF55" s="12" t="n"/>
+      <c r="AG55" s="12" t="n"/>
+      <c r="AH55" s="12" t="n"/>
+      <c r="AI55" s="12" t="n"/>
+      <c r="AJ55" s="14" t="n"/>
+      <c r="AK55" s="15">
         <f>IF(TODAY()&lt;AD55, 0, IF(TODAY()&gt;AE55, AF55, AF55 * (TODAY()-AD55)/(AE55-AD55+1)))</f>
         <v/>
       </c>
-      <c r="AL55" s="5">
+      <c r="AL55" s="15">
         <f>AF55 * (AJ55/100)</f>
         <v/>
       </c>
-      <c r="AM55" s="5">
+      <c r="AM55" s="16">
         <f>AI55</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="L56" s="4" t="n"/>
-      <c r="M56" s="5">
+      <c r="A56" s="11" t="n"/>
+      <c r="B56" s="12" t="n"/>
+      <c r="C56" s="13" t="n"/>
+      <c r="D56" s="12" t="n"/>
+      <c r="E56" s="12" t="n"/>
+      <c r="F56" s="12" t="n"/>
+      <c r="G56" s="12" t="n"/>
+      <c r="H56" s="12" t="n"/>
+      <c r="I56" s="12" t="n"/>
+      <c r="J56" s="12" t="n"/>
+      <c r="K56" s="12" t="n"/>
+      <c r="L56" s="14" t="n"/>
+      <c r="M56" s="15">
         <f>IF(TODAY()&lt;F56, 0, IF(TODAY()&gt;G56, H56, H56 * (TODAY()-F56)/(G56-F56+1)))</f>
         <v/>
       </c>
-      <c r="N56" s="5">
+      <c r="N56" s="15">
         <f>H56 * (L56/100)</f>
         <v/>
       </c>
-      <c r="O56" s="5">
+      <c r="O56" s="16">
         <f>K56</f>
         <v/>
       </c>
-      <c r="X56" s="4" t="n"/>
-      <c r="Y56" s="5">
+      <c r="P56" s="12" t="n"/>
+      <c r="Q56" s="12" t="n"/>
+      <c r="R56" s="12" t="n"/>
+      <c r="S56" s="12" t="n"/>
+      <c r="T56" s="12" t="n"/>
+      <c r="U56" s="12" t="n"/>
+      <c r="V56" s="12" t="n"/>
+      <c r="W56" s="12" t="n"/>
+      <c r="X56" s="14" t="n"/>
+      <c r="Y56" s="15">
         <f>IF(TODAY()&lt;R56, 0, IF(TODAY()&gt;S56, T56, T56 * (TODAY()-R56)/(S56-R56+1)))</f>
         <v/>
       </c>
-      <c r="Z56" s="5">
+      <c r="Z56" s="15">
         <f>T56 * (X56/100)</f>
         <v/>
       </c>
-      <c r="AA56" s="5">
+      <c r="AA56" s="16">
         <f>W56</f>
         <v/>
       </c>
-      <c r="AJ56" s="4" t="n"/>
-      <c r="AK56" s="5">
+      <c r="AB56" s="12" t="n"/>
+      <c r="AC56" s="12" t="n"/>
+      <c r="AD56" s="12" t="n"/>
+      <c r="AE56" s="12" t="n"/>
+      <c r="AF56" s="12" t="n"/>
+      <c r="AG56" s="12" t="n"/>
+      <c r="AH56" s="12" t="n"/>
+      <c r="AI56" s="12" t="n"/>
+      <c r="AJ56" s="14" t="n"/>
+      <c r="AK56" s="15">
         <f>IF(TODAY()&lt;AD56, 0, IF(TODAY()&gt;AE56, AF56, AF56 * (TODAY()-AD56)/(AE56-AD56+1)))</f>
         <v/>
       </c>
-      <c r="AL56" s="5">
+      <c r="AL56" s="15">
         <f>AF56 * (AJ56/100)</f>
         <v/>
       </c>
-      <c r="AM56" s="5">
+      <c r="AM56" s="16">
         <f>AI56</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="L57" s="4" t="n"/>
-      <c r="M57" s="5">
+      <c r="A57" s="11" t="n"/>
+      <c r="B57" s="12" t="n"/>
+      <c r="C57" s="13" t="n"/>
+      <c r="D57" s="12" t="n"/>
+      <c r="E57" s="12" t="n"/>
+      <c r="F57" s="12" t="n"/>
+      <c r="G57" s="12" t="n"/>
+      <c r="H57" s="12" t="n"/>
+      <c r="I57" s="12" t="n"/>
+      <c r="J57" s="12" t="n"/>
+      <c r="K57" s="12" t="n"/>
+      <c r="L57" s="14" t="n"/>
+      <c r="M57" s="15">
         <f>IF(TODAY()&lt;F57, 0, IF(TODAY()&gt;G57, H57, H57 * (TODAY()-F57)/(G57-F57+1)))</f>
         <v/>
       </c>
-      <c r="N57" s="5">
+      <c r="N57" s="15">
         <f>H57 * (L57/100)</f>
         <v/>
       </c>
-      <c r="O57" s="5">
+      <c r="O57" s="16">
         <f>K57</f>
         <v/>
       </c>
-      <c r="X57" s="4" t="n"/>
-      <c r="Y57" s="5">
+      <c r="P57" s="12" t="n"/>
+      <c r="Q57" s="12" t="n"/>
+      <c r="R57" s="12" t="n"/>
+      <c r="S57" s="12" t="n"/>
+      <c r="T57" s="12" t="n"/>
+      <c r="U57" s="12" t="n"/>
+      <c r="V57" s="12" t="n"/>
+      <c r="W57" s="12" t="n"/>
+      <c r="X57" s="14" t="n"/>
+      <c r="Y57" s="15">
         <f>IF(TODAY()&lt;R57, 0, IF(TODAY()&gt;S57, T57, T57 * (TODAY()-R57)/(S57-R57+1)))</f>
         <v/>
       </c>
-      <c r="Z57" s="5">
+      <c r="Z57" s="15">
         <f>T57 * (X57/100)</f>
         <v/>
       </c>
-      <c r="AA57" s="5">
+      <c r="AA57" s="16">
         <f>W57</f>
         <v/>
       </c>
-      <c r="AJ57" s="4" t="n"/>
-      <c r="AK57" s="5">
+      <c r="AB57" s="12" t="n"/>
+      <c r="AC57" s="12" t="n"/>
+      <c r="AD57" s="12" t="n"/>
+      <c r="AE57" s="12" t="n"/>
+      <c r="AF57" s="12" t="n"/>
+      <c r="AG57" s="12" t="n"/>
+      <c r="AH57" s="12" t="n"/>
+      <c r="AI57" s="12" t="n"/>
+      <c r="AJ57" s="14" t="n"/>
+      <c r="AK57" s="15">
         <f>IF(TODAY()&lt;AD57, 0, IF(TODAY()&gt;AE57, AF57, AF57 * (TODAY()-AD57)/(AE57-AD57+1)))</f>
         <v/>
       </c>
-      <c r="AL57" s="5">
+      <c r="AL57" s="15">
         <f>AF57 * (AJ57/100)</f>
         <v/>
       </c>
-      <c r="AM57" s="5">
+      <c r="AM57" s="16">
         <f>AI57</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="L58" s="4" t="n"/>
-      <c r="M58" s="5">
+      <c r="A58" s="11" t="n"/>
+      <c r="B58" s="12" t="n"/>
+      <c r="C58" s="13" t="n"/>
+      <c r="D58" s="12" t="n"/>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="12" t="n"/>
+      <c r="G58" s="12" t="n"/>
+      <c r="H58" s="12" t="n"/>
+      <c r="I58" s="12" t="n"/>
+      <c r="J58" s="12" t="n"/>
+      <c r="K58" s="12" t="n"/>
+      <c r="L58" s="14" t="n"/>
+      <c r="M58" s="15">
         <f>IF(TODAY()&lt;F58, 0, IF(TODAY()&gt;G58, H58, H58 * (TODAY()-F58)/(G58-F58+1)))</f>
         <v/>
       </c>
-      <c r="N58" s="5">
+      <c r="N58" s="15">
         <f>H58 * (L58/100)</f>
         <v/>
       </c>
-      <c r="O58" s="5">
+      <c r="O58" s="16">
         <f>K58</f>
         <v/>
       </c>
-      <c r="X58" s="4" t="n"/>
-      <c r="Y58" s="5">
+      <c r="P58" s="12" t="n"/>
+      <c r="Q58" s="12" t="n"/>
+      <c r="R58" s="12" t="n"/>
+      <c r="S58" s="12" t="n"/>
+      <c r="T58" s="12" t="n"/>
+      <c r="U58" s="12" t="n"/>
+      <c r="V58" s="12" t="n"/>
+      <c r="W58" s="12" t="n"/>
+      <c r="X58" s="14" t="n"/>
+      <c r="Y58" s="15">
         <f>IF(TODAY()&lt;R58, 0, IF(TODAY()&gt;S58, T58, T58 * (TODAY()-R58)/(S58-R58+1)))</f>
         <v/>
       </c>
-      <c r="Z58" s="5">
+      <c r="Z58" s="15">
         <f>T58 * (X58/100)</f>
         <v/>
       </c>
-      <c r="AA58" s="5">
+      <c r="AA58" s="16">
         <f>W58</f>
         <v/>
       </c>
-      <c r="AJ58" s="4" t="n"/>
-      <c r="AK58" s="5">
+      <c r="AB58" s="12" t="n"/>
+      <c r="AC58" s="12" t="n"/>
+      <c r="AD58" s="12" t="n"/>
+      <c r="AE58" s="12" t="n"/>
+      <c r="AF58" s="12" t="n"/>
+      <c r="AG58" s="12" t="n"/>
+      <c r="AH58" s="12" t="n"/>
+      <c r="AI58" s="12" t="n"/>
+      <c r="AJ58" s="14" t="n"/>
+      <c r="AK58" s="15">
         <f>IF(TODAY()&lt;AD58, 0, IF(TODAY()&gt;AE58, AF58, AF58 * (TODAY()-AD58)/(AE58-AD58+1)))</f>
         <v/>
       </c>
-      <c r="AL58" s="5">
+      <c r="AL58" s="15">
         <f>AF58 * (AJ58/100)</f>
         <v/>
       </c>
-      <c r="AM58" s="5">
+      <c r="AM58" s="16">
         <f>AI58</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="L59" s="4" t="n"/>
-      <c r="M59" s="5">
+      <c r="A59" s="11" t="n"/>
+      <c r="B59" s="12" t="n"/>
+      <c r="C59" s="13" t="n"/>
+      <c r="D59" s="12" t="n"/>
+      <c r="E59" s="12" t="n"/>
+      <c r="F59" s="12" t="n"/>
+      <c r="G59" s="12" t="n"/>
+      <c r="H59" s="12" t="n"/>
+      <c r="I59" s="12" t="n"/>
+      <c r="J59" s="12" t="n"/>
+      <c r="K59" s="12" t="n"/>
+      <c r="L59" s="14" t="n"/>
+      <c r="M59" s="15">
         <f>IF(TODAY()&lt;F59, 0, IF(TODAY()&gt;G59, H59, H59 * (TODAY()-F59)/(G59-F59+1)))</f>
         <v/>
       </c>
-      <c r="N59" s="5">
+      <c r="N59" s="15">
         <f>H59 * (L59/100)</f>
         <v/>
       </c>
-      <c r="O59" s="5">
+      <c r="O59" s="16">
         <f>K59</f>
         <v/>
       </c>
-      <c r="X59" s="4" t="n"/>
-      <c r="Y59" s="5">
+      <c r="P59" s="12" t="n"/>
+      <c r="Q59" s="12" t="n"/>
+      <c r="R59" s="12" t="n"/>
+      <c r="S59" s="12" t="n"/>
+      <c r="T59" s="12" t="n"/>
+      <c r="U59" s="12" t="n"/>
+      <c r="V59" s="12" t="n"/>
+      <c r="W59" s="12" t="n"/>
+      <c r="X59" s="14" t="n"/>
+      <c r="Y59" s="15">
         <f>IF(TODAY()&lt;R59, 0, IF(TODAY()&gt;S59, T59, T59 * (TODAY()-R59)/(S59-R59+1)))</f>
         <v/>
       </c>
-      <c r="Z59" s="5">
+      <c r="Z59" s="15">
         <f>T59 * (X59/100)</f>
         <v/>
       </c>
-      <c r="AA59" s="5">
+      <c r="AA59" s="16">
         <f>W59</f>
         <v/>
       </c>
-      <c r="AJ59" s="4" t="n"/>
-      <c r="AK59" s="5">
+      <c r="AB59" s="12" t="n"/>
+      <c r="AC59" s="12" t="n"/>
+      <c r="AD59" s="12" t="n"/>
+      <c r="AE59" s="12" t="n"/>
+      <c r="AF59" s="12" t="n"/>
+      <c r="AG59" s="12" t="n"/>
+      <c r="AH59" s="12" t="n"/>
+      <c r="AI59" s="12" t="n"/>
+      <c r="AJ59" s="14" t="n"/>
+      <c r="AK59" s="15">
         <f>IF(TODAY()&lt;AD59, 0, IF(TODAY()&gt;AE59, AF59, AF59 * (TODAY()-AD59)/(AE59-AD59+1)))</f>
         <v/>
       </c>
-      <c r="AL59" s="5">
+      <c r="AL59" s="15">
         <f>AF59 * (AJ59/100)</f>
         <v/>
       </c>
-      <c r="AM59" s="5">
+      <c r="AM59" s="16">
         <f>AI59</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="L60" s="4" t="n"/>
-      <c r="M60" s="5">
+      <c r="A60" s="11" t="n"/>
+      <c r="B60" s="12" t="n"/>
+      <c r="C60" s="13" t="n"/>
+      <c r="D60" s="12" t="n"/>
+      <c r="E60" s="12" t="n"/>
+      <c r="F60" s="12" t="n"/>
+      <c r="G60" s="12" t="n"/>
+      <c r="H60" s="12" t="n"/>
+      <c r="I60" s="12" t="n"/>
+      <c r="J60" s="12" t="n"/>
+      <c r="K60" s="12" t="n"/>
+      <c r="L60" s="14" t="n"/>
+      <c r="M60" s="15">
         <f>IF(TODAY()&lt;F60, 0, IF(TODAY()&gt;G60, H60, H60 * (TODAY()-F60)/(G60-F60+1)))</f>
         <v/>
       </c>
-      <c r="N60" s="5">
+      <c r="N60" s="15">
         <f>H60 * (L60/100)</f>
         <v/>
       </c>
-      <c r="O60" s="5">
+      <c r="O60" s="16">
         <f>K60</f>
         <v/>
       </c>
-      <c r="X60" s="4" t="n"/>
-      <c r="Y60" s="5">
+      <c r="P60" s="12" t="n"/>
+      <c r="Q60" s="12" t="n"/>
+      <c r="R60" s="12" t="n"/>
+      <c r="S60" s="12" t="n"/>
+      <c r="T60" s="12" t="n"/>
+      <c r="U60" s="12" t="n"/>
+      <c r="V60" s="12" t="n"/>
+      <c r="W60" s="12" t="n"/>
+      <c r="X60" s="14" t="n"/>
+      <c r="Y60" s="15">
         <f>IF(TODAY()&lt;R60, 0, IF(TODAY()&gt;S60, T60, T60 * (TODAY()-R60)/(S60-R60+1)))</f>
         <v/>
       </c>
-      <c r="Z60" s="5">
+      <c r="Z60" s="15">
         <f>T60 * (X60/100)</f>
         <v/>
       </c>
-      <c r="AA60" s="5">
+      <c r="AA60" s="16">
         <f>W60</f>
         <v/>
       </c>
-      <c r="AJ60" s="4" t="n"/>
-      <c r="AK60" s="5">
+      <c r="AB60" s="12" t="n"/>
+      <c r="AC60" s="12" t="n"/>
+      <c r="AD60" s="12" t="n"/>
+      <c r="AE60" s="12" t="n"/>
+      <c r="AF60" s="12" t="n"/>
+      <c r="AG60" s="12" t="n"/>
+      <c r="AH60" s="12" t="n"/>
+      <c r="AI60" s="12" t="n"/>
+      <c r="AJ60" s="14" t="n"/>
+      <c r="AK60" s="15">
         <f>IF(TODAY()&lt;AD60, 0, IF(TODAY()&gt;AE60, AF60, AF60 * (TODAY()-AD60)/(AE60-AD60+1)))</f>
         <v/>
       </c>
-      <c r="AL60" s="5">
+      <c r="AL60" s="15">
         <f>AF60 * (AJ60/100)</f>
         <v/>
       </c>
-      <c r="AM60" s="5">
+      <c r="AM60" s="16">
         <f>AI60</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="L61" s="4" t="n"/>
-      <c r="M61" s="5">
+      <c r="A61" s="11" t="n"/>
+      <c r="B61" s="12" t="n"/>
+      <c r="C61" s="13" t="n"/>
+      <c r="D61" s="12" t="n"/>
+      <c r="E61" s="12" t="n"/>
+      <c r="F61" s="12" t="n"/>
+      <c r="G61" s="12" t="n"/>
+      <c r="H61" s="12" t="n"/>
+      <c r="I61" s="12" t="n"/>
+      <c r="J61" s="12" t="n"/>
+      <c r="K61" s="12" t="n"/>
+      <c r="L61" s="14" t="n"/>
+      <c r="M61" s="15">
         <f>IF(TODAY()&lt;F61, 0, IF(TODAY()&gt;G61, H61, H61 * (TODAY()-F61)/(G61-F61+1)))</f>
         <v/>
       </c>
-      <c r="N61" s="5">
+      <c r="N61" s="15">
         <f>H61 * (L61/100)</f>
         <v/>
       </c>
-      <c r="O61" s="5">
+      <c r="O61" s="16">
         <f>K61</f>
         <v/>
       </c>
-      <c r="X61" s="4" t="n"/>
-      <c r="Y61" s="5">
+      <c r="P61" s="12" t="n"/>
+      <c r="Q61" s="12" t="n"/>
+      <c r="R61" s="12" t="n"/>
+      <c r="S61" s="12" t="n"/>
+      <c r="T61" s="12" t="n"/>
+      <c r="U61" s="12" t="n"/>
+      <c r="V61" s="12" t="n"/>
+      <c r="W61" s="12" t="n"/>
+      <c r="X61" s="14" t="n"/>
+      <c r="Y61" s="15">
         <f>IF(TODAY()&lt;R61, 0, IF(TODAY()&gt;S61, T61, T61 * (TODAY()-R61)/(S61-R61+1)))</f>
         <v/>
       </c>
-      <c r="Z61" s="5">
+      <c r="Z61" s="15">
         <f>T61 * (X61/100)</f>
         <v/>
       </c>
-      <c r="AA61" s="5">
+      <c r="AA61" s="16">
         <f>W61</f>
         <v/>
       </c>
-      <c r="AJ61" s="4" t="n"/>
-      <c r="AK61" s="5">
+      <c r="AB61" s="12" t="n"/>
+      <c r="AC61" s="12" t="n"/>
+      <c r="AD61" s="12" t="n"/>
+      <c r="AE61" s="12" t="n"/>
+      <c r="AF61" s="12" t="n"/>
+      <c r="AG61" s="12" t="n"/>
+      <c r="AH61" s="12" t="n"/>
+      <c r="AI61" s="12" t="n"/>
+      <c r="AJ61" s="14" t="n"/>
+      <c r="AK61" s="15">
         <f>IF(TODAY()&lt;AD61, 0, IF(TODAY()&gt;AE61, AF61, AF61 * (TODAY()-AD61)/(AE61-AD61+1)))</f>
         <v/>
       </c>
-      <c r="AL61" s="5">
+      <c r="AL61" s="15">
         <f>AF61 * (AJ61/100)</f>
         <v/>
       </c>
-      <c r="AM61" s="5">
+      <c r="AM61" s="16">
         <f>AI61</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="L62" s="4" t="n"/>
-      <c r="M62" s="5">
+      <c r="A62" s="11" t="n"/>
+      <c r="B62" s="12" t="n"/>
+      <c r="C62" s="13" t="n"/>
+      <c r="D62" s="12" t="n"/>
+      <c r="E62" s="12" t="n"/>
+      <c r="F62" s="12" t="n"/>
+      <c r="G62" s="12" t="n"/>
+      <c r="H62" s="12" t="n"/>
+      <c r="I62" s="12" t="n"/>
+      <c r="J62" s="12" t="n"/>
+      <c r="K62" s="12" t="n"/>
+      <c r="L62" s="14" t="n"/>
+      <c r="M62" s="15">
         <f>IF(TODAY()&lt;F62, 0, IF(TODAY()&gt;G62, H62, H62 * (TODAY()-F62)/(G62-F62+1)))</f>
         <v/>
       </c>
-      <c r="N62" s="5">
+      <c r="N62" s="15">
         <f>H62 * (L62/100)</f>
         <v/>
       </c>
-      <c r="O62" s="5">
+      <c r="O62" s="16">
         <f>K62</f>
         <v/>
       </c>
-      <c r="X62" s="4" t="n"/>
-      <c r="Y62" s="5">
+      <c r="P62" s="12" t="n"/>
+      <c r="Q62" s="12" t="n"/>
+      <c r="R62" s="12" t="n"/>
+      <c r="S62" s="12" t="n"/>
+      <c r="T62" s="12" t="n"/>
+      <c r="U62" s="12" t="n"/>
+      <c r="V62" s="12" t="n"/>
+      <c r="W62" s="12" t="n"/>
+      <c r="X62" s="14" t="n"/>
+      <c r="Y62" s="15">
         <f>IF(TODAY()&lt;R62, 0, IF(TODAY()&gt;S62, T62, T62 * (TODAY()-R62)/(S62-R62+1)))</f>
         <v/>
       </c>
-      <c r="Z62" s="5">
+      <c r="Z62" s="15">
         <f>T62 * (X62/100)</f>
         <v/>
       </c>
-      <c r="AA62" s="5">
+      <c r="AA62" s="16">
         <f>W62</f>
         <v/>
       </c>
-      <c r="AJ62" s="4" t="n"/>
-      <c r="AK62" s="5">
+      <c r="AB62" s="12" t="n"/>
+      <c r="AC62" s="12" t="n"/>
+      <c r="AD62" s="12" t="n"/>
+      <c r="AE62" s="12" t="n"/>
+      <c r="AF62" s="12" t="n"/>
+      <c r="AG62" s="12" t="n"/>
+      <c r="AH62" s="12" t="n"/>
+      <c r="AI62" s="12" t="n"/>
+      <c r="AJ62" s="14" t="n"/>
+      <c r="AK62" s="15">
         <f>IF(TODAY()&lt;AD62, 0, IF(TODAY()&gt;AE62, AF62, AF62 * (TODAY()-AD62)/(AE62-AD62+1)))</f>
         <v/>
       </c>
-      <c r="AL62" s="5">
+      <c r="AL62" s="15">
         <f>AF62 * (AJ62/100)</f>
         <v/>
       </c>
-      <c r="AM62" s="5">
+      <c r="AM62" s="16">
         <f>AI62</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="L63" s="4" t="n"/>
-      <c r="M63" s="5">
+      <c r="A63" s="11" t="n"/>
+      <c r="B63" s="12" t="n"/>
+      <c r="C63" s="13" t="n"/>
+      <c r="D63" s="12" t="n"/>
+      <c r="E63" s="12" t="n"/>
+      <c r="F63" s="12" t="n"/>
+      <c r="G63" s="12" t="n"/>
+      <c r="H63" s="12" t="n"/>
+      <c r="I63" s="12" t="n"/>
+      <c r="J63" s="12" t="n"/>
+      <c r="K63" s="12" t="n"/>
+      <c r="L63" s="14" t="n"/>
+      <c r="M63" s="15">
         <f>IF(TODAY()&lt;F63, 0, IF(TODAY()&gt;G63, H63, H63 * (TODAY()-F63)/(G63-F63+1)))</f>
         <v/>
       </c>
-      <c r="N63" s="5">
+      <c r="N63" s="15">
         <f>H63 * (L63/100)</f>
         <v/>
       </c>
-      <c r="O63" s="5">
+      <c r="O63" s="16">
         <f>K63</f>
         <v/>
       </c>
-      <c r="X63" s="4" t="n"/>
-      <c r="Y63" s="5">
+      <c r="P63" s="12" t="n"/>
+      <c r="Q63" s="12" t="n"/>
+      <c r="R63" s="12" t="n"/>
+      <c r="S63" s="12" t="n"/>
+      <c r="T63" s="12" t="n"/>
+      <c r="U63" s="12" t="n"/>
+      <c r="V63" s="12" t="n"/>
+      <c r="W63" s="12" t="n"/>
+      <c r="X63" s="14" t="n"/>
+      <c r="Y63" s="15">
         <f>IF(TODAY()&lt;R63, 0, IF(TODAY()&gt;S63, T63, T63 * (TODAY()-R63)/(S63-R63+1)))</f>
         <v/>
       </c>
-      <c r="Z63" s="5">
+      <c r="Z63" s="15">
         <f>T63 * (X63/100)</f>
         <v/>
       </c>
-      <c r="AA63" s="5">
+      <c r="AA63" s="16">
         <f>W63</f>
         <v/>
       </c>
-      <c r="AJ63" s="4" t="n"/>
-      <c r="AK63" s="5">
+      <c r="AB63" s="12" t="n"/>
+      <c r="AC63" s="12" t="n"/>
+      <c r="AD63" s="12" t="n"/>
+      <c r="AE63" s="12" t="n"/>
+      <c r="AF63" s="12" t="n"/>
+      <c r="AG63" s="12" t="n"/>
+      <c r="AH63" s="12" t="n"/>
+      <c r="AI63" s="12" t="n"/>
+      <c r="AJ63" s="14" t="n"/>
+      <c r="AK63" s="15">
         <f>IF(TODAY()&lt;AD63, 0, IF(TODAY()&gt;AE63, AF63, AF63 * (TODAY()-AD63)/(AE63-AD63+1)))</f>
         <v/>
       </c>
-      <c r="AL63" s="5">
+      <c r="AL63" s="15">
         <f>AF63 * (AJ63/100)</f>
         <v/>
       </c>
-      <c r="AM63" s="5">
+      <c r="AM63" s="16">
         <f>AI63</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="L64" s="4" t="n"/>
-      <c r="M64" s="5">
+      <c r="A64" s="11" t="n"/>
+      <c r="B64" s="12" t="n"/>
+      <c r="C64" s="13" t="n"/>
+      <c r="D64" s="12" t="n"/>
+      <c r="E64" s="12" t="n"/>
+      <c r="F64" s="12" t="n"/>
+      <c r="G64" s="12" t="n"/>
+      <c r="H64" s="12" t="n"/>
+      <c r="I64" s="12" t="n"/>
+      <c r="J64" s="12" t="n"/>
+      <c r="K64" s="12" t="n"/>
+      <c r="L64" s="14" t="n"/>
+      <c r="M64" s="15">
         <f>IF(TODAY()&lt;F64, 0, IF(TODAY()&gt;G64, H64, H64 * (TODAY()-F64)/(G64-F64+1)))</f>
         <v/>
       </c>
-      <c r="N64" s="5">
+      <c r="N64" s="15">
         <f>H64 * (L64/100)</f>
         <v/>
       </c>
-      <c r="O64" s="5">
+      <c r="O64" s="16">
         <f>K64</f>
         <v/>
       </c>
-      <c r="X64" s="4" t="n"/>
-      <c r="Y64" s="5">
+      <c r="P64" s="12" t="n"/>
+      <c r="Q64" s="12" t="n"/>
+      <c r="R64" s="12" t="n"/>
+      <c r="S64" s="12" t="n"/>
+      <c r="T64" s="12" t="n"/>
+      <c r="U64" s="12" t="n"/>
+      <c r="V64" s="12" t="n"/>
+      <c r="W64" s="12" t="n"/>
+      <c r="X64" s="14" t="n"/>
+      <c r="Y64" s="15">
         <f>IF(TODAY()&lt;R64, 0, IF(TODAY()&gt;S64, T64, T64 * (TODAY()-R64)/(S64-R64+1)))</f>
         <v/>
       </c>
-      <c r="Z64" s="5">
+      <c r="Z64" s="15">
         <f>T64 * (X64/100)</f>
         <v/>
       </c>
-      <c r="AA64" s="5">
+      <c r="AA64" s="16">
         <f>W64</f>
         <v/>
       </c>
-      <c r="AJ64" s="4" t="n"/>
-      <c r="AK64" s="5">
+      <c r="AB64" s="12" t="n"/>
+      <c r="AC64" s="12" t="n"/>
+      <c r="AD64" s="12" t="n"/>
+      <c r="AE64" s="12" t="n"/>
+      <c r="AF64" s="12" t="n"/>
+      <c r="AG64" s="12" t="n"/>
+      <c r="AH64" s="12" t="n"/>
+      <c r="AI64" s="12" t="n"/>
+      <c r="AJ64" s="14" t="n"/>
+      <c r="AK64" s="15">
         <f>IF(TODAY()&lt;AD64, 0, IF(TODAY()&gt;AE64, AF64, AF64 * (TODAY()-AD64)/(AE64-AD64+1)))</f>
         <v/>
       </c>
-      <c r="AL64" s="5">
+      <c r="AL64" s="15">
         <f>AF64 * (AJ64/100)</f>
         <v/>
       </c>
-      <c r="AM64" s="5">
+      <c r="AM64" s="16">
         <f>AI64</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="L65" s="4" t="n"/>
-      <c r="M65" s="5">
+      <c r="A65" s="11" t="n"/>
+      <c r="B65" s="12" t="n"/>
+      <c r="C65" s="13" t="n"/>
+      <c r="D65" s="12" t="n"/>
+      <c r="E65" s="12" t="n"/>
+      <c r="F65" s="12" t="n"/>
+      <c r="G65" s="12" t="n"/>
+      <c r="H65" s="12" t="n"/>
+      <c r="I65" s="12" t="n"/>
+      <c r="J65" s="12" t="n"/>
+      <c r="K65" s="12" t="n"/>
+      <c r="L65" s="14" t="n"/>
+      <c r="M65" s="15">
         <f>IF(TODAY()&lt;F65, 0, IF(TODAY()&gt;G65, H65, H65 * (TODAY()-F65)/(G65-F65+1)))</f>
         <v/>
       </c>
-      <c r="N65" s="5">
+      <c r="N65" s="15">
         <f>H65 * (L65/100)</f>
         <v/>
       </c>
-      <c r="O65" s="5">
+      <c r="O65" s="16">
         <f>K65</f>
         <v/>
       </c>
-      <c r="X65" s="4" t="n"/>
-      <c r="Y65" s="5">
+      <c r="P65" s="12" t="n"/>
+      <c r="Q65" s="12" t="n"/>
+      <c r="R65" s="12" t="n"/>
+      <c r="S65" s="12" t="n"/>
+      <c r="T65" s="12" t="n"/>
+      <c r="U65" s="12" t="n"/>
+      <c r="V65" s="12" t="n"/>
+      <c r="W65" s="12" t="n"/>
+      <c r="X65" s="14" t="n"/>
+      <c r="Y65" s="15">
         <f>IF(TODAY()&lt;R65, 0, IF(TODAY()&gt;S65, T65, T65 * (TODAY()-R65)/(S65-R65+1)))</f>
         <v/>
       </c>
-      <c r="Z65" s="5">
+      <c r="Z65" s="15">
         <f>T65 * (X65/100)</f>
         <v/>
       </c>
-      <c r="AA65" s="5">
+      <c r="AA65" s="16">
         <f>W65</f>
         <v/>
       </c>
-      <c r="AJ65" s="4" t="n"/>
-      <c r="AK65" s="5">
+      <c r="AB65" s="12" t="n"/>
+      <c r="AC65" s="12" t="n"/>
+      <c r="AD65" s="12" t="n"/>
+      <c r="AE65" s="12" t="n"/>
+      <c r="AF65" s="12" t="n"/>
+      <c r="AG65" s="12" t="n"/>
+      <c r="AH65" s="12" t="n"/>
+      <c r="AI65" s="12" t="n"/>
+      <c r="AJ65" s="14" t="n"/>
+      <c r="AK65" s="15">
         <f>IF(TODAY()&lt;AD65, 0, IF(TODAY()&gt;AE65, AF65, AF65 * (TODAY()-AD65)/(AE65-AD65+1)))</f>
         <v/>
       </c>
-      <c r="AL65" s="5">
+      <c r="AL65" s="15">
         <f>AF65 * (AJ65/100)</f>
         <v/>
       </c>
-      <c r="AM65" s="5">
+      <c r="AM65" s="16">
         <f>AI65</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="L66" s="4" t="n"/>
-      <c r="M66" s="5">
+      <c r="A66" s="11" t="n"/>
+      <c r="B66" s="12" t="n"/>
+      <c r="C66" s="13" t="n"/>
+      <c r="D66" s="12" t="n"/>
+      <c r="E66" s="12" t="n"/>
+      <c r="F66" s="12" t="n"/>
+      <c r="G66" s="12" t="n"/>
+      <c r="H66" s="12" t="n"/>
+      <c r="I66" s="12" t="n"/>
+      <c r="J66" s="12" t="n"/>
+      <c r="K66" s="12" t="n"/>
+      <c r="L66" s="14" t="n"/>
+      <c r="M66" s="15">
         <f>IF(TODAY()&lt;F66, 0, IF(TODAY()&gt;G66, H66, H66 * (TODAY()-F66)/(G66-F66+1)))</f>
         <v/>
       </c>
-      <c r="N66" s="5">
+      <c r="N66" s="15">
         <f>H66 * (L66/100)</f>
         <v/>
       </c>
-      <c r="O66" s="5">
+      <c r="O66" s="16">
         <f>K66</f>
         <v/>
       </c>
-      <c r="X66" s="4" t="n"/>
-      <c r="Y66" s="5">
+      <c r="P66" s="12" t="n"/>
+      <c r="Q66" s="12" t="n"/>
+      <c r="R66" s="12" t="n"/>
+      <c r="S66" s="12" t="n"/>
+      <c r="T66" s="12" t="n"/>
+      <c r="U66" s="12" t="n"/>
+      <c r="V66" s="12" t="n"/>
+      <c r="W66" s="12" t="n"/>
+      <c r="X66" s="14" t="n"/>
+      <c r="Y66" s="15">
         <f>IF(TODAY()&lt;R66, 0, IF(TODAY()&gt;S66, T66, T66 * (TODAY()-R66)/(S66-R66+1)))</f>
         <v/>
       </c>
-      <c r="Z66" s="5">
+      <c r="Z66" s="15">
         <f>T66 * (X66/100)</f>
         <v/>
       </c>
-      <c r="AA66" s="5">
+      <c r="AA66" s="16">
         <f>W66</f>
         <v/>
       </c>
-      <c r="AJ66" s="4" t="n"/>
-      <c r="AK66" s="5">
+      <c r="AB66" s="12" t="n"/>
+      <c r="AC66" s="12" t="n"/>
+      <c r="AD66" s="12" t="n"/>
+      <c r="AE66" s="12" t="n"/>
+      <c r="AF66" s="12" t="n"/>
+      <c r="AG66" s="12" t="n"/>
+      <c r="AH66" s="12" t="n"/>
+      <c r="AI66" s="12" t="n"/>
+      <c r="AJ66" s="14" t="n"/>
+      <c r="AK66" s="15">
         <f>IF(TODAY()&lt;AD66, 0, IF(TODAY()&gt;AE66, AF66, AF66 * (TODAY()-AD66)/(AE66-AD66+1)))</f>
         <v/>
       </c>
-      <c r="AL66" s="5">
+      <c r="AL66" s="15">
         <f>AF66 * (AJ66/100)</f>
         <v/>
       </c>
-      <c r="AM66" s="5">
+      <c r="AM66" s="16">
         <f>AI66</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="L67" s="4" t="n"/>
-      <c r="M67" s="5">
+      <c r="A67" s="11" t="n"/>
+      <c r="B67" s="12" t="n"/>
+      <c r="C67" s="13" t="n"/>
+      <c r="D67" s="12" t="n"/>
+      <c r="E67" s="12" t="n"/>
+      <c r="F67" s="12" t="n"/>
+      <c r="G67" s="12" t="n"/>
+      <c r="H67" s="12" t="n"/>
+      <c r="I67" s="12" t="n"/>
+      <c r="J67" s="12" t="n"/>
+      <c r="K67" s="12" t="n"/>
+      <c r="L67" s="14" t="n"/>
+      <c r="M67" s="15">
         <f>IF(TODAY()&lt;F67, 0, IF(TODAY()&gt;G67, H67, H67 * (TODAY()-F67)/(G67-F67+1)))</f>
         <v/>
       </c>
-      <c r="N67" s="5">
+      <c r="N67" s="15">
         <f>H67 * (L67/100)</f>
         <v/>
       </c>
-      <c r="O67" s="5">
+      <c r="O67" s="16">
         <f>K67</f>
         <v/>
       </c>
-      <c r="X67" s="4" t="n"/>
-      <c r="Y67" s="5">
+      <c r="P67" s="12" t="n"/>
+      <c r="Q67" s="12" t="n"/>
+      <c r="R67" s="12" t="n"/>
+      <c r="S67" s="12" t="n"/>
+      <c r="T67" s="12" t="n"/>
+      <c r="U67" s="12" t="n"/>
+      <c r="V67" s="12" t="n"/>
+      <c r="W67" s="12" t="n"/>
+      <c r="X67" s="14" t="n"/>
+      <c r="Y67" s="15">
         <f>IF(TODAY()&lt;R67, 0, IF(TODAY()&gt;S67, T67, T67 * (TODAY()-R67)/(S67-R67+1)))</f>
         <v/>
       </c>
-      <c r="Z67" s="5">
+      <c r="Z67" s="15">
         <f>T67 * (X67/100)</f>
         <v/>
       </c>
-      <c r="AA67" s="5">
+      <c r="AA67" s="16">
         <f>W67</f>
         <v/>
       </c>
-      <c r="AJ67" s="4" t="n"/>
-      <c r="AK67" s="5">
+      <c r="AB67" s="12" t="n"/>
+      <c r="AC67" s="12" t="n"/>
+      <c r="AD67" s="12" t="n"/>
+      <c r="AE67" s="12" t="n"/>
+      <c r="AF67" s="12" t="n"/>
+      <c r="AG67" s="12" t="n"/>
+      <c r="AH67" s="12" t="n"/>
+      <c r="AI67" s="12" t="n"/>
+      <c r="AJ67" s="14" t="n"/>
+      <c r="AK67" s="15">
         <f>IF(TODAY()&lt;AD67, 0, IF(TODAY()&gt;AE67, AF67, AF67 * (TODAY()-AD67)/(AE67-AD67+1)))</f>
         <v/>
       </c>
-      <c r="AL67" s="5">
+      <c r="AL67" s="15">
         <f>AF67 * (AJ67/100)</f>
         <v/>
       </c>
-      <c r="AM67" s="5">
+      <c r="AM67" s="16">
         <f>AI67</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="L68" s="4" t="n"/>
-      <c r="M68" s="5">
+      <c r="A68" s="11" t="n"/>
+      <c r="B68" s="12" t="n"/>
+      <c r="C68" s="13" t="n"/>
+      <c r="D68" s="12" t="n"/>
+      <c r="E68" s="12" t="n"/>
+      <c r="F68" s="12" t="n"/>
+      <c r="G68" s="12" t="n"/>
+      <c r="H68" s="12" t="n"/>
+      <c r="I68" s="12" t="n"/>
+      <c r="J68" s="12" t="n"/>
+      <c r="K68" s="12" t="n"/>
+      <c r="L68" s="14" t="n"/>
+      <c r="M68" s="15">
         <f>IF(TODAY()&lt;F68, 0, IF(TODAY()&gt;G68, H68, H68 * (TODAY()-F68)/(G68-F68+1)))</f>
         <v/>
       </c>
-      <c r="N68" s="5">
+      <c r="N68" s="15">
         <f>H68 * (L68/100)</f>
         <v/>
       </c>
-      <c r="O68" s="5">
+      <c r="O68" s="16">
         <f>K68</f>
         <v/>
       </c>
-      <c r="X68" s="4" t="n"/>
-      <c r="Y68" s="5">
+      <c r="P68" s="12" t="n"/>
+      <c r="Q68" s="12" t="n"/>
+      <c r="R68" s="12" t="n"/>
+      <c r="S68" s="12" t="n"/>
+      <c r="T68" s="12" t="n"/>
+      <c r="U68" s="12" t="n"/>
+      <c r="V68" s="12" t="n"/>
+      <c r="W68" s="12" t="n"/>
+      <c r="X68" s="14" t="n"/>
+      <c r="Y68" s="15">
         <f>IF(TODAY()&lt;R68, 0, IF(TODAY()&gt;S68, T68, T68 * (TODAY()-R68)/(S68-R68+1)))</f>
         <v/>
       </c>
-      <c r="Z68" s="5">
+      <c r="Z68" s="15">
         <f>T68 * (X68/100)</f>
         <v/>
       </c>
-      <c r="AA68" s="5">
+      <c r="AA68" s="16">
         <f>W68</f>
         <v/>
       </c>
-      <c r="AJ68" s="4" t="n"/>
-      <c r="AK68" s="5">
+      <c r="AB68" s="12" t="n"/>
+      <c r="AC68" s="12" t="n"/>
+      <c r="AD68" s="12" t="n"/>
+      <c r="AE68" s="12" t="n"/>
+      <c r="AF68" s="12" t="n"/>
+      <c r="AG68" s="12" t="n"/>
+      <c r="AH68" s="12" t="n"/>
+      <c r="AI68" s="12" t="n"/>
+      <c r="AJ68" s="14" t="n"/>
+      <c r="AK68" s="15">
         <f>IF(TODAY()&lt;AD68, 0, IF(TODAY()&gt;AE68, AF68, AF68 * (TODAY()-AD68)/(AE68-AD68+1)))</f>
         <v/>
       </c>
-      <c r="AL68" s="5">
+      <c r="AL68" s="15">
         <f>AF68 * (AJ68/100)</f>
         <v/>
       </c>
-      <c r="AM68" s="5">
+      <c r="AM68" s="16">
         <f>AI68</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="L69" s="4" t="n"/>
-      <c r="M69" s="5">
+      <c r="A69" s="11" t="n"/>
+      <c r="B69" s="12" t="n"/>
+      <c r="C69" s="13" t="n"/>
+      <c r="D69" s="12" t="n"/>
+      <c r="E69" s="12" t="n"/>
+      <c r="F69" s="12" t="n"/>
+      <c r="G69" s="12" t="n"/>
+      <c r="H69" s="12" t="n"/>
+      <c r="I69" s="12" t="n"/>
+      <c r="J69" s="12" t="n"/>
+      <c r="K69" s="12" t="n"/>
+      <c r="L69" s="14" t="n"/>
+      <c r="M69" s="15">
         <f>IF(TODAY()&lt;F69, 0, IF(TODAY()&gt;G69, H69, H69 * (TODAY()-F69)/(G69-F69+1)))</f>
         <v/>
       </c>
-      <c r="N69" s="5">
+      <c r="N69" s="15">
         <f>H69 * (L69/100)</f>
         <v/>
       </c>
-      <c r="O69" s="5">
+      <c r="O69" s="16">
         <f>K69</f>
         <v/>
       </c>
-      <c r="X69" s="4" t="n"/>
-      <c r="Y69" s="5">
+      <c r="P69" s="12" t="n"/>
+      <c r="Q69" s="12" t="n"/>
+      <c r="R69" s="12" t="n"/>
+      <c r="S69" s="12" t="n"/>
+      <c r="T69" s="12" t="n"/>
+      <c r="U69" s="12" t="n"/>
+      <c r="V69" s="12" t="n"/>
+      <c r="W69" s="12" t="n"/>
+      <c r="X69" s="14" t="n"/>
+      <c r="Y69" s="15">
         <f>IF(TODAY()&lt;R69, 0, IF(TODAY()&gt;S69, T69, T69 * (TODAY()-R69)/(S69-R69+1)))</f>
         <v/>
       </c>
-      <c r="Z69" s="5">
+      <c r="Z69" s="15">
         <f>T69 * (X69/100)</f>
         <v/>
       </c>
-      <c r="AA69" s="5">
+      <c r="AA69" s="16">
         <f>W69</f>
         <v/>
       </c>
-      <c r="AJ69" s="4" t="n"/>
-      <c r="AK69" s="5">
+      <c r="AB69" s="12" t="n"/>
+      <c r="AC69" s="12" t="n"/>
+      <c r="AD69" s="12" t="n"/>
+      <c r="AE69" s="12" t="n"/>
+      <c r="AF69" s="12" t="n"/>
+      <c r="AG69" s="12" t="n"/>
+      <c r="AH69" s="12" t="n"/>
+      <c r="AI69" s="12" t="n"/>
+      <c r="AJ69" s="14" t="n"/>
+      <c r="AK69" s="15">
         <f>IF(TODAY()&lt;AD69, 0, IF(TODAY()&gt;AE69, AF69, AF69 * (TODAY()-AD69)/(AE69-AD69+1)))</f>
         <v/>
       </c>
-      <c r="AL69" s="5">
+      <c r="AL69" s="15">
         <f>AF69 * (AJ69/100)</f>
         <v/>
       </c>
-      <c r="AM69" s="5">
+      <c r="AM69" s="16">
         <f>AI69</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="L70" s="4" t="n"/>
-      <c r="M70" s="5">
+      <c r="A70" s="11" t="n"/>
+      <c r="B70" s="12" t="n"/>
+      <c r="C70" s="13" t="n"/>
+      <c r="D70" s="12" t="n"/>
+      <c r="E70" s="12" t="n"/>
+      <c r="F70" s="12" t="n"/>
+      <c r="G70" s="12" t="n"/>
+      <c r="H70" s="12" t="n"/>
+      <c r="I70" s="12" t="n"/>
+      <c r="J70" s="12" t="n"/>
+      <c r="K70" s="12" t="n"/>
+      <c r="L70" s="14" t="n"/>
+      <c r="M70" s="15">
         <f>IF(TODAY()&lt;F70, 0, IF(TODAY()&gt;G70, H70, H70 * (TODAY()-F70)/(G70-F70+1)))</f>
         <v/>
       </c>
-      <c r="N70" s="5">
+      <c r="N70" s="15">
         <f>H70 * (L70/100)</f>
         <v/>
       </c>
-      <c r="O70" s="5">
+      <c r="O70" s="16">
         <f>K70</f>
         <v/>
       </c>
-      <c r="X70" s="4" t="n"/>
-      <c r="Y70" s="5">
+      <c r="P70" s="12" t="n"/>
+      <c r="Q70" s="12" t="n"/>
+      <c r="R70" s="12" t="n"/>
+      <c r="S70" s="12" t="n"/>
+      <c r="T70" s="12" t="n"/>
+      <c r="U70" s="12" t="n"/>
+      <c r="V70" s="12" t="n"/>
+      <c r="W70" s="12" t="n"/>
+      <c r="X70" s="14" t="n"/>
+      <c r="Y70" s="15">
         <f>IF(TODAY()&lt;R70, 0, IF(TODAY()&gt;S70, T70, T70 * (TODAY()-R70)/(S70-R70+1)))</f>
         <v/>
       </c>
-      <c r="Z70" s="5">
+      <c r="Z70" s="15">
         <f>T70 * (X70/100)</f>
         <v/>
       </c>
-      <c r="AA70" s="5">
+      <c r="AA70" s="16">
         <f>W70</f>
         <v/>
       </c>
-      <c r="AJ70" s="4" t="n"/>
-      <c r="AK70" s="5">
+      <c r="AB70" s="12" t="n"/>
+      <c r="AC70" s="12" t="n"/>
+      <c r="AD70" s="12" t="n"/>
+      <c r="AE70" s="12" t="n"/>
+      <c r="AF70" s="12" t="n"/>
+      <c r="AG70" s="12" t="n"/>
+      <c r="AH70" s="12" t="n"/>
+      <c r="AI70" s="12" t="n"/>
+      <c r="AJ70" s="14" t="n"/>
+      <c r="AK70" s="15">
         <f>IF(TODAY()&lt;AD70, 0, IF(TODAY()&gt;AE70, AF70, AF70 * (TODAY()-AD70)/(AE70-AD70+1)))</f>
         <v/>
       </c>
-      <c r="AL70" s="5">
+      <c r="AL70" s="15">
         <f>AF70 * (AJ70/100)</f>
         <v/>
       </c>
-      <c r="AM70" s="5">
+      <c r="AM70" s="16">
         <f>AI70</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="L71" s="4" t="n"/>
-      <c r="M71" s="5">
+      <c r="A71" s="11" t="n"/>
+      <c r="B71" s="12" t="n"/>
+      <c r="C71" s="13" t="n"/>
+      <c r="D71" s="12" t="n"/>
+      <c r="E71" s="12" t="n"/>
+      <c r="F71" s="12" t="n"/>
+      <c r="G71" s="12" t="n"/>
+      <c r="H71" s="12" t="n"/>
+      <c r="I71" s="12" t="n"/>
+      <c r="J71" s="12" t="n"/>
+      <c r="K71" s="12" t="n"/>
+      <c r="L71" s="14" t="n"/>
+      <c r="M71" s="15">
         <f>IF(TODAY()&lt;F71, 0, IF(TODAY()&gt;G71, H71, H71 * (TODAY()-F71)/(G71-F71+1)))</f>
         <v/>
       </c>
-      <c r="N71" s="5">
+      <c r="N71" s="15">
         <f>H71 * (L71/100)</f>
         <v/>
       </c>
-      <c r="O71" s="5">
+      <c r="O71" s="16">
         <f>K71</f>
         <v/>
       </c>
-      <c r="X71" s="4" t="n"/>
-      <c r="Y71" s="5">
+      <c r="P71" s="12" t="n"/>
+      <c r="Q71" s="12" t="n"/>
+      <c r="R71" s="12" t="n"/>
+      <c r="S71" s="12" t="n"/>
+      <c r="T71" s="12" t="n"/>
+      <c r="U71" s="12" t="n"/>
+      <c r="V71" s="12" t="n"/>
+      <c r="W71" s="12" t="n"/>
+      <c r="X71" s="14" t="n"/>
+      <c r="Y71" s="15">
         <f>IF(TODAY()&lt;R71, 0, IF(TODAY()&gt;S71, T71, T71 * (TODAY()-R71)/(S71-R71+1)))</f>
         <v/>
       </c>
-      <c r="Z71" s="5">
+      <c r="Z71" s="15">
         <f>T71 * (X71/100)</f>
         <v/>
       </c>
-      <c r="AA71" s="5">
+      <c r="AA71" s="16">
         <f>W71</f>
         <v/>
       </c>
-      <c r="AJ71" s="4" t="n"/>
-      <c r="AK71" s="5">
+      <c r="AB71" s="12" t="n"/>
+      <c r="AC71" s="12" t="n"/>
+      <c r="AD71" s="12" t="n"/>
+      <c r="AE71" s="12" t="n"/>
+      <c r="AF71" s="12" t="n"/>
+      <c r="AG71" s="12" t="n"/>
+      <c r="AH71" s="12" t="n"/>
+      <c r="AI71" s="12" t="n"/>
+      <c r="AJ71" s="14" t="n"/>
+      <c r="AK71" s="15">
         <f>IF(TODAY()&lt;AD71, 0, IF(TODAY()&gt;AE71, AF71, AF71 * (TODAY()-AD71)/(AE71-AD71+1)))</f>
         <v/>
       </c>
-      <c r="AL71" s="5">
+      <c r="AL71" s="15">
         <f>AF71 * (AJ71/100)</f>
         <v/>
       </c>
-      <c r="AM71" s="5">
+      <c r="AM71" s="16">
         <f>AI71</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="L72" s="4" t="n"/>
-      <c r="M72" s="5">
+      <c r="A72" s="11" t="n"/>
+      <c r="B72" s="12" t="n"/>
+      <c r="C72" s="13" t="n"/>
+      <c r="D72" s="12" t="n"/>
+      <c r="E72" s="12" t="n"/>
+      <c r="F72" s="12" t="n"/>
+      <c r="G72" s="12" t="n"/>
+      <c r="H72" s="12" t="n"/>
+      <c r="I72" s="12" t="n"/>
+      <c r="J72" s="12" t="n"/>
+      <c r="K72" s="12" t="n"/>
+      <c r="L72" s="14" t="n"/>
+      <c r="M72" s="15">
         <f>IF(TODAY()&lt;F72, 0, IF(TODAY()&gt;G72, H72, H72 * (TODAY()-F72)/(G72-F72+1)))</f>
         <v/>
       </c>
-      <c r="N72" s="5">
+      <c r="N72" s="15">
         <f>H72 * (L72/100)</f>
         <v/>
       </c>
-      <c r="O72" s="5">
+      <c r="O72" s="16">
         <f>K72</f>
         <v/>
       </c>
-      <c r="X72" s="4" t="n"/>
-      <c r="Y72" s="5">
+      <c r="P72" s="12" t="n"/>
+      <c r="Q72" s="12" t="n"/>
+      <c r="R72" s="12" t="n"/>
+      <c r="S72" s="12" t="n"/>
+      <c r="T72" s="12" t="n"/>
+      <c r="U72" s="12" t="n"/>
+      <c r="V72" s="12" t="n"/>
+      <c r="W72" s="12" t="n"/>
+      <c r="X72" s="14" t="n"/>
+      <c r="Y72" s="15">
         <f>IF(TODAY()&lt;R72, 0, IF(TODAY()&gt;S72, T72, T72 * (TODAY()-R72)/(S72-R72+1)))</f>
         <v/>
       </c>
-      <c r="Z72" s="5">
+      <c r="Z72" s="15">
         <f>T72 * (X72/100)</f>
         <v/>
       </c>
-      <c r="AA72" s="5">
+      <c r="AA72" s="16">
         <f>W72</f>
         <v/>
       </c>
-      <c r="AJ72" s="4" t="n"/>
-      <c r="AK72" s="5">
+      <c r="AB72" s="12" t="n"/>
+      <c r="AC72" s="12" t="n"/>
+      <c r="AD72" s="12" t="n"/>
+      <c r="AE72" s="12" t="n"/>
+      <c r="AF72" s="12" t="n"/>
+      <c r="AG72" s="12" t="n"/>
+      <c r="AH72" s="12" t="n"/>
+      <c r="AI72" s="12" t="n"/>
+      <c r="AJ72" s="14" t="n"/>
+      <c r="AK72" s="15">
         <f>IF(TODAY()&lt;AD72, 0, IF(TODAY()&gt;AE72, AF72, AF72 * (TODAY()-AD72)/(AE72-AD72+1)))</f>
         <v/>
       </c>
-      <c r="AL72" s="5">
+      <c r="AL72" s="15">
         <f>AF72 * (AJ72/100)</f>
         <v/>
       </c>
-      <c r="AM72" s="5">
+      <c r="AM72" s="16">
         <f>AI72</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="L73" s="4" t="n"/>
-      <c r="M73" s="5">
+      <c r="A73" s="11" t="n"/>
+      <c r="B73" s="12" t="n"/>
+      <c r="C73" s="13" t="n"/>
+      <c r="D73" s="12" t="n"/>
+      <c r="E73" s="12" t="n"/>
+      <c r="F73" s="12" t="n"/>
+      <c r="G73" s="12" t="n"/>
+      <c r="H73" s="12" t="n"/>
+      <c r="I73" s="12" t="n"/>
+      <c r="J73" s="12" t="n"/>
+      <c r="K73" s="12" t="n"/>
+      <c r="L73" s="14" t="n"/>
+      <c r="M73" s="15">
         <f>IF(TODAY()&lt;F73, 0, IF(TODAY()&gt;G73, H73, H73 * (TODAY()-F73)/(G73-F73+1)))</f>
         <v/>
       </c>
-      <c r="N73" s="5">
+      <c r="N73" s="15">
         <f>H73 * (L73/100)</f>
         <v/>
       </c>
-      <c r="O73" s="5">
+      <c r="O73" s="16">
         <f>K73</f>
         <v/>
       </c>
-      <c r="X73" s="4" t="n"/>
-      <c r="Y73" s="5">
+      <c r="P73" s="12" t="n"/>
+      <c r="Q73" s="12" t="n"/>
+      <c r="R73" s="12" t="n"/>
+      <c r="S73" s="12" t="n"/>
+      <c r="T73" s="12" t="n"/>
+      <c r="U73" s="12" t="n"/>
+      <c r="V73" s="12" t="n"/>
+      <c r="W73" s="12" t="n"/>
+      <c r="X73" s="14" t="n"/>
+      <c r="Y73" s="15">
         <f>IF(TODAY()&lt;R73, 0, IF(TODAY()&gt;S73, T73, T73 * (TODAY()-R73)/(S73-R73+1)))</f>
         <v/>
       </c>
-      <c r="Z73" s="5">
+      <c r="Z73" s="15">
         <f>T73 * (X73/100)</f>
         <v/>
       </c>
-      <c r="AA73" s="5">
+      <c r="AA73" s="16">
         <f>W73</f>
         <v/>
       </c>
-      <c r="AJ73" s="4" t="n"/>
-      <c r="AK73" s="5">
+      <c r="AB73" s="12" t="n"/>
+      <c r="AC73" s="12" t="n"/>
+      <c r="AD73" s="12" t="n"/>
+      <c r="AE73" s="12" t="n"/>
+      <c r="AF73" s="12" t="n"/>
+      <c r="AG73" s="12" t="n"/>
+      <c r="AH73" s="12" t="n"/>
+      <c r="AI73" s="12" t="n"/>
+      <c r="AJ73" s="14" t="n"/>
+      <c r="AK73" s="15">
         <f>IF(TODAY()&lt;AD73, 0, IF(TODAY()&gt;AE73, AF73, AF73 * (TODAY()-AD73)/(AE73-AD73+1)))</f>
         <v/>
       </c>
-      <c r="AL73" s="5">
+      <c r="AL73" s="15">
         <f>AF73 * (AJ73/100)</f>
         <v/>
       </c>
-      <c r="AM73" s="5">
+      <c r="AM73" s="16">
         <f>AI73</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="L74" s="4" t="n"/>
-      <c r="M74" s="5">
+      <c r="A74" s="11" t="n"/>
+      <c r="B74" s="12" t="n"/>
+      <c r="C74" s="13" t="n"/>
+      <c r="D74" s="12" t="n"/>
+      <c r="E74" s="12" t="n"/>
+      <c r="F74" s="12" t="n"/>
+      <c r="G74" s="12" t="n"/>
+      <c r="H74" s="12" t="n"/>
+      <c r="I74" s="12" t="n"/>
+      <c r="J74" s="12" t="n"/>
+      <c r="K74" s="12" t="n"/>
+      <c r="L74" s="14" t="n"/>
+      <c r="M74" s="15">
         <f>IF(TODAY()&lt;F74, 0, IF(TODAY()&gt;G74, H74, H74 * (TODAY()-F74)/(G74-F74+1)))</f>
         <v/>
       </c>
-      <c r="N74" s="5">
+      <c r="N74" s="15">
         <f>H74 * (L74/100)</f>
         <v/>
       </c>
-      <c r="O74" s="5">
+      <c r="O74" s="16">
         <f>K74</f>
         <v/>
       </c>
-      <c r="X74" s="4" t="n"/>
-      <c r="Y74" s="5">
+      <c r="P74" s="12" t="n"/>
+      <c r="Q74" s="12" t="n"/>
+      <c r="R74" s="12" t="n"/>
+      <c r="S74" s="12" t="n"/>
+      <c r="T74" s="12" t="n"/>
+      <c r="U74" s="12" t="n"/>
+      <c r="V74" s="12" t="n"/>
+      <c r="W74" s="12" t="n"/>
+      <c r="X74" s="14" t="n"/>
+      <c r="Y74" s="15">
         <f>IF(TODAY()&lt;R74, 0, IF(TODAY()&gt;S74, T74, T74 * (TODAY()-R74)/(S74-R74+1)))</f>
         <v/>
       </c>
-      <c r="Z74" s="5">
+      <c r="Z74" s="15">
         <f>T74 * (X74/100)</f>
         <v/>
       </c>
-      <c r="AA74" s="5">
+      <c r="AA74" s="16">
         <f>W74</f>
         <v/>
       </c>
-      <c r="AJ74" s="4" t="n"/>
-      <c r="AK74" s="5">
+      <c r="AB74" s="12" t="n"/>
+      <c r="AC74" s="12" t="n"/>
+      <c r="AD74" s="12" t="n"/>
+      <c r="AE74" s="12" t="n"/>
+      <c r="AF74" s="12" t="n"/>
+      <c r="AG74" s="12" t="n"/>
+      <c r="AH74" s="12" t="n"/>
+      <c r="AI74" s="12" t="n"/>
+      <c r="AJ74" s="14" t="n"/>
+      <c r="AK74" s="15">
         <f>IF(TODAY()&lt;AD74, 0, IF(TODAY()&gt;AE74, AF74, AF74 * (TODAY()-AD74)/(AE74-AD74+1)))</f>
         <v/>
       </c>
-      <c r="AL74" s="5">
+      <c r="AL74" s="15">
         <f>AF74 * (AJ74/100)</f>
         <v/>
       </c>
-      <c r="AM74" s="5">
+      <c r="AM74" s="16">
         <f>AI74</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="L75" s="4" t="n"/>
-      <c r="M75" s="5">
+      <c r="A75" s="11" t="n"/>
+      <c r="B75" s="12" t="n"/>
+      <c r="C75" s="13" t="n"/>
+      <c r="D75" s="12" t="n"/>
+      <c r="E75" s="12" t="n"/>
+      <c r="F75" s="12" t="n"/>
+      <c r="G75" s="12" t="n"/>
+      <c r="H75" s="12" t="n"/>
+      <c r="I75" s="12" t="n"/>
+      <c r="J75" s="12" t="n"/>
+      <c r="K75" s="12" t="n"/>
+      <c r="L75" s="14" t="n"/>
+      <c r="M75" s="15">
         <f>IF(TODAY()&lt;F75, 0, IF(TODAY()&gt;G75, H75, H75 * (TODAY()-F75)/(G75-F75+1)))</f>
         <v/>
       </c>
-      <c r="N75" s="5">
+      <c r="N75" s="15">
         <f>H75 * (L75/100)</f>
         <v/>
       </c>
-      <c r="O75" s="5">
+      <c r="O75" s="16">
         <f>K75</f>
         <v/>
       </c>
-      <c r="X75" s="4" t="n"/>
-      <c r="Y75" s="5">
+      <c r="P75" s="12" t="n"/>
+      <c r="Q75" s="12" t="n"/>
+      <c r="R75" s="12" t="n"/>
+      <c r="S75" s="12" t="n"/>
+      <c r="T75" s="12" t="n"/>
+      <c r="U75" s="12" t="n"/>
+      <c r="V75" s="12" t="n"/>
+      <c r="W75" s="12" t="n"/>
+      <c r="X75" s="14" t="n"/>
+      <c r="Y75" s="15">
         <f>IF(TODAY()&lt;R75, 0, IF(TODAY()&gt;S75, T75, T75 * (TODAY()-R75)/(S75-R75+1)))</f>
         <v/>
       </c>
-      <c r="Z75" s="5">
+      <c r="Z75" s="15">
         <f>T75 * (X75/100)</f>
         <v/>
       </c>
-      <c r="AA75" s="5">
+      <c r="AA75" s="16">
         <f>W75</f>
         <v/>
       </c>
-      <c r="AJ75" s="4" t="n"/>
-      <c r="AK75" s="5">
+      <c r="AB75" s="12" t="n"/>
+      <c r="AC75" s="12" t="n"/>
+      <c r="AD75" s="12" t="n"/>
+      <c r="AE75" s="12" t="n"/>
+      <c r="AF75" s="12" t="n"/>
+      <c r="AG75" s="12" t="n"/>
+      <c r="AH75" s="12" t="n"/>
+      <c r="AI75" s="12" t="n"/>
+      <c r="AJ75" s="14" t="n"/>
+      <c r="AK75" s="15">
         <f>IF(TODAY()&lt;AD75, 0, IF(TODAY()&gt;AE75, AF75, AF75 * (TODAY()-AD75)/(AE75-AD75+1)))</f>
         <v/>
       </c>
-      <c r="AL75" s="5">
+      <c r="AL75" s="15">
         <f>AF75 * (AJ75/100)</f>
         <v/>
       </c>
-      <c r="AM75" s="5">
+      <c r="AM75" s="16">
         <f>AI75</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="L76" s="4" t="n"/>
-      <c r="M76" s="5">
+      <c r="A76" s="11" t="n"/>
+      <c r="B76" s="12" t="n"/>
+      <c r="C76" s="13" t="n"/>
+      <c r="D76" s="12" t="n"/>
+      <c r="E76" s="12" t="n"/>
+      <c r="F76" s="12" t="n"/>
+      <c r="G76" s="12" t="n"/>
+      <c r="H76" s="12" t="n"/>
+      <c r="I76" s="12" t="n"/>
+      <c r="J76" s="12" t="n"/>
+      <c r="K76" s="12" t="n"/>
+      <c r="L76" s="14" t="n"/>
+      <c r="M76" s="15">
         <f>IF(TODAY()&lt;F76, 0, IF(TODAY()&gt;G76, H76, H76 * (TODAY()-F76)/(G76-F76+1)))</f>
         <v/>
       </c>
-      <c r="N76" s="5">
+      <c r="N76" s="15">
         <f>H76 * (L76/100)</f>
         <v/>
       </c>
-      <c r="O76" s="5">
+      <c r="O76" s="16">
         <f>K76</f>
         <v/>
       </c>
-      <c r="X76" s="4" t="n"/>
-      <c r="Y76" s="5">
+      <c r="P76" s="12" t="n"/>
+      <c r="Q76" s="12" t="n"/>
+      <c r="R76" s="12" t="n"/>
+      <c r="S76" s="12" t="n"/>
+      <c r="T76" s="12" t="n"/>
+      <c r="U76" s="12" t="n"/>
+      <c r="V76" s="12" t="n"/>
+      <c r="W76" s="12" t="n"/>
+      <c r="X76" s="14" t="n"/>
+      <c r="Y76" s="15">
         <f>IF(TODAY()&lt;R76, 0, IF(TODAY()&gt;S76, T76, T76 * (TODAY()-R76)/(S76-R76+1)))</f>
         <v/>
       </c>
-      <c r="Z76" s="5">
+      <c r="Z76" s="15">
         <f>T76 * (X76/100)</f>
         <v/>
       </c>
-      <c r="AA76" s="5">
+      <c r="AA76" s="16">
         <f>W76</f>
         <v/>
       </c>
-      <c r="AJ76" s="4" t="n"/>
-      <c r="AK76" s="5">
+      <c r="AB76" s="12" t="n"/>
+      <c r="AC76" s="12" t="n"/>
+      <c r="AD76" s="12" t="n"/>
+      <c r="AE76" s="12" t="n"/>
+      <c r="AF76" s="12" t="n"/>
+      <c r="AG76" s="12" t="n"/>
+      <c r="AH76" s="12" t="n"/>
+      <c r="AI76" s="12" t="n"/>
+      <c r="AJ76" s="14" t="n"/>
+      <c r="AK76" s="15">
         <f>IF(TODAY()&lt;AD76, 0, IF(TODAY()&gt;AE76, AF76, AF76 * (TODAY()-AD76)/(AE76-AD76+1)))</f>
         <v/>
       </c>
-      <c r="AL76" s="5">
+      <c r="AL76" s="15">
         <f>AF76 * (AJ76/100)</f>
         <v/>
       </c>
-      <c r="AM76" s="5">
+      <c r="AM76" s="16">
         <f>AI76</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="L77" s="4" t="n"/>
-      <c r="M77" s="5">
+      <c r="A77" s="11" t="n"/>
+      <c r="B77" s="12" t="n"/>
+      <c r="C77" s="13" t="n"/>
+      <c r="D77" s="12" t="n"/>
+      <c r="E77" s="12" t="n"/>
+      <c r="F77" s="12" t="n"/>
+      <c r="G77" s="12" t="n"/>
+      <c r="H77" s="12" t="n"/>
+      <c r="I77" s="12" t="n"/>
+      <c r="J77" s="12" t="n"/>
+      <c r="K77" s="12" t="n"/>
+      <c r="L77" s="14" t="n"/>
+      <c r="M77" s="15">
         <f>IF(TODAY()&lt;F77, 0, IF(TODAY()&gt;G77, H77, H77 * (TODAY()-F77)/(G77-F77+1)))</f>
         <v/>
       </c>
-      <c r="N77" s="5">
+      <c r="N77" s="15">
         <f>H77 * (L77/100)</f>
         <v/>
       </c>
-      <c r="O77" s="5">
+      <c r="O77" s="16">
         <f>K77</f>
         <v/>
       </c>
-      <c r="X77" s="4" t="n"/>
-      <c r="Y77" s="5">
+      <c r="P77" s="12" t="n"/>
+      <c r="Q77" s="12" t="n"/>
+      <c r="R77" s="12" t="n"/>
+      <c r="S77" s="12" t="n"/>
+      <c r="T77" s="12" t="n"/>
+      <c r="U77" s="12" t="n"/>
+      <c r="V77" s="12" t="n"/>
+      <c r="W77" s="12" t="n"/>
+      <c r="X77" s="14" t="n"/>
+      <c r="Y77" s="15">
         <f>IF(TODAY()&lt;R77, 0, IF(TODAY()&gt;S77, T77, T77 * (TODAY()-R77)/(S77-R77+1)))</f>
         <v/>
       </c>
-      <c r="Z77" s="5">
+      <c r="Z77" s="15">
         <f>T77 * (X77/100)</f>
         <v/>
       </c>
-      <c r="AA77" s="5">
+      <c r="AA77" s="16">
         <f>W77</f>
         <v/>
       </c>
-      <c r="AJ77" s="4" t="n"/>
-      <c r="AK77" s="5">
+      <c r="AB77" s="12" t="n"/>
+      <c r="AC77" s="12" t="n"/>
+      <c r="AD77" s="12" t="n"/>
+      <c r="AE77" s="12" t="n"/>
+      <c r="AF77" s="12" t="n"/>
+      <c r="AG77" s="12" t="n"/>
+      <c r="AH77" s="12" t="n"/>
+      <c r="AI77" s="12" t="n"/>
+      <c r="AJ77" s="14" t="n"/>
+      <c r="AK77" s="15">
         <f>IF(TODAY()&lt;AD77, 0, IF(TODAY()&gt;AE77, AF77, AF77 * (TODAY()-AD77)/(AE77-AD77+1)))</f>
         <v/>
       </c>
-      <c r="AL77" s="5">
+      <c r="AL77" s="15">
         <f>AF77 * (AJ77/100)</f>
         <v/>
       </c>
-      <c r="AM77" s="5">
+      <c r="AM77" s="16">
         <f>AI77</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="L78" s="4" t="n"/>
-      <c r="M78" s="5">
+      <c r="A78" s="11" t="n"/>
+      <c r="B78" s="12" t="n"/>
+      <c r="C78" s="13" t="n"/>
+      <c r="D78" s="12" t="n"/>
+      <c r="E78" s="12" t="n"/>
+      <c r="F78" s="12" t="n"/>
+      <c r="G78" s="12" t="n"/>
+      <c r="H78" s="12" t="n"/>
+      <c r="I78" s="12" t="n"/>
+      <c r="J78" s="12" t="n"/>
+      <c r="K78" s="12" t="n"/>
+      <c r="L78" s="14" t="n"/>
+      <c r="M78" s="15">
         <f>IF(TODAY()&lt;F78, 0, IF(TODAY()&gt;G78, H78, H78 * (TODAY()-F78)/(G78-F78+1)))</f>
         <v/>
       </c>
-      <c r="N78" s="5">
+      <c r="N78" s="15">
         <f>H78 * (L78/100)</f>
         <v/>
       </c>
-      <c r="O78" s="5">
+      <c r="O78" s="16">
         <f>K78</f>
         <v/>
       </c>
-      <c r="X78" s="4" t="n"/>
-      <c r="Y78" s="5">
+      <c r="P78" s="12" t="n"/>
+      <c r="Q78" s="12" t="n"/>
+      <c r="R78" s="12" t="n"/>
+      <c r="S78" s="12" t="n"/>
+      <c r="T78" s="12" t="n"/>
+      <c r="U78" s="12" t="n"/>
+      <c r="V78" s="12" t="n"/>
+      <c r="W78" s="12" t="n"/>
+      <c r="X78" s="14" t="n"/>
+      <c r="Y78" s="15">
         <f>IF(TODAY()&lt;R78, 0, IF(TODAY()&gt;S78, T78, T78 * (TODAY()-R78)/(S78-R78+1)))</f>
         <v/>
       </c>
-      <c r="Z78" s="5">
+      <c r="Z78" s="15">
         <f>T78 * (X78/100)</f>
         <v/>
       </c>
-      <c r="AA78" s="5">
+      <c r="AA78" s="16">
         <f>W78</f>
         <v/>
       </c>
-      <c r="AJ78" s="4" t="n"/>
-      <c r="AK78" s="5">
+      <c r="AB78" s="12" t="n"/>
+      <c r="AC78" s="12" t="n"/>
+      <c r="AD78" s="12" t="n"/>
+      <c r="AE78" s="12" t="n"/>
+      <c r="AF78" s="12" t="n"/>
+      <c r="AG78" s="12" t="n"/>
+      <c r="AH78" s="12" t="n"/>
+      <c r="AI78" s="12" t="n"/>
+      <c r="AJ78" s="14" t="n"/>
+      <c r="AK78" s="15">
         <f>IF(TODAY()&lt;AD78, 0, IF(TODAY()&gt;AE78, AF78, AF78 * (TODAY()-AD78)/(AE78-AD78+1)))</f>
         <v/>
       </c>
-      <c r="AL78" s="5">
+      <c r="AL78" s="15">
         <f>AF78 * (AJ78/100)</f>
         <v/>
       </c>
-      <c r="AM78" s="5">
+      <c r="AM78" s="16">
         <f>AI78</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="L79" s="4" t="n"/>
-      <c r="M79" s="5">
+      <c r="A79" s="11" t="n"/>
+      <c r="B79" s="12" t="n"/>
+      <c r="C79" s="13" t="n"/>
+      <c r="D79" s="12" t="n"/>
+      <c r="E79" s="12" t="n"/>
+      <c r="F79" s="12" t="n"/>
+      <c r="G79" s="12" t="n"/>
+      <c r="H79" s="12" t="n"/>
+      <c r="I79" s="12" t="n"/>
+      <c r="J79" s="12" t="n"/>
+      <c r="K79" s="12" t="n"/>
+      <c r="L79" s="14" t="n"/>
+      <c r="M79" s="15">
         <f>IF(TODAY()&lt;F79, 0, IF(TODAY()&gt;G79, H79, H79 * (TODAY()-F79)/(G79-F79+1)))</f>
         <v/>
       </c>
-      <c r="N79" s="5">
+      <c r="N79" s="15">
         <f>H79 * (L79/100)</f>
         <v/>
       </c>
-      <c r="O79" s="5">
+      <c r="O79" s="16">
         <f>K79</f>
         <v/>
       </c>
-      <c r="X79" s="4" t="n"/>
-      <c r="Y79" s="5">
+      <c r="P79" s="12" t="n"/>
+      <c r="Q79" s="12" t="n"/>
+      <c r="R79" s="12" t="n"/>
+      <c r="S79" s="12" t="n"/>
+      <c r="T79" s="12" t="n"/>
+      <c r="U79" s="12" t="n"/>
+      <c r="V79" s="12" t="n"/>
+      <c r="W79" s="12" t="n"/>
+      <c r="X79" s="14" t="n"/>
+      <c r="Y79" s="15">
         <f>IF(TODAY()&lt;R79, 0, IF(TODAY()&gt;S79, T79, T79 * (TODAY()-R79)/(S79-R79+1)))</f>
         <v/>
       </c>
-      <c r="Z79" s="5">
+      <c r="Z79" s="15">
         <f>T79 * (X79/100)</f>
         <v/>
       </c>
-      <c r="AA79" s="5">
+      <c r="AA79" s="16">
         <f>W79</f>
         <v/>
       </c>
-      <c r="AJ79" s="4" t="n"/>
-      <c r="AK79" s="5">
+      <c r="AB79" s="12" t="n"/>
+      <c r="AC79" s="12" t="n"/>
+      <c r="AD79" s="12" t="n"/>
+      <c r="AE79" s="12" t="n"/>
+      <c r="AF79" s="12" t="n"/>
+      <c r="AG79" s="12" t="n"/>
+      <c r="AH79" s="12" t="n"/>
+      <c r="AI79" s="12" t="n"/>
+      <c r="AJ79" s="14" t="n"/>
+      <c r="AK79" s="15">
         <f>IF(TODAY()&lt;AD79, 0, IF(TODAY()&gt;AE79, AF79, AF79 * (TODAY()-AD79)/(AE79-AD79+1)))</f>
         <v/>
       </c>
-      <c r="AL79" s="5">
+      <c r="AL79" s="15">
         <f>AF79 * (AJ79/100)</f>
         <v/>
       </c>
-      <c r="AM79" s="5">
+      <c r="AM79" s="16">
         <f>AI79</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="L80" s="4" t="n"/>
-      <c r="M80" s="5">
+      <c r="A80" s="11" t="n"/>
+      <c r="B80" s="12" t="n"/>
+      <c r="C80" s="13" t="n"/>
+      <c r="D80" s="12" t="n"/>
+      <c r="E80" s="12" t="n"/>
+      <c r="F80" s="12" t="n"/>
+      <c r="G80" s="12" t="n"/>
+      <c r="H80" s="12" t="n"/>
+      <c r="I80" s="12" t="n"/>
+      <c r="J80" s="12" t="n"/>
+      <c r="K80" s="12" t="n"/>
+      <c r="L80" s="14" t="n"/>
+      <c r="M80" s="15">
         <f>IF(TODAY()&lt;F80, 0, IF(TODAY()&gt;G80, H80, H80 * (TODAY()-F80)/(G80-F80+1)))</f>
         <v/>
       </c>
-      <c r="N80" s="5">
+      <c r="N80" s="15">
         <f>H80 * (L80/100)</f>
         <v/>
       </c>
-      <c r="O80" s="5">
+      <c r="O80" s="16">
         <f>K80</f>
         <v/>
       </c>
-      <c r="X80" s="4" t="n"/>
-      <c r="Y80" s="5">
+      <c r="P80" s="12" t="n"/>
+      <c r="Q80" s="12" t="n"/>
+      <c r="R80" s="12" t="n"/>
+      <c r="S80" s="12" t="n"/>
+      <c r="T80" s="12" t="n"/>
+      <c r="U80" s="12" t="n"/>
+      <c r="V80" s="12" t="n"/>
+      <c r="W80" s="12" t="n"/>
+      <c r="X80" s="14" t="n"/>
+      <c r="Y80" s="15">
         <f>IF(TODAY()&lt;R80, 0, IF(TODAY()&gt;S80, T80, T80 * (TODAY()-R80)/(S80-R80+1)))</f>
         <v/>
       </c>
-      <c r="Z80" s="5">
+      <c r="Z80" s="15">
         <f>T80 * (X80/100)</f>
         <v/>
       </c>
-      <c r="AA80" s="5">
+      <c r="AA80" s="16">
         <f>W80</f>
         <v/>
       </c>
-      <c r="AJ80" s="4" t="n"/>
-      <c r="AK80" s="5">
+      <c r="AB80" s="12" t="n"/>
+      <c r="AC80" s="12" t="n"/>
+      <c r="AD80" s="12" t="n"/>
+      <c r="AE80" s="12" t="n"/>
+      <c r="AF80" s="12" t="n"/>
+      <c r="AG80" s="12" t="n"/>
+      <c r="AH80" s="12" t="n"/>
+      <c r="AI80" s="12" t="n"/>
+      <c r="AJ80" s="14" t="n"/>
+      <c r="AK80" s="15">
         <f>IF(TODAY()&lt;AD80, 0, IF(TODAY()&gt;AE80, AF80, AF80 * (TODAY()-AD80)/(AE80-AD80+1)))</f>
         <v/>
       </c>
-      <c r="AL80" s="5">
+      <c r="AL80" s="15">
         <f>AF80 * (AJ80/100)</f>
         <v/>
       </c>
-      <c r="AM80" s="5">
+      <c r="AM80" s="16">
         <f>AI80</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="L81" s="4" t="n"/>
-      <c r="M81" s="5">
+      <c r="A81" s="11" t="n"/>
+      <c r="B81" s="12" t="n"/>
+      <c r="C81" s="13" t="n"/>
+      <c r="D81" s="12" t="n"/>
+      <c r="E81" s="12" t="n"/>
+      <c r="F81" s="12" t="n"/>
+      <c r="G81" s="12" t="n"/>
+      <c r="H81" s="12" t="n"/>
+      <c r="I81" s="12" t="n"/>
+      <c r="J81" s="12" t="n"/>
+      <c r="K81" s="12" t="n"/>
+      <c r="L81" s="14" t="n"/>
+      <c r="M81" s="15">
         <f>IF(TODAY()&lt;F81, 0, IF(TODAY()&gt;G81, H81, H81 * (TODAY()-F81)/(G81-F81+1)))</f>
         <v/>
       </c>
-      <c r="N81" s="5">
+      <c r="N81" s="15">
         <f>H81 * (L81/100)</f>
         <v/>
       </c>
-      <c r="O81" s="5">
+      <c r="O81" s="16">
         <f>K81</f>
         <v/>
       </c>
-      <c r="X81" s="4" t="n"/>
-      <c r="Y81" s="5">
+      <c r="P81" s="12" t="n"/>
+      <c r="Q81" s="12" t="n"/>
+      <c r="R81" s="12" t="n"/>
+      <c r="S81" s="12" t="n"/>
+      <c r="T81" s="12" t="n"/>
+      <c r="U81" s="12" t="n"/>
+      <c r="V81" s="12" t="n"/>
+      <c r="W81" s="12" t="n"/>
+      <c r="X81" s="14" t="n"/>
+      <c r="Y81" s="15">
         <f>IF(TODAY()&lt;R81, 0, IF(TODAY()&gt;S81, T81, T81 * (TODAY()-R81)/(S81-R81+1)))</f>
         <v/>
       </c>
-      <c r="Z81" s="5">
+      <c r="Z81" s="15">
         <f>T81 * (X81/100)</f>
         <v/>
       </c>
-      <c r="AA81" s="5">
+      <c r="AA81" s="16">
         <f>W81</f>
         <v/>
       </c>
-      <c r="AJ81" s="4" t="n"/>
-      <c r="AK81" s="5">
+      <c r="AB81" s="12" t="n"/>
+      <c r="AC81" s="12" t="n"/>
+      <c r="AD81" s="12" t="n"/>
+      <c r="AE81" s="12" t="n"/>
+      <c r="AF81" s="12" t="n"/>
+      <c r="AG81" s="12" t="n"/>
+      <c r="AH81" s="12" t="n"/>
+      <c r="AI81" s="12" t="n"/>
+      <c r="AJ81" s="14" t="n"/>
+      <c r="AK81" s="15">
         <f>IF(TODAY()&lt;AD81, 0, IF(TODAY()&gt;AE81, AF81, AF81 * (TODAY()-AD81)/(AE81-AD81+1)))</f>
         <v/>
       </c>
-      <c r="AL81" s="5">
+      <c r="AL81" s="15">
         <f>AF81 * (AJ81/100)</f>
         <v/>
       </c>
-      <c r="AM81" s="5">
+      <c r="AM81" s="16">
         <f>AI81</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="L82" s="4" t="n"/>
-      <c r="M82" s="5">
+      <c r="A82" s="11" t="n"/>
+      <c r="B82" s="12" t="n"/>
+      <c r="C82" s="13" t="n"/>
+      <c r="D82" s="12" t="n"/>
+      <c r="E82" s="12" t="n"/>
+      <c r="F82" s="12" t="n"/>
+      <c r="G82" s="12" t="n"/>
+      <c r="H82" s="12" t="n"/>
+      <c r="I82" s="12" t="n"/>
+      <c r="J82" s="12" t="n"/>
+      <c r="K82" s="12" t="n"/>
+      <c r="L82" s="14" t="n"/>
+      <c r="M82" s="15">
         <f>IF(TODAY()&lt;F82, 0, IF(TODAY()&gt;G82, H82, H82 * (TODAY()-F82)/(G82-F82+1)))</f>
         <v/>
       </c>
-      <c r="N82" s="5">
+      <c r="N82" s="15">
         <f>H82 * (L82/100)</f>
         <v/>
       </c>
-      <c r="O82" s="5">
+      <c r="O82" s="16">
         <f>K82</f>
         <v/>
       </c>
-      <c r="X82" s="4" t="n"/>
-      <c r="Y82" s="5">
+      <c r="P82" s="12" t="n"/>
+      <c r="Q82" s="12" t="n"/>
+      <c r="R82" s="12" t="n"/>
+      <c r="S82" s="12" t="n"/>
+      <c r="T82" s="12" t="n"/>
+      <c r="U82" s="12" t="n"/>
+      <c r="V82" s="12" t="n"/>
+      <c r="W82" s="12" t="n"/>
+      <c r="X82" s="14" t="n"/>
+      <c r="Y82" s="15">
         <f>IF(TODAY()&lt;R82, 0, IF(TODAY()&gt;S82, T82, T82 * (TODAY()-R82)/(S82-R82+1)))</f>
         <v/>
       </c>
-      <c r="Z82" s="5">
+      <c r="Z82" s="15">
         <f>T82 * (X82/100)</f>
         <v/>
       </c>
-      <c r="AA82" s="5">
+      <c r="AA82" s="16">
         <f>W82</f>
         <v/>
       </c>
-      <c r="AJ82" s="4" t="n"/>
-      <c r="AK82" s="5">
+      <c r="AB82" s="12" t="n"/>
+      <c r="AC82" s="12" t="n"/>
+      <c r="AD82" s="12" t="n"/>
+      <c r="AE82" s="12" t="n"/>
+      <c r="AF82" s="12" t="n"/>
+      <c r="AG82" s="12" t="n"/>
+      <c r="AH82" s="12" t="n"/>
+      <c r="AI82" s="12" t="n"/>
+      <c r="AJ82" s="14" t="n"/>
+      <c r="AK82" s="15">
         <f>IF(TODAY()&lt;AD82, 0, IF(TODAY()&gt;AE82, AF82, AF82 * (TODAY()-AD82)/(AE82-AD82+1)))</f>
         <v/>
       </c>
-      <c r="AL82" s="5">
+      <c r="AL82" s="15">
         <f>AF82 * (AJ82/100)</f>
         <v/>
       </c>
-      <c r="AM82" s="5">
+      <c r="AM82" s="16">
         <f>AI82</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="L83" s="4" t="n"/>
-      <c r="M83" s="5">
+      <c r="A83" s="11" t="n"/>
+      <c r="B83" s="12" t="n"/>
+      <c r="C83" s="13" t="n"/>
+      <c r="D83" s="12" t="n"/>
+      <c r="E83" s="12" t="n"/>
+      <c r="F83" s="12" t="n"/>
+      <c r="G83" s="12" t="n"/>
+      <c r="H83" s="12" t="n"/>
+      <c r="I83" s="12" t="n"/>
+      <c r="J83" s="12" t="n"/>
+      <c r="K83" s="12" t="n"/>
+      <c r="L83" s="14" t="n"/>
+      <c r="M83" s="15">
         <f>IF(TODAY()&lt;F83, 0, IF(TODAY()&gt;G83, H83, H83 * (TODAY()-F83)/(G83-F83+1)))</f>
         <v/>
       </c>
-      <c r="N83" s="5">
+      <c r="N83" s="15">
         <f>H83 * (L83/100)</f>
         <v/>
       </c>
-      <c r="O83" s="5">
+      <c r="O83" s="16">
         <f>K83</f>
         <v/>
       </c>
-      <c r="X83" s="4" t="n"/>
-      <c r="Y83" s="5">
+      <c r="P83" s="12" t="n"/>
+      <c r="Q83" s="12" t="n"/>
+      <c r="R83" s="12" t="n"/>
+      <c r="S83" s="12" t="n"/>
+      <c r="T83" s="12" t="n"/>
+      <c r="U83" s="12" t="n"/>
+      <c r="V83" s="12" t="n"/>
+      <c r="W83" s="12" t="n"/>
+      <c r="X83" s="14" t="n"/>
+      <c r="Y83" s="15">
         <f>IF(TODAY()&lt;R83, 0, IF(TODAY()&gt;S83, T83, T83 * (TODAY()-R83)/(S83-R83+1)))</f>
         <v/>
       </c>
-      <c r="Z83" s="5">
+      <c r="Z83" s="15">
         <f>T83 * (X83/100)</f>
         <v/>
       </c>
-      <c r="AA83" s="5">
+      <c r="AA83" s="16">
         <f>W83</f>
         <v/>
       </c>
-      <c r="AJ83" s="4" t="n"/>
-      <c r="AK83" s="5">
+      <c r="AB83" s="12" t="n"/>
+      <c r="AC83" s="12" t="n"/>
+      <c r="AD83" s="12" t="n"/>
+      <c r="AE83" s="12" t="n"/>
+      <c r="AF83" s="12" t="n"/>
+      <c r="AG83" s="12" t="n"/>
+      <c r="AH83" s="12" t="n"/>
+      <c r="AI83" s="12" t="n"/>
+      <c r="AJ83" s="14" t="n"/>
+      <c r="AK83" s="15">
         <f>IF(TODAY()&lt;AD83, 0, IF(TODAY()&gt;AE83, AF83, AF83 * (TODAY()-AD83)/(AE83-AD83+1)))</f>
         <v/>
       </c>
-      <c r="AL83" s="5">
+      <c r="AL83" s="15">
         <f>AF83 * (AJ83/100)</f>
         <v/>
       </c>
-      <c r="AM83" s="5">
+      <c r="AM83" s="16">
         <f>AI83</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="L84" s="4" t="n"/>
-      <c r="M84" s="5">
+      <c r="A84" s="11" t="n"/>
+      <c r="B84" s="12" t="n"/>
+      <c r="C84" s="13" t="n"/>
+      <c r="D84" s="12" t="n"/>
+      <c r="E84" s="12" t="n"/>
+      <c r="F84" s="12" t="n"/>
+      <c r="G84" s="12" t="n"/>
+      <c r="H84" s="12" t="n"/>
+      <c r="I84" s="12" t="n"/>
+      <c r="J84" s="12" t="n"/>
+      <c r="K84" s="12" t="n"/>
+      <c r="L84" s="14" t="n"/>
+      <c r="M84" s="15">
         <f>IF(TODAY()&lt;F84, 0, IF(TODAY()&gt;G84, H84, H84 * (TODAY()-F84)/(G84-F84+1)))</f>
         <v/>
       </c>
-      <c r="N84" s="5">
+      <c r="N84" s="15">
         <f>H84 * (L84/100)</f>
         <v/>
       </c>
-      <c r="O84" s="5">
+      <c r="O84" s="16">
         <f>K84</f>
         <v/>
       </c>
-      <c r="X84" s="4" t="n"/>
-      <c r="Y84" s="5">
+      <c r="P84" s="12" t="n"/>
+      <c r="Q84" s="12" t="n"/>
+      <c r="R84" s="12" t="n"/>
+      <c r="S84" s="12" t="n"/>
+      <c r="T84" s="12" t="n"/>
+      <c r="U84" s="12" t="n"/>
+      <c r="V84" s="12" t="n"/>
+      <c r="W84" s="12" t="n"/>
+      <c r="X84" s="14" t="n"/>
+      <c r="Y84" s="15">
         <f>IF(TODAY()&lt;R84, 0, IF(TODAY()&gt;S84, T84, T84 * (TODAY()-R84)/(S84-R84+1)))</f>
         <v/>
       </c>
-      <c r="Z84" s="5">
+      <c r="Z84" s="15">
         <f>T84 * (X84/100)</f>
         <v/>
       </c>
-      <c r="AA84" s="5">
+      <c r="AA84" s="16">
         <f>W84</f>
         <v/>
       </c>
-      <c r="AJ84" s="4" t="n"/>
-      <c r="AK84" s="5">
+      <c r="AB84" s="12" t="n"/>
+      <c r="AC84" s="12" t="n"/>
+      <c r="AD84" s="12" t="n"/>
+      <c r="AE84" s="12" t="n"/>
+      <c r="AF84" s="12" t="n"/>
+      <c r="AG84" s="12" t="n"/>
+      <c r="AH84" s="12" t="n"/>
+      <c r="AI84" s="12" t="n"/>
+      <c r="AJ84" s="14" t="n"/>
+      <c r="AK84" s="15">
         <f>IF(TODAY()&lt;AD84, 0, IF(TODAY()&gt;AE84, AF84, AF84 * (TODAY()-AD84)/(AE84-AD84+1)))</f>
         <v/>
       </c>
-      <c r="AL84" s="5">
+      <c r="AL84" s="15">
         <f>AF84 * (AJ84/100)</f>
         <v/>
       </c>
-      <c r="AM84" s="5">
+      <c r="AM84" s="16">
         <f>AI84</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="L85" s="4" t="n"/>
-      <c r="M85" s="5">
+      <c r="A85" s="11" t="n"/>
+      <c r="B85" s="12" t="n"/>
+      <c r="C85" s="13" t="n"/>
+      <c r="D85" s="12" t="n"/>
+      <c r="E85" s="12" t="n"/>
+      <c r="F85" s="12" t="n"/>
+      <c r="G85" s="12" t="n"/>
+      <c r="H85" s="12" t="n"/>
+      <c r="I85" s="12" t="n"/>
+      <c r="J85" s="12" t="n"/>
+      <c r="K85" s="12" t="n"/>
+      <c r="L85" s="14" t="n"/>
+      <c r="M85" s="15">
         <f>IF(TODAY()&lt;F85, 0, IF(TODAY()&gt;G85, H85, H85 * (TODAY()-F85)/(G85-F85+1)))</f>
         <v/>
       </c>
-      <c r="N85" s="5">
+      <c r="N85" s="15">
         <f>H85 * (L85/100)</f>
         <v/>
       </c>
-      <c r="O85" s="5">
+      <c r="O85" s="16">
         <f>K85</f>
         <v/>
       </c>
-      <c r="X85" s="4" t="n"/>
-      <c r="Y85" s="5">
+      <c r="P85" s="12" t="n"/>
+      <c r="Q85" s="12" t="n"/>
+      <c r="R85" s="12" t="n"/>
+      <c r="S85" s="12" t="n"/>
+      <c r="T85" s="12" t="n"/>
+      <c r="U85" s="12" t="n"/>
+      <c r="V85" s="12" t="n"/>
+      <c r="W85" s="12" t="n"/>
+      <c r="X85" s="14" t="n"/>
+      <c r="Y85" s="15">
         <f>IF(TODAY()&lt;R85, 0, IF(TODAY()&gt;S85, T85, T85 * (TODAY()-R85)/(S85-R85+1)))</f>
         <v/>
       </c>
-      <c r="Z85" s="5">
+      <c r="Z85" s="15">
         <f>T85 * (X85/100)</f>
         <v/>
       </c>
-      <c r="AA85" s="5">
+      <c r="AA85" s="16">
         <f>W85</f>
         <v/>
       </c>
-      <c r="AJ85" s="4" t="n"/>
-      <c r="AK85" s="5">
+      <c r="AB85" s="12" t="n"/>
+      <c r="AC85" s="12" t="n"/>
+      <c r="AD85" s="12" t="n"/>
+      <c r="AE85" s="12" t="n"/>
+      <c r="AF85" s="12" t="n"/>
+      <c r="AG85" s="12" t="n"/>
+      <c r="AH85" s="12" t="n"/>
+      <c r="AI85" s="12" t="n"/>
+      <c r="AJ85" s="14" t="n"/>
+      <c r="AK85" s="15">
         <f>IF(TODAY()&lt;AD85, 0, IF(TODAY()&gt;AE85, AF85, AF85 * (TODAY()-AD85)/(AE85-AD85+1)))</f>
         <v/>
       </c>
-      <c r="AL85" s="5">
+      <c r="AL85" s="15">
         <f>AF85 * (AJ85/100)</f>
         <v/>
       </c>
-      <c r="AM85" s="5">
+      <c r="AM85" s="16">
         <f>AI85</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="L86" s="4" t="n"/>
-      <c r="M86" s="5">
+      <c r="A86" s="11" t="n"/>
+      <c r="B86" s="12" t="n"/>
+      <c r="C86" s="13" t="n"/>
+      <c r="D86" s="12" t="n"/>
+      <c r="E86" s="12" t="n"/>
+      <c r="F86" s="12" t="n"/>
+      <c r="G86" s="12" t="n"/>
+      <c r="H86" s="12" t="n"/>
+      <c r="I86" s="12" t="n"/>
+      <c r="J86" s="12" t="n"/>
+      <c r="K86" s="12" t="n"/>
+      <c r="L86" s="14" t="n"/>
+      <c r="M86" s="15">
         <f>IF(TODAY()&lt;F86, 0, IF(TODAY()&gt;G86, H86, H86 * (TODAY()-F86)/(G86-F86+1)))</f>
         <v/>
       </c>
-      <c r="N86" s="5">
+      <c r="N86" s="15">
         <f>H86 * (L86/100)</f>
         <v/>
       </c>
-      <c r="O86" s="5">
+      <c r="O86" s="16">
         <f>K86</f>
         <v/>
       </c>
-      <c r="X86" s="4" t="n"/>
-      <c r="Y86" s="5">
+      <c r="P86" s="12" t="n"/>
+      <c r="Q86" s="12" t="n"/>
+      <c r="R86" s="12" t="n"/>
+      <c r="S86" s="12" t="n"/>
+      <c r="T86" s="12" t="n"/>
+      <c r="U86" s="12" t="n"/>
+      <c r="V86" s="12" t="n"/>
+      <c r="W86" s="12" t="n"/>
+      <c r="X86" s="14" t="n"/>
+      <c r="Y86" s="15">
         <f>IF(TODAY()&lt;R86, 0, IF(TODAY()&gt;S86, T86, T86 * (TODAY()-R86)/(S86-R86+1)))</f>
         <v/>
       </c>
-      <c r="Z86" s="5">
+      <c r="Z86" s="15">
         <f>T86 * (X86/100)</f>
         <v/>
       </c>
-      <c r="AA86" s="5">
+      <c r="AA86" s="16">
         <f>W86</f>
         <v/>
       </c>
-      <c r="AJ86" s="4" t="n"/>
-      <c r="AK86" s="5">
+      <c r="AB86" s="12" t="n"/>
+      <c r="AC86" s="12" t="n"/>
+      <c r="AD86" s="12" t="n"/>
+      <c r="AE86" s="12" t="n"/>
+      <c r="AF86" s="12" t="n"/>
+      <c r="AG86" s="12" t="n"/>
+      <c r="AH86" s="12" t="n"/>
+      <c r="AI86" s="12" t="n"/>
+      <c r="AJ86" s="14" t="n"/>
+      <c r="AK86" s="15">
         <f>IF(TODAY()&lt;AD86, 0, IF(TODAY()&gt;AE86, AF86, AF86 * (TODAY()-AD86)/(AE86-AD86+1)))</f>
         <v/>
       </c>
-      <c r="AL86" s="5">
+      <c r="AL86" s="15">
         <f>AF86 * (AJ86/100)</f>
         <v/>
       </c>
-      <c r="AM86" s="5">
+      <c r="AM86" s="16">
         <f>AI86</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="L87" s="4" t="n"/>
-      <c r="M87" s="5">
+      <c r="A87" s="11" t="n"/>
+      <c r="B87" s="12" t="n"/>
+      <c r="C87" s="13" t="n"/>
+      <c r="D87" s="12" t="n"/>
+      <c r="E87" s="12" t="n"/>
+      <c r="F87" s="12" t="n"/>
+      <c r="G87" s="12" t="n"/>
+      <c r="H87" s="12" t="n"/>
+      <c r="I87" s="12" t="n"/>
+      <c r="J87" s="12" t="n"/>
+      <c r="K87" s="12" t="n"/>
+      <c r="L87" s="14" t="n"/>
+      <c r="M87" s="15">
         <f>IF(TODAY()&lt;F87, 0, IF(TODAY()&gt;G87, H87, H87 * (TODAY()-F87)/(G87-F87+1)))</f>
         <v/>
       </c>
-      <c r="N87" s="5">
+      <c r="N87" s="15">
         <f>H87 * (L87/100)</f>
         <v/>
       </c>
-      <c r="O87" s="5">
+      <c r="O87" s="16">
         <f>K87</f>
         <v/>
       </c>
-      <c r="X87" s="4" t="n"/>
-      <c r="Y87" s="5">
+      <c r="P87" s="12" t="n"/>
+      <c r="Q87" s="12" t="n"/>
+      <c r="R87" s="12" t="n"/>
+      <c r="S87" s="12" t="n"/>
+      <c r="T87" s="12" t="n"/>
+      <c r="U87" s="12" t="n"/>
+      <c r="V87" s="12" t="n"/>
+      <c r="W87" s="12" t="n"/>
+      <c r="X87" s="14" t="n"/>
+      <c r="Y87" s="15">
         <f>IF(TODAY()&lt;R87, 0, IF(TODAY()&gt;S87, T87, T87 * (TODAY()-R87)/(S87-R87+1)))</f>
         <v/>
       </c>
-      <c r="Z87" s="5">
+      <c r="Z87" s="15">
         <f>T87 * (X87/100)</f>
         <v/>
       </c>
-      <c r="AA87" s="5">
+      <c r="AA87" s="16">
         <f>W87</f>
         <v/>
       </c>
-      <c r="AJ87" s="4" t="n"/>
-      <c r="AK87" s="5">
+      <c r="AB87" s="12" t="n"/>
+      <c r="AC87" s="12" t="n"/>
+      <c r="AD87" s="12" t="n"/>
+      <c r="AE87" s="12" t="n"/>
+      <c r="AF87" s="12" t="n"/>
+      <c r="AG87" s="12" t="n"/>
+      <c r="AH87" s="12" t="n"/>
+      <c r="AI87" s="12" t="n"/>
+      <c r="AJ87" s="14" t="n"/>
+      <c r="AK87" s="15">
         <f>IF(TODAY()&lt;AD87, 0, IF(TODAY()&gt;AE87, AF87, AF87 * (TODAY()-AD87)/(AE87-AD87+1)))</f>
         <v/>
       </c>
-      <c r="AL87" s="5">
+      <c r="AL87" s="15">
         <f>AF87 * (AJ87/100)</f>
         <v/>
       </c>
-      <c r="AM87" s="5">
+      <c r="AM87" s="16">
         <f>AI87</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="L88" s="4" t="n"/>
-      <c r="M88" s="5">
+      <c r="A88" s="11" t="n"/>
+      <c r="B88" s="12" t="n"/>
+      <c r="C88" s="13" t="n"/>
+      <c r="D88" s="12" t="n"/>
+      <c r="E88" s="12" t="n"/>
+      <c r="F88" s="12" t="n"/>
+      <c r="G88" s="12" t="n"/>
+      <c r="H88" s="12" t="n"/>
+      <c r="I88" s="12" t="n"/>
+      <c r="J88" s="12" t="n"/>
+      <c r="K88" s="12" t="n"/>
+      <c r="L88" s="14" t="n"/>
+      <c r="M88" s="15">
         <f>IF(TODAY()&lt;F88, 0, IF(TODAY()&gt;G88, H88, H88 * (TODAY()-F88)/(G88-F88+1)))</f>
         <v/>
       </c>
-      <c r="N88" s="5">
+      <c r="N88" s="15">
         <f>H88 * (L88/100)</f>
         <v/>
       </c>
-      <c r="O88" s="5">
+      <c r="O88" s="16">
         <f>K88</f>
         <v/>
       </c>
-      <c r="X88" s="4" t="n"/>
-      <c r="Y88" s="5">
+      <c r="P88" s="12" t="n"/>
+      <c r="Q88" s="12" t="n"/>
+      <c r="R88" s="12" t="n"/>
+      <c r="S88" s="12" t="n"/>
+      <c r="T88" s="12" t="n"/>
+      <c r="U88" s="12" t="n"/>
+      <c r="V88" s="12" t="n"/>
+      <c r="W88" s="12" t="n"/>
+      <c r="X88" s="14" t="n"/>
+      <c r="Y88" s="15">
         <f>IF(TODAY()&lt;R88, 0, IF(TODAY()&gt;S88, T88, T88 * (TODAY()-R88)/(S88-R88+1)))</f>
         <v/>
       </c>
-      <c r="Z88" s="5">
+      <c r="Z88" s="15">
         <f>T88 * (X88/100)</f>
         <v/>
       </c>
-      <c r="AA88" s="5">
+      <c r="AA88" s="16">
         <f>W88</f>
         <v/>
       </c>
-      <c r="AJ88" s="4" t="n"/>
-      <c r="AK88" s="5">
+      <c r="AB88" s="12" t="n"/>
+      <c r="AC88" s="12" t="n"/>
+      <c r="AD88" s="12" t="n"/>
+      <c r="AE88" s="12" t="n"/>
+      <c r="AF88" s="12" t="n"/>
+      <c r="AG88" s="12" t="n"/>
+      <c r="AH88" s="12" t="n"/>
+      <c r="AI88" s="12" t="n"/>
+      <c r="AJ88" s="14" t="n"/>
+      <c r="AK88" s="15">
         <f>IF(TODAY()&lt;AD88, 0, IF(TODAY()&gt;AE88, AF88, AF88 * (TODAY()-AD88)/(AE88-AD88+1)))</f>
         <v/>
       </c>
-      <c r="AL88" s="5">
+      <c r="AL88" s="15">
         <f>AF88 * (AJ88/100)</f>
         <v/>
       </c>
-      <c r="AM88" s="5">
+      <c r="AM88" s="16">
         <f>AI88</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="L89" s="4" t="n"/>
-      <c r="M89" s="5">
+      <c r="A89" s="11" t="n"/>
+      <c r="B89" s="12" t="n"/>
+      <c r="C89" s="13" t="n"/>
+      <c r="D89" s="12" t="n"/>
+      <c r="E89" s="12" t="n"/>
+      <c r="F89" s="12" t="n"/>
+      <c r="G89" s="12" t="n"/>
+      <c r="H89" s="12" t="n"/>
+      <c r="I89" s="12" t="n"/>
+      <c r="J89" s="12" t="n"/>
+      <c r="K89" s="12" t="n"/>
+      <c r="L89" s="14" t="n"/>
+      <c r="M89" s="15">
         <f>IF(TODAY()&lt;F89, 0, IF(TODAY()&gt;G89, H89, H89 * (TODAY()-F89)/(G89-F89+1)))</f>
         <v/>
       </c>
-      <c r="N89" s="5">
+      <c r="N89" s="15">
         <f>H89 * (L89/100)</f>
         <v/>
       </c>
-      <c r="O89" s="5">
+      <c r="O89" s="16">
         <f>K89</f>
         <v/>
       </c>
-      <c r="X89" s="4" t="n"/>
-      <c r="Y89" s="5">
+      <c r="P89" s="12" t="n"/>
+      <c r="Q89" s="12" t="n"/>
+      <c r="R89" s="12" t="n"/>
+      <c r="S89" s="12" t="n"/>
+      <c r="T89" s="12" t="n"/>
+      <c r="U89" s="12" t="n"/>
+      <c r="V89" s="12" t="n"/>
+      <c r="W89" s="12" t="n"/>
+      <c r="X89" s="14" t="n"/>
+      <c r="Y89" s="15">
         <f>IF(TODAY()&lt;R89, 0, IF(TODAY()&gt;S89, T89, T89 * (TODAY()-R89)/(S89-R89+1)))</f>
         <v/>
       </c>
-      <c r="Z89" s="5">
+      <c r="Z89" s="15">
         <f>T89 * (X89/100)</f>
         <v/>
       </c>
-      <c r="AA89" s="5">
+      <c r="AA89" s="16">
         <f>W89</f>
         <v/>
       </c>
-      <c r="AJ89" s="4" t="n"/>
-      <c r="AK89" s="5">
+      <c r="AB89" s="12" t="n"/>
+      <c r="AC89" s="12" t="n"/>
+      <c r="AD89" s="12" t="n"/>
+      <c r="AE89" s="12" t="n"/>
+      <c r="AF89" s="12" t="n"/>
+      <c r="AG89" s="12" t="n"/>
+      <c r="AH89" s="12" t="n"/>
+      <c r="AI89" s="12" t="n"/>
+      <c r="AJ89" s="14" t="n"/>
+      <c r="AK89" s="15">
         <f>IF(TODAY()&lt;AD89, 0, IF(TODAY()&gt;AE89, AF89, AF89 * (TODAY()-AD89)/(AE89-AD89+1)))</f>
         <v/>
       </c>
-      <c r="AL89" s="5">
+      <c r="AL89" s="15">
         <f>AF89 * (AJ89/100)</f>
         <v/>
       </c>
-      <c r="AM89" s="5">
+      <c r="AM89" s="16">
         <f>AI89</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="L90" s="4" t="n"/>
-      <c r="M90" s="5">
+      <c r="A90" s="11" t="n"/>
+      <c r="B90" s="12" t="n"/>
+      <c r="C90" s="13" t="n"/>
+      <c r="D90" s="12" t="n"/>
+      <c r="E90" s="12" t="n"/>
+      <c r="F90" s="12" t="n"/>
+      <c r="G90" s="12" t="n"/>
+      <c r="H90" s="12" t="n"/>
+      <c r="I90" s="12" t="n"/>
+      <c r="J90" s="12" t="n"/>
+      <c r="K90" s="12" t="n"/>
+      <c r="L90" s="14" t="n"/>
+      <c r="M90" s="15">
         <f>IF(TODAY()&lt;F90, 0, IF(TODAY()&gt;G90, H90, H90 * (TODAY()-F90)/(G90-F90+1)))</f>
         <v/>
       </c>
-      <c r="N90" s="5">
+      <c r="N90" s="15">
         <f>H90 * (L90/100)</f>
         <v/>
       </c>
-      <c r="O90" s="5">
+      <c r="O90" s="16">
         <f>K90</f>
         <v/>
       </c>
-      <c r="X90" s="4" t="n"/>
-      <c r="Y90" s="5">
+      <c r="P90" s="12" t="n"/>
+      <c r="Q90" s="12" t="n"/>
+      <c r="R90" s="12" t="n"/>
+      <c r="S90" s="12" t="n"/>
+      <c r="T90" s="12" t="n"/>
+      <c r="U90" s="12" t="n"/>
+      <c r="V90" s="12" t="n"/>
+      <c r="W90" s="12" t="n"/>
+      <c r="X90" s="14" t="n"/>
+      <c r="Y90" s="15">
         <f>IF(TODAY()&lt;R90, 0, IF(TODAY()&gt;S90, T90, T90 * (TODAY()-R90)/(S90-R90+1)))</f>
         <v/>
       </c>
-      <c r="Z90" s="5">
+      <c r="Z90" s="15">
         <f>T90 * (X90/100)</f>
         <v/>
       </c>
-      <c r="AA90" s="5">
+      <c r="AA90" s="16">
         <f>W90</f>
         <v/>
       </c>
-      <c r="AJ90" s="4" t="n"/>
-      <c r="AK90" s="5">
+      <c r="AB90" s="12" t="n"/>
+      <c r="AC90" s="12" t="n"/>
+      <c r="AD90" s="12" t="n"/>
+      <c r="AE90" s="12" t="n"/>
+      <c r="AF90" s="12" t="n"/>
+      <c r="AG90" s="12" t="n"/>
+      <c r="AH90" s="12" t="n"/>
+      <c r="AI90" s="12" t="n"/>
+      <c r="AJ90" s="14" t="n"/>
+      <c r="AK90" s="15">
         <f>IF(TODAY()&lt;AD90, 0, IF(TODAY()&gt;AE90, AF90, AF90 * (TODAY()-AD90)/(AE90-AD90+1)))</f>
         <v/>
       </c>
-      <c r="AL90" s="5">
+      <c r="AL90" s="15">
         <f>AF90 * (AJ90/100)</f>
         <v/>
       </c>
-      <c r="AM90" s="5">
+      <c r="AM90" s="16">
         <f>AI90</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="L91" s="4" t="n"/>
-      <c r="M91" s="5">
+      <c r="A91" s="11" t="n"/>
+      <c r="B91" s="12" t="n"/>
+      <c r="C91" s="13" t="n"/>
+      <c r="D91" s="12" t="n"/>
+      <c r="E91" s="12" t="n"/>
+      <c r="F91" s="12" t="n"/>
+      <c r="G91" s="12" t="n"/>
+      <c r="H91" s="12" t="n"/>
+      <c r="I91" s="12" t="n"/>
+      <c r="J91" s="12" t="n"/>
+      <c r="K91" s="12" t="n"/>
+      <c r="L91" s="14" t="n"/>
+      <c r="M91" s="15">
         <f>IF(TODAY()&lt;F91, 0, IF(TODAY()&gt;G91, H91, H91 * (TODAY()-F91)/(G91-F91+1)))</f>
         <v/>
       </c>
-      <c r="N91" s="5">
+      <c r="N91" s="15">
         <f>H91 * (L91/100)</f>
         <v/>
       </c>
-      <c r="O91" s="5">
+      <c r="O91" s="16">
         <f>K91</f>
         <v/>
       </c>
-      <c r="X91" s="4" t="n"/>
-      <c r="Y91" s="5">
+      <c r="P91" s="12" t="n"/>
+      <c r="Q91" s="12" t="n"/>
+      <c r="R91" s="12" t="n"/>
+      <c r="S91" s="12" t="n"/>
+      <c r="T91" s="12" t="n"/>
+      <c r="U91" s="12" t="n"/>
+      <c r="V91" s="12" t="n"/>
+      <c r="W91" s="12" t="n"/>
+      <c r="X91" s="14" t="n"/>
+      <c r="Y91" s="15">
         <f>IF(TODAY()&lt;R91, 0, IF(TODAY()&gt;S91, T91, T91 * (TODAY()-R91)/(S91-R91+1)))</f>
         <v/>
       </c>
-      <c r="Z91" s="5">
+      <c r="Z91" s="15">
         <f>T91 * (X91/100)</f>
         <v/>
       </c>
-      <c r="AA91" s="5">
+      <c r="AA91" s="16">
         <f>W91</f>
         <v/>
       </c>
-      <c r="AJ91" s="4" t="n"/>
-      <c r="AK91" s="5">
+      <c r="AB91" s="12" t="n"/>
+      <c r="AC91" s="12" t="n"/>
+      <c r="AD91" s="12" t="n"/>
+      <c r="AE91" s="12" t="n"/>
+      <c r="AF91" s="12" t="n"/>
+      <c r="AG91" s="12" t="n"/>
+      <c r="AH91" s="12" t="n"/>
+      <c r="AI91" s="12" t="n"/>
+      <c r="AJ91" s="14" t="n"/>
+      <c r="AK91" s="15">
         <f>IF(TODAY()&lt;AD91, 0, IF(TODAY()&gt;AE91, AF91, AF91 * (TODAY()-AD91)/(AE91-AD91+1)))</f>
         <v/>
       </c>
-      <c r="AL91" s="5">
+      <c r="AL91" s="15">
         <f>AF91 * (AJ91/100)</f>
         <v/>
       </c>
-      <c r="AM91" s="5">
+      <c r="AM91" s="16">
         <f>AI91</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="L92" s="4" t="n"/>
-      <c r="M92" s="5">
+      <c r="A92" s="11" t="n"/>
+      <c r="B92" s="12" t="n"/>
+      <c r="C92" s="13" t="n"/>
+      <c r="D92" s="12" t="n"/>
+      <c r="E92" s="12" t="n"/>
+      <c r="F92" s="12" t="n"/>
+      <c r="G92" s="12" t="n"/>
+      <c r="H92" s="12" t="n"/>
+      <c r="I92" s="12" t="n"/>
+      <c r="J92" s="12" t="n"/>
+      <c r="K92" s="12" t="n"/>
+      <c r="L92" s="14" t="n"/>
+      <c r="M92" s="15">
         <f>IF(TODAY()&lt;F92, 0, IF(TODAY()&gt;G92, H92, H92 * (TODAY()-F92)/(G92-F92+1)))</f>
         <v/>
       </c>
-      <c r="N92" s="5">
+      <c r="N92" s="15">
         <f>H92 * (L92/100)</f>
         <v/>
       </c>
-      <c r="O92" s="5">
+      <c r="O92" s="16">
         <f>K92</f>
         <v/>
       </c>
-      <c r="X92" s="4" t="n"/>
-      <c r="Y92" s="5">
+      <c r="P92" s="12" t="n"/>
+      <c r="Q92" s="12" t="n"/>
+      <c r="R92" s="12" t="n"/>
+      <c r="S92" s="12" t="n"/>
+      <c r="T92" s="12" t="n"/>
+      <c r="U92" s="12" t="n"/>
+      <c r="V92" s="12" t="n"/>
+      <c r="W92" s="12" t="n"/>
+      <c r="X92" s="14" t="n"/>
+      <c r="Y92" s="15">
         <f>IF(TODAY()&lt;R92, 0, IF(TODAY()&gt;S92, T92, T92 * (TODAY()-R92)/(S92-R92+1)))</f>
         <v/>
       </c>
-      <c r="Z92" s="5">
+      <c r="Z92" s="15">
         <f>T92 * (X92/100)</f>
         <v/>
       </c>
-      <c r="AA92" s="5">
+      <c r="AA92" s="16">
         <f>W92</f>
         <v/>
       </c>
-      <c r="AJ92" s="4" t="n"/>
-      <c r="AK92" s="5">
+      <c r="AB92" s="12" t="n"/>
+      <c r="AC92" s="12" t="n"/>
+      <c r="AD92" s="12" t="n"/>
+      <c r="AE92" s="12" t="n"/>
+      <c r="AF92" s="12" t="n"/>
+      <c r="AG92" s="12" t="n"/>
+      <c r="AH92" s="12" t="n"/>
+      <c r="AI92" s="12" t="n"/>
+      <c r="AJ92" s="14" t="n"/>
+      <c r="AK92" s="15">
         <f>IF(TODAY()&lt;AD92, 0, IF(TODAY()&gt;AE92, AF92, AF92 * (TODAY()-AD92)/(AE92-AD92+1)))</f>
         <v/>
       </c>
-      <c r="AL92" s="5">
+      <c r="AL92" s="15">
         <f>AF92 * (AJ92/100)</f>
         <v/>
       </c>
-      <c r="AM92" s="5">
+      <c r="AM92" s="16">
         <f>AI92</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="L93" s="4" t="n"/>
-      <c r="M93" s="5">
+      <c r="A93" s="11" t="n"/>
+      <c r="B93" s="12" t="n"/>
+      <c r="C93" s="13" t="n"/>
+      <c r="D93" s="12" t="n"/>
+      <c r="E93" s="12" t="n"/>
+      <c r="F93" s="12" t="n"/>
+      <c r="G93" s="12" t="n"/>
+      <c r="H93" s="12" t="n"/>
+      <c r="I93" s="12" t="n"/>
+      <c r="J93" s="12" t="n"/>
+      <c r="K93" s="12" t="n"/>
+      <c r="L93" s="14" t="n"/>
+      <c r="M93" s="15">
         <f>IF(TODAY()&lt;F93, 0, IF(TODAY()&gt;G93, H93, H93 * (TODAY()-F93)/(G93-F93+1)))</f>
         <v/>
       </c>
-      <c r="N93" s="5">
+      <c r="N93" s="15">
         <f>H93 * (L93/100)</f>
         <v/>
       </c>
-      <c r="O93" s="5">
+      <c r="O93" s="16">
         <f>K93</f>
         <v/>
       </c>
-      <c r="X93" s="4" t="n"/>
-      <c r="Y93" s="5">
+      <c r="P93" s="12" t="n"/>
+      <c r="Q93" s="12" t="n"/>
+      <c r="R93" s="12" t="n"/>
+      <c r="S93" s="12" t="n"/>
+      <c r="T93" s="12" t="n"/>
+      <c r="U93" s="12" t="n"/>
+      <c r="V93" s="12" t="n"/>
+      <c r="W93" s="12" t="n"/>
+      <c r="X93" s="14" t="n"/>
+      <c r="Y93" s="15">
         <f>IF(TODAY()&lt;R93, 0, IF(TODAY()&gt;S93, T93, T93 * (TODAY()-R93)/(S93-R93+1)))</f>
         <v/>
       </c>
-      <c r="Z93" s="5">
+      <c r="Z93" s="15">
         <f>T93 * (X93/100)</f>
         <v/>
       </c>
-      <c r="AA93" s="5">
+      <c r="AA93" s="16">
         <f>W93</f>
         <v/>
       </c>
-      <c r="AJ93" s="4" t="n"/>
-      <c r="AK93" s="5">
+      <c r="AB93" s="12" t="n"/>
+      <c r="AC93" s="12" t="n"/>
+      <c r="AD93" s="12" t="n"/>
+      <c r="AE93" s="12" t="n"/>
+      <c r="AF93" s="12" t="n"/>
+      <c r="AG93" s="12" t="n"/>
+      <c r="AH93" s="12" t="n"/>
+      <c r="AI93" s="12" t="n"/>
+      <c r="AJ93" s="14" t="n"/>
+      <c r="AK93" s="15">
         <f>IF(TODAY()&lt;AD93, 0, IF(TODAY()&gt;AE93, AF93, AF93 * (TODAY()-AD93)/(AE93-AD93+1)))</f>
         <v/>
       </c>
-      <c r="AL93" s="5">
+      <c r="AL93" s="15">
         <f>AF93 * (AJ93/100)</f>
         <v/>
       </c>
-      <c r="AM93" s="5">
+      <c r="AM93" s="16">
         <f>AI93</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="L94" s="4" t="n"/>
-      <c r="M94" s="5">
+      <c r="A94" s="11" t="n"/>
+      <c r="B94" s="12" t="n"/>
+      <c r="C94" s="13" t="n"/>
+      <c r="D94" s="12" t="n"/>
+      <c r="E94" s="12" t="n"/>
+      <c r="F94" s="12" t="n"/>
+      <c r="G94" s="12" t="n"/>
+      <c r="H94" s="12" t="n"/>
+      <c r="I94" s="12" t="n"/>
+      <c r="J94" s="12" t="n"/>
+      <c r="K94" s="12" t="n"/>
+      <c r="L94" s="14" t="n"/>
+      <c r="M94" s="15">
         <f>IF(TODAY()&lt;F94, 0, IF(TODAY()&gt;G94, H94, H94 * (TODAY()-F94)/(G94-F94+1)))</f>
         <v/>
       </c>
-      <c r="N94" s="5">
+      <c r="N94" s="15">
         <f>H94 * (L94/100)</f>
         <v/>
       </c>
-      <c r="O94" s="5">
+      <c r="O94" s="16">
         <f>K94</f>
         <v/>
       </c>
-      <c r="X94" s="4" t="n"/>
-      <c r="Y94" s="5">
+      <c r="P94" s="12" t="n"/>
+      <c r="Q94" s="12" t="n"/>
+      <c r="R94" s="12" t="n"/>
+      <c r="S94" s="12" t="n"/>
+      <c r="T94" s="12" t="n"/>
+      <c r="U94" s="12" t="n"/>
+      <c r="V94" s="12" t="n"/>
+      <c r="W94" s="12" t="n"/>
+      <c r="X94" s="14" t="n"/>
+      <c r="Y94" s="15">
         <f>IF(TODAY()&lt;R94, 0, IF(TODAY()&gt;S94, T94, T94 * (TODAY()-R94)/(S94-R94+1)))</f>
         <v/>
       </c>
-      <c r="Z94" s="5">
+      <c r="Z94" s="15">
         <f>T94 * (X94/100)</f>
         <v/>
       </c>
-      <c r="AA94" s="5">
+      <c r="AA94" s="16">
         <f>W94</f>
         <v/>
       </c>
-      <c r="AJ94" s="4" t="n"/>
-      <c r="AK94" s="5">
+      <c r="AB94" s="12" t="n"/>
+      <c r="AC94" s="12" t="n"/>
+      <c r="AD94" s="12" t="n"/>
+      <c r="AE94" s="12" t="n"/>
+      <c r="AF94" s="12" t="n"/>
+      <c r="AG94" s="12" t="n"/>
+      <c r="AH94" s="12" t="n"/>
+      <c r="AI94" s="12" t="n"/>
+      <c r="AJ94" s="14" t="n"/>
+      <c r="AK94" s="15">
         <f>IF(TODAY()&lt;AD94, 0, IF(TODAY()&gt;AE94, AF94, AF94 * (TODAY()-AD94)/(AE94-AD94+1)))</f>
         <v/>
       </c>
-      <c r="AL94" s="5">
+      <c r="AL94" s="15">
         <f>AF94 * (AJ94/100)</f>
         <v/>
       </c>
-      <c r="AM94" s="5">
+      <c r="AM94" s="16">
         <f>AI94</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="L95" s="4" t="n"/>
-      <c r="M95" s="5">
+      <c r="A95" s="11" t="n"/>
+      <c r="B95" s="12" t="n"/>
+      <c r="C95" s="13" t="n"/>
+      <c r="D95" s="12" t="n"/>
+      <c r="E95" s="12" t="n"/>
+      <c r="F95" s="12" t="n"/>
+      <c r="G95" s="12" t="n"/>
+      <c r="H95" s="12" t="n"/>
+      <c r="I95" s="12" t="n"/>
+      <c r="J95" s="12" t="n"/>
+      <c r="K95" s="12" t="n"/>
+      <c r="L95" s="14" t="n"/>
+      <c r="M95" s="15">
         <f>IF(TODAY()&lt;F95, 0, IF(TODAY()&gt;G95, H95, H95 * (TODAY()-F95)/(G95-F95+1)))</f>
         <v/>
       </c>
-      <c r="N95" s="5">
+      <c r="N95" s="15">
         <f>H95 * (L95/100)</f>
         <v/>
       </c>
-      <c r="O95" s="5">
+      <c r="O95" s="16">
         <f>K95</f>
         <v/>
       </c>
-      <c r="X95" s="4" t="n"/>
-      <c r="Y95" s="5">
+      <c r="P95" s="12" t="n"/>
+      <c r="Q95" s="12" t="n"/>
+      <c r="R95" s="12" t="n"/>
+      <c r="S95" s="12" t="n"/>
+      <c r="T95" s="12" t="n"/>
+      <c r="U95" s="12" t="n"/>
+      <c r="V95" s="12" t="n"/>
+      <c r="W95" s="12" t="n"/>
+      <c r="X95" s="14" t="n"/>
+      <c r="Y95" s="15">
         <f>IF(TODAY()&lt;R95, 0, IF(TODAY()&gt;S95, T95, T95 * (TODAY()-R95)/(S95-R95+1)))</f>
         <v/>
       </c>
-      <c r="Z95" s="5">
+      <c r="Z95" s="15">
         <f>T95 * (X95/100)</f>
         <v/>
       </c>
-      <c r="AA95" s="5">
+      <c r="AA95" s="16">
         <f>W95</f>
         <v/>
       </c>
-      <c r="AJ95" s="4" t="n"/>
-      <c r="AK95" s="5">
+      <c r="AB95" s="12" t="n"/>
+      <c r="AC95" s="12" t="n"/>
+      <c r="AD95" s="12" t="n"/>
+      <c r="AE95" s="12" t="n"/>
+      <c r="AF95" s="12" t="n"/>
+      <c r="AG95" s="12" t="n"/>
+      <c r="AH95" s="12" t="n"/>
+      <c r="AI95" s="12" t="n"/>
+      <c r="AJ95" s="14" t="n"/>
+      <c r="AK95" s="15">
         <f>IF(TODAY()&lt;AD95, 0, IF(TODAY()&gt;AE95, AF95, AF95 * (TODAY()-AD95)/(AE95-AD95+1)))</f>
         <v/>
       </c>
-      <c r="AL95" s="5">
+      <c r="AL95" s="15">
         <f>AF95 * (AJ95/100)</f>
         <v/>
       </c>
-      <c r="AM95" s="5">
+      <c r="AM95" s="16">
         <f>AI95</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="L96" s="4" t="n"/>
-      <c r="M96" s="5">
+      <c r="A96" s="11" t="n"/>
+      <c r="B96" s="12" t="n"/>
+      <c r="C96" s="13" t="n"/>
+      <c r="D96" s="12" t="n"/>
+      <c r="E96" s="12" t="n"/>
+      <c r="F96" s="12" t="n"/>
+      <c r="G96" s="12" t="n"/>
+      <c r="H96" s="12" t="n"/>
+      <c r="I96" s="12" t="n"/>
+      <c r="J96" s="12" t="n"/>
+      <c r="K96" s="12" t="n"/>
+      <c r="L96" s="14" t="n"/>
+      <c r="M96" s="15">
         <f>IF(TODAY()&lt;F96, 0, IF(TODAY()&gt;G96, H96, H96 * (TODAY()-F96)/(G96-F96+1)))</f>
         <v/>
       </c>
-      <c r="N96" s="5">
+      <c r="N96" s="15">
         <f>H96 * (L96/100)</f>
         <v/>
       </c>
-      <c r="O96" s="5">
+      <c r="O96" s="16">
         <f>K96</f>
         <v/>
       </c>
-      <c r="X96" s="4" t="n"/>
-      <c r="Y96" s="5">
+      <c r="P96" s="12" t="n"/>
+      <c r="Q96" s="12" t="n"/>
+      <c r="R96" s="12" t="n"/>
+      <c r="S96" s="12" t="n"/>
+      <c r="T96" s="12" t="n"/>
+      <c r="U96" s="12" t="n"/>
+      <c r="V96" s="12" t="n"/>
+      <c r="W96" s="12" t="n"/>
+      <c r="X96" s="14" t="n"/>
+      <c r="Y96" s="15">
         <f>IF(TODAY()&lt;R96, 0, IF(TODAY()&gt;S96, T96, T96 * (TODAY()-R96)/(S96-R96+1)))</f>
         <v/>
       </c>
-      <c r="Z96" s="5">
+      <c r="Z96" s="15">
         <f>T96 * (X96/100)</f>
         <v/>
       </c>
-      <c r="AA96" s="5">
+      <c r="AA96" s="16">
         <f>W96</f>
         <v/>
       </c>
-      <c r="AJ96" s="4" t="n"/>
-      <c r="AK96" s="5">
+      <c r="AB96" s="12" t="n"/>
+      <c r="AC96" s="12" t="n"/>
+      <c r="AD96" s="12" t="n"/>
+      <c r="AE96" s="12" t="n"/>
+      <c r="AF96" s="12" t="n"/>
+      <c r="AG96" s="12" t="n"/>
+      <c r="AH96" s="12" t="n"/>
+      <c r="AI96" s="12" t="n"/>
+      <c r="AJ96" s="14" t="n"/>
+      <c r="AK96" s="15">
         <f>IF(TODAY()&lt;AD96, 0, IF(TODAY()&gt;AE96, AF96, AF96 * (TODAY()-AD96)/(AE96-AD96+1)))</f>
         <v/>
       </c>
-      <c r="AL96" s="5">
+      <c r="AL96" s="15">
         <f>AF96 * (AJ96/100)</f>
         <v/>
       </c>
-      <c r="AM96" s="5">
+      <c r="AM96" s="16">
         <f>AI96</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="L97" s="4" t="n"/>
-      <c r="M97" s="5">
+      <c r="A97" s="11" t="n"/>
+      <c r="B97" s="12" t="n"/>
+      <c r="C97" s="13" t="n"/>
+      <c r="D97" s="12" t="n"/>
+      <c r="E97" s="12" t="n"/>
+      <c r="F97" s="12" t="n"/>
+      <c r="G97" s="12" t="n"/>
+      <c r="H97" s="12" t="n"/>
+      <c r="I97" s="12" t="n"/>
+      <c r="J97" s="12" t="n"/>
+      <c r="K97" s="12" t="n"/>
+      <c r="L97" s="14" t="n"/>
+      <c r="M97" s="15">
         <f>IF(TODAY()&lt;F97, 0, IF(TODAY()&gt;G97, H97, H97 * (TODAY()-F97)/(G97-F97+1)))</f>
         <v/>
       </c>
-      <c r="N97" s="5">
+      <c r="N97" s="15">
         <f>H97 * (L97/100)</f>
         <v/>
       </c>
-      <c r="O97" s="5">
+      <c r="O97" s="16">
         <f>K97</f>
         <v/>
       </c>
-      <c r="X97" s="4" t="n"/>
-      <c r="Y97" s="5">
+      <c r="P97" s="12" t="n"/>
+      <c r="Q97" s="12" t="n"/>
+      <c r="R97" s="12" t="n"/>
+      <c r="S97" s="12" t="n"/>
+      <c r="T97" s="12" t="n"/>
+      <c r="U97" s="12" t="n"/>
+      <c r="V97" s="12" t="n"/>
+      <c r="W97" s="12" t="n"/>
+      <c r="X97" s="14" t="n"/>
+      <c r="Y97" s="15">
         <f>IF(TODAY()&lt;R97, 0, IF(TODAY()&gt;S97, T97, T97 * (TODAY()-R97)/(S97-R97+1)))</f>
         <v/>
       </c>
-      <c r="Z97" s="5">
+      <c r="Z97" s="15">
         <f>T97 * (X97/100)</f>
         <v/>
       </c>
-      <c r="AA97" s="5">
+      <c r="AA97" s="16">
         <f>W97</f>
         <v/>
       </c>
-      <c r="AJ97" s="4" t="n"/>
-      <c r="AK97" s="5">
+      <c r="AB97" s="12" t="n"/>
+      <c r="AC97" s="12" t="n"/>
+      <c r="AD97" s="12" t="n"/>
+      <c r="AE97" s="12" t="n"/>
+      <c r="AF97" s="12" t="n"/>
+      <c r="AG97" s="12" t="n"/>
+      <c r="AH97" s="12" t="n"/>
+      <c r="AI97" s="12" t="n"/>
+      <c r="AJ97" s="14" t="n"/>
+      <c r="AK97" s="15">
         <f>IF(TODAY()&lt;AD97, 0, IF(TODAY()&gt;AE97, AF97, AF97 * (TODAY()-AD97)/(AE97-AD97+1)))</f>
         <v/>
       </c>
-      <c r="AL97" s="5">
+      <c r="AL97" s="15">
         <f>AF97 * (AJ97/100)</f>
         <v/>
       </c>
-      <c r="AM97" s="5">
+      <c r="AM97" s="16">
         <f>AI97</f>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="L98" s="4" t="n"/>
-      <c r="M98" s="5">
+      <c r="A98" s="11" t="n"/>
+      <c r="B98" s="12" t="n"/>
+      <c r="C98" s="13" t="n"/>
+      <c r="D98" s="12" t="n"/>
+      <c r="E98" s="12" t="n"/>
+      <c r="F98" s="12" t="n"/>
+      <c r="G98" s="12" t="n"/>
+      <c r="H98" s="12" t="n"/>
+      <c r="I98" s="12" t="n"/>
+      <c r="J98" s="12" t="n"/>
+      <c r="K98" s="12" t="n"/>
+      <c r="L98" s="14" t="n"/>
+      <c r="M98" s="15">
         <f>IF(TODAY()&lt;F98, 0, IF(TODAY()&gt;G98, H98, H98 * (TODAY()-F98)/(G98-F98+1)))</f>
         <v/>
       </c>
-      <c r="N98" s="5">
+      <c r="N98" s="15">
         <f>H98 * (L98/100)</f>
         <v/>
       </c>
-      <c r="O98" s="5">
+      <c r="O98" s="16">
         <f>K98</f>
         <v/>
       </c>
-      <c r="X98" s="4" t="n"/>
-      <c r="Y98" s="5">
+      <c r="P98" s="12" t="n"/>
+      <c r="Q98" s="12" t="n"/>
+      <c r="R98" s="12" t="n"/>
+      <c r="S98" s="12" t="n"/>
+      <c r="T98" s="12" t="n"/>
+      <c r="U98" s="12" t="n"/>
+      <c r="V98" s="12" t="n"/>
+      <c r="W98" s="12" t="n"/>
+      <c r="X98" s="14" t="n"/>
+      <c r="Y98" s="15">
         <f>IF(TODAY()&lt;R98, 0, IF(TODAY()&gt;S98, T98, T98 * (TODAY()-R98)/(S98-R98+1)))</f>
         <v/>
       </c>
-      <c r="Z98" s="5">
+      <c r="Z98" s="15">
         <f>T98 * (X98/100)</f>
         <v/>
       </c>
-      <c r="AA98" s="5">
+      <c r="AA98" s="16">
         <f>W98</f>
         <v/>
       </c>
-      <c r="AJ98" s="4" t="n"/>
-      <c r="AK98" s="5">
+      <c r="AB98" s="12" t="n"/>
+      <c r="AC98" s="12" t="n"/>
+      <c r="AD98" s="12" t="n"/>
+      <c r="AE98" s="12" t="n"/>
+      <c r="AF98" s="12" t="n"/>
+      <c r="AG98" s="12" t="n"/>
+      <c r="AH98" s="12" t="n"/>
+      <c r="AI98" s="12" t="n"/>
+      <c r="AJ98" s="14" t="n"/>
+      <c r="AK98" s="15">
         <f>IF(TODAY()&lt;AD98, 0, IF(TODAY()&gt;AE98, AF98, AF98 * (TODAY()-AD98)/(AE98-AD98+1)))</f>
         <v/>
       </c>
-      <c r="AL98" s="5">
+      <c r="AL98" s="15">
         <f>AF98 * (AJ98/100)</f>
         <v/>
       </c>
-      <c r="AM98" s="5">
+      <c r="AM98" s="16">
         <f>AI98</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="L99" s="4" t="n"/>
-      <c r="M99" s="5">
+      <c r="A99" s="11" t="n"/>
+      <c r="B99" s="12" t="n"/>
+      <c r="C99" s="13" t="n"/>
+      <c r="D99" s="12" t="n"/>
+      <c r="E99" s="12" t="n"/>
+      <c r="F99" s="12" t="n"/>
+      <c r="G99" s="12" t="n"/>
+      <c r="H99" s="12" t="n"/>
+      <c r="I99" s="12" t="n"/>
+      <c r="J99" s="12" t="n"/>
+      <c r="K99" s="12" t="n"/>
+      <c r="L99" s="14" t="n"/>
+      <c r="M99" s="15">
         <f>IF(TODAY()&lt;F99, 0, IF(TODAY()&gt;G99, H99, H99 * (TODAY()-F99)/(G99-F99+1)))</f>
         <v/>
       </c>
-      <c r="N99" s="5">
+      <c r="N99" s="15">
         <f>H99 * (L99/100)</f>
         <v/>
       </c>
-      <c r="O99" s="5">
+      <c r="O99" s="16">
         <f>K99</f>
         <v/>
       </c>
-      <c r="X99" s="4" t="n"/>
-      <c r="Y99" s="5">
+      <c r="P99" s="12" t="n"/>
+      <c r="Q99" s="12" t="n"/>
+      <c r="R99" s="12" t="n"/>
+      <c r="S99" s="12" t="n"/>
+      <c r="T99" s="12" t="n"/>
+      <c r="U99" s="12" t="n"/>
+      <c r="V99" s="12" t="n"/>
+      <c r="W99" s="12" t="n"/>
+      <c r="X99" s="14" t="n"/>
+      <c r="Y99" s="15">
         <f>IF(TODAY()&lt;R99, 0, IF(TODAY()&gt;S99, T99, T99 * (TODAY()-R99)/(S99-R99+1)))</f>
         <v/>
       </c>
-      <c r="Z99" s="5">
+      <c r="Z99" s="15">
         <f>T99 * (X99/100)</f>
         <v/>
       </c>
-      <c r="AA99" s="5">
+      <c r="AA99" s="16">
         <f>W99</f>
         <v/>
       </c>
-      <c r="AJ99" s="4" t="n"/>
-      <c r="AK99" s="5">
+      <c r="AB99" s="12" t="n"/>
+      <c r="AC99" s="12" t="n"/>
+      <c r="AD99" s="12" t="n"/>
+      <c r="AE99" s="12" t="n"/>
+      <c r="AF99" s="12" t="n"/>
+      <c r="AG99" s="12" t="n"/>
+      <c r="AH99" s="12" t="n"/>
+      <c r="AI99" s="12" t="n"/>
+      <c r="AJ99" s="14" t="n"/>
+      <c r="AK99" s="15">
         <f>IF(TODAY()&lt;AD99, 0, IF(TODAY()&gt;AE99, AF99, AF99 * (TODAY()-AD99)/(AE99-AD99+1)))</f>
         <v/>
       </c>
-      <c r="AL99" s="5">
+      <c r="AL99" s="15">
         <f>AF99 * (AJ99/100)</f>
         <v/>
       </c>
-      <c r="AM99" s="5">
+      <c r="AM99" s="16">
         <f>AI99</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="L100" s="4" t="n"/>
-      <c r="M100" s="5">
+      <c r="A100" s="11" t="n"/>
+      <c r="B100" s="12" t="n"/>
+      <c r="C100" s="13" t="n"/>
+      <c r="D100" s="12" t="n"/>
+      <c r="E100" s="12" t="n"/>
+      <c r="F100" s="12" t="n"/>
+      <c r="G100" s="12" t="n"/>
+      <c r="H100" s="12" t="n"/>
+      <c r="I100" s="12" t="n"/>
+      <c r="J100" s="12" t="n"/>
+      <c r="K100" s="12" t="n"/>
+      <c r="L100" s="14" t="n"/>
+      <c r="M100" s="15">
         <f>IF(TODAY()&lt;F100, 0, IF(TODAY()&gt;G100, H100, H100 * (TODAY()-F100)/(G100-F100+1)))</f>
         <v/>
       </c>
-      <c r="N100" s="5">
+      <c r="N100" s="15">
         <f>H100 * (L100/100)</f>
         <v/>
       </c>
-      <c r="O100" s="5">
+      <c r="O100" s="16">
         <f>K100</f>
         <v/>
       </c>
-      <c r="X100" s="4" t="n"/>
-      <c r="Y100" s="5">
+      <c r="P100" s="12" t="n"/>
+      <c r="Q100" s="12" t="n"/>
+      <c r="R100" s="12" t="n"/>
+      <c r="S100" s="12" t="n"/>
+      <c r="T100" s="12" t="n"/>
+      <c r="U100" s="12" t="n"/>
+      <c r="V100" s="12" t="n"/>
+      <c r="W100" s="12" t="n"/>
+      <c r="X100" s="14" t="n"/>
+      <c r="Y100" s="15">
         <f>IF(TODAY()&lt;R100, 0, IF(TODAY()&gt;S100, T100, T100 * (TODAY()-R100)/(S100-R100+1)))</f>
         <v/>
       </c>
-      <c r="Z100" s="5">
+      <c r="Z100" s="15">
         <f>T100 * (X100/100)</f>
         <v/>
       </c>
-      <c r="AA100" s="5">
+      <c r="AA100" s="16">
         <f>W100</f>
         <v/>
       </c>
-      <c r="AJ100" s="4" t="n"/>
-      <c r="AK100" s="5">
+      <c r="AB100" s="12" t="n"/>
+      <c r="AC100" s="12" t="n"/>
+      <c r="AD100" s="12" t="n"/>
+      <c r="AE100" s="12" t="n"/>
+      <c r="AF100" s="12" t="n"/>
+      <c r="AG100" s="12" t="n"/>
+      <c r="AH100" s="12" t="n"/>
+      <c r="AI100" s="12" t="n"/>
+      <c r="AJ100" s="14" t="n"/>
+      <c r="AK100" s="15">
         <f>IF(TODAY()&lt;AD100, 0, IF(TODAY()&gt;AE100, AF100, AF100 * (TODAY()-AD100)/(AE100-AD100+1)))</f>
         <v/>
       </c>
-      <c r="AL100" s="5">
+      <c r="AL100" s="15">
         <f>AF100 * (AJ100/100)</f>
         <v/>
       </c>
-      <c r="AM100" s="5">
+      <c r="AM100" s="16">
         <f>AI100</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="L101" s="4" t="n"/>
-      <c r="M101" s="5">
+      <c r="A101" s="11" t="n"/>
+      <c r="B101" s="12" t="n"/>
+      <c r="C101" s="13" t="n"/>
+      <c r="D101" s="12" t="n"/>
+      <c r="E101" s="12" t="n"/>
+      <c r="F101" s="12" t="n"/>
+      <c r="G101" s="12" t="n"/>
+      <c r="H101" s="12" t="n"/>
+      <c r="I101" s="12" t="n"/>
+      <c r="J101" s="12" t="n"/>
+      <c r="K101" s="12" t="n"/>
+      <c r="L101" s="14" t="n"/>
+      <c r="M101" s="15">
         <f>IF(TODAY()&lt;F101, 0, IF(TODAY()&gt;G101, H101, H101 * (TODAY()-F101)/(G101-F101+1)))</f>
         <v/>
       </c>
-      <c r="N101" s="5">
+      <c r="N101" s="15">
         <f>H101 * (L101/100)</f>
         <v/>
       </c>
-      <c r="O101" s="5">
+      <c r="O101" s="16">
         <f>K101</f>
         <v/>
       </c>
-      <c r="X101" s="4" t="n"/>
-      <c r="Y101" s="5">
+      <c r="P101" s="12" t="n"/>
+      <c r="Q101" s="12" t="n"/>
+      <c r="R101" s="12" t="n"/>
+      <c r="S101" s="12" t="n"/>
+      <c r="T101" s="12" t="n"/>
+      <c r="U101" s="12" t="n"/>
+      <c r="V101" s="12" t="n"/>
+      <c r="W101" s="12" t="n"/>
+      <c r="X101" s="14" t="n"/>
+      <c r="Y101" s="15">
         <f>IF(TODAY()&lt;R101, 0, IF(TODAY()&gt;S101, T101, T101 * (TODAY()-R101)/(S101-R101+1)))</f>
         <v/>
       </c>
-      <c r="Z101" s="5">
+      <c r="Z101" s="15">
         <f>T101 * (X101/100)</f>
         <v/>
       </c>
-      <c r="AA101" s="5">
+      <c r="AA101" s="16">
         <f>W101</f>
         <v/>
       </c>
-      <c r="AJ101" s="4" t="n"/>
-      <c r="AK101" s="5">
+      <c r="AB101" s="12" t="n"/>
+      <c r="AC101" s="12" t="n"/>
+      <c r="AD101" s="12" t="n"/>
+      <c r="AE101" s="12" t="n"/>
+      <c r="AF101" s="12" t="n"/>
+      <c r="AG101" s="12" t="n"/>
+      <c r="AH101" s="12" t="n"/>
+      <c r="AI101" s="12" t="n"/>
+      <c r="AJ101" s="14" t="n"/>
+      <c r="AK101" s="15">
         <f>IF(TODAY()&lt;AD101, 0, IF(TODAY()&gt;AE101, AF101, AF101 * (TODAY()-AD101)/(AE101-AD101+1)))</f>
         <v/>
       </c>
-      <c r="AL101" s="5">
+      <c r="AL101" s="15">
         <f>AF101 * (AJ101/100)</f>
         <v/>
       </c>
-      <c r="AM101" s="5">
+      <c r="AM101" s="16">
         <f>AI101</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="L102" s="4" t="n"/>
-      <c r="M102" s="5">
+      <c r="A102" s="17" t="n"/>
+      <c r="B102" s="18" t="n"/>
+      <c r="C102" s="19" t="n"/>
+      <c r="D102" s="18" t="n"/>
+      <c r="E102" s="18" t="n"/>
+      <c r="F102" s="18" t="n"/>
+      <c r="G102" s="18" t="n"/>
+      <c r="H102" s="18" t="n"/>
+      <c r="I102" s="18" t="n"/>
+      <c r="J102" s="18" t="n"/>
+      <c r="K102" s="18" t="n"/>
+      <c r="L102" s="20" t="n"/>
+      <c r="M102" s="21">
         <f>IF(TODAY()&lt;F102, 0, IF(TODAY()&gt;G102, H102, H102 * (TODAY()-F102)/(G102-F102+1)))</f>
         <v/>
       </c>
-      <c r="N102" s="5">
+      <c r="N102" s="21">
         <f>H102 * (L102/100)</f>
         <v/>
       </c>
-      <c r="O102" s="5">
+      <c r="O102" s="22">
         <f>K102</f>
         <v/>
       </c>
-      <c r="X102" s="4" t="n"/>
-      <c r="Y102" s="5">
+      <c r="P102" s="18" t="n"/>
+      <c r="Q102" s="18" t="n"/>
+      <c r="R102" s="18" t="n"/>
+      <c r="S102" s="18" t="n"/>
+      <c r="T102" s="18" t="n"/>
+      <c r="U102" s="18" t="n"/>
+      <c r="V102" s="18" t="n"/>
+      <c r="W102" s="18" t="n"/>
+      <c r="X102" s="20" t="n"/>
+      <c r="Y102" s="21">
         <f>IF(TODAY()&lt;R102, 0, IF(TODAY()&gt;S102, T102, T102 * (TODAY()-R102)/(S102-R102+1)))</f>
         <v/>
       </c>
-      <c r="Z102" s="5">
+      <c r="Z102" s="21">
         <f>T102 * (X102/100)</f>
         <v/>
       </c>
-      <c r="AA102" s="5">
+      <c r="AA102" s="22">
         <f>W102</f>
         <v/>
       </c>
-      <c r="AJ102" s="4" t="n"/>
-      <c r="AK102" s="5">
+      <c r="AB102" s="18" t="n"/>
+      <c r="AC102" s="18" t="n"/>
+      <c r="AD102" s="18" t="n"/>
+      <c r="AE102" s="18" t="n"/>
+      <c r="AF102" s="18" t="n"/>
+      <c r="AG102" s="18" t="n"/>
+      <c r="AH102" s="18" t="n"/>
+      <c r="AI102" s="18" t="n"/>
+      <c r="AJ102" s="20" t="n"/>
+      <c r="AK102" s="21">
         <f>IF(TODAY()&lt;AD102, 0, IF(TODAY()&gt;AE102, AF102, AF102 * (TODAY()-AD102)/(AE102-AD102+1)))</f>
         <v/>
       </c>
-      <c r="AL102" s="5">
+      <c r="AL102" s="21">
         <f>AF102 * (AJ102/100)</f>
         <v/>
       </c>
-      <c r="AM102" s="5">
+      <c r="AM102" s="22">
         <f>AI102</f>
         <v/>
       </c>
@@ -4976,494 +7798,590 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Aさんチーム</t>
         </is>
       </c>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="4" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>EVM指標集計</t>
         </is>
       </c>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="12" t="n"/>
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>フェーズ</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>PV (計画値)</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>EV (出来高)</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>AC (実績コスト)</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="26" t="inlineStr">
         <is>
           <t>SV</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="26" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="26" t="inlineStr">
         <is>
           <t>SPI</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="27" t="inlineStr">
         <is>
           <t>CPI</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>作成</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="B4" s="12">
         <f>SUMIFS(WBS_EVM!M:M, WBS_EVM!$E:$E, "Aさん")</f>
         <v/>
       </c>
-      <c r="C4">
+      <c r="C4" s="12">
         <f>SUMIFS(WBS_EVM!N:N, WBS_EVM!$E:$E, "Aさん")</f>
         <v/>
       </c>
-      <c r="D4">
+      <c r="D4" s="12">
         <f>SUMIFS(WBS_EVM!O:O, WBS_EVM!$E:$E, "Aさん")</f>
         <v/>
       </c>
-      <c r="E4">
+      <c r="E4" s="12">
         <f>C4-B4</f>
         <v/>
       </c>
-      <c r="F4">
+      <c r="F4" s="12">
         <f>C4-D4</f>
         <v/>
       </c>
-      <c r="G4">
+      <c r="G4" s="12">
         <f>IFERROR(C4/B4, 1)</f>
         <v/>
       </c>
-      <c r="H4">
+      <c r="H4" s="13">
         <f>IFERROR(C4/D4, 1)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>レビュー実施</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="B5" s="12">
         <f>SUMIFS(WBS_EVM!Y:Y, WBS_EVM!$Q:$Q, "Aさん")</f>
         <v/>
       </c>
-      <c r="C5">
+      <c r="C5" s="12">
         <f>SUMIFS(WBS_EVM!Z:Z, WBS_EVM!$Q:$Q, "Aさん")</f>
         <v/>
       </c>
-      <c r="D5">
+      <c r="D5" s="12">
         <f>SUMIFS(WBS_EVM!AA:AA, WBS_EVM!$Q:$Q, "Aさん")</f>
         <v/>
       </c>
-      <c r="E5">
+      <c r="E5" s="12">
         <f>C5-B5</f>
         <v/>
       </c>
-      <c r="F5">
+      <c r="F5" s="12">
         <f>C5-D5</f>
         <v/>
       </c>
-      <c r="G5">
+      <c r="G5" s="12">
         <f>IFERROR(C5/B5, 1)</f>
         <v/>
       </c>
-      <c r="H5">
+      <c r="H5" s="13">
         <f>IFERROR(C5/D5, 1)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>レビュー後修正</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="B6" s="12">
         <f>SUMIFS(WBS_EVM!AK:AK, WBS_EVM!$AC:$AC, "Aさん")</f>
         <v/>
       </c>
-      <c r="C6">
+      <c r="C6" s="12">
         <f>SUMIFS(WBS_EVM!AL:AL, WBS_EVM!$AC:$AC, "Aさん")</f>
         <v/>
       </c>
-      <c r="D6">
+      <c r="D6" s="12">
         <f>SUMIFS(WBS_EVM!AM:AM, WBS_EVM!$AC:$AC, "Aさん")</f>
         <v/>
       </c>
-      <c r="E6">
+      <c r="E6" s="12">
         <f>C6-B6</f>
         <v/>
       </c>
-      <c r="F6">
+      <c r="F6" s="12">
         <f>C6-D6</f>
         <v/>
       </c>
-      <c r="G6">
+      <c r="G6" s="12">
         <f>IFERROR(C6/B6, 1)</f>
         <v/>
       </c>
-      <c r="H6">
+      <c r="H6" s="13">
         <f>IFERROR(C6/D6, 1)</f>
         <v/>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="13" t="n"/>
+    </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>タスクメトリクス</t>
         </is>
       </c>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="12" t="n"/>
+      <c r="H8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>フェーズ</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>総数</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>仕掛かり(予定)</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>仕掛かり(実績)</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>完了(予定)</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="26" t="inlineStr">
         <is>
           <t>完了(実績)</t>
         </is>
       </c>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="13" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>作成</t>
         </is>
       </c>
-      <c r="B10">
+      <c r="B10" s="12">
         <f>COUNTIFS(WBS_EVM!$E:$E, "Aさん", WBS_EVM!$H:$H, "&gt;0")</f>
         <v/>
       </c>
-      <c r="F10">
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12">
         <f>COUNTIFS(WBS_EVM!$E:$E, "Aさん", WBS_EVM!$K:$K, "&lt;&gt;")</f>
         <v/>
       </c>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="13" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>レビュー実施</t>
         </is>
       </c>
-      <c r="B11">
+      <c r="B11" s="12">
         <f>COUNTIFS(WBS_EVM!$Q:$Q, "Aさん", WBS_EVM!$T:$T, "&gt;0")</f>
         <v/>
       </c>
-      <c r="F11">
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12">
         <f>COUNTIFS(WBS_EVM!$Q:$Q, "Aさん", WBS_EVM!$W:$W, "&lt;&gt;")</f>
         <v/>
       </c>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="13" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>レビュー後修正</t>
         </is>
       </c>
-      <c r="B12">
+      <c r="B12" s="18">
         <f>COUNTIFS(WBS_EVM!$AC:$AC, "Aさん", WBS_EVM!$AF:$AF, "&gt;0")</f>
         <v/>
       </c>
-      <c r="F12">
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18">
         <f>COUNTIFS(WBS_EVM!$AC:$AC, "Aさん", WBS_EVM!$AI:$AI, "&lt;&gt;")</f>
         <v/>
       </c>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="19" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>Dさんチーム</t>
         </is>
       </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>EVM指標集計</t>
         </is>
       </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="13" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>フェーズ</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>PV (計画値)</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>EV (出来高)</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
         <is>
           <t>AC (実績コスト)</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t>SV</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="26" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="26" t="inlineStr">
         <is>
           <t>SPI</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="27" t="inlineStr">
         <is>
           <t>CPI</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>作成</t>
         </is>
       </c>
-      <c r="B18">
+      <c r="B18" s="12">
         <f>SUMIFS(WBS_EVM!M:M, WBS_EVM!$E:$E, "Dさん")</f>
         <v/>
       </c>
-      <c r="C18">
+      <c r="C18" s="12">
         <f>SUMIFS(WBS_EVM!N:N, WBS_EVM!$E:$E, "Dさん")</f>
         <v/>
       </c>
-      <c r="D18">
+      <c r="D18" s="12">
         <f>SUMIFS(WBS_EVM!O:O, WBS_EVM!$E:$E, "Dさん")</f>
         <v/>
       </c>
-      <c r="E18">
+      <c r="E18" s="12">
         <f>C18-B18</f>
         <v/>
       </c>
-      <c r="F18">
+      <c r="F18" s="12">
         <f>C18-D18</f>
         <v/>
       </c>
-      <c r="G18">
+      <c r="G18" s="12">
         <f>IFERROR(C18/B18, 1)</f>
         <v/>
       </c>
-      <c r="H18">
+      <c r="H18" s="13">
         <f>IFERROR(C18/D18, 1)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>レビュー実施</t>
         </is>
       </c>
-      <c r="B19">
+      <c r="B19" s="12">
         <f>SUMIFS(WBS_EVM!Y:Y, WBS_EVM!$Q:$Q, "Dさん")</f>
         <v/>
       </c>
-      <c r="C19">
+      <c r="C19" s="12">
         <f>SUMIFS(WBS_EVM!Z:Z, WBS_EVM!$Q:$Q, "Dさん")</f>
         <v/>
       </c>
-      <c r="D19">
+      <c r="D19" s="12">
         <f>SUMIFS(WBS_EVM!AA:AA, WBS_EVM!$Q:$Q, "Dさん")</f>
         <v/>
       </c>
-      <c r="E19">
+      <c r="E19" s="12">
         <f>C19-B19</f>
         <v/>
       </c>
-      <c r="F19">
+      <c r="F19" s="12">
         <f>C19-D19</f>
         <v/>
       </c>
-      <c r="G19">
+      <c r="G19" s="12">
         <f>IFERROR(C19/B19, 1)</f>
         <v/>
       </c>
-      <c r="H19">
+      <c r="H19" s="13">
         <f>IFERROR(C19/D19, 1)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>レビュー後修正</t>
         </is>
       </c>
-      <c r="B20">
+      <c r="B20" s="12">
         <f>SUMIFS(WBS_EVM!AK:AK, WBS_EVM!$AC:$AC, "Dさん")</f>
         <v/>
       </c>
-      <c r="C20">
+      <c r="C20" s="12">
         <f>SUMIFS(WBS_EVM!AL:AL, WBS_EVM!$AC:$AC, "Dさん")</f>
         <v/>
       </c>
-      <c r="D20">
+      <c r="D20" s="12">
         <f>SUMIFS(WBS_EVM!AM:AM, WBS_EVM!$AC:$AC, "Dさん")</f>
         <v/>
       </c>
-      <c r="E20">
+      <c r="E20" s="12">
         <f>C20-B20</f>
         <v/>
       </c>
-      <c r="F20">
+      <c r="F20" s="12">
         <f>C20-D20</f>
         <v/>
       </c>
-      <c r="G20">
+      <c r="G20" s="12">
         <f>IFERROR(C20/B20, 1)</f>
         <v/>
       </c>
-      <c r="H20">
+      <c r="H20" s="13">
         <f>IFERROR(C20/D20, 1)</f>
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="13" t="n"/>
+    </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>タスクメトリクス</t>
         </is>
       </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="13" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>フェーズ</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>総数</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
         <is>
           <t>仕掛かり(予定)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="26" t="inlineStr">
         <is>
           <t>仕掛かり(実績)</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>完了(予定)</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F23" s="26" t="inlineStr">
         <is>
           <t>完了(実績)</t>
         </is>
       </c>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="13" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>作成</t>
         </is>
       </c>
-      <c r="B24">
+      <c r="B24" s="12">
         <f>COUNTIFS(WBS_EVM!$E:$E, "Dさん", WBS_EVM!$H:$H, "&gt;0")</f>
         <v/>
       </c>
-      <c r="F24">
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="12">
         <f>COUNTIFS(WBS_EVM!$E:$E, "Dさん", WBS_EVM!$K:$K, "&lt;&gt;")</f>
         <v/>
       </c>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>レビュー実施</t>
         </is>
       </c>
-      <c r="B25">
+      <c r="B25" s="12">
         <f>COUNTIFS(WBS_EVM!$Q:$Q, "Dさん", WBS_EVM!$T:$T, "&gt;0")</f>
         <v/>
       </c>
-      <c r="F25">
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12">
         <f>COUNTIFS(WBS_EVM!$Q:$Q, "Dさん", WBS_EVM!$W:$W, "&lt;&gt;")</f>
         <v/>
       </c>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="13" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>レビュー後修正</t>
         </is>
       </c>
-      <c r="B26">
+      <c r="B26" s="18">
         <f>COUNTIFS(WBS_EVM!$AC:$AC, "Dさん", WBS_EVM!$AF:$AF, "&gt;0")</f>
         <v/>
       </c>
-      <c r="F26">
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="18">
         <f>COUNTIFS(WBS_EVM!$AC:$AC, "Dさん", WBS_EVM!$AI:$AI, "&lt;&gt;")</f>
         <v/>
       </c>
+      <c r="G26" s="18" t="n"/>
+      <c r="H26" s="19" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="WBS_EVM" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="チームEVM" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="個人SV" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="MEMBER_LIST">Settings!$A$5:$A$100</definedName>
@@ -129,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,6 +177,18 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8386,4 +8399,158 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="29" t="inlineStr">
+        <is>
+          <t>メンバー</t>
+        </is>
+      </c>
+      <c r="C1" s="29" t="inlineStr">
+        <is>
+          <t>前日</t>
+        </is>
+      </c>
+      <c r="D1" s="29" t="inlineStr">
+        <is>
+          <t>当日</t>
+        </is>
+      </c>
+      <c r="E1" s="29" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="n"/>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="30" t="inlineStr">
+        <is>
+          <t>5月3日(日)</t>
+        </is>
+      </c>
+      <c r="F2" s="30" t="inlineStr">
+        <is>
+          <t>5月4日(月)</t>
+        </is>
+      </c>
+      <c r="G2" s="31" t="inlineStr">
+        <is>
+          <t>5月5日(火)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Aさん</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="12" t="n"/>
+      <c r="G3" s="13" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Bさん</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="13" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Cさん</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="13" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Dさん</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="13" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Eさん</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="13" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Fさん</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="19" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,8 +43,11 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <color rgb="00FF0000"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -63,8 +66,14 @@
         <bgColor rgb="00E0E0E0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDDDDD"/>
+        <bgColor rgb="00DDDDDD"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -126,11 +135,39 @@
       <top style="thin"/>
       <bottom style="medium"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -189,6 +226,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -723,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM102"/>
+  <dimension ref="A1:AN102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -735,49 +778,49 @@
           <t>作成</t>
         </is>
       </c>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
-      <c r="O1" s="4" t="n"/>
+      <c r="E1" s="32" t="n"/>
+      <c r="F1" s="32" t="n"/>
+      <c r="G1" s="32" t="n"/>
+      <c r="H1" s="32" t="n"/>
+      <c r="I1" s="32" t="n"/>
+      <c r="J1" s="32" t="n"/>
+      <c r="K1" s="32" t="n"/>
+      <c r="L1" s="32" t="n"/>
+      <c r="M1" s="32" t="n"/>
+      <c r="N1" s="32" t="n"/>
+      <c r="O1" s="33" t="n"/>
       <c r="P1" s="5" t="inlineStr">
         <is>
           <t>レビュー実施</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="n"/>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
-      <c r="X1" s="3" t="n"/>
-      <c r="Y1" s="3" t="n"/>
-      <c r="Z1" s="3" t="n"/>
-      <c r="AA1" s="4" t="n"/>
+      <c r="Q1" s="32" t="n"/>
+      <c r="R1" s="32" t="n"/>
+      <c r="S1" s="32" t="n"/>
+      <c r="T1" s="32" t="n"/>
+      <c r="U1" s="32" t="n"/>
+      <c r="V1" s="32" t="n"/>
+      <c r="W1" s="32" t="n"/>
+      <c r="X1" s="32" t="n"/>
+      <c r="Y1" s="32" t="n"/>
+      <c r="Z1" s="32" t="n"/>
+      <c r="AA1" s="33" t="n"/>
       <c r="AB1" s="5" t="inlineStr">
         <is>
           <t>レビュー後修正</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="n"/>
-      <c r="AD1" s="3" t="n"/>
-      <c r="AE1" s="3" t="n"/>
-      <c r="AF1" s="3" t="n"/>
-      <c r="AG1" s="3" t="n"/>
-      <c r="AH1" s="3" t="n"/>
-      <c r="AI1" s="3" t="n"/>
-      <c r="AJ1" s="3" t="n"/>
-      <c r="AK1" s="3" t="n"/>
-      <c r="AL1" s="3" t="n"/>
-      <c r="AM1" s="4" t="n"/>
+      <c r="AC1" s="32" t="n"/>
+      <c r="AD1" s="32" t="n"/>
+      <c r="AE1" s="32" t="n"/>
+      <c r="AF1" s="32" t="n"/>
+      <c r="AG1" s="32" t="n"/>
+      <c r="AH1" s="32" t="n"/>
+      <c r="AI1" s="32" t="n"/>
+      <c r="AJ1" s="32" t="n"/>
+      <c r="AK1" s="32" t="n"/>
+      <c r="AL1" s="32" t="n"/>
+      <c r="AM1" s="33" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -973,6 +1016,11 @@
       <c r="AM2" s="10" t="inlineStr">
         <is>
           <t>AC (実績コスト)</t>
+        </is>
+      </c>
+      <c r="AN2" s="34" t="inlineStr">
+        <is>
+          <t>整合性チェック結果</t>
         </is>
       </c>
     </row>
@@ -1043,6 +1091,7 @@
         <f>AI3</f>
         <v/>
       </c>
+      <c r="AN3" s="35" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n"/>
@@ -1111,6 +1160,7 @@
         <f>AI4</f>
         <v/>
       </c>
+      <c r="AN4" s="35" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,11 +43,8 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
-    <font>
-      <color rgb="00FF0000"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -66,14 +63,8 @@
         <bgColor rgb="00E0E0E0"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDDDDD"/>
-        <bgColor rgb="00DDDDDD"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="14">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -135,39 +126,11 @@
       <top style="thin"/>
       <bottom style="medium"/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -226,12 +189,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -766,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN102"/>
+  <dimension ref="A1:AM102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,49 +735,49 @@
           <t>作成</t>
         </is>
       </c>
-      <c r="E1" s="32" t="n"/>
-      <c r="F1" s="32" t="n"/>
-      <c r="G1" s="32" t="n"/>
-      <c r="H1" s="32" t="n"/>
-      <c r="I1" s="32" t="n"/>
-      <c r="J1" s="32" t="n"/>
-      <c r="K1" s="32" t="n"/>
-      <c r="L1" s="32" t="n"/>
-      <c r="M1" s="32" t="n"/>
-      <c r="N1" s="32" t="n"/>
-      <c r="O1" s="33" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+      <c r="O1" s="4" t="n"/>
       <c r="P1" s="5" t="inlineStr">
         <is>
           <t>レビュー実施</t>
         </is>
       </c>
-      <c r="Q1" s="32" t="n"/>
-      <c r="R1" s="32" t="n"/>
-      <c r="S1" s="32" t="n"/>
-      <c r="T1" s="32" t="n"/>
-      <c r="U1" s="32" t="n"/>
-      <c r="V1" s="32" t="n"/>
-      <c r="W1" s="32" t="n"/>
-      <c r="X1" s="32" t="n"/>
-      <c r="Y1" s="32" t="n"/>
-      <c r="Z1" s="32" t="n"/>
-      <c r="AA1" s="33" t="n"/>
+      <c r="Q1" s="3" t="n"/>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="T1" s="3" t="n"/>
+      <c r="U1" s="3" t="n"/>
+      <c r="V1" s="3" t="n"/>
+      <c r="W1" s="3" t="n"/>
+      <c r="X1" s="3" t="n"/>
+      <c r="Y1" s="3" t="n"/>
+      <c r="Z1" s="3" t="n"/>
+      <c r="AA1" s="4" t="n"/>
       <c r="AB1" s="5" t="inlineStr">
         <is>
           <t>レビュー後修正</t>
         </is>
       </c>
-      <c r="AC1" s="32" t="n"/>
-      <c r="AD1" s="32" t="n"/>
-      <c r="AE1" s="32" t="n"/>
-      <c r="AF1" s="32" t="n"/>
-      <c r="AG1" s="32" t="n"/>
-      <c r="AH1" s="32" t="n"/>
-      <c r="AI1" s="32" t="n"/>
-      <c r="AJ1" s="32" t="n"/>
-      <c r="AK1" s="32" t="n"/>
-      <c r="AL1" s="32" t="n"/>
-      <c r="AM1" s="33" t="n"/>
+      <c r="AC1" s="3" t="n"/>
+      <c r="AD1" s="3" t="n"/>
+      <c r="AE1" s="3" t="n"/>
+      <c r="AF1" s="3" t="n"/>
+      <c r="AG1" s="3" t="n"/>
+      <c r="AH1" s="3" t="n"/>
+      <c r="AI1" s="3" t="n"/>
+      <c r="AJ1" s="3" t="n"/>
+      <c r="AK1" s="3" t="n"/>
+      <c r="AL1" s="3" t="n"/>
+      <c r="AM1" s="4" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -1016,11 +973,6 @@
       <c r="AM2" s="10" t="inlineStr">
         <is>
           <t>AC (実績コスト)</t>
-        </is>
-      </c>
-      <c r="AN2" s="34" t="inlineStr">
-        <is>
-          <t>整合性チェック結果</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1043,6 @@
         <f>AI3</f>
         <v/>
       </c>
-      <c r="AN3" s="35" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n"/>
@@ -1160,7 +1111,6 @@
         <f>AI4</f>
         <v/>
       </c>
-      <c r="AN4" s="35" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -990,7 +990,7 @@
       <c r="K3" s="12" t="n"/>
       <c r="L3" s="14" t="n"/>
       <c r="M3" s="15">
-        <f>IF(TODAY()&lt;F3, 0, IF(TODAY()&gt;G3, H3, H3 * (TODAY()-F3)/(G3-F3+1)))</f>
+        <f>IF(TODAY()&lt;F3, 0, IF(TODAY()&gt;G3, H3, H3 * (TODAY()-F3)/MAX(1, G3-F3+1)))</f>
         <v/>
       </c>
       <c r="N3" s="15">
@@ -1011,7 +1011,7 @@
       <c r="W3" s="12" t="n"/>
       <c r="X3" s="14" t="n"/>
       <c r="Y3" s="15">
-        <f>IF(TODAY()&lt;R3, 0, IF(TODAY()&gt;S3, T3, T3 * (TODAY()-R3)/(S3-R3+1)))</f>
+        <f>IF(TODAY()&lt;R3, 0, IF(TODAY()&gt;S3, T3, T3 * (TODAY()-R3)/MAX(1, S3-R3+1)))</f>
         <v/>
       </c>
       <c r="Z3" s="15">
@@ -1032,7 +1032,7 @@
       <c r="AI3" s="12" t="n"/>
       <c r="AJ3" s="14" t="n"/>
       <c r="AK3" s="15">
-        <f>IF(TODAY()&lt;AD3, 0, IF(TODAY()&gt;AE3, AF3, AF3 * (TODAY()-AD3)/(AE3-AD3+1)))</f>
+        <f>IF(TODAY()&lt;AD3, 0, IF(TODAY()&gt;AE3, AF3, AF3 * (TODAY()-AD3)/MAX(1, AE3-AD3+1)))</f>
         <v/>
       </c>
       <c r="AL3" s="15">
@@ -1058,7 +1058,7 @@
       <c r="K4" s="12" t="n"/>
       <c r="L4" s="14" t="n"/>
       <c r="M4" s="15">
-        <f>IF(TODAY()&lt;F4, 0, IF(TODAY()&gt;G4, H4, H4 * (TODAY()-F4)/(G4-F4+1)))</f>
+        <f>IF(TODAY()&lt;F4, 0, IF(TODAY()&gt;G4, H4, H4 * (TODAY()-F4)/MAX(1, G4-F4+1)))</f>
         <v/>
       </c>
       <c r="N4" s="15">
@@ -1079,7 +1079,7 @@
       <c r="W4" s="12" t="n"/>
       <c r="X4" s="14" t="n"/>
       <c r="Y4" s="15">
-        <f>IF(TODAY()&lt;R4, 0, IF(TODAY()&gt;S4, T4, T4 * (TODAY()-R4)/(S4-R4+1)))</f>
+        <f>IF(TODAY()&lt;R4, 0, IF(TODAY()&gt;S4, T4, T4 * (TODAY()-R4)/MAX(1, S4-R4+1)))</f>
         <v/>
       </c>
       <c r="Z4" s="15">
@@ -1100,7 +1100,7 @@
       <c r="AI4" s="12" t="n"/>
       <c r="AJ4" s="14" t="n"/>
       <c r="AK4" s="15">
-        <f>IF(TODAY()&lt;AD4, 0, IF(TODAY()&gt;AE4, AF4, AF4 * (TODAY()-AD4)/(AE4-AD4+1)))</f>
+        <f>IF(TODAY()&lt;AD4, 0, IF(TODAY()&gt;AE4, AF4, AF4 * (TODAY()-AD4)/MAX(1, AE4-AD4+1)))</f>
         <v/>
       </c>
       <c r="AL4" s="15">
@@ -1126,7 +1126,7 @@
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="14" t="n"/>
       <c r="M5" s="15">
-        <f>IF(TODAY()&lt;F5, 0, IF(TODAY()&gt;G5, H5, H5 * (TODAY()-F5)/(G5-F5+1)))</f>
+        <f>IF(TODAY()&lt;F5, 0, IF(TODAY()&gt;G5, H5, H5 * (TODAY()-F5)/MAX(1, G5-F5+1)))</f>
         <v/>
       </c>
       <c r="N5" s="15">
@@ -1147,7 +1147,7 @@
       <c r="W5" s="12" t="n"/>
       <c r="X5" s="14" t="n"/>
       <c r="Y5" s="15">
-        <f>IF(TODAY()&lt;R5, 0, IF(TODAY()&gt;S5, T5, T5 * (TODAY()-R5)/(S5-R5+1)))</f>
+        <f>IF(TODAY()&lt;R5, 0, IF(TODAY()&gt;S5, T5, T5 * (TODAY()-R5)/MAX(1, S5-R5+1)))</f>
         <v/>
       </c>
       <c r="Z5" s="15">
@@ -1168,7 +1168,7 @@
       <c r="AI5" s="12" t="n"/>
       <c r="AJ5" s="14" t="n"/>
       <c r="AK5" s="15">
-        <f>IF(TODAY()&lt;AD5, 0, IF(TODAY()&gt;AE5, AF5, AF5 * (TODAY()-AD5)/(AE5-AD5+1)))</f>
+        <f>IF(TODAY()&lt;AD5, 0, IF(TODAY()&gt;AE5, AF5, AF5 * (TODAY()-AD5)/MAX(1, AE5-AD5+1)))</f>
         <v/>
       </c>
       <c r="AL5" s="15">
@@ -1194,7 +1194,7 @@
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="14" t="n"/>
       <c r="M6" s="15">
-        <f>IF(TODAY()&lt;F6, 0, IF(TODAY()&gt;G6, H6, H6 * (TODAY()-F6)/(G6-F6+1)))</f>
+        <f>IF(TODAY()&lt;F6, 0, IF(TODAY()&gt;G6, H6, H6 * (TODAY()-F6)/MAX(1, G6-F6+1)))</f>
         <v/>
       </c>
       <c r="N6" s="15">
@@ -1215,7 +1215,7 @@
       <c r="W6" s="12" t="n"/>
       <c r="X6" s="14" t="n"/>
       <c r="Y6" s="15">
-        <f>IF(TODAY()&lt;R6, 0, IF(TODAY()&gt;S6, T6, T6 * (TODAY()-R6)/(S6-R6+1)))</f>
+        <f>IF(TODAY()&lt;R6, 0, IF(TODAY()&gt;S6, T6, T6 * (TODAY()-R6)/MAX(1, S6-R6+1)))</f>
         <v/>
       </c>
       <c r="Z6" s="15">
@@ -1236,7 +1236,7 @@
       <c r="AI6" s="12" t="n"/>
       <c r="AJ6" s="14" t="n"/>
       <c r="AK6" s="15">
-        <f>IF(TODAY()&lt;AD6, 0, IF(TODAY()&gt;AE6, AF6, AF6 * (TODAY()-AD6)/(AE6-AD6+1)))</f>
+        <f>IF(TODAY()&lt;AD6, 0, IF(TODAY()&gt;AE6, AF6, AF6 * (TODAY()-AD6)/MAX(1, AE6-AD6+1)))</f>
         <v/>
       </c>
       <c r="AL6" s="15">
@@ -1262,7 +1262,7 @@
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="14" t="n"/>
       <c r="M7" s="15">
-        <f>IF(TODAY()&lt;F7, 0, IF(TODAY()&gt;G7, H7, H7 * (TODAY()-F7)/(G7-F7+1)))</f>
+        <f>IF(TODAY()&lt;F7, 0, IF(TODAY()&gt;G7, H7, H7 * (TODAY()-F7)/MAX(1, G7-F7+1)))</f>
         <v/>
       </c>
       <c r="N7" s="15">
@@ -1283,7 +1283,7 @@
       <c r="W7" s="12" t="n"/>
       <c r="X7" s="14" t="n"/>
       <c r="Y7" s="15">
-        <f>IF(TODAY()&lt;R7, 0, IF(TODAY()&gt;S7, T7, T7 * (TODAY()-R7)/(S7-R7+1)))</f>
+        <f>IF(TODAY()&lt;R7, 0, IF(TODAY()&gt;S7, T7, T7 * (TODAY()-R7)/MAX(1, S7-R7+1)))</f>
         <v/>
       </c>
       <c r="Z7" s="15">
@@ -1304,7 +1304,7 @@
       <c r="AI7" s="12" t="n"/>
       <c r="AJ7" s="14" t="n"/>
       <c r="AK7" s="15">
-        <f>IF(TODAY()&lt;AD7, 0, IF(TODAY()&gt;AE7, AF7, AF7 * (TODAY()-AD7)/(AE7-AD7+1)))</f>
+        <f>IF(TODAY()&lt;AD7, 0, IF(TODAY()&gt;AE7, AF7, AF7 * (TODAY()-AD7)/MAX(1, AE7-AD7+1)))</f>
         <v/>
       </c>
       <c r="AL7" s="15">
@@ -1330,7 +1330,7 @@
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="14" t="n"/>
       <c r="M8" s="15">
-        <f>IF(TODAY()&lt;F8, 0, IF(TODAY()&gt;G8, H8, H8 * (TODAY()-F8)/(G8-F8+1)))</f>
+        <f>IF(TODAY()&lt;F8, 0, IF(TODAY()&gt;G8, H8, H8 * (TODAY()-F8)/MAX(1, G8-F8+1)))</f>
         <v/>
       </c>
       <c r="N8" s="15">
@@ -1351,7 +1351,7 @@
       <c r="W8" s="12" t="n"/>
       <c r="X8" s="14" t="n"/>
       <c r="Y8" s="15">
-        <f>IF(TODAY()&lt;R8, 0, IF(TODAY()&gt;S8, T8, T8 * (TODAY()-R8)/(S8-R8+1)))</f>
+        <f>IF(TODAY()&lt;R8, 0, IF(TODAY()&gt;S8, T8, T8 * (TODAY()-R8)/MAX(1, S8-R8+1)))</f>
         <v/>
       </c>
       <c r="Z8" s="15">
@@ -1372,7 +1372,7 @@
       <c r="AI8" s="12" t="n"/>
       <c r="AJ8" s="14" t="n"/>
       <c r="AK8" s="15">
-        <f>IF(TODAY()&lt;AD8, 0, IF(TODAY()&gt;AE8, AF8, AF8 * (TODAY()-AD8)/(AE8-AD8+1)))</f>
+        <f>IF(TODAY()&lt;AD8, 0, IF(TODAY()&gt;AE8, AF8, AF8 * (TODAY()-AD8)/MAX(1, AE8-AD8+1)))</f>
         <v/>
       </c>
       <c r="AL8" s="15">
@@ -1398,7 +1398,7 @@
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="14" t="n"/>
       <c r="M9" s="15">
-        <f>IF(TODAY()&lt;F9, 0, IF(TODAY()&gt;G9, H9, H9 * (TODAY()-F9)/(G9-F9+1)))</f>
+        <f>IF(TODAY()&lt;F9, 0, IF(TODAY()&gt;G9, H9, H9 * (TODAY()-F9)/MAX(1, G9-F9+1)))</f>
         <v/>
       </c>
       <c r="N9" s="15">
@@ -1419,7 +1419,7 @@
       <c r="W9" s="12" t="n"/>
       <c r="X9" s="14" t="n"/>
       <c r="Y9" s="15">
-        <f>IF(TODAY()&lt;R9, 0, IF(TODAY()&gt;S9, T9, T9 * (TODAY()-R9)/(S9-R9+1)))</f>
+        <f>IF(TODAY()&lt;R9, 0, IF(TODAY()&gt;S9, T9, T9 * (TODAY()-R9)/MAX(1, S9-R9+1)))</f>
         <v/>
       </c>
       <c r="Z9" s="15">
@@ -1440,7 +1440,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AJ9" s="14" t="n"/>
       <c r="AK9" s="15">
-        <f>IF(TODAY()&lt;AD9, 0, IF(TODAY()&gt;AE9, AF9, AF9 * (TODAY()-AD9)/(AE9-AD9+1)))</f>
+        <f>IF(TODAY()&lt;AD9, 0, IF(TODAY()&gt;AE9, AF9, AF9 * (TODAY()-AD9)/MAX(1, AE9-AD9+1)))</f>
         <v/>
       </c>
       <c r="AL9" s="15">
@@ -1466,7 +1466,7 @@
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="14" t="n"/>
       <c r="M10" s="15">
-        <f>IF(TODAY()&lt;F10, 0, IF(TODAY()&gt;G10, H10, H10 * (TODAY()-F10)/(G10-F10+1)))</f>
+        <f>IF(TODAY()&lt;F10, 0, IF(TODAY()&gt;G10, H10, H10 * (TODAY()-F10)/MAX(1, G10-F10+1)))</f>
         <v/>
       </c>
       <c r="N10" s="15">
@@ -1487,7 +1487,7 @@
       <c r="W10" s="12" t="n"/>
       <c r="X10" s="14" t="n"/>
       <c r="Y10" s="15">
-        <f>IF(TODAY()&lt;R10, 0, IF(TODAY()&gt;S10, T10, T10 * (TODAY()-R10)/(S10-R10+1)))</f>
+        <f>IF(TODAY()&lt;R10, 0, IF(TODAY()&gt;S10, T10, T10 * (TODAY()-R10)/MAX(1, S10-R10+1)))</f>
         <v/>
       </c>
       <c r="Z10" s="15">
@@ -1508,7 +1508,7 @@
       <c r="AI10" s="12" t="n"/>
       <c r="AJ10" s="14" t="n"/>
       <c r="AK10" s="15">
-        <f>IF(TODAY()&lt;AD10, 0, IF(TODAY()&gt;AE10, AF10, AF10 * (TODAY()-AD10)/(AE10-AD10+1)))</f>
+        <f>IF(TODAY()&lt;AD10, 0, IF(TODAY()&gt;AE10, AF10, AF10 * (TODAY()-AD10)/MAX(1, AE10-AD10+1)))</f>
         <v/>
       </c>
       <c r="AL10" s="15">
@@ -1534,7 +1534,7 @@
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="14" t="n"/>
       <c r="M11" s="15">
-        <f>IF(TODAY()&lt;F11, 0, IF(TODAY()&gt;G11, H11, H11 * (TODAY()-F11)/(G11-F11+1)))</f>
+        <f>IF(TODAY()&lt;F11, 0, IF(TODAY()&gt;G11, H11, H11 * (TODAY()-F11)/MAX(1, G11-F11+1)))</f>
         <v/>
       </c>
       <c r="N11" s="15">
@@ -1555,7 +1555,7 @@
       <c r="W11" s="12" t="n"/>
       <c r="X11" s="14" t="n"/>
       <c r="Y11" s="15">
-        <f>IF(TODAY()&lt;R11, 0, IF(TODAY()&gt;S11, T11, T11 * (TODAY()-R11)/(S11-R11+1)))</f>
+        <f>IF(TODAY()&lt;R11, 0, IF(TODAY()&gt;S11, T11, T11 * (TODAY()-R11)/MAX(1, S11-R11+1)))</f>
         <v/>
       </c>
       <c r="Z11" s="15">
@@ -1576,7 +1576,7 @@
       <c r="AI11" s="12" t="n"/>
       <c r="AJ11" s="14" t="n"/>
       <c r="AK11" s="15">
-        <f>IF(TODAY()&lt;AD11, 0, IF(TODAY()&gt;AE11, AF11, AF11 * (TODAY()-AD11)/(AE11-AD11+1)))</f>
+        <f>IF(TODAY()&lt;AD11, 0, IF(TODAY()&gt;AE11, AF11, AF11 * (TODAY()-AD11)/MAX(1, AE11-AD11+1)))</f>
         <v/>
       </c>
       <c r="AL11" s="15">
@@ -1602,7 +1602,7 @@
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="14" t="n"/>
       <c r="M12" s="15">
-        <f>IF(TODAY()&lt;F12, 0, IF(TODAY()&gt;G12, H12, H12 * (TODAY()-F12)/(G12-F12+1)))</f>
+        <f>IF(TODAY()&lt;F12, 0, IF(TODAY()&gt;G12, H12, H12 * (TODAY()-F12)/MAX(1, G12-F12+1)))</f>
         <v/>
       </c>
       <c r="N12" s="15">
@@ -1623,7 +1623,7 @@
       <c r="W12" s="12" t="n"/>
       <c r="X12" s="14" t="n"/>
       <c r="Y12" s="15">
-        <f>IF(TODAY()&lt;R12, 0, IF(TODAY()&gt;S12, T12, T12 * (TODAY()-R12)/(S12-R12+1)))</f>
+        <f>IF(TODAY()&lt;R12, 0, IF(TODAY()&gt;S12, T12, T12 * (TODAY()-R12)/MAX(1, S12-R12+1)))</f>
         <v/>
       </c>
       <c r="Z12" s="15">
@@ -1644,7 +1644,7 @@
       <c r="AI12" s="12" t="n"/>
       <c r="AJ12" s="14" t="n"/>
       <c r="AK12" s="15">
-        <f>IF(TODAY()&lt;AD12, 0, IF(TODAY()&gt;AE12, AF12, AF12 * (TODAY()-AD12)/(AE12-AD12+1)))</f>
+        <f>IF(TODAY()&lt;AD12, 0, IF(TODAY()&gt;AE12, AF12, AF12 * (TODAY()-AD12)/MAX(1, AE12-AD12+1)))</f>
         <v/>
       </c>
       <c r="AL12" s="15">
@@ -1670,7 +1670,7 @@
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="14" t="n"/>
       <c r="M13" s="15">
-        <f>IF(TODAY()&lt;F13, 0, IF(TODAY()&gt;G13, H13, H13 * (TODAY()-F13)/(G13-F13+1)))</f>
+        <f>IF(TODAY()&lt;F13, 0, IF(TODAY()&gt;G13, H13, H13 * (TODAY()-F13)/MAX(1, G13-F13+1)))</f>
         <v/>
       </c>
       <c r="N13" s="15">
@@ -1691,7 +1691,7 @@
       <c r="W13" s="12" t="n"/>
       <c r="X13" s="14" t="n"/>
       <c r="Y13" s="15">
-        <f>IF(TODAY()&lt;R13, 0, IF(TODAY()&gt;S13, T13, T13 * (TODAY()-R13)/(S13-R13+1)))</f>
+        <f>IF(TODAY()&lt;R13, 0, IF(TODAY()&gt;S13, T13, T13 * (TODAY()-R13)/MAX(1, S13-R13+1)))</f>
         <v/>
       </c>
       <c r="Z13" s="15">
@@ -1712,7 +1712,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AJ13" s="14" t="n"/>
       <c r="AK13" s="15">
-        <f>IF(TODAY()&lt;AD13, 0, IF(TODAY()&gt;AE13, AF13, AF13 * (TODAY()-AD13)/(AE13-AD13+1)))</f>
+        <f>IF(TODAY()&lt;AD13, 0, IF(TODAY()&gt;AE13, AF13, AF13 * (TODAY()-AD13)/MAX(1, AE13-AD13+1)))</f>
         <v/>
       </c>
       <c r="AL13" s="15">
@@ -1738,7 +1738,7 @@
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="14" t="n"/>
       <c r="M14" s="15">
-        <f>IF(TODAY()&lt;F14, 0, IF(TODAY()&gt;G14, H14, H14 * (TODAY()-F14)/(G14-F14+1)))</f>
+        <f>IF(TODAY()&lt;F14, 0, IF(TODAY()&gt;G14, H14, H14 * (TODAY()-F14)/MAX(1, G14-F14+1)))</f>
         <v/>
       </c>
       <c r="N14" s="15">
@@ -1759,7 +1759,7 @@
       <c r="W14" s="12" t="n"/>
       <c r="X14" s="14" t="n"/>
       <c r="Y14" s="15">
-        <f>IF(TODAY()&lt;R14, 0, IF(TODAY()&gt;S14, T14, T14 * (TODAY()-R14)/(S14-R14+1)))</f>
+        <f>IF(TODAY()&lt;R14, 0, IF(TODAY()&gt;S14, T14, T14 * (TODAY()-R14)/MAX(1, S14-R14+1)))</f>
         <v/>
       </c>
       <c r="Z14" s="15">
@@ -1780,7 +1780,7 @@
       <c r="AI14" s="12" t="n"/>
       <c r="AJ14" s="14" t="n"/>
       <c r="AK14" s="15">
-        <f>IF(TODAY()&lt;AD14, 0, IF(TODAY()&gt;AE14, AF14, AF14 * (TODAY()-AD14)/(AE14-AD14+1)))</f>
+        <f>IF(TODAY()&lt;AD14, 0, IF(TODAY()&gt;AE14, AF14, AF14 * (TODAY()-AD14)/MAX(1, AE14-AD14+1)))</f>
         <v/>
       </c>
       <c r="AL14" s="15">
@@ -1806,7 +1806,7 @@
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="14" t="n"/>
       <c r="M15" s="15">
-        <f>IF(TODAY()&lt;F15, 0, IF(TODAY()&gt;G15, H15, H15 * (TODAY()-F15)/(G15-F15+1)))</f>
+        <f>IF(TODAY()&lt;F15, 0, IF(TODAY()&gt;G15, H15, H15 * (TODAY()-F15)/MAX(1, G15-F15+1)))</f>
         <v/>
       </c>
       <c r="N15" s="15">
@@ -1827,7 +1827,7 @@
       <c r="W15" s="12" t="n"/>
       <c r="X15" s="14" t="n"/>
       <c r="Y15" s="15">
-        <f>IF(TODAY()&lt;R15, 0, IF(TODAY()&gt;S15, T15, T15 * (TODAY()-R15)/(S15-R15+1)))</f>
+        <f>IF(TODAY()&lt;R15, 0, IF(TODAY()&gt;S15, T15, T15 * (TODAY()-R15)/MAX(1, S15-R15+1)))</f>
         <v/>
       </c>
       <c r="Z15" s="15">
@@ -1848,7 +1848,7 @@
       <c r="AI15" s="12" t="n"/>
       <c r="AJ15" s="14" t="n"/>
       <c r="AK15" s="15">
-        <f>IF(TODAY()&lt;AD15, 0, IF(TODAY()&gt;AE15, AF15, AF15 * (TODAY()-AD15)/(AE15-AD15+1)))</f>
+        <f>IF(TODAY()&lt;AD15, 0, IF(TODAY()&gt;AE15, AF15, AF15 * (TODAY()-AD15)/MAX(1, AE15-AD15+1)))</f>
         <v/>
       </c>
       <c r="AL15" s="15">
@@ -1874,7 +1874,7 @@
       <c r="K16" s="12" t="n"/>
       <c r="L16" s="14" t="n"/>
       <c r="M16" s="15">
-        <f>IF(TODAY()&lt;F16, 0, IF(TODAY()&gt;G16, H16, H16 * (TODAY()-F16)/(G16-F16+1)))</f>
+        <f>IF(TODAY()&lt;F16, 0, IF(TODAY()&gt;G16, H16, H16 * (TODAY()-F16)/MAX(1, G16-F16+1)))</f>
         <v/>
       </c>
       <c r="N16" s="15">
@@ -1895,7 +1895,7 @@
       <c r="W16" s="12" t="n"/>
       <c r="X16" s="14" t="n"/>
       <c r="Y16" s="15">
-        <f>IF(TODAY()&lt;R16, 0, IF(TODAY()&gt;S16, T16, T16 * (TODAY()-R16)/(S16-R16+1)))</f>
+        <f>IF(TODAY()&lt;R16, 0, IF(TODAY()&gt;S16, T16, T16 * (TODAY()-R16)/MAX(1, S16-R16+1)))</f>
         <v/>
       </c>
       <c r="Z16" s="15">
@@ -1916,7 +1916,7 @@
       <c r="AI16" s="12" t="n"/>
       <c r="AJ16" s="14" t="n"/>
       <c r="AK16" s="15">
-        <f>IF(TODAY()&lt;AD16, 0, IF(TODAY()&gt;AE16, AF16, AF16 * (TODAY()-AD16)/(AE16-AD16+1)))</f>
+        <f>IF(TODAY()&lt;AD16, 0, IF(TODAY()&gt;AE16, AF16, AF16 * (TODAY()-AD16)/MAX(1, AE16-AD16+1)))</f>
         <v/>
       </c>
       <c r="AL16" s="15">
@@ -1942,7 +1942,7 @@
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="14" t="n"/>
       <c r="M17" s="15">
-        <f>IF(TODAY()&lt;F17, 0, IF(TODAY()&gt;G17, H17, H17 * (TODAY()-F17)/(G17-F17+1)))</f>
+        <f>IF(TODAY()&lt;F17, 0, IF(TODAY()&gt;G17, H17, H17 * (TODAY()-F17)/MAX(1, G17-F17+1)))</f>
         <v/>
       </c>
       <c r="N17" s="15">
@@ -1963,7 +1963,7 @@
       <c r="W17" s="12" t="n"/>
       <c r="X17" s="14" t="n"/>
       <c r="Y17" s="15">
-        <f>IF(TODAY()&lt;R17, 0, IF(TODAY()&gt;S17, T17, T17 * (TODAY()-R17)/(S17-R17+1)))</f>
+        <f>IF(TODAY()&lt;R17, 0, IF(TODAY()&gt;S17, T17, T17 * (TODAY()-R17)/MAX(1, S17-R17+1)))</f>
         <v/>
       </c>
       <c r="Z17" s="15">
@@ -1984,7 +1984,7 @@
       <c r="AI17" s="12" t="n"/>
       <c r="AJ17" s="14" t="n"/>
       <c r="AK17" s="15">
-        <f>IF(TODAY()&lt;AD17, 0, IF(TODAY()&gt;AE17, AF17, AF17 * (TODAY()-AD17)/(AE17-AD17+1)))</f>
+        <f>IF(TODAY()&lt;AD17, 0, IF(TODAY()&gt;AE17, AF17, AF17 * (TODAY()-AD17)/MAX(1, AE17-AD17+1)))</f>
         <v/>
       </c>
       <c r="AL17" s="15">
@@ -2010,7 +2010,7 @@
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="14" t="n"/>
       <c r="M18" s="15">
-        <f>IF(TODAY()&lt;F18, 0, IF(TODAY()&gt;G18, H18, H18 * (TODAY()-F18)/(G18-F18+1)))</f>
+        <f>IF(TODAY()&lt;F18, 0, IF(TODAY()&gt;G18, H18, H18 * (TODAY()-F18)/MAX(1, G18-F18+1)))</f>
         <v/>
       </c>
       <c r="N18" s="15">
@@ -2031,7 +2031,7 @@
       <c r="W18" s="12" t="n"/>
       <c r="X18" s="14" t="n"/>
       <c r="Y18" s="15">
-        <f>IF(TODAY()&lt;R18, 0, IF(TODAY()&gt;S18, T18, T18 * (TODAY()-R18)/(S18-R18+1)))</f>
+        <f>IF(TODAY()&lt;R18, 0, IF(TODAY()&gt;S18, T18, T18 * (TODAY()-R18)/MAX(1, S18-R18+1)))</f>
         <v/>
       </c>
       <c r="Z18" s="15">
@@ -2052,7 +2052,7 @@
       <c r="AI18" s="12" t="n"/>
       <c r="AJ18" s="14" t="n"/>
       <c r="AK18" s="15">
-        <f>IF(TODAY()&lt;AD18, 0, IF(TODAY()&gt;AE18, AF18, AF18 * (TODAY()-AD18)/(AE18-AD18+1)))</f>
+        <f>IF(TODAY()&lt;AD18, 0, IF(TODAY()&gt;AE18, AF18, AF18 * (TODAY()-AD18)/MAX(1, AE18-AD18+1)))</f>
         <v/>
       </c>
       <c r="AL18" s="15">
@@ -2078,7 +2078,7 @@
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="14" t="n"/>
       <c r="M19" s="15">
-        <f>IF(TODAY()&lt;F19, 0, IF(TODAY()&gt;G19, H19, H19 * (TODAY()-F19)/(G19-F19+1)))</f>
+        <f>IF(TODAY()&lt;F19, 0, IF(TODAY()&gt;G19, H19, H19 * (TODAY()-F19)/MAX(1, G19-F19+1)))</f>
         <v/>
       </c>
       <c r="N19" s="15">
@@ -2099,7 +2099,7 @@
       <c r="W19" s="12" t="n"/>
       <c r="X19" s="14" t="n"/>
       <c r="Y19" s="15">
-        <f>IF(TODAY()&lt;R19, 0, IF(TODAY()&gt;S19, T19, T19 * (TODAY()-R19)/(S19-R19+1)))</f>
+        <f>IF(TODAY()&lt;R19, 0, IF(TODAY()&gt;S19, T19, T19 * (TODAY()-R19)/MAX(1, S19-R19+1)))</f>
         <v/>
       </c>
       <c r="Z19" s="15">
@@ -2120,7 +2120,7 @@
       <c r="AI19" s="12" t="n"/>
       <c r="AJ19" s="14" t="n"/>
       <c r="AK19" s="15">
-        <f>IF(TODAY()&lt;AD19, 0, IF(TODAY()&gt;AE19, AF19, AF19 * (TODAY()-AD19)/(AE19-AD19+1)))</f>
+        <f>IF(TODAY()&lt;AD19, 0, IF(TODAY()&gt;AE19, AF19, AF19 * (TODAY()-AD19)/MAX(1, AE19-AD19+1)))</f>
         <v/>
       </c>
       <c r="AL19" s="15">
@@ -2146,7 +2146,7 @@
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="14" t="n"/>
       <c r="M20" s="15">
-        <f>IF(TODAY()&lt;F20, 0, IF(TODAY()&gt;G20, H20, H20 * (TODAY()-F20)/(G20-F20+1)))</f>
+        <f>IF(TODAY()&lt;F20, 0, IF(TODAY()&gt;G20, H20, H20 * (TODAY()-F20)/MAX(1, G20-F20+1)))</f>
         <v/>
       </c>
       <c r="N20" s="15">
@@ -2167,7 +2167,7 @@
       <c r="W20" s="12" t="n"/>
       <c r="X20" s="14" t="n"/>
       <c r="Y20" s="15">
-        <f>IF(TODAY()&lt;R20, 0, IF(TODAY()&gt;S20, T20, T20 * (TODAY()-R20)/(S20-R20+1)))</f>
+        <f>IF(TODAY()&lt;R20, 0, IF(TODAY()&gt;S20, T20, T20 * (TODAY()-R20)/MAX(1, S20-R20+1)))</f>
         <v/>
       </c>
       <c r="Z20" s="15">
@@ -2188,7 +2188,7 @@
       <c r="AI20" s="12" t="n"/>
       <c r="AJ20" s="14" t="n"/>
       <c r="AK20" s="15">
-        <f>IF(TODAY()&lt;AD20, 0, IF(TODAY()&gt;AE20, AF20, AF20 * (TODAY()-AD20)/(AE20-AD20+1)))</f>
+        <f>IF(TODAY()&lt;AD20, 0, IF(TODAY()&gt;AE20, AF20, AF20 * (TODAY()-AD20)/MAX(1, AE20-AD20+1)))</f>
         <v/>
       </c>
       <c r="AL20" s="15">
@@ -2214,7 +2214,7 @@
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="14" t="n"/>
       <c r="M21" s="15">
-        <f>IF(TODAY()&lt;F21, 0, IF(TODAY()&gt;G21, H21, H21 * (TODAY()-F21)/(G21-F21+1)))</f>
+        <f>IF(TODAY()&lt;F21, 0, IF(TODAY()&gt;G21, H21, H21 * (TODAY()-F21)/MAX(1, G21-F21+1)))</f>
         <v/>
       </c>
       <c r="N21" s="15">
@@ -2235,7 +2235,7 @@
       <c r="W21" s="12" t="n"/>
       <c r="X21" s="14" t="n"/>
       <c r="Y21" s="15">
-        <f>IF(TODAY()&lt;R21, 0, IF(TODAY()&gt;S21, T21, T21 * (TODAY()-R21)/(S21-R21+1)))</f>
+        <f>IF(TODAY()&lt;R21, 0, IF(TODAY()&gt;S21, T21, T21 * (TODAY()-R21)/MAX(1, S21-R21+1)))</f>
         <v/>
       </c>
       <c r="Z21" s="15">
@@ -2256,7 +2256,7 @@
       <c r="AI21" s="12" t="n"/>
       <c r="AJ21" s="14" t="n"/>
       <c r="AK21" s="15">
-        <f>IF(TODAY()&lt;AD21, 0, IF(TODAY()&gt;AE21, AF21, AF21 * (TODAY()-AD21)/(AE21-AD21+1)))</f>
+        <f>IF(TODAY()&lt;AD21, 0, IF(TODAY()&gt;AE21, AF21, AF21 * (TODAY()-AD21)/MAX(1, AE21-AD21+1)))</f>
         <v/>
       </c>
       <c r="AL21" s="15">
@@ -2282,7 +2282,7 @@
       <c r="K22" s="12" t="n"/>
       <c r="L22" s="14" t="n"/>
       <c r="M22" s="15">
-        <f>IF(TODAY()&lt;F22, 0, IF(TODAY()&gt;G22, H22, H22 * (TODAY()-F22)/(G22-F22+1)))</f>
+        <f>IF(TODAY()&lt;F22, 0, IF(TODAY()&gt;G22, H22, H22 * (TODAY()-F22)/MAX(1, G22-F22+1)))</f>
         <v/>
       </c>
       <c r="N22" s="15">
@@ -2303,7 +2303,7 @@
       <c r="W22" s="12" t="n"/>
       <c r="X22" s="14" t="n"/>
       <c r="Y22" s="15">
-        <f>IF(TODAY()&lt;R22, 0, IF(TODAY()&gt;S22, T22, T22 * (TODAY()-R22)/(S22-R22+1)))</f>
+        <f>IF(TODAY()&lt;R22, 0, IF(TODAY()&gt;S22, T22, T22 * (TODAY()-R22)/MAX(1, S22-R22+1)))</f>
         <v/>
       </c>
       <c r="Z22" s="15">
@@ -2324,7 +2324,7 @@
       <c r="AI22" s="12" t="n"/>
       <c r="AJ22" s="14" t="n"/>
       <c r="AK22" s="15">
-        <f>IF(TODAY()&lt;AD22, 0, IF(TODAY()&gt;AE22, AF22, AF22 * (TODAY()-AD22)/(AE22-AD22+1)))</f>
+        <f>IF(TODAY()&lt;AD22, 0, IF(TODAY()&gt;AE22, AF22, AF22 * (TODAY()-AD22)/MAX(1, AE22-AD22+1)))</f>
         <v/>
       </c>
       <c r="AL22" s="15">
@@ -2350,7 +2350,7 @@
       <c r="K23" s="12" t="n"/>
       <c r="L23" s="14" t="n"/>
       <c r="M23" s="15">
-        <f>IF(TODAY()&lt;F23, 0, IF(TODAY()&gt;G23, H23, H23 * (TODAY()-F23)/(G23-F23+1)))</f>
+        <f>IF(TODAY()&lt;F23, 0, IF(TODAY()&gt;G23, H23, H23 * (TODAY()-F23)/MAX(1, G23-F23+1)))</f>
         <v/>
       </c>
       <c r="N23" s="15">
@@ -2371,7 +2371,7 @@
       <c r="W23" s="12" t="n"/>
       <c r="X23" s="14" t="n"/>
       <c r="Y23" s="15">
-        <f>IF(TODAY()&lt;R23, 0, IF(TODAY()&gt;S23, T23, T23 * (TODAY()-R23)/(S23-R23+1)))</f>
+        <f>IF(TODAY()&lt;R23, 0, IF(TODAY()&gt;S23, T23, T23 * (TODAY()-R23)/MAX(1, S23-R23+1)))</f>
         <v/>
       </c>
       <c r="Z23" s="15">
@@ -2392,7 +2392,7 @@
       <c r="AI23" s="12" t="n"/>
       <c r="AJ23" s="14" t="n"/>
       <c r="AK23" s="15">
-        <f>IF(TODAY()&lt;AD23, 0, IF(TODAY()&gt;AE23, AF23, AF23 * (TODAY()-AD23)/(AE23-AD23+1)))</f>
+        <f>IF(TODAY()&lt;AD23, 0, IF(TODAY()&gt;AE23, AF23, AF23 * (TODAY()-AD23)/MAX(1, AE23-AD23+1)))</f>
         <v/>
       </c>
       <c r="AL23" s="15">
@@ -2418,7 +2418,7 @@
       <c r="K24" s="12" t="n"/>
       <c r="L24" s="14" t="n"/>
       <c r="M24" s="15">
-        <f>IF(TODAY()&lt;F24, 0, IF(TODAY()&gt;G24, H24, H24 * (TODAY()-F24)/(G24-F24+1)))</f>
+        <f>IF(TODAY()&lt;F24, 0, IF(TODAY()&gt;G24, H24, H24 * (TODAY()-F24)/MAX(1, G24-F24+1)))</f>
         <v/>
       </c>
       <c r="N24" s="15">
@@ -2439,7 +2439,7 @@
       <c r="W24" s="12" t="n"/>
       <c r="X24" s="14" t="n"/>
       <c r="Y24" s="15">
-        <f>IF(TODAY()&lt;R24, 0, IF(TODAY()&gt;S24, T24, T24 * (TODAY()-R24)/(S24-R24+1)))</f>
+        <f>IF(TODAY()&lt;R24, 0, IF(TODAY()&gt;S24, T24, T24 * (TODAY()-R24)/MAX(1, S24-R24+1)))</f>
         <v/>
       </c>
       <c r="Z24" s="15">
@@ -2460,7 +2460,7 @@
       <c r="AI24" s="12" t="n"/>
       <c r="AJ24" s="14" t="n"/>
       <c r="AK24" s="15">
-        <f>IF(TODAY()&lt;AD24, 0, IF(TODAY()&gt;AE24, AF24, AF24 * (TODAY()-AD24)/(AE24-AD24+1)))</f>
+        <f>IF(TODAY()&lt;AD24, 0, IF(TODAY()&gt;AE24, AF24, AF24 * (TODAY()-AD24)/MAX(1, AE24-AD24+1)))</f>
         <v/>
       </c>
       <c r="AL24" s="15">
@@ -2486,7 +2486,7 @@
       <c r="K25" s="12" t="n"/>
       <c r="L25" s="14" t="n"/>
       <c r="M25" s="15">
-        <f>IF(TODAY()&lt;F25, 0, IF(TODAY()&gt;G25, H25, H25 * (TODAY()-F25)/(G25-F25+1)))</f>
+        <f>IF(TODAY()&lt;F25, 0, IF(TODAY()&gt;G25, H25, H25 * (TODAY()-F25)/MAX(1, G25-F25+1)))</f>
         <v/>
       </c>
       <c r="N25" s="15">
@@ -2507,7 +2507,7 @@
       <c r="W25" s="12" t="n"/>
       <c r="X25" s="14" t="n"/>
       <c r="Y25" s="15">
-        <f>IF(TODAY()&lt;R25, 0, IF(TODAY()&gt;S25, T25, T25 * (TODAY()-R25)/(S25-R25+1)))</f>
+        <f>IF(TODAY()&lt;R25, 0, IF(TODAY()&gt;S25, T25, T25 * (TODAY()-R25)/MAX(1, S25-R25+1)))</f>
         <v/>
       </c>
       <c r="Z25" s="15">
@@ -2528,7 +2528,7 @@
       <c r="AI25" s="12" t="n"/>
       <c r="AJ25" s="14" t="n"/>
       <c r="AK25" s="15">
-        <f>IF(TODAY()&lt;AD25, 0, IF(TODAY()&gt;AE25, AF25, AF25 * (TODAY()-AD25)/(AE25-AD25+1)))</f>
+        <f>IF(TODAY()&lt;AD25, 0, IF(TODAY()&gt;AE25, AF25, AF25 * (TODAY()-AD25)/MAX(1, AE25-AD25+1)))</f>
         <v/>
       </c>
       <c r="AL25" s="15">
@@ -2554,7 +2554,7 @@
       <c r="K26" s="12" t="n"/>
       <c r="L26" s="14" t="n"/>
       <c r="M26" s="15">
-        <f>IF(TODAY()&lt;F26, 0, IF(TODAY()&gt;G26, H26, H26 * (TODAY()-F26)/(G26-F26+1)))</f>
+        <f>IF(TODAY()&lt;F26, 0, IF(TODAY()&gt;G26, H26, H26 * (TODAY()-F26)/MAX(1, G26-F26+1)))</f>
         <v/>
       </c>
       <c r="N26" s="15">
@@ -2575,7 +2575,7 @@
       <c r="W26" s="12" t="n"/>
       <c r="X26" s="14" t="n"/>
       <c r="Y26" s="15">
-        <f>IF(TODAY()&lt;R26, 0, IF(TODAY()&gt;S26, T26, T26 * (TODAY()-R26)/(S26-R26+1)))</f>
+        <f>IF(TODAY()&lt;R26, 0, IF(TODAY()&gt;S26, T26, T26 * (TODAY()-R26)/MAX(1, S26-R26+1)))</f>
         <v/>
       </c>
       <c r="Z26" s="15">
@@ -2596,7 +2596,7 @@
       <c r="AI26" s="12" t="n"/>
       <c r="AJ26" s="14" t="n"/>
       <c r="AK26" s="15">
-        <f>IF(TODAY()&lt;AD26, 0, IF(TODAY()&gt;AE26, AF26, AF26 * (TODAY()-AD26)/(AE26-AD26+1)))</f>
+        <f>IF(TODAY()&lt;AD26, 0, IF(TODAY()&gt;AE26, AF26, AF26 * (TODAY()-AD26)/MAX(1, AE26-AD26+1)))</f>
         <v/>
       </c>
       <c r="AL26" s="15">
@@ -2622,7 +2622,7 @@
       <c r="K27" s="12" t="n"/>
       <c r="L27" s="14" t="n"/>
       <c r="M27" s="15">
-        <f>IF(TODAY()&lt;F27, 0, IF(TODAY()&gt;G27, H27, H27 * (TODAY()-F27)/(G27-F27+1)))</f>
+        <f>IF(TODAY()&lt;F27, 0, IF(TODAY()&gt;G27, H27, H27 * (TODAY()-F27)/MAX(1, G27-F27+1)))</f>
         <v/>
       </c>
       <c r="N27" s="15">
@@ -2643,7 +2643,7 @@
       <c r="W27" s="12" t="n"/>
       <c r="X27" s="14" t="n"/>
       <c r="Y27" s="15">
-        <f>IF(TODAY()&lt;R27, 0, IF(TODAY()&gt;S27, T27, T27 * (TODAY()-R27)/(S27-R27+1)))</f>
+        <f>IF(TODAY()&lt;R27, 0, IF(TODAY()&gt;S27, T27, T27 * (TODAY()-R27)/MAX(1, S27-R27+1)))</f>
         <v/>
       </c>
       <c r="Z27" s="15">
@@ -2664,7 +2664,7 @@
       <c r="AI27" s="12" t="n"/>
       <c r="AJ27" s="14" t="n"/>
       <c r="AK27" s="15">
-        <f>IF(TODAY()&lt;AD27, 0, IF(TODAY()&gt;AE27, AF27, AF27 * (TODAY()-AD27)/(AE27-AD27+1)))</f>
+        <f>IF(TODAY()&lt;AD27, 0, IF(TODAY()&gt;AE27, AF27, AF27 * (TODAY()-AD27)/MAX(1, AE27-AD27+1)))</f>
         <v/>
       </c>
       <c r="AL27" s="15">
@@ -2690,7 +2690,7 @@
       <c r="K28" s="12" t="n"/>
       <c r="L28" s="14" t="n"/>
       <c r="M28" s="15">
-        <f>IF(TODAY()&lt;F28, 0, IF(TODAY()&gt;G28, H28, H28 * (TODAY()-F28)/(G28-F28+1)))</f>
+        <f>IF(TODAY()&lt;F28, 0, IF(TODAY()&gt;G28, H28, H28 * (TODAY()-F28)/MAX(1, G28-F28+1)))</f>
         <v/>
       </c>
       <c r="N28" s="15">
@@ -2711,7 +2711,7 @@
       <c r="W28" s="12" t="n"/>
       <c r="X28" s="14" t="n"/>
       <c r="Y28" s="15">
-        <f>IF(TODAY()&lt;R28, 0, IF(TODAY()&gt;S28, T28, T28 * (TODAY()-R28)/(S28-R28+1)))</f>
+        <f>IF(TODAY()&lt;R28, 0, IF(TODAY()&gt;S28, T28, T28 * (TODAY()-R28)/MAX(1, S28-R28+1)))</f>
         <v/>
       </c>
       <c r="Z28" s="15">
@@ -2732,7 +2732,7 @@
       <c r="AI28" s="12" t="n"/>
       <c r="AJ28" s="14" t="n"/>
       <c r="AK28" s="15">
-        <f>IF(TODAY()&lt;AD28, 0, IF(TODAY()&gt;AE28, AF28, AF28 * (TODAY()-AD28)/(AE28-AD28+1)))</f>
+        <f>IF(TODAY()&lt;AD28, 0, IF(TODAY()&gt;AE28, AF28, AF28 * (TODAY()-AD28)/MAX(1, AE28-AD28+1)))</f>
         <v/>
       </c>
       <c r="AL28" s="15">
@@ -2758,7 +2758,7 @@
       <c r="K29" s="12" t="n"/>
       <c r="L29" s="14" t="n"/>
       <c r="M29" s="15">
-        <f>IF(TODAY()&lt;F29, 0, IF(TODAY()&gt;G29, H29, H29 * (TODAY()-F29)/(G29-F29+1)))</f>
+        <f>IF(TODAY()&lt;F29, 0, IF(TODAY()&gt;G29, H29, H29 * (TODAY()-F29)/MAX(1, G29-F29+1)))</f>
         <v/>
       </c>
       <c r="N29" s="15">
@@ -2779,7 +2779,7 @@
       <c r="W29" s="12" t="n"/>
       <c r="X29" s="14" t="n"/>
       <c r="Y29" s="15">
-        <f>IF(TODAY()&lt;R29, 0, IF(TODAY()&gt;S29, T29, T29 * (TODAY()-R29)/(S29-R29+1)))</f>
+        <f>IF(TODAY()&lt;R29, 0, IF(TODAY()&gt;S29, T29, T29 * (TODAY()-R29)/MAX(1, S29-R29+1)))</f>
         <v/>
       </c>
       <c r="Z29" s="15">
@@ -2800,7 +2800,7 @@
       <c r="AI29" s="12" t="n"/>
       <c r="AJ29" s="14" t="n"/>
       <c r="AK29" s="15">
-        <f>IF(TODAY()&lt;AD29, 0, IF(TODAY()&gt;AE29, AF29, AF29 * (TODAY()-AD29)/(AE29-AD29+1)))</f>
+        <f>IF(TODAY()&lt;AD29, 0, IF(TODAY()&gt;AE29, AF29, AF29 * (TODAY()-AD29)/MAX(1, AE29-AD29+1)))</f>
         <v/>
       </c>
       <c r="AL29" s="15">
@@ -2826,7 +2826,7 @@
       <c r="K30" s="12" t="n"/>
       <c r="L30" s="14" t="n"/>
       <c r="M30" s="15">
-        <f>IF(TODAY()&lt;F30, 0, IF(TODAY()&gt;G30, H30, H30 * (TODAY()-F30)/(G30-F30+1)))</f>
+        <f>IF(TODAY()&lt;F30, 0, IF(TODAY()&gt;G30, H30, H30 * (TODAY()-F30)/MAX(1, G30-F30+1)))</f>
         <v/>
       </c>
       <c r="N30" s="15">
@@ -2847,7 +2847,7 @@
       <c r="W30" s="12" t="n"/>
       <c r="X30" s="14" t="n"/>
       <c r="Y30" s="15">
-        <f>IF(TODAY()&lt;R30, 0, IF(TODAY()&gt;S30, T30, T30 * (TODAY()-R30)/(S30-R30+1)))</f>
+        <f>IF(TODAY()&lt;R30, 0, IF(TODAY()&gt;S30, T30, T30 * (TODAY()-R30)/MAX(1, S30-R30+1)))</f>
         <v/>
       </c>
       <c r="Z30" s="15">
@@ -2868,7 +2868,7 @@
       <c r="AI30" s="12" t="n"/>
       <c r="AJ30" s="14" t="n"/>
       <c r="AK30" s="15">
-        <f>IF(TODAY()&lt;AD30, 0, IF(TODAY()&gt;AE30, AF30, AF30 * (TODAY()-AD30)/(AE30-AD30+1)))</f>
+        <f>IF(TODAY()&lt;AD30, 0, IF(TODAY()&gt;AE30, AF30, AF30 * (TODAY()-AD30)/MAX(1, AE30-AD30+1)))</f>
         <v/>
       </c>
       <c r="AL30" s="15">
@@ -2894,7 +2894,7 @@
       <c r="K31" s="12" t="n"/>
       <c r="L31" s="14" t="n"/>
       <c r="M31" s="15">
-        <f>IF(TODAY()&lt;F31, 0, IF(TODAY()&gt;G31, H31, H31 * (TODAY()-F31)/(G31-F31+1)))</f>
+        <f>IF(TODAY()&lt;F31, 0, IF(TODAY()&gt;G31, H31, H31 * (TODAY()-F31)/MAX(1, G31-F31+1)))</f>
         <v/>
       </c>
       <c r="N31" s="15">
@@ -2915,7 +2915,7 @@
       <c r="W31" s="12" t="n"/>
       <c r="X31" s="14" t="n"/>
       <c r="Y31" s="15">
-        <f>IF(TODAY()&lt;R31, 0, IF(TODAY()&gt;S31, T31, T31 * (TODAY()-R31)/(S31-R31+1)))</f>
+        <f>IF(TODAY()&lt;R31, 0, IF(TODAY()&gt;S31, T31, T31 * (TODAY()-R31)/MAX(1, S31-R31+1)))</f>
         <v/>
       </c>
       <c r="Z31" s="15">
@@ -2936,7 +2936,7 @@
       <c r="AI31" s="12" t="n"/>
       <c r="AJ31" s="14" t="n"/>
       <c r="AK31" s="15">
-        <f>IF(TODAY()&lt;AD31, 0, IF(TODAY()&gt;AE31, AF31, AF31 * (TODAY()-AD31)/(AE31-AD31+1)))</f>
+        <f>IF(TODAY()&lt;AD31, 0, IF(TODAY()&gt;AE31, AF31, AF31 * (TODAY()-AD31)/MAX(1, AE31-AD31+1)))</f>
         <v/>
       </c>
       <c r="AL31" s="15">
@@ -2962,7 +2962,7 @@
       <c r="K32" s="12" t="n"/>
       <c r="L32" s="14" t="n"/>
       <c r="M32" s="15">
-        <f>IF(TODAY()&lt;F32, 0, IF(TODAY()&gt;G32, H32, H32 * (TODAY()-F32)/(G32-F32+1)))</f>
+        <f>IF(TODAY()&lt;F32, 0, IF(TODAY()&gt;G32, H32, H32 * (TODAY()-F32)/MAX(1, G32-F32+1)))</f>
         <v/>
       </c>
       <c r="N32" s="15">
@@ -2983,7 +2983,7 @@
       <c r="W32" s="12" t="n"/>
       <c r="X32" s="14" t="n"/>
       <c r="Y32" s="15">
-        <f>IF(TODAY()&lt;R32, 0, IF(TODAY()&gt;S32, T32, T32 * (TODAY()-R32)/(S32-R32+1)))</f>
+        <f>IF(TODAY()&lt;R32, 0, IF(TODAY()&gt;S32, T32, T32 * (TODAY()-R32)/MAX(1, S32-R32+1)))</f>
         <v/>
       </c>
       <c r="Z32" s="15">
@@ -3004,7 +3004,7 @@
       <c r="AI32" s="12" t="n"/>
       <c r="AJ32" s="14" t="n"/>
       <c r="AK32" s="15">
-        <f>IF(TODAY()&lt;AD32, 0, IF(TODAY()&gt;AE32, AF32, AF32 * (TODAY()-AD32)/(AE32-AD32+1)))</f>
+        <f>IF(TODAY()&lt;AD32, 0, IF(TODAY()&gt;AE32, AF32, AF32 * (TODAY()-AD32)/MAX(1, AE32-AD32+1)))</f>
         <v/>
       </c>
       <c r="AL32" s="15">
@@ -3030,7 +3030,7 @@
       <c r="K33" s="12" t="n"/>
       <c r="L33" s="14" t="n"/>
       <c r="M33" s="15">
-        <f>IF(TODAY()&lt;F33, 0, IF(TODAY()&gt;G33, H33, H33 * (TODAY()-F33)/(G33-F33+1)))</f>
+        <f>IF(TODAY()&lt;F33, 0, IF(TODAY()&gt;G33, H33, H33 * (TODAY()-F33)/MAX(1, G33-F33+1)))</f>
         <v/>
       </c>
       <c r="N33" s="15">
@@ -3051,7 +3051,7 @@
       <c r="W33" s="12" t="n"/>
       <c r="X33" s="14" t="n"/>
       <c r="Y33" s="15">
-        <f>IF(TODAY()&lt;R33, 0, IF(TODAY()&gt;S33, T33, T33 * (TODAY()-R33)/(S33-R33+1)))</f>
+        <f>IF(TODAY()&lt;R33, 0, IF(TODAY()&gt;S33, T33, T33 * (TODAY()-R33)/MAX(1, S33-R33+1)))</f>
         <v/>
       </c>
       <c r="Z33" s="15">
@@ -3072,7 +3072,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AJ33" s="14" t="n"/>
       <c r="AK33" s="15">
-        <f>IF(TODAY()&lt;AD33, 0, IF(TODAY()&gt;AE33, AF33, AF33 * (TODAY()-AD33)/(AE33-AD33+1)))</f>
+        <f>IF(TODAY()&lt;AD33, 0, IF(TODAY()&gt;AE33, AF33, AF33 * (TODAY()-AD33)/MAX(1, AE33-AD33+1)))</f>
         <v/>
       </c>
       <c r="AL33" s="15">
@@ -3098,7 +3098,7 @@
       <c r="K34" s="12" t="n"/>
       <c r="L34" s="14" t="n"/>
       <c r="M34" s="15">
-        <f>IF(TODAY()&lt;F34, 0, IF(TODAY()&gt;G34, H34, H34 * (TODAY()-F34)/(G34-F34+1)))</f>
+        <f>IF(TODAY()&lt;F34, 0, IF(TODAY()&gt;G34, H34, H34 * (TODAY()-F34)/MAX(1, G34-F34+1)))</f>
         <v/>
       </c>
       <c r="N34" s="15">
@@ -3119,7 +3119,7 @@
       <c r="W34" s="12" t="n"/>
       <c r="X34" s="14" t="n"/>
       <c r="Y34" s="15">
-        <f>IF(TODAY()&lt;R34, 0, IF(TODAY()&gt;S34, T34, T34 * (TODAY()-R34)/(S34-R34+1)))</f>
+        <f>IF(TODAY()&lt;R34, 0, IF(TODAY()&gt;S34, T34, T34 * (TODAY()-R34)/MAX(1, S34-R34+1)))</f>
         <v/>
       </c>
       <c r="Z34" s="15">
@@ -3140,7 +3140,7 @@
       <c r="AI34" s="12" t="n"/>
       <c r="AJ34" s="14" t="n"/>
       <c r="AK34" s="15">
-        <f>IF(TODAY()&lt;AD34, 0, IF(TODAY()&gt;AE34, AF34, AF34 * (TODAY()-AD34)/(AE34-AD34+1)))</f>
+        <f>IF(TODAY()&lt;AD34, 0, IF(TODAY()&gt;AE34, AF34, AF34 * (TODAY()-AD34)/MAX(1, AE34-AD34+1)))</f>
         <v/>
       </c>
       <c r="AL34" s="15">
@@ -3166,7 +3166,7 @@
       <c r="K35" s="12" t="n"/>
       <c r="L35" s="14" t="n"/>
       <c r="M35" s="15">
-        <f>IF(TODAY()&lt;F35, 0, IF(TODAY()&gt;G35, H35, H35 * (TODAY()-F35)/(G35-F35+1)))</f>
+        <f>IF(TODAY()&lt;F35, 0, IF(TODAY()&gt;G35, H35, H35 * (TODAY()-F35)/MAX(1, G35-F35+1)))</f>
         <v/>
       </c>
       <c r="N35" s="15">
@@ -3187,7 +3187,7 @@
       <c r="W35" s="12" t="n"/>
       <c r="X35" s="14" t="n"/>
       <c r="Y35" s="15">
-        <f>IF(TODAY()&lt;R35, 0, IF(TODAY()&gt;S35, T35, T35 * (TODAY()-R35)/(S35-R35+1)))</f>
+        <f>IF(TODAY()&lt;R35, 0, IF(TODAY()&gt;S35, T35, T35 * (TODAY()-R35)/MAX(1, S35-R35+1)))</f>
         <v/>
       </c>
       <c r="Z35" s="15">
@@ -3208,7 +3208,7 @@
       <c r="AI35" s="12" t="n"/>
       <c r="AJ35" s="14" t="n"/>
       <c r="AK35" s="15">
-        <f>IF(TODAY()&lt;AD35, 0, IF(TODAY()&gt;AE35, AF35, AF35 * (TODAY()-AD35)/(AE35-AD35+1)))</f>
+        <f>IF(TODAY()&lt;AD35, 0, IF(TODAY()&gt;AE35, AF35, AF35 * (TODAY()-AD35)/MAX(1, AE35-AD35+1)))</f>
         <v/>
       </c>
       <c r="AL35" s="15">
@@ -3234,7 +3234,7 @@
       <c r="K36" s="12" t="n"/>
       <c r="L36" s="14" t="n"/>
       <c r="M36" s="15">
-        <f>IF(TODAY()&lt;F36, 0, IF(TODAY()&gt;G36, H36, H36 * (TODAY()-F36)/(G36-F36+1)))</f>
+        <f>IF(TODAY()&lt;F36, 0, IF(TODAY()&gt;G36, H36, H36 * (TODAY()-F36)/MAX(1, G36-F36+1)))</f>
         <v/>
       </c>
       <c r="N36" s="15">
@@ -3255,7 +3255,7 @@
       <c r="W36" s="12" t="n"/>
       <c r="X36" s="14" t="n"/>
       <c r="Y36" s="15">
-        <f>IF(TODAY()&lt;R36, 0, IF(TODAY()&gt;S36, T36, T36 * (TODAY()-R36)/(S36-R36+1)))</f>
+        <f>IF(TODAY()&lt;R36, 0, IF(TODAY()&gt;S36, T36, T36 * (TODAY()-R36)/MAX(1, S36-R36+1)))</f>
         <v/>
       </c>
       <c r="Z36" s="15">
@@ -3276,7 +3276,7 @@
       <c r="AI36" s="12" t="n"/>
       <c r="AJ36" s="14" t="n"/>
       <c r="AK36" s="15">
-        <f>IF(TODAY()&lt;AD36, 0, IF(TODAY()&gt;AE36, AF36, AF36 * (TODAY()-AD36)/(AE36-AD36+1)))</f>
+        <f>IF(TODAY()&lt;AD36, 0, IF(TODAY()&gt;AE36, AF36, AF36 * (TODAY()-AD36)/MAX(1, AE36-AD36+1)))</f>
         <v/>
       </c>
       <c r="AL36" s="15">
@@ -3302,7 +3302,7 @@
       <c r="K37" s="12" t="n"/>
       <c r="L37" s="14" t="n"/>
       <c r="M37" s="15">
-        <f>IF(TODAY()&lt;F37, 0, IF(TODAY()&gt;G37, H37, H37 * (TODAY()-F37)/(G37-F37+1)))</f>
+        <f>IF(TODAY()&lt;F37, 0, IF(TODAY()&gt;G37, H37, H37 * (TODAY()-F37)/MAX(1, G37-F37+1)))</f>
         <v/>
       </c>
       <c r="N37" s="15">
@@ -3323,7 +3323,7 @@
       <c r="W37" s="12" t="n"/>
       <c r="X37" s="14" t="n"/>
       <c r="Y37" s="15">
-        <f>IF(TODAY()&lt;R37, 0, IF(TODAY()&gt;S37, T37, T37 * (TODAY()-R37)/(S37-R37+1)))</f>
+        <f>IF(TODAY()&lt;R37, 0, IF(TODAY()&gt;S37, T37, T37 * (TODAY()-R37)/MAX(1, S37-R37+1)))</f>
         <v/>
       </c>
       <c r="Z37" s="15">
@@ -3344,7 +3344,7 @@
       <c r="AI37" s="12" t="n"/>
       <c r="AJ37" s="14" t="n"/>
       <c r="AK37" s="15">
-        <f>IF(TODAY()&lt;AD37, 0, IF(TODAY()&gt;AE37, AF37, AF37 * (TODAY()-AD37)/(AE37-AD37+1)))</f>
+        <f>IF(TODAY()&lt;AD37, 0, IF(TODAY()&gt;AE37, AF37, AF37 * (TODAY()-AD37)/MAX(1, AE37-AD37+1)))</f>
         <v/>
       </c>
       <c r="AL37" s="15">
@@ -3370,7 +3370,7 @@
       <c r="K38" s="12" t="n"/>
       <c r="L38" s="14" t="n"/>
       <c r="M38" s="15">
-        <f>IF(TODAY()&lt;F38, 0, IF(TODAY()&gt;G38, H38, H38 * (TODAY()-F38)/(G38-F38+1)))</f>
+        <f>IF(TODAY()&lt;F38, 0, IF(TODAY()&gt;G38, H38, H38 * (TODAY()-F38)/MAX(1, G38-F38+1)))</f>
         <v/>
       </c>
       <c r="N38" s="15">
@@ -3391,7 +3391,7 @@
       <c r="W38" s="12" t="n"/>
       <c r="X38" s="14" t="n"/>
       <c r="Y38" s="15">
-        <f>IF(TODAY()&lt;R38, 0, IF(TODAY()&gt;S38, T38, T38 * (TODAY()-R38)/(S38-R38+1)))</f>
+        <f>IF(TODAY()&lt;R38, 0, IF(TODAY()&gt;S38, T38, T38 * (TODAY()-R38)/MAX(1, S38-R38+1)))</f>
         <v/>
       </c>
       <c r="Z38" s="15">
@@ -3412,7 +3412,7 @@
       <c r="AI38" s="12" t="n"/>
       <c r="AJ38" s="14" t="n"/>
       <c r="AK38" s="15">
-        <f>IF(TODAY()&lt;AD38, 0, IF(TODAY()&gt;AE38, AF38, AF38 * (TODAY()-AD38)/(AE38-AD38+1)))</f>
+        <f>IF(TODAY()&lt;AD38, 0, IF(TODAY()&gt;AE38, AF38, AF38 * (TODAY()-AD38)/MAX(1, AE38-AD38+1)))</f>
         <v/>
       </c>
       <c r="AL38" s="15">
@@ -3438,7 +3438,7 @@
       <c r="K39" s="12" t="n"/>
       <c r="L39" s="14" t="n"/>
       <c r="M39" s="15">
-        <f>IF(TODAY()&lt;F39, 0, IF(TODAY()&gt;G39, H39, H39 * (TODAY()-F39)/(G39-F39+1)))</f>
+        <f>IF(TODAY()&lt;F39, 0, IF(TODAY()&gt;G39, H39, H39 * (TODAY()-F39)/MAX(1, G39-F39+1)))</f>
         <v/>
       </c>
       <c r="N39" s="15">
@@ -3459,7 +3459,7 @@
       <c r="W39" s="12" t="n"/>
       <c r="X39" s="14" t="n"/>
       <c r="Y39" s="15">
-        <f>IF(TODAY()&lt;R39, 0, IF(TODAY()&gt;S39, T39, T39 * (TODAY()-R39)/(S39-R39+1)))</f>
+        <f>IF(TODAY()&lt;R39, 0, IF(TODAY()&gt;S39, T39, T39 * (TODAY()-R39)/MAX(1, S39-R39+1)))</f>
         <v/>
       </c>
       <c r="Z39" s="15">
@@ -3480,7 +3480,7 @@
       <c r="AI39" s="12" t="n"/>
       <c r="AJ39" s="14" t="n"/>
       <c r="AK39" s="15">
-        <f>IF(TODAY()&lt;AD39, 0, IF(TODAY()&gt;AE39, AF39, AF39 * (TODAY()-AD39)/(AE39-AD39+1)))</f>
+        <f>IF(TODAY()&lt;AD39, 0, IF(TODAY()&gt;AE39, AF39, AF39 * (TODAY()-AD39)/MAX(1, AE39-AD39+1)))</f>
         <v/>
       </c>
       <c r="AL39" s="15">
@@ -3506,7 +3506,7 @@
       <c r="K40" s="12" t="n"/>
       <c r="L40" s="14" t="n"/>
       <c r="M40" s="15">
-        <f>IF(TODAY()&lt;F40, 0, IF(TODAY()&gt;G40, H40, H40 * (TODAY()-F40)/(G40-F40+1)))</f>
+        <f>IF(TODAY()&lt;F40, 0, IF(TODAY()&gt;G40, H40, H40 * (TODAY()-F40)/MAX(1, G40-F40+1)))</f>
         <v/>
       </c>
       <c r="N40" s="15">
@@ -3527,7 +3527,7 @@
       <c r="W40" s="12" t="n"/>
       <c r="X40" s="14" t="n"/>
       <c r="Y40" s="15">
-        <f>IF(TODAY()&lt;R40, 0, IF(TODAY()&gt;S40, T40, T40 * (TODAY()-R40)/(S40-R40+1)))</f>
+        <f>IF(TODAY()&lt;R40, 0, IF(TODAY()&gt;S40, T40, T40 * (TODAY()-R40)/MAX(1, S40-R40+1)))</f>
         <v/>
       </c>
       <c r="Z40" s="15">
@@ -3548,7 +3548,7 @@
       <c r="AI40" s="12" t="n"/>
       <c r="AJ40" s="14" t="n"/>
       <c r="AK40" s="15">
-        <f>IF(TODAY()&lt;AD40, 0, IF(TODAY()&gt;AE40, AF40, AF40 * (TODAY()-AD40)/(AE40-AD40+1)))</f>
+        <f>IF(TODAY()&lt;AD40, 0, IF(TODAY()&gt;AE40, AF40, AF40 * (TODAY()-AD40)/MAX(1, AE40-AD40+1)))</f>
         <v/>
       </c>
       <c r="AL40" s="15">
@@ -3574,7 +3574,7 @@
       <c r="K41" s="12" t="n"/>
       <c r="L41" s="14" t="n"/>
       <c r="M41" s="15">
-        <f>IF(TODAY()&lt;F41, 0, IF(TODAY()&gt;G41, H41, H41 * (TODAY()-F41)/(G41-F41+1)))</f>
+        <f>IF(TODAY()&lt;F41, 0, IF(TODAY()&gt;G41, H41, H41 * (TODAY()-F41)/MAX(1, G41-F41+1)))</f>
         <v/>
       </c>
       <c r="N41" s="15">
@@ -3595,7 +3595,7 @@
       <c r="W41" s="12" t="n"/>
       <c r="X41" s="14" t="n"/>
       <c r="Y41" s="15">
-        <f>IF(TODAY()&lt;R41, 0, IF(TODAY()&gt;S41, T41, T41 * (TODAY()-R41)/(S41-R41+1)))</f>
+        <f>IF(TODAY()&lt;R41, 0, IF(TODAY()&gt;S41, T41, T41 * (TODAY()-R41)/MAX(1, S41-R41+1)))</f>
         <v/>
       </c>
       <c r="Z41" s="15">
@@ -3616,7 +3616,7 @@
       <c r="AI41" s="12" t="n"/>
       <c r="AJ41" s="14" t="n"/>
       <c r="AK41" s="15">
-        <f>IF(TODAY()&lt;AD41, 0, IF(TODAY()&gt;AE41, AF41, AF41 * (TODAY()-AD41)/(AE41-AD41+1)))</f>
+        <f>IF(TODAY()&lt;AD41, 0, IF(TODAY()&gt;AE41, AF41, AF41 * (TODAY()-AD41)/MAX(1, AE41-AD41+1)))</f>
         <v/>
       </c>
       <c r="AL41" s="15">
@@ -3642,7 +3642,7 @@
       <c r="K42" s="12" t="n"/>
       <c r="L42" s="14" t="n"/>
       <c r="M42" s="15">
-        <f>IF(TODAY()&lt;F42, 0, IF(TODAY()&gt;G42, H42, H42 * (TODAY()-F42)/(G42-F42+1)))</f>
+        <f>IF(TODAY()&lt;F42, 0, IF(TODAY()&gt;G42, H42, H42 * (TODAY()-F42)/MAX(1, G42-F42+1)))</f>
         <v/>
       </c>
       <c r="N42" s="15">
@@ -3663,7 +3663,7 @@
       <c r="W42" s="12" t="n"/>
       <c r="X42" s="14" t="n"/>
       <c r="Y42" s="15">
-        <f>IF(TODAY()&lt;R42, 0, IF(TODAY()&gt;S42, T42, T42 * (TODAY()-R42)/(S42-R42+1)))</f>
+        <f>IF(TODAY()&lt;R42, 0, IF(TODAY()&gt;S42, T42, T42 * (TODAY()-R42)/MAX(1, S42-R42+1)))</f>
         <v/>
       </c>
       <c r="Z42" s="15">
@@ -3684,7 +3684,7 @@
       <c r="AI42" s="12" t="n"/>
       <c r="AJ42" s="14" t="n"/>
       <c r="AK42" s="15">
-        <f>IF(TODAY()&lt;AD42, 0, IF(TODAY()&gt;AE42, AF42, AF42 * (TODAY()-AD42)/(AE42-AD42+1)))</f>
+        <f>IF(TODAY()&lt;AD42, 0, IF(TODAY()&gt;AE42, AF42, AF42 * (TODAY()-AD42)/MAX(1, AE42-AD42+1)))</f>
         <v/>
       </c>
       <c r="AL42" s="15">
@@ -3710,7 +3710,7 @@
       <c r="K43" s="12" t="n"/>
       <c r="L43" s="14" t="n"/>
       <c r="M43" s="15">
-        <f>IF(TODAY()&lt;F43, 0, IF(TODAY()&gt;G43, H43, H43 * (TODAY()-F43)/(G43-F43+1)))</f>
+        <f>IF(TODAY()&lt;F43, 0, IF(TODAY()&gt;G43, H43, H43 * (TODAY()-F43)/MAX(1, G43-F43+1)))</f>
         <v/>
       </c>
       <c r="N43" s="15">
@@ -3731,7 +3731,7 @@
       <c r="W43" s="12" t="n"/>
       <c r="X43" s="14" t="n"/>
       <c r="Y43" s="15">
-        <f>IF(TODAY()&lt;R43, 0, IF(TODAY()&gt;S43, T43, T43 * (TODAY()-R43)/(S43-R43+1)))</f>
+        <f>IF(TODAY()&lt;R43, 0, IF(TODAY()&gt;S43, T43, T43 * (TODAY()-R43)/MAX(1, S43-R43+1)))</f>
         <v/>
       </c>
       <c r="Z43" s="15">
@@ -3752,7 +3752,7 @@
       <c r="AI43" s="12" t="n"/>
       <c r="AJ43" s="14" t="n"/>
       <c r="AK43" s="15">
-        <f>IF(TODAY()&lt;AD43, 0, IF(TODAY()&gt;AE43, AF43, AF43 * (TODAY()-AD43)/(AE43-AD43+1)))</f>
+        <f>IF(TODAY()&lt;AD43, 0, IF(TODAY()&gt;AE43, AF43, AF43 * (TODAY()-AD43)/MAX(1, AE43-AD43+1)))</f>
         <v/>
       </c>
       <c r="AL43" s="15">
@@ -3778,7 +3778,7 @@
       <c r="K44" s="12" t="n"/>
       <c r="L44" s="14" t="n"/>
       <c r="M44" s="15">
-        <f>IF(TODAY()&lt;F44, 0, IF(TODAY()&gt;G44, H44, H44 * (TODAY()-F44)/(G44-F44+1)))</f>
+        <f>IF(TODAY()&lt;F44, 0, IF(TODAY()&gt;G44, H44, H44 * (TODAY()-F44)/MAX(1, G44-F44+1)))</f>
         <v/>
       </c>
       <c r="N44" s="15">
@@ -3799,7 +3799,7 @@
       <c r="W44" s="12" t="n"/>
       <c r="X44" s="14" t="n"/>
       <c r="Y44" s="15">
-        <f>IF(TODAY()&lt;R44, 0, IF(TODAY()&gt;S44, T44, T44 * (TODAY()-R44)/(S44-R44+1)))</f>
+        <f>IF(TODAY()&lt;R44, 0, IF(TODAY()&gt;S44, T44, T44 * (TODAY()-R44)/MAX(1, S44-R44+1)))</f>
         <v/>
       </c>
       <c r="Z44" s="15">
@@ -3820,7 +3820,7 @@
       <c r="AI44" s="12" t="n"/>
       <c r="AJ44" s="14" t="n"/>
       <c r="AK44" s="15">
-        <f>IF(TODAY()&lt;AD44, 0, IF(TODAY()&gt;AE44, AF44, AF44 * (TODAY()-AD44)/(AE44-AD44+1)))</f>
+        <f>IF(TODAY()&lt;AD44, 0, IF(TODAY()&gt;AE44, AF44, AF44 * (TODAY()-AD44)/MAX(1, AE44-AD44+1)))</f>
         <v/>
       </c>
       <c r="AL44" s="15">
@@ -3846,7 +3846,7 @@
       <c r="K45" s="12" t="n"/>
       <c r="L45" s="14" t="n"/>
       <c r="M45" s="15">
-        <f>IF(TODAY()&lt;F45, 0, IF(TODAY()&gt;G45, H45, H45 * (TODAY()-F45)/(G45-F45+1)))</f>
+        <f>IF(TODAY()&lt;F45, 0, IF(TODAY()&gt;G45, H45, H45 * (TODAY()-F45)/MAX(1, G45-F45+1)))</f>
         <v/>
       </c>
       <c r="N45" s="15">
@@ -3867,7 +3867,7 @@
       <c r="W45" s="12" t="n"/>
       <c r="X45" s="14" t="n"/>
       <c r="Y45" s="15">
-        <f>IF(TODAY()&lt;R45, 0, IF(TODAY()&gt;S45, T45, T45 * (TODAY()-R45)/(S45-R45+1)))</f>
+        <f>IF(TODAY()&lt;R45, 0, IF(TODAY()&gt;S45, T45, T45 * (TODAY()-R45)/MAX(1, S45-R45+1)))</f>
         <v/>
       </c>
       <c r="Z45" s="15">
@@ -3888,7 +3888,7 @@
       <c r="AI45" s="12" t="n"/>
       <c r="AJ45" s="14" t="n"/>
       <c r="AK45" s="15">
-        <f>IF(TODAY()&lt;AD45, 0, IF(TODAY()&gt;AE45, AF45, AF45 * (TODAY()-AD45)/(AE45-AD45+1)))</f>
+        <f>IF(TODAY()&lt;AD45, 0, IF(TODAY()&gt;AE45, AF45, AF45 * (TODAY()-AD45)/MAX(1, AE45-AD45+1)))</f>
         <v/>
       </c>
       <c r="AL45" s="15">
@@ -3914,7 +3914,7 @@
       <c r="K46" s="12" t="n"/>
       <c r="L46" s="14" t="n"/>
       <c r="M46" s="15">
-        <f>IF(TODAY()&lt;F46, 0, IF(TODAY()&gt;G46, H46, H46 * (TODAY()-F46)/(G46-F46+1)))</f>
+        <f>IF(TODAY()&lt;F46, 0, IF(TODAY()&gt;G46, H46, H46 * (TODAY()-F46)/MAX(1, G46-F46+1)))</f>
         <v/>
       </c>
       <c r="N46" s="15">
@@ -3935,7 +3935,7 @@
       <c r="W46" s="12" t="n"/>
       <c r="X46" s="14" t="n"/>
       <c r="Y46" s="15">
-        <f>IF(TODAY()&lt;R46, 0, IF(TODAY()&gt;S46, T46, T46 * (TODAY()-R46)/(S46-R46+1)))</f>
+        <f>IF(TODAY()&lt;R46, 0, IF(TODAY()&gt;S46, T46, T46 * (TODAY()-R46)/MAX(1, S46-R46+1)))</f>
         <v/>
       </c>
       <c r="Z46" s="15">
@@ -3956,7 +3956,7 @@
       <c r="AI46" s="12" t="n"/>
       <c r="AJ46" s="14" t="n"/>
       <c r="AK46" s="15">
-        <f>IF(TODAY()&lt;AD46, 0, IF(TODAY()&gt;AE46, AF46, AF46 * (TODAY()-AD46)/(AE46-AD46+1)))</f>
+        <f>IF(TODAY()&lt;AD46, 0, IF(TODAY()&gt;AE46, AF46, AF46 * (TODAY()-AD46)/MAX(1, AE46-AD46+1)))</f>
         <v/>
       </c>
       <c r="AL46" s="15">
@@ -3982,7 +3982,7 @@
       <c r="K47" s="12" t="n"/>
       <c r="L47" s="14" t="n"/>
       <c r="M47" s="15">
-        <f>IF(TODAY()&lt;F47, 0, IF(TODAY()&gt;G47, H47, H47 * (TODAY()-F47)/(G47-F47+1)))</f>
+        <f>IF(TODAY()&lt;F47, 0, IF(TODAY()&gt;G47, H47, H47 * (TODAY()-F47)/MAX(1, G47-F47+1)))</f>
         <v/>
       </c>
       <c r="N47" s="15">
@@ -4003,7 +4003,7 @@
       <c r="W47" s="12" t="n"/>
       <c r="X47" s="14" t="n"/>
       <c r="Y47" s="15">
-        <f>IF(TODAY()&lt;R47, 0, IF(TODAY()&gt;S47, T47, T47 * (TODAY()-R47)/(S47-R47+1)))</f>
+        <f>IF(TODAY()&lt;R47, 0, IF(TODAY()&gt;S47, T47, T47 * (TODAY()-R47)/MAX(1, S47-R47+1)))</f>
         <v/>
       </c>
       <c r="Z47" s="15">
@@ -4024,7 +4024,7 @@
       <c r="AI47" s="12" t="n"/>
       <c r="AJ47" s="14" t="n"/>
       <c r="AK47" s="15">
-        <f>IF(TODAY()&lt;AD47, 0, IF(TODAY()&gt;AE47, AF47, AF47 * (TODAY()-AD47)/(AE47-AD47+1)))</f>
+        <f>IF(TODAY()&lt;AD47, 0, IF(TODAY()&gt;AE47, AF47, AF47 * (TODAY()-AD47)/MAX(1, AE47-AD47+1)))</f>
         <v/>
       </c>
       <c r="AL47" s="15">
@@ -4050,7 +4050,7 @@
       <c r="K48" s="12" t="n"/>
       <c r="L48" s="14" t="n"/>
       <c r="M48" s="15">
-        <f>IF(TODAY()&lt;F48, 0, IF(TODAY()&gt;G48, H48, H48 * (TODAY()-F48)/(G48-F48+1)))</f>
+        <f>IF(TODAY()&lt;F48, 0, IF(TODAY()&gt;G48, H48, H48 * (TODAY()-F48)/MAX(1, G48-F48+1)))</f>
         <v/>
       </c>
       <c r="N48" s="15">
@@ -4071,7 +4071,7 @@
       <c r="W48" s="12" t="n"/>
       <c r="X48" s="14" t="n"/>
       <c r="Y48" s="15">
-        <f>IF(TODAY()&lt;R48, 0, IF(TODAY()&gt;S48, T48, T48 * (TODAY()-R48)/(S48-R48+1)))</f>
+        <f>IF(TODAY()&lt;R48, 0, IF(TODAY()&gt;S48, T48, T48 * (TODAY()-R48)/MAX(1, S48-R48+1)))</f>
         <v/>
       </c>
       <c r="Z48" s="15">
@@ -4092,7 +4092,7 @@
       <c r="AI48" s="12" t="n"/>
       <c r="AJ48" s="14" t="n"/>
       <c r="AK48" s="15">
-        <f>IF(TODAY()&lt;AD48, 0, IF(TODAY()&gt;AE48, AF48, AF48 * (TODAY()-AD48)/(AE48-AD48+1)))</f>
+        <f>IF(TODAY()&lt;AD48, 0, IF(TODAY()&gt;AE48, AF48, AF48 * (TODAY()-AD48)/MAX(1, AE48-AD48+1)))</f>
         <v/>
       </c>
       <c r="AL48" s="15">
@@ -4118,7 +4118,7 @@
       <c r="K49" s="12" t="n"/>
       <c r="L49" s="14" t="n"/>
       <c r="M49" s="15">
-        <f>IF(TODAY()&lt;F49, 0, IF(TODAY()&gt;G49, H49, H49 * (TODAY()-F49)/(G49-F49+1)))</f>
+        <f>IF(TODAY()&lt;F49, 0, IF(TODAY()&gt;G49, H49, H49 * (TODAY()-F49)/MAX(1, G49-F49+1)))</f>
         <v/>
       </c>
       <c r="N49" s="15">
@@ -4139,7 +4139,7 @@
       <c r="W49" s="12" t="n"/>
       <c r="X49" s="14" t="n"/>
       <c r="Y49" s="15">
-        <f>IF(TODAY()&lt;R49, 0, IF(TODAY()&gt;S49, T49, T49 * (TODAY()-R49)/(S49-R49+1)))</f>
+        <f>IF(TODAY()&lt;R49, 0, IF(TODAY()&gt;S49, T49, T49 * (TODAY()-R49)/MAX(1, S49-R49+1)))</f>
         <v/>
       </c>
       <c r="Z49" s="15">
@@ -4160,7 +4160,7 @@
       <c r="AI49" s="12" t="n"/>
       <c r="AJ49" s="14" t="n"/>
       <c r="AK49" s="15">
-        <f>IF(TODAY()&lt;AD49, 0, IF(TODAY()&gt;AE49, AF49, AF49 * (TODAY()-AD49)/(AE49-AD49+1)))</f>
+        <f>IF(TODAY()&lt;AD49, 0, IF(TODAY()&gt;AE49, AF49, AF49 * (TODAY()-AD49)/MAX(1, AE49-AD49+1)))</f>
         <v/>
       </c>
       <c r="AL49" s="15">
@@ -4186,7 +4186,7 @@
       <c r="K50" s="12" t="n"/>
       <c r="L50" s="14" t="n"/>
       <c r="M50" s="15">
-        <f>IF(TODAY()&lt;F50, 0, IF(TODAY()&gt;G50, H50, H50 * (TODAY()-F50)/(G50-F50+1)))</f>
+        <f>IF(TODAY()&lt;F50, 0, IF(TODAY()&gt;G50, H50, H50 * (TODAY()-F50)/MAX(1, G50-F50+1)))</f>
         <v/>
       </c>
       <c r="N50" s="15">
@@ -4207,7 +4207,7 @@
       <c r="W50" s="12" t="n"/>
       <c r="X50" s="14" t="n"/>
       <c r="Y50" s="15">
-        <f>IF(TODAY()&lt;R50, 0, IF(TODAY()&gt;S50, T50, T50 * (TODAY()-R50)/(S50-R50+1)))</f>
+        <f>IF(TODAY()&lt;R50, 0, IF(TODAY()&gt;S50, T50, T50 * (TODAY()-R50)/MAX(1, S50-R50+1)))</f>
         <v/>
       </c>
       <c r="Z50" s="15">
@@ -4228,7 +4228,7 @@
       <c r="AI50" s="12" t="n"/>
       <c r="AJ50" s="14" t="n"/>
       <c r="AK50" s="15">
-        <f>IF(TODAY()&lt;AD50, 0, IF(TODAY()&gt;AE50, AF50, AF50 * (TODAY()-AD50)/(AE50-AD50+1)))</f>
+        <f>IF(TODAY()&lt;AD50, 0, IF(TODAY()&gt;AE50, AF50, AF50 * (TODAY()-AD50)/MAX(1, AE50-AD50+1)))</f>
         <v/>
       </c>
       <c r="AL50" s="15">
@@ -4254,7 +4254,7 @@
       <c r="K51" s="12" t="n"/>
       <c r="L51" s="14" t="n"/>
       <c r="M51" s="15">
-        <f>IF(TODAY()&lt;F51, 0, IF(TODAY()&gt;G51, H51, H51 * (TODAY()-F51)/(G51-F51+1)))</f>
+        <f>IF(TODAY()&lt;F51, 0, IF(TODAY()&gt;G51, H51, H51 * (TODAY()-F51)/MAX(1, G51-F51+1)))</f>
         <v/>
       </c>
       <c r="N51" s="15">
@@ -4275,7 +4275,7 @@
       <c r="W51" s="12" t="n"/>
       <c r="X51" s="14" t="n"/>
       <c r="Y51" s="15">
-        <f>IF(TODAY()&lt;R51, 0, IF(TODAY()&gt;S51, T51, T51 * (TODAY()-R51)/(S51-R51+1)))</f>
+        <f>IF(TODAY()&lt;R51, 0, IF(TODAY()&gt;S51, T51, T51 * (TODAY()-R51)/MAX(1, S51-R51+1)))</f>
         <v/>
       </c>
       <c r="Z51" s="15">
@@ -4296,7 +4296,7 @@
       <c r="AI51" s="12" t="n"/>
       <c r="AJ51" s="14" t="n"/>
       <c r="AK51" s="15">
-        <f>IF(TODAY()&lt;AD51, 0, IF(TODAY()&gt;AE51, AF51, AF51 * (TODAY()-AD51)/(AE51-AD51+1)))</f>
+        <f>IF(TODAY()&lt;AD51, 0, IF(TODAY()&gt;AE51, AF51, AF51 * (TODAY()-AD51)/MAX(1, AE51-AD51+1)))</f>
         <v/>
       </c>
       <c r="AL51" s="15">
@@ -4322,7 +4322,7 @@
       <c r="K52" s="12" t="n"/>
       <c r="L52" s="14" t="n"/>
       <c r="M52" s="15">
-        <f>IF(TODAY()&lt;F52, 0, IF(TODAY()&gt;G52, H52, H52 * (TODAY()-F52)/(G52-F52+1)))</f>
+        <f>IF(TODAY()&lt;F52, 0, IF(TODAY()&gt;G52, H52, H52 * (TODAY()-F52)/MAX(1, G52-F52+1)))</f>
         <v/>
       </c>
       <c r="N52" s="15">
@@ -4343,7 +4343,7 @@
       <c r="W52" s="12" t="n"/>
       <c r="X52" s="14" t="n"/>
       <c r="Y52" s="15">
-        <f>IF(TODAY()&lt;R52, 0, IF(TODAY()&gt;S52, T52, T52 * (TODAY()-R52)/(S52-R52+1)))</f>
+        <f>IF(TODAY()&lt;R52, 0, IF(TODAY()&gt;S52, T52, T52 * (TODAY()-R52)/MAX(1, S52-R52+1)))</f>
         <v/>
       </c>
       <c r="Z52" s="15">
@@ -4364,7 +4364,7 @@
       <c r="AI52" s="12" t="n"/>
       <c r="AJ52" s="14" t="n"/>
       <c r="AK52" s="15">
-        <f>IF(TODAY()&lt;AD52, 0, IF(TODAY()&gt;AE52, AF52, AF52 * (TODAY()-AD52)/(AE52-AD52+1)))</f>
+        <f>IF(TODAY()&lt;AD52, 0, IF(TODAY()&gt;AE52, AF52, AF52 * (TODAY()-AD52)/MAX(1, AE52-AD52+1)))</f>
         <v/>
       </c>
       <c r="AL52" s="15">
@@ -4390,7 +4390,7 @@
       <c r="K53" s="12" t="n"/>
       <c r="L53" s="14" t="n"/>
       <c r="M53" s="15">
-        <f>IF(TODAY()&lt;F53, 0, IF(TODAY()&gt;G53, H53, H53 * (TODAY()-F53)/(G53-F53+1)))</f>
+        <f>IF(TODAY()&lt;F53, 0, IF(TODAY()&gt;G53, H53, H53 * (TODAY()-F53)/MAX(1, G53-F53+1)))</f>
         <v/>
       </c>
       <c r="N53" s="15">
@@ -4411,7 +4411,7 @@
       <c r="W53" s="12" t="n"/>
       <c r="X53" s="14" t="n"/>
       <c r="Y53" s="15">
-        <f>IF(TODAY()&lt;R53, 0, IF(TODAY()&gt;S53, T53, T53 * (TODAY()-R53)/(S53-R53+1)))</f>
+        <f>IF(TODAY()&lt;R53, 0, IF(TODAY()&gt;S53, T53, T53 * (TODAY()-R53)/MAX(1, S53-R53+1)))</f>
         <v/>
       </c>
       <c r="Z53" s="15">
@@ -4432,7 +4432,7 @@
       <c r="AI53" s="12" t="n"/>
       <c r="AJ53" s="14" t="n"/>
       <c r="AK53" s="15">
-        <f>IF(TODAY()&lt;AD53, 0, IF(TODAY()&gt;AE53, AF53, AF53 * (TODAY()-AD53)/(AE53-AD53+1)))</f>
+        <f>IF(TODAY()&lt;AD53, 0, IF(TODAY()&gt;AE53, AF53, AF53 * (TODAY()-AD53)/MAX(1, AE53-AD53+1)))</f>
         <v/>
       </c>
       <c r="AL53" s="15">
@@ -4458,7 +4458,7 @@
       <c r="K54" s="12" t="n"/>
       <c r="L54" s="14" t="n"/>
       <c r="M54" s="15">
-        <f>IF(TODAY()&lt;F54, 0, IF(TODAY()&gt;G54, H54, H54 * (TODAY()-F54)/(G54-F54+1)))</f>
+        <f>IF(TODAY()&lt;F54, 0, IF(TODAY()&gt;G54, H54, H54 * (TODAY()-F54)/MAX(1, G54-F54+1)))</f>
         <v/>
       </c>
       <c r="N54" s="15">
@@ -4479,7 +4479,7 @@
       <c r="W54" s="12" t="n"/>
       <c r="X54" s="14" t="n"/>
       <c r="Y54" s="15">
-        <f>IF(TODAY()&lt;R54, 0, IF(TODAY()&gt;S54, T54, T54 * (TODAY()-R54)/(S54-R54+1)))</f>
+        <f>IF(TODAY()&lt;R54, 0, IF(TODAY()&gt;S54, T54, T54 * (TODAY()-R54)/MAX(1, S54-R54+1)))</f>
         <v/>
       </c>
       <c r="Z54" s="15">
@@ -4500,7 +4500,7 @@
       <c r="AI54" s="12" t="n"/>
       <c r="AJ54" s="14" t="n"/>
       <c r="AK54" s="15">
-        <f>IF(TODAY()&lt;AD54, 0, IF(TODAY()&gt;AE54, AF54, AF54 * (TODAY()-AD54)/(AE54-AD54+1)))</f>
+        <f>IF(TODAY()&lt;AD54, 0, IF(TODAY()&gt;AE54, AF54, AF54 * (TODAY()-AD54)/MAX(1, AE54-AD54+1)))</f>
         <v/>
       </c>
       <c r="AL54" s="15">
@@ -4526,7 +4526,7 @@
       <c r="K55" s="12" t="n"/>
       <c r="L55" s="14" t="n"/>
       <c r="M55" s="15">
-        <f>IF(TODAY()&lt;F55, 0, IF(TODAY()&gt;G55, H55, H55 * (TODAY()-F55)/(G55-F55+1)))</f>
+        <f>IF(TODAY()&lt;F55, 0, IF(TODAY()&gt;G55, H55, H55 * (TODAY()-F55)/MAX(1, G55-F55+1)))</f>
         <v/>
       </c>
       <c r="N55" s="15">
@@ -4547,7 +4547,7 @@
       <c r="W55" s="12" t="n"/>
       <c r="X55" s="14" t="n"/>
       <c r="Y55" s="15">
-        <f>IF(TODAY()&lt;R55, 0, IF(TODAY()&gt;S55, T55, T55 * (TODAY()-R55)/(S55-R55+1)))</f>
+        <f>IF(TODAY()&lt;R55, 0, IF(TODAY()&gt;S55, T55, T55 * (TODAY()-R55)/MAX(1, S55-R55+1)))</f>
         <v/>
       </c>
       <c r="Z55" s="15">
@@ -4568,7 +4568,7 @@
       <c r="AI55" s="12" t="n"/>
       <c r="AJ55" s="14" t="n"/>
       <c r="AK55" s="15">
-        <f>IF(TODAY()&lt;AD55, 0, IF(TODAY()&gt;AE55, AF55, AF55 * (TODAY()-AD55)/(AE55-AD55+1)))</f>
+        <f>IF(TODAY()&lt;AD55, 0, IF(TODAY()&gt;AE55, AF55, AF55 * (TODAY()-AD55)/MAX(1, AE55-AD55+1)))</f>
         <v/>
       </c>
       <c r="AL55" s="15">
@@ -4594,7 +4594,7 @@
       <c r="K56" s="12" t="n"/>
       <c r="L56" s="14" t="n"/>
       <c r="M56" s="15">
-        <f>IF(TODAY()&lt;F56, 0, IF(TODAY()&gt;G56, H56, H56 * (TODAY()-F56)/(G56-F56+1)))</f>
+        <f>IF(TODAY()&lt;F56, 0, IF(TODAY()&gt;G56, H56, H56 * (TODAY()-F56)/MAX(1, G56-F56+1)))</f>
         <v/>
       </c>
       <c r="N56" s="15">
@@ -4615,7 +4615,7 @@
       <c r="W56" s="12" t="n"/>
       <c r="X56" s="14" t="n"/>
       <c r="Y56" s="15">
-        <f>IF(TODAY()&lt;R56, 0, IF(TODAY()&gt;S56, T56, T56 * (TODAY()-R56)/(S56-R56+1)))</f>
+        <f>IF(TODAY()&lt;R56, 0, IF(TODAY()&gt;S56, T56, T56 * (TODAY()-R56)/MAX(1, S56-R56+1)))</f>
         <v/>
       </c>
       <c r="Z56" s="15">
@@ -4636,7 +4636,7 @@
       <c r="AI56" s="12" t="n"/>
       <c r="AJ56" s="14" t="n"/>
       <c r="AK56" s="15">
-        <f>IF(TODAY()&lt;AD56, 0, IF(TODAY()&gt;AE56, AF56, AF56 * (TODAY()-AD56)/(AE56-AD56+1)))</f>
+        <f>IF(TODAY()&lt;AD56, 0, IF(TODAY()&gt;AE56, AF56, AF56 * (TODAY()-AD56)/MAX(1, AE56-AD56+1)))</f>
         <v/>
       </c>
       <c r="AL56" s="15">
@@ -4662,7 +4662,7 @@
       <c r="K57" s="12" t="n"/>
       <c r="L57" s="14" t="n"/>
       <c r="M57" s="15">
-        <f>IF(TODAY()&lt;F57, 0, IF(TODAY()&gt;G57, H57, H57 * (TODAY()-F57)/(G57-F57+1)))</f>
+        <f>IF(TODAY()&lt;F57, 0, IF(TODAY()&gt;G57, H57, H57 * (TODAY()-F57)/MAX(1, G57-F57+1)))</f>
         <v/>
       </c>
       <c r="N57" s="15">
@@ -4683,7 +4683,7 @@
       <c r="W57" s="12" t="n"/>
       <c r="X57" s="14" t="n"/>
       <c r="Y57" s="15">
-        <f>IF(TODAY()&lt;R57, 0, IF(TODAY()&gt;S57, T57, T57 * (TODAY()-R57)/(S57-R57+1)))</f>
+        <f>IF(TODAY()&lt;R57, 0, IF(TODAY()&gt;S57, T57, T57 * (TODAY()-R57)/MAX(1, S57-R57+1)))</f>
         <v/>
       </c>
       <c r="Z57" s="15">
@@ -4704,7 +4704,7 @@
       <c r="AI57" s="12" t="n"/>
       <c r="AJ57" s="14" t="n"/>
       <c r="AK57" s="15">
-        <f>IF(TODAY()&lt;AD57, 0, IF(TODAY()&gt;AE57, AF57, AF57 * (TODAY()-AD57)/(AE57-AD57+1)))</f>
+        <f>IF(TODAY()&lt;AD57, 0, IF(TODAY()&gt;AE57, AF57, AF57 * (TODAY()-AD57)/MAX(1, AE57-AD57+1)))</f>
         <v/>
       </c>
       <c r="AL57" s="15">
@@ -4730,7 +4730,7 @@
       <c r="K58" s="12" t="n"/>
       <c r="L58" s="14" t="n"/>
       <c r="M58" s="15">
-        <f>IF(TODAY()&lt;F58, 0, IF(TODAY()&gt;G58, H58, H58 * (TODAY()-F58)/(G58-F58+1)))</f>
+        <f>IF(TODAY()&lt;F58, 0, IF(TODAY()&gt;G58, H58, H58 * (TODAY()-F58)/MAX(1, G58-F58+1)))</f>
         <v/>
       </c>
       <c r="N58" s="15">
@@ -4751,7 +4751,7 @@
       <c r="W58" s="12" t="n"/>
       <c r="X58" s="14" t="n"/>
       <c r="Y58" s="15">
-        <f>IF(TODAY()&lt;R58, 0, IF(TODAY()&gt;S58, T58, T58 * (TODAY()-R58)/(S58-R58+1)))</f>
+        <f>IF(TODAY()&lt;R58, 0, IF(TODAY()&gt;S58, T58, T58 * (TODAY()-R58)/MAX(1, S58-R58+1)))</f>
         <v/>
       </c>
       <c r="Z58" s="15">
@@ -4772,7 +4772,7 @@
       <c r="AI58" s="12" t="n"/>
       <c r="AJ58" s="14" t="n"/>
       <c r="AK58" s="15">
-        <f>IF(TODAY()&lt;AD58, 0, IF(TODAY()&gt;AE58, AF58, AF58 * (TODAY()-AD58)/(AE58-AD58+1)))</f>
+        <f>IF(TODAY()&lt;AD58, 0, IF(TODAY()&gt;AE58, AF58, AF58 * (TODAY()-AD58)/MAX(1, AE58-AD58+1)))</f>
         <v/>
       </c>
       <c r="AL58" s="15">
@@ -4798,7 +4798,7 @@
       <c r="K59" s="12" t="n"/>
       <c r="L59" s="14" t="n"/>
       <c r="M59" s="15">
-        <f>IF(TODAY()&lt;F59, 0, IF(TODAY()&gt;G59, H59, H59 * (TODAY()-F59)/(G59-F59+1)))</f>
+        <f>IF(TODAY()&lt;F59, 0, IF(TODAY()&gt;G59, H59, H59 * (TODAY()-F59)/MAX(1, G59-F59+1)))</f>
         <v/>
       </c>
       <c r="N59" s="15">
@@ -4819,7 +4819,7 @@
       <c r="W59" s="12" t="n"/>
       <c r="X59" s="14" t="n"/>
       <c r="Y59" s="15">
-        <f>IF(TODAY()&lt;R59, 0, IF(TODAY()&gt;S59, T59, T59 * (TODAY()-R59)/(S59-R59+1)))</f>
+        <f>IF(TODAY()&lt;R59, 0, IF(TODAY()&gt;S59, T59, T59 * (TODAY()-R59)/MAX(1, S59-R59+1)))</f>
         <v/>
       </c>
       <c r="Z59" s="15">
@@ -4840,7 +4840,7 @@
       <c r="AI59" s="12" t="n"/>
       <c r="AJ59" s="14" t="n"/>
       <c r="AK59" s="15">
-        <f>IF(TODAY()&lt;AD59, 0, IF(TODAY()&gt;AE59, AF59, AF59 * (TODAY()-AD59)/(AE59-AD59+1)))</f>
+        <f>IF(TODAY()&lt;AD59, 0, IF(TODAY()&gt;AE59, AF59, AF59 * (TODAY()-AD59)/MAX(1, AE59-AD59+1)))</f>
         <v/>
       </c>
       <c r="AL59" s="15">
@@ -4866,7 +4866,7 @@
       <c r="K60" s="12" t="n"/>
       <c r="L60" s="14" t="n"/>
       <c r="M60" s="15">
-        <f>IF(TODAY()&lt;F60, 0, IF(TODAY()&gt;G60, H60, H60 * (TODAY()-F60)/(G60-F60+1)))</f>
+        <f>IF(TODAY()&lt;F60, 0, IF(TODAY()&gt;G60, H60, H60 * (TODAY()-F60)/MAX(1, G60-F60+1)))</f>
         <v/>
       </c>
       <c r="N60" s="15">
@@ -4887,7 +4887,7 @@
       <c r="W60" s="12" t="n"/>
       <c r="X60" s="14" t="n"/>
       <c r="Y60" s="15">
-        <f>IF(TODAY()&lt;R60, 0, IF(TODAY()&gt;S60, T60, T60 * (TODAY()-R60)/(S60-R60+1)))</f>
+        <f>IF(TODAY()&lt;R60, 0, IF(TODAY()&gt;S60, T60, T60 * (TODAY()-R60)/MAX(1, S60-R60+1)))</f>
         <v/>
       </c>
       <c r="Z60" s="15">
@@ -4908,7 +4908,7 @@
       <c r="AI60" s="12" t="n"/>
       <c r="AJ60" s="14" t="n"/>
       <c r="AK60" s="15">
-        <f>IF(TODAY()&lt;AD60, 0, IF(TODAY()&gt;AE60, AF60, AF60 * (TODAY()-AD60)/(AE60-AD60+1)))</f>
+        <f>IF(TODAY()&lt;AD60, 0, IF(TODAY()&gt;AE60, AF60, AF60 * (TODAY()-AD60)/MAX(1, AE60-AD60+1)))</f>
         <v/>
       </c>
       <c r="AL60" s="15">
@@ -4934,7 +4934,7 @@
       <c r="K61" s="12" t="n"/>
       <c r="L61" s="14" t="n"/>
       <c r="M61" s="15">
-        <f>IF(TODAY()&lt;F61, 0, IF(TODAY()&gt;G61, H61, H61 * (TODAY()-F61)/(G61-F61+1)))</f>
+        <f>IF(TODAY()&lt;F61, 0, IF(TODAY()&gt;G61, H61, H61 * (TODAY()-F61)/MAX(1, G61-F61+1)))</f>
         <v/>
       </c>
       <c r="N61" s="15">
@@ -4955,7 +4955,7 @@
       <c r="W61" s="12" t="n"/>
       <c r="X61" s="14" t="n"/>
       <c r="Y61" s="15">
-        <f>IF(TODAY()&lt;R61, 0, IF(TODAY()&gt;S61, T61, T61 * (TODAY()-R61)/(S61-R61+1)))</f>
+        <f>IF(TODAY()&lt;R61, 0, IF(TODAY()&gt;S61, T61, T61 * (TODAY()-R61)/MAX(1, S61-R61+1)))</f>
         <v/>
       </c>
       <c r="Z61" s="15">
@@ -4976,7 +4976,7 @@
       <c r="AI61" s="12" t="n"/>
       <c r="AJ61" s="14" t="n"/>
       <c r="AK61" s="15">
-        <f>IF(TODAY()&lt;AD61, 0, IF(TODAY()&gt;AE61, AF61, AF61 * (TODAY()-AD61)/(AE61-AD61+1)))</f>
+        <f>IF(TODAY()&lt;AD61, 0, IF(TODAY()&gt;AE61, AF61, AF61 * (TODAY()-AD61)/MAX(1, AE61-AD61+1)))</f>
         <v/>
       </c>
       <c r="AL61" s="15">
@@ -5002,7 +5002,7 @@
       <c r="K62" s="12" t="n"/>
       <c r="L62" s="14" t="n"/>
       <c r="M62" s="15">
-        <f>IF(TODAY()&lt;F62, 0, IF(TODAY()&gt;G62, H62, H62 * (TODAY()-F62)/(G62-F62+1)))</f>
+        <f>IF(TODAY()&lt;F62, 0, IF(TODAY()&gt;G62, H62, H62 * (TODAY()-F62)/MAX(1, G62-F62+1)))</f>
         <v/>
       </c>
       <c r="N62" s="15">
@@ -5023,7 +5023,7 @@
       <c r="W62" s="12" t="n"/>
       <c r="X62" s="14" t="n"/>
       <c r="Y62" s="15">
-        <f>IF(TODAY()&lt;R62, 0, IF(TODAY()&gt;S62, T62, T62 * (TODAY()-R62)/(S62-R62+1)))</f>
+        <f>IF(TODAY()&lt;R62, 0, IF(TODAY()&gt;S62, T62, T62 * (TODAY()-R62)/MAX(1, S62-R62+1)))</f>
         <v/>
       </c>
       <c r="Z62" s="15">
@@ -5044,7 +5044,7 @@
       <c r="AI62" s="12" t="n"/>
       <c r="AJ62" s="14" t="n"/>
       <c r="AK62" s="15">
-        <f>IF(TODAY()&lt;AD62, 0, IF(TODAY()&gt;AE62, AF62, AF62 * (TODAY()-AD62)/(AE62-AD62+1)))</f>
+        <f>IF(TODAY()&lt;AD62, 0, IF(TODAY()&gt;AE62, AF62, AF62 * (TODAY()-AD62)/MAX(1, AE62-AD62+1)))</f>
         <v/>
       </c>
       <c r="AL62" s="15">
@@ -5070,7 +5070,7 @@
       <c r="K63" s="12" t="n"/>
       <c r="L63" s="14" t="n"/>
       <c r="M63" s="15">
-        <f>IF(TODAY()&lt;F63, 0, IF(TODAY()&gt;G63, H63, H63 * (TODAY()-F63)/(G63-F63+1)))</f>
+        <f>IF(TODAY()&lt;F63, 0, IF(TODAY()&gt;G63, H63, H63 * (TODAY()-F63)/MAX(1, G63-F63+1)))</f>
         <v/>
       </c>
       <c r="N63" s="15">
@@ -5091,7 +5091,7 @@
       <c r="W63" s="12" t="n"/>
       <c r="X63" s="14" t="n"/>
       <c r="Y63" s="15">
-        <f>IF(TODAY()&lt;R63, 0, IF(TODAY()&gt;S63, T63, T63 * (TODAY()-R63)/(S63-R63+1)))</f>
+        <f>IF(TODAY()&lt;R63, 0, IF(TODAY()&gt;S63, T63, T63 * (TODAY()-R63)/MAX(1, S63-R63+1)))</f>
         <v/>
       </c>
       <c r="Z63" s="15">
@@ -5112,7 +5112,7 @@
       <c r="AI63" s="12" t="n"/>
       <c r="AJ63" s="14" t="n"/>
       <c r="AK63" s="15">
-        <f>IF(TODAY()&lt;AD63, 0, IF(TODAY()&gt;AE63, AF63, AF63 * (TODAY()-AD63)/(AE63-AD63+1)))</f>
+        <f>IF(TODAY()&lt;AD63, 0, IF(TODAY()&gt;AE63, AF63, AF63 * (TODAY()-AD63)/MAX(1, AE63-AD63+1)))</f>
         <v/>
       </c>
       <c r="AL63" s="15">
@@ -5138,7 +5138,7 @@
       <c r="K64" s="12" t="n"/>
       <c r="L64" s="14" t="n"/>
       <c r="M64" s="15">
-        <f>IF(TODAY()&lt;F64, 0, IF(TODAY()&gt;G64, H64, H64 * (TODAY()-F64)/(G64-F64+1)))</f>
+        <f>IF(TODAY()&lt;F64, 0, IF(TODAY()&gt;G64, H64, H64 * (TODAY()-F64)/MAX(1, G64-F64+1)))</f>
         <v/>
       </c>
       <c r="N64" s="15">
@@ -5159,7 +5159,7 @@
       <c r="W64" s="12" t="n"/>
       <c r="X64" s="14" t="n"/>
       <c r="Y64" s="15">
-        <f>IF(TODAY()&lt;R64, 0, IF(TODAY()&gt;S64, T64, T64 * (TODAY()-R64)/(S64-R64+1)))</f>
+        <f>IF(TODAY()&lt;R64, 0, IF(TODAY()&gt;S64, T64, T64 * (TODAY()-R64)/MAX(1, S64-R64+1)))</f>
         <v/>
       </c>
       <c r="Z64" s="15">
@@ -5180,7 +5180,7 @@
       <c r="AI64" s="12" t="n"/>
       <c r="AJ64" s="14" t="n"/>
       <c r="AK64" s="15">
-        <f>IF(TODAY()&lt;AD64, 0, IF(TODAY()&gt;AE64, AF64, AF64 * (TODAY()-AD64)/(AE64-AD64+1)))</f>
+        <f>IF(TODAY()&lt;AD64, 0, IF(TODAY()&gt;AE64, AF64, AF64 * (TODAY()-AD64)/MAX(1, AE64-AD64+1)))</f>
         <v/>
       </c>
       <c r="AL64" s="15">
@@ -5206,7 +5206,7 @@
       <c r="K65" s="12" t="n"/>
       <c r="L65" s="14" t="n"/>
       <c r="M65" s="15">
-        <f>IF(TODAY()&lt;F65, 0, IF(TODAY()&gt;G65, H65, H65 * (TODAY()-F65)/(G65-F65+1)))</f>
+        <f>IF(TODAY()&lt;F65, 0, IF(TODAY()&gt;G65, H65, H65 * (TODAY()-F65)/MAX(1, G65-F65+1)))</f>
         <v/>
       </c>
       <c r="N65" s="15">
@@ -5227,7 +5227,7 @@
       <c r="W65" s="12" t="n"/>
       <c r="X65" s="14" t="n"/>
       <c r="Y65" s="15">
-        <f>IF(TODAY()&lt;R65, 0, IF(TODAY()&gt;S65, T65, T65 * (TODAY()-R65)/(S65-R65+1)))</f>
+        <f>IF(TODAY()&lt;R65, 0, IF(TODAY()&gt;S65, T65, T65 * (TODAY()-R65)/MAX(1, S65-R65+1)))</f>
         <v/>
       </c>
       <c r="Z65" s="15">
@@ -5248,7 +5248,7 @@
       <c r="AI65" s="12" t="n"/>
       <c r="AJ65" s="14" t="n"/>
       <c r="AK65" s="15">
-        <f>IF(TODAY()&lt;AD65, 0, IF(TODAY()&gt;AE65, AF65, AF65 * (TODAY()-AD65)/(AE65-AD65+1)))</f>
+        <f>IF(TODAY()&lt;AD65, 0, IF(TODAY()&gt;AE65, AF65, AF65 * (TODAY()-AD65)/MAX(1, AE65-AD65+1)))</f>
         <v/>
       </c>
       <c r="AL65" s="15">
@@ -5274,7 +5274,7 @@
       <c r="K66" s="12" t="n"/>
       <c r="L66" s="14" t="n"/>
       <c r="M66" s="15">
-        <f>IF(TODAY()&lt;F66, 0, IF(TODAY()&gt;G66, H66, H66 * (TODAY()-F66)/(G66-F66+1)))</f>
+        <f>IF(TODAY()&lt;F66, 0, IF(TODAY()&gt;G66, H66, H66 * (TODAY()-F66)/MAX(1, G66-F66+1)))</f>
         <v/>
       </c>
       <c r="N66" s="15">
@@ -5295,7 +5295,7 @@
       <c r="W66" s="12" t="n"/>
       <c r="X66" s="14" t="n"/>
       <c r="Y66" s="15">
-        <f>IF(TODAY()&lt;R66, 0, IF(TODAY()&gt;S66, T66, T66 * (TODAY()-R66)/(S66-R66+1)))</f>
+        <f>IF(TODAY()&lt;R66, 0, IF(TODAY()&gt;S66, T66, T66 * (TODAY()-R66)/MAX(1, S66-R66+1)))</f>
         <v/>
       </c>
       <c r="Z66" s="15">
@@ -5316,7 +5316,7 @@
       <c r="AI66" s="12" t="n"/>
       <c r="AJ66" s="14" t="n"/>
       <c r="AK66" s="15">
-        <f>IF(TODAY()&lt;AD66, 0, IF(TODAY()&gt;AE66, AF66, AF66 * (TODAY()-AD66)/(AE66-AD66+1)))</f>
+        <f>IF(TODAY()&lt;AD66, 0, IF(TODAY()&gt;AE66, AF66, AF66 * (TODAY()-AD66)/MAX(1, AE66-AD66+1)))</f>
         <v/>
       </c>
       <c r="AL66" s="15">
@@ -5342,7 +5342,7 @@
       <c r="K67" s="12" t="n"/>
       <c r="L67" s="14" t="n"/>
       <c r="M67" s="15">
-        <f>IF(TODAY()&lt;F67, 0, IF(TODAY()&gt;G67, H67, H67 * (TODAY()-F67)/(G67-F67+1)))</f>
+        <f>IF(TODAY()&lt;F67, 0, IF(TODAY()&gt;G67, H67, H67 * (TODAY()-F67)/MAX(1, G67-F67+1)))</f>
         <v/>
       </c>
       <c r="N67" s="15">
@@ -5363,7 +5363,7 @@
       <c r="W67" s="12" t="n"/>
       <c r="X67" s="14" t="n"/>
       <c r="Y67" s="15">
-        <f>IF(TODAY()&lt;R67, 0, IF(TODAY()&gt;S67, T67, T67 * (TODAY()-R67)/(S67-R67+1)))</f>
+        <f>IF(TODAY()&lt;R67, 0, IF(TODAY()&gt;S67, T67, T67 * (TODAY()-R67)/MAX(1, S67-R67+1)))</f>
         <v/>
       </c>
       <c r="Z67" s="15">
@@ -5384,7 +5384,7 @@
       <c r="AI67" s="12" t="n"/>
       <c r="AJ67" s="14" t="n"/>
       <c r="AK67" s="15">
-        <f>IF(TODAY()&lt;AD67, 0, IF(TODAY()&gt;AE67, AF67, AF67 * (TODAY()-AD67)/(AE67-AD67+1)))</f>
+        <f>IF(TODAY()&lt;AD67, 0, IF(TODAY()&gt;AE67, AF67, AF67 * (TODAY()-AD67)/MAX(1, AE67-AD67+1)))</f>
         <v/>
       </c>
       <c r="AL67" s="15">
@@ -5410,7 +5410,7 @@
       <c r="K68" s="12" t="n"/>
       <c r="L68" s="14" t="n"/>
       <c r="M68" s="15">
-        <f>IF(TODAY()&lt;F68, 0, IF(TODAY()&gt;G68, H68, H68 * (TODAY()-F68)/(G68-F68+1)))</f>
+        <f>IF(TODAY()&lt;F68, 0, IF(TODAY()&gt;G68, H68, H68 * (TODAY()-F68)/MAX(1, G68-F68+1)))</f>
         <v/>
       </c>
       <c r="N68" s="15">
@@ -5431,7 +5431,7 @@
       <c r="W68" s="12" t="n"/>
       <c r="X68" s="14" t="n"/>
       <c r="Y68" s="15">
-        <f>IF(TODAY()&lt;R68, 0, IF(TODAY()&gt;S68, T68, T68 * (TODAY()-R68)/(S68-R68+1)))</f>
+        <f>IF(TODAY()&lt;R68, 0, IF(TODAY()&gt;S68, T68, T68 * (TODAY()-R68)/MAX(1, S68-R68+1)))</f>
         <v/>
       </c>
       <c r="Z68" s="15">
@@ -5452,7 +5452,7 @@
       <c r="AI68" s="12" t="n"/>
       <c r="AJ68" s="14" t="n"/>
       <c r="AK68" s="15">
-        <f>IF(TODAY()&lt;AD68, 0, IF(TODAY()&gt;AE68, AF68, AF68 * (TODAY()-AD68)/(AE68-AD68+1)))</f>
+        <f>IF(TODAY()&lt;AD68, 0, IF(TODAY()&gt;AE68, AF68, AF68 * (TODAY()-AD68)/MAX(1, AE68-AD68+1)))</f>
         <v/>
       </c>
       <c r="AL68" s="15">
@@ -5478,7 +5478,7 @@
       <c r="K69" s="12" t="n"/>
       <c r="L69" s="14" t="n"/>
       <c r="M69" s="15">
-        <f>IF(TODAY()&lt;F69, 0, IF(TODAY()&gt;G69, H69, H69 * (TODAY()-F69)/(G69-F69+1)))</f>
+        <f>IF(TODAY()&lt;F69, 0, IF(TODAY()&gt;G69, H69, H69 * (TODAY()-F69)/MAX(1, G69-F69+1)))</f>
         <v/>
       </c>
       <c r="N69" s="15">
@@ -5499,7 +5499,7 @@
       <c r="W69" s="12" t="n"/>
       <c r="X69" s="14" t="n"/>
       <c r="Y69" s="15">
-        <f>IF(TODAY()&lt;R69, 0, IF(TODAY()&gt;S69, T69, T69 * (TODAY()-R69)/(S69-R69+1)))</f>
+        <f>IF(TODAY()&lt;R69, 0, IF(TODAY()&gt;S69, T69, T69 * (TODAY()-R69)/MAX(1, S69-R69+1)))</f>
         <v/>
       </c>
       <c r="Z69" s="15">
@@ -5520,7 +5520,7 @@
       <c r="AI69" s="12" t="n"/>
       <c r="AJ69" s="14" t="n"/>
       <c r="AK69" s="15">
-        <f>IF(TODAY()&lt;AD69, 0, IF(TODAY()&gt;AE69, AF69, AF69 * (TODAY()-AD69)/(AE69-AD69+1)))</f>
+        <f>IF(TODAY()&lt;AD69, 0, IF(TODAY()&gt;AE69, AF69, AF69 * (TODAY()-AD69)/MAX(1, AE69-AD69+1)))</f>
         <v/>
       </c>
       <c r="AL69" s="15">
@@ -5546,7 +5546,7 @@
       <c r="K70" s="12" t="n"/>
       <c r="L70" s="14" t="n"/>
       <c r="M70" s="15">
-        <f>IF(TODAY()&lt;F70, 0, IF(TODAY()&gt;G70, H70, H70 * (TODAY()-F70)/(G70-F70+1)))</f>
+        <f>IF(TODAY()&lt;F70, 0, IF(TODAY()&gt;G70, H70, H70 * (TODAY()-F70)/MAX(1, G70-F70+1)))</f>
         <v/>
       </c>
       <c r="N70" s="15">
@@ -5567,7 +5567,7 @@
       <c r="W70" s="12" t="n"/>
       <c r="X70" s="14" t="n"/>
       <c r="Y70" s="15">
-        <f>IF(TODAY()&lt;R70, 0, IF(TODAY()&gt;S70, T70, T70 * (TODAY()-R70)/(S70-R70+1)))</f>
+        <f>IF(TODAY()&lt;R70, 0, IF(TODAY()&gt;S70, T70, T70 * (TODAY()-R70)/MAX(1, S70-R70+1)))</f>
         <v/>
       </c>
       <c r="Z70" s="15">
@@ -5588,7 +5588,7 @@
       <c r="AI70" s="12" t="n"/>
       <c r="AJ70" s="14" t="n"/>
       <c r="AK70" s="15">
-        <f>IF(TODAY()&lt;AD70, 0, IF(TODAY()&gt;AE70, AF70, AF70 * (TODAY()-AD70)/(AE70-AD70+1)))</f>
+        <f>IF(TODAY()&lt;AD70, 0, IF(TODAY()&gt;AE70, AF70, AF70 * (TODAY()-AD70)/MAX(1, AE70-AD70+1)))</f>
         <v/>
       </c>
       <c r="AL70" s="15">
@@ -5614,7 +5614,7 @@
       <c r="K71" s="12" t="n"/>
       <c r="L71" s="14" t="n"/>
       <c r="M71" s="15">
-        <f>IF(TODAY()&lt;F71, 0, IF(TODAY()&gt;G71, H71, H71 * (TODAY()-F71)/(G71-F71+1)))</f>
+        <f>IF(TODAY()&lt;F71, 0, IF(TODAY()&gt;G71, H71, H71 * (TODAY()-F71)/MAX(1, G71-F71+1)))</f>
         <v/>
       </c>
       <c r="N71" s="15">
@@ -5635,7 +5635,7 @@
       <c r="W71" s="12" t="n"/>
       <c r="X71" s="14" t="n"/>
       <c r="Y71" s="15">
-        <f>IF(TODAY()&lt;R71, 0, IF(TODAY()&gt;S71, T71, T71 * (TODAY()-R71)/(S71-R71+1)))</f>
+        <f>IF(TODAY()&lt;R71, 0, IF(TODAY()&gt;S71, T71, T71 * (TODAY()-R71)/MAX(1, S71-R71+1)))</f>
         <v/>
       </c>
       <c r="Z71" s="15">
@@ -5656,7 +5656,7 @@
       <c r="AI71" s="12" t="n"/>
       <c r="AJ71" s="14" t="n"/>
       <c r="AK71" s="15">
-        <f>IF(TODAY()&lt;AD71, 0, IF(TODAY()&gt;AE71, AF71, AF71 * (TODAY()-AD71)/(AE71-AD71+1)))</f>
+        <f>IF(TODAY()&lt;AD71, 0, IF(TODAY()&gt;AE71, AF71, AF71 * (TODAY()-AD71)/MAX(1, AE71-AD71+1)))</f>
         <v/>
       </c>
       <c r="AL71" s="15">
@@ -5682,7 +5682,7 @@
       <c r="K72" s="12" t="n"/>
       <c r="L72" s="14" t="n"/>
       <c r="M72" s="15">
-        <f>IF(TODAY()&lt;F72, 0, IF(TODAY()&gt;G72, H72, H72 * (TODAY()-F72)/(G72-F72+1)))</f>
+        <f>IF(TODAY()&lt;F72, 0, IF(TODAY()&gt;G72, H72, H72 * (TODAY()-F72)/MAX(1, G72-F72+1)))</f>
         <v/>
       </c>
       <c r="N72" s="15">
@@ -5703,7 +5703,7 @@
       <c r="W72" s="12" t="n"/>
       <c r="X72" s="14" t="n"/>
       <c r="Y72" s="15">
-        <f>IF(TODAY()&lt;R72, 0, IF(TODAY()&gt;S72, T72, T72 * (TODAY()-R72)/(S72-R72+1)))</f>
+        <f>IF(TODAY()&lt;R72, 0, IF(TODAY()&gt;S72, T72, T72 * (TODAY()-R72)/MAX(1, S72-R72+1)))</f>
         <v/>
       </c>
       <c r="Z72" s="15">
@@ -5724,7 +5724,7 @@
       <c r="AI72" s="12" t="n"/>
       <c r="AJ72" s="14" t="n"/>
       <c r="AK72" s="15">
-        <f>IF(TODAY()&lt;AD72, 0, IF(TODAY()&gt;AE72, AF72, AF72 * (TODAY()-AD72)/(AE72-AD72+1)))</f>
+        <f>IF(TODAY()&lt;AD72, 0, IF(TODAY()&gt;AE72, AF72, AF72 * (TODAY()-AD72)/MAX(1, AE72-AD72+1)))</f>
         <v/>
       </c>
       <c r="AL72" s="15">
@@ -5750,7 +5750,7 @@
       <c r="K73" s="12" t="n"/>
       <c r="L73" s="14" t="n"/>
       <c r="M73" s="15">
-        <f>IF(TODAY()&lt;F73, 0, IF(TODAY()&gt;G73, H73, H73 * (TODAY()-F73)/(G73-F73+1)))</f>
+        <f>IF(TODAY()&lt;F73, 0, IF(TODAY()&gt;G73, H73, H73 * (TODAY()-F73)/MAX(1, G73-F73+1)))</f>
         <v/>
       </c>
       <c r="N73" s="15">
@@ -5771,7 +5771,7 @@
       <c r="W73" s="12" t="n"/>
       <c r="X73" s="14" t="n"/>
       <c r="Y73" s="15">
-        <f>IF(TODAY()&lt;R73, 0, IF(TODAY()&gt;S73, T73, T73 * (TODAY()-R73)/(S73-R73+1)))</f>
+        <f>IF(TODAY()&lt;R73, 0, IF(TODAY()&gt;S73, T73, T73 * (TODAY()-R73)/MAX(1, S73-R73+1)))</f>
         <v/>
       </c>
       <c r="Z73" s="15">
@@ -5792,7 +5792,7 @@
       <c r="AI73" s="12" t="n"/>
       <c r="AJ73" s="14" t="n"/>
       <c r="AK73" s="15">
-        <f>IF(TODAY()&lt;AD73, 0, IF(TODAY()&gt;AE73, AF73, AF73 * (TODAY()-AD73)/(AE73-AD73+1)))</f>
+        <f>IF(TODAY()&lt;AD73, 0, IF(TODAY()&gt;AE73, AF73, AF73 * (TODAY()-AD73)/MAX(1, AE73-AD73+1)))</f>
         <v/>
       </c>
       <c r="AL73" s="15">
@@ -5818,7 +5818,7 @@
       <c r="K74" s="12" t="n"/>
       <c r="L74" s="14" t="n"/>
       <c r="M74" s="15">
-        <f>IF(TODAY()&lt;F74, 0, IF(TODAY()&gt;G74, H74, H74 * (TODAY()-F74)/(G74-F74+1)))</f>
+        <f>IF(TODAY()&lt;F74, 0, IF(TODAY()&gt;G74, H74, H74 * (TODAY()-F74)/MAX(1, G74-F74+1)))</f>
         <v/>
       </c>
       <c r="N74" s="15">
@@ -5839,7 +5839,7 @@
       <c r="W74" s="12" t="n"/>
       <c r="X74" s="14" t="n"/>
       <c r="Y74" s="15">
-        <f>IF(TODAY()&lt;R74, 0, IF(TODAY()&gt;S74, T74, T74 * (TODAY()-R74)/(S74-R74+1)))</f>
+        <f>IF(TODAY()&lt;R74, 0, IF(TODAY()&gt;S74, T74, T74 * (TODAY()-R74)/MAX(1, S74-R74+1)))</f>
         <v/>
       </c>
       <c r="Z74" s="15">
@@ -5860,7 +5860,7 @@
       <c r="AI74" s="12" t="n"/>
       <c r="AJ74" s="14" t="n"/>
       <c r="AK74" s="15">
-        <f>IF(TODAY()&lt;AD74, 0, IF(TODAY()&gt;AE74, AF74, AF74 * (TODAY()-AD74)/(AE74-AD74+1)))</f>
+        <f>IF(TODAY()&lt;AD74, 0, IF(TODAY()&gt;AE74, AF74, AF74 * (TODAY()-AD74)/MAX(1, AE74-AD74+1)))</f>
         <v/>
       </c>
       <c r="AL74" s="15">
@@ -5886,7 +5886,7 @@
       <c r="K75" s="12" t="n"/>
       <c r="L75" s="14" t="n"/>
       <c r="M75" s="15">
-        <f>IF(TODAY()&lt;F75, 0, IF(TODAY()&gt;G75, H75, H75 * (TODAY()-F75)/(G75-F75+1)))</f>
+        <f>IF(TODAY()&lt;F75, 0, IF(TODAY()&gt;G75, H75, H75 * (TODAY()-F75)/MAX(1, G75-F75+1)))</f>
         <v/>
       </c>
       <c r="N75" s="15">
@@ -5907,7 +5907,7 @@
       <c r="W75" s="12" t="n"/>
       <c r="X75" s="14" t="n"/>
       <c r="Y75" s="15">
-        <f>IF(TODAY()&lt;R75, 0, IF(TODAY()&gt;S75, T75, T75 * (TODAY()-R75)/(S75-R75+1)))</f>
+        <f>IF(TODAY()&lt;R75, 0, IF(TODAY()&gt;S75, T75, T75 * (TODAY()-R75)/MAX(1, S75-R75+1)))</f>
         <v/>
       </c>
       <c r="Z75" s="15">
@@ -5928,7 +5928,7 @@
       <c r="AI75" s="12" t="n"/>
       <c r="AJ75" s="14" t="n"/>
       <c r="AK75" s="15">
-        <f>IF(TODAY()&lt;AD75, 0, IF(TODAY()&gt;AE75, AF75, AF75 * (TODAY()-AD75)/(AE75-AD75+1)))</f>
+        <f>IF(TODAY()&lt;AD75, 0, IF(TODAY()&gt;AE75, AF75, AF75 * (TODAY()-AD75)/MAX(1, AE75-AD75+1)))</f>
         <v/>
       </c>
       <c r="AL75" s="15">
@@ -5954,7 +5954,7 @@
       <c r="K76" s="12" t="n"/>
       <c r="L76" s="14" t="n"/>
       <c r="M76" s="15">
-        <f>IF(TODAY()&lt;F76, 0, IF(TODAY()&gt;G76, H76, H76 * (TODAY()-F76)/(G76-F76+1)))</f>
+        <f>IF(TODAY()&lt;F76, 0, IF(TODAY()&gt;G76, H76, H76 * (TODAY()-F76)/MAX(1, G76-F76+1)))</f>
         <v/>
       </c>
       <c r="N76" s="15">
@@ -5975,7 +5975,7 @@
       <c r="W76" s="12" t="n"/>
       <c r="X76" s="14" t="n"/>
       <c r="Y76" s="15">
-        <f>IF(TODAY()&lt;R76, 0, IF(TODAY()&gt;S76, T76, T76 * (TODAY()-R76)/(S76-R76+1)))</f>
+        <f>IF(TODAY()&lt;R76, 0, IF(TODAY()&gt;S76, T76, T76 * (TODAY()-R76)/MAX(1, S76-R76+1)))</f>
         <v/>
       </c>
       <c r="Z76" s="15">
@@ -5996,7 +5996,7 @@
       <c r="AI76" s="12" t="n"/>
       <c r="AJ76" s="14" t="n"/>
       <c r="AK76" s="15">
-        <f>IF(TODAY()&lt;AD76, 0, IF(TODAY()&gt;AE76, AF76, AF76 * (TODAY()-AD76)/(AE76-AD76+1)))</f>
+        <f>IF(TODAY()&lt;AD76, 0, IF(TODAY()&gt;AE76, AF76, AF76 * (TODAY()-AD76)/MAX(1, AE76-AD76+1)))</f>
         <v/>
       </c>
       <c r="AL76" s="15">
@@ -6022,7 +6022,7 @@
       <c r="K77" s="12" t="n"/>
       <c r="L77" s="14" t="n"/>
       <c r="M77" s="15">
-        <f>IF(TODAY()&lt;F77, 0, IF(TODAY()&gt;G77, H77, H77 * (TODAY()-F77)/(G77-F77+1)))</f>
+        <f>IF(TODAY()&lt;F77, 0, IF(TODAY()&gt;G77, H77, H77 * (TODAY()-F77)/MAX(1, G77-F77+1)))</f>
         <v/>
       </c>
       <c r="N77" s="15">
@@ -6043,7 +6043,7 @@
       <c r="W77" s="12" t="n"/>
       <c r="X77" s="14" t="n"/>
       <c r="Y77" s="15">
-        <f>IF(TODAY()&lt;R77, 0, IF(TODAY()&gt;S77, T77, T77 * (TODAY()-R77)/(S77-R77+1)))</f>
+        <f>IF(TODAY()&lt;R77, 0, IF(TODAY()&gt;S77, T77, T77 * (TODAY()-R77)/MAX(1, S77-R77+1)))</f>
         <v/>
       </c>
       <c r="Z77" s="15">
@@ -6064,7 +6064,7 @@
       <c r="AI77" s="12" t="n"/>
       <c r="AJ77" s="14" t="n"/>
       <c r="AK77" s="15">
-        <f>IF(TODAY()&lt;AD77, 0, IF(TODAY()&gt;AE77, AF77, AF77 * (TODAY()-AD77)/(AE77-AD77+1)))</f>
+        <f>IF(TODAY()&lt;AD77, 0, IF(TODAY()&gt;AE77, AF77, AF77 * (TODAY()-AD77)/MAX(1, AE77-AD77+1)))</f>
         <v/>
       </c>
       <c r="AL77" s="15">
@@ -6090,7 +6090,7 @@
       <c r="K78" s="12" t="n"/>
       <c r="L78" s="14" t="n"/>
       <c r="M78" s="15">
-        <f>IF(TODAY()&lt;F78, 0, IF(TODAY()&gt;G78, H78, H78 * (TODAY()-F78)/(G78-F78+1)))</f>
+        <f>IF(TODAY()&lt;F78, 0, IF(TODAY()&gt;G78, H78, H78 * (TODAY()-F78)/MAX(1, G78-F78+1)))</f>
         <v/>
       </c>
       <c r="N78" s="15">
@@ -6111,7 +6111,7 @@
       <c r="W78" s="12" t="n"/>
       <c r="X78" s="14" t="n"/>
       <c r="Y78" s="15">
-        <f>IF(TODAY()&lt;R78, 0, IF(TODAY()&gt;S78, T78, T78 * (TODAY()-R78)/(S78-R78+1)))</f>
+        <f>IF(TODAY()&lt;R78, 0, IF(TODAY()&gt;S78, T78, T78 * (TODAY()-R78)/MAX(1, S78-R78+1)))</f>
         <v/>
       </c>
       <c r="Z78" s="15">
@@ -6132,7 +6132,7 @@
       <c r="AI78" s="12" t="n"/>
       <c r="AJ78" s="14" t="n"/>
       <c r="AK78" s="15">
-        <f>IF(TODAY()&lt;AD78, 0, IF(TODAY()&gt;AE78, AF78, AF78 * (TODAY()-AD78)/(AE78-AD78+1)))</f>
+        <f>IF(TODAY()&lt;AD78, 0, IF(TODAY()&gt;AE78, AF78, AF78 * (TODAY()-AD78)/MAX(1, AE78-AD78+1)))</f>
         <v/>
       </c>
       <c r="AL78" s="15">
@@ -6158,7 +6158,7 @@
       <c r="K79" s="12" t="n"/>
       <c r="L79" s="14" t="n"/>
       <c r="M79" s="15">
-        <f>IF(TODAY()&lt;F79, 0, IF(TODAY()&gt;G79, H79, H79 * (TODAY()-F79)/(G79-F79+1)))</f>
+        <f>IF(TODAY()&lt;F79, 0, IF(TODAY()&gt;G79, H79, H79 * (TODAY()-F79)/MAX(1, G79-F79+1)))</f>
         <v/>
       </c>
       <c r="N79" s="15">
@@ -6179,7 +6179,7 @@
       <c r="W79" s="12" t="n"/>
       <c r="X79" s="14" t="n"/>
       <c r="Y79" s="15">
-        <f>IF(TODAY()&lt;R79, 0, IF(TODAY()&gt;S79, T79, T79 * (TODAY()-R79)/(S79-R79+1)))</f>
+        <f>IF(TODAY()&lt;R79, 0, IF(TODAY()&gt;S79, T79, T79 * (TODAY()-R79)/MAX(1, S79-R79+1)))</f>
         <v/>
       </c>
       <c r="Z79" s="15">
@@ -6200,7 +6200,7 @@
       <c r="AI79" s="12" t="n"/>
       <c r="AJ79" s="14" t="n"/>
       <c r="AK79" s="15">
-        <f>IF(TODAY()&lt;AD79, 0, IF(TODAY()&gt;AE79, AF79, AF79 * (TODAY()-AD79)/(AE79-AD79+1)))</f>
+        <f>IF(TODAY()&lt;AD79, 0, IF(TODAY()&gt;AE79, AF79, AF79 * (TODAY()-AD79)/MAX(1, AE79-AD79+1)))</f>
         <v/>
       </c>
       <c r="AL79" s="15">
@@ -6226,7 +6226,7 @@
       <c r="K80" s="12" t="n"/>
       <c r="L80" s="14" t="n"/>
       <c r="M80" s="15">
-        <f>IF(TODAY()&lt;F80, 0, IF(TODAY()&gt;G80, H80, H80 * (TODAY()-F80)/(G80-F80+1)))</f>
+        <f>IF(TODAY()&lt;F80, 0, IF(TODAY()&gt;G80, H80, H80 * (TODAY()-F80)/MAX(1, G80-F80+1)))</f>
         <v/>
       </c>
       <c r="N80" s="15">
@@ -6247,7 +6247,7 @@
       <c r="W80" s="12" t="n"/>
       <c r="X80" s="14" t="n"/>
       <c r="Y80" s="15">
-        <f>IF(TODAY()&lt;R80, 0, IF(TODAY()&gt;S80, T80, T80 * (TODAY()-R80)/(S80-R80+1)))</f>
+        <f>IF(TODAY()&lt;R80, 0, IF(TODAY()&gt;S80, T80, T80 * (TODAY()-R80)/MAX(1, S80-R80+1)))</f>
         <v/>
       </c>
       <c r="Z80" s="15">
@@ -6268,7 +6268,7 @@
       <c r="AI80" s="12" t="n"/>
       <c r="AJ80" s="14" t="n"/>
       <c r="AK80" s="15">
-        <f>IF(TODAY()&lt;AD80, 0, IF(TODAY()&gt;AE80, AF80, AF80 * (TODAY()-AD80)/(AE80-AD80+1)))</f>
+        <f>IF(TODAY()&lt;AD80, 0, IF(TODAY()&gt;AE80, AF80, AF80 * (TODAY()-AD80)/MAX(1, AE80-AD80+1)))</f>
         <v/>
       </c>
       <c r="AL80" s="15">
@@ -6294,7 +6294,7 @@
       <c r="K81" s="12" t="n"/>
       <c r="L81" s="14" t="n"/>
       <c r="M81" s="15">
-        <f>IF(TODAY()&lt;F81, 0, IF(TODAY()&gt;G81, H81, H81 * (TODAY()-F81)/(G81-F81+1)))</f>
+        <f>IF(TODAY()&lt;F81, 0, IF(TODAY()&gt;G81, H81, H81 * (TODAY()-F81)/MAX(1, G81-F81+1)))</f>
         <v/>
       </c>
       <c r="N81" s="15">
@@ -6315,7 +6315,7 @@
       <c r="W81" s="12" t="n"/>
       <c r="X81" s="14" t="n"/>
       <c r="Y81" s="15">
-        <f>IF(TODAY()&lt;R81, 0, IF(TODAY()&gt;S81, T81, T81 * (TODAY()-R81)/(S81-R81+1)))</f>
+        <f>IF(TODAY()&lt;R81, 0, IF(TODAY()&gt;S81, T81, T81 * (TODAY()-R81)/MAX(1, S81-R81+1)))</f>
         <v/>
       </c>
       <c r="Z81" s="15">
@@ -6336,7 +6336,7 @@
       <c r="AI81" s="12" t="n"/>
       <c r="AJ81" s="14" t="n"/>
       <c r="AK81" s="15">
-        <f>IF(TODAY()&lt;AD81, 0, IF(TODAY()&gt;AE81, AF81, AF81 * (TODAY()-AD81)/(AE81-AD81+1)))</f>
+        <f>IF(TODAY()&lt;AD81, 0, IF(TODAY()&gt;AE81, AF81, AF81 * (TODAY()-AD81)/MAX(1, AE81-AD81+1)))</f>
         <v/>
       </c>
       <c r="AL81" s="15">
@@ -6362,7 +6362,7 @@
       <c r="K82" s="12" t="n"/>
       <c r="L82" s="14" t="n"/>
       <c r="M82" s="15">
-        <f>IF(TODAY()&lt;F82, 0, IF(TODAY()&gt;G82, H82, H82 * (TODAY()-F82)/(G82-F82+1)))</f>
+        <f>IF(TODAY()&lt;F82, 0, IF(TODAY()&gt;G82, H82, H82 * (TODAY()-F82)/MAX(1, G82-F82+1)))</f>
         <v/>
       </c>
       <c r="N82" s="15">
@@ -6383,7 +6383,7 @@
       <c r="W82" s="12" t="n"/>
       <c r="X82" s="14" t="n"/>
       <c r="Y82" s="15">
-        <f>IF(TODAY()&lt;R82, 0, IF(TODAY()&gt;S82, T82, T82 * (TODAY()-R82)/(S82-R82+1)))</f>
+        <f>IF(TODAY()&lt;R82, 0, IF(TODAY()&gt;S82, T82, T82 * (TODAY()-R82)/MAX(1, S82-R82+1)))</f>
         <v/>
       </c>
       <c r="Z82" s="15">
@@ -6404,7 +6404,7 @@
       <c r="AI82" s="12" t="n"/>
       <c r="AJ82" s="14" t="n"/>
       <c r="AK82" s="15">
-        <f>IF(TODAY()&lt;AD82, 0, IF(TODAY()&gt;AE82, AF82, AF82 * (TODAY()-AD82)/(AE82-AD82+1)))</f>
+        <f>IF(TODAY()&lt;AD82, 0, IF(TODAY()&gt;AE82, AF82, AF82 * (TODAY()-AD82)/MAX(1, AE82-AD82+1)))</f>
         <v/>
       </c>
       <c r="AL82" s="15">
@@ -6430,7 +6430,7 @@
       <c r="K83" s="12" t="n"/>
       <c r="L83" s="14" t="n"/>
       <c r="M83" s="15">
-        <f>IF(TODAY()&lt;F83, 0, IF(TODAY()&gt;G83, H83, H83 * (TODAY()-F83)/(G83-F83+1)))</f>
+        <f>IF(TODAY()&lt;F83, 0, IF(TODAY()&gt;G83, H83, H83 * (TODAY()-F83)/MAX(1, G83-F83+1)))</f>
         <v/>
       </c>
       <c r="N83" s="15">
@@ -6451,7 +6451,7 @@
       <c r="W83" s="12" t="n"/>
       <c r="X83" s="14" t="n"/>
       <c r="Y83" s="15">
-        <f>IF(TODAY()&lt;R83, 0, IF(TODAY()&gt;S83, T83, T83 * (TODAY()-R83)/(S83-R83+1)))</f>
+        <f>IF(TODAY()&lt;R83, 0, IF(TODAY()&gt;S83, T83, T83 * (TODAY()-R83)/MAX(1, S83-R83+1)))</f>
         <v/>
       </c>
       <c r="Z83" s="15">
@@ -6472,7 +6472,7 @@
       <c r="AI83" s="12" t="n"/>
       <c r="AJ83" s="14" t="n"/>
       <c r="AK83" s="15">
-        <f>IF(TODAY()&lt;AD83, 0, IF(TODAY()&gt;AE83, AF83, AF83 * (TODAY()-AD83)/(AE83-AD83+1)))</f>
+        <f>IF(TODAY()&lt;AD83, 0, IF(TODAY()&gt;AE83, AF83, AF83 * (TODAY()-AD83)/MAX(1, AE83-AD83+1)))</f>
         <v/>
       </c>
       <c r="AL83" s="15">
@@ -6498,7 +6498,7 @@
       <c r="K84" s="12" t="n"/>
       <c r="L84" s="14" t="n"/>
       <c r="M84" s="15">
-        <f>IF(TODAY()&lt;F84, 0, IF(TODAY()&gt;G84, H84, H84 * (TODAY()-F84)/(G84-F84+1)))</f>
+        <f>IF(TODAY()&lt;F84, 0, IF(TODAY()&gt;G84, H84, H84 * (TODAY()-F84)/MAX(1, G84-F84+1)))</f>
         <v/>
       </c>
       <c r="N84" s="15">
@@ -6519,7 +6519,7 @@
       <c r="W84" s="12" t="n"/>
       <c r="X84" s="14" t="n"/>
       <c r="Y84" s="15">
-        <f>IF(TODAY()&lt;R84, 0, IF(TODAY()&gt;S84, T84, T84 * (TODAY()-R84)/(S84-R84+1)))</f>
+        <f>IF(TODAY()&lt;R84, 0, IF(TODAY()&gt;S84, T84, T84 * (TODAY()-R84)/MAX(1, S84-R84+1)))</f>
         <v/>
       </c>
       <c r="Z84" s="15">
@@ -6540,7 +6540,7 @@
       <c r="AI84" s="12" t="n"/>
       <c r="AJ84" s="14" t="n"/>
       <c r="AK84" s="15">
-        <f>IF(TODAY()&lt;AD84, 0, IF(TODAY()&gt;AE84, AF84, AF84 * (TODAY()-AD84)/(AE84-AD84+1)))</f>
+        <f>IF(TODAY()&lt;AD84, 0, IF(TODAY()&gt;AE84, AF84, AF84 * (TODAY()-AD84)/MAX(1, AE84-AD84+1)))</f>
         <v/>
       </c>
       <c r="AL84" s="15">
@@ -6566,7 +6566,7 @@
       <c r="K85" s="12" t="n"/>
       <c r="L85" s="14" t="n"/>
       <c r="M85" s="15">
-        <f>IF(TODAY()&lt;F85, 0, IF(TODAY()&gt;G85, H85, H85 * (TODAY()-F85)/(G85-F85+1)))</f>
+        <f>IF(TODAY()&lt;F85, 0, IF(TODAY()&gt;G85, H85, H85 * (TODAY()-F85)/MAX(1, G85-F85+1)))</f>
         <v/>
       </c>
       <c r="N85" s="15">
@@ -6587,7 +6587,7 @@
       <c r="W85" s="12" t="n"/>
       <c r="X85" s="14" t="n"/>
       <c r="Y85" s="15">
-        <f>IF(TODAY()&lt;R85, 0, IF(TODAY()&gt;S85, T85, T85 * (TODAY()-R85)/(S85-R85+1)))</f>
+        <f>IF(TODAY()&lt;R85, 0, IF(TODAY()&gt;S85, T85, T85 * (TODAY()-R85)/MAX(1, S85-R85+1)))</f>
         <v/>
       </c>
       <c r="Z85" s="15">
@@ -6608,7 +6608,7 @@
       <c r="AI85" s="12" t="n"/>
       <c r="AJ85" s="14" t="n"/>
       <c r="AK85" s="15">
-        <f>IF(TODAY()&lt;AD85, 0, IF(TODAY()&gt;AE85, AF85, AF85 * (TODAY()-AD85)/(AE85-AD85+1)))</f>
+        <f>IF(TODAY()&lt;AD85, 0, IF(TODAY()&gt;AE85, AF85, AF85 * (TODAY()-AD85)/MAX(1, AE85-AD85+1)))</f>
         <v/>
       </c>
       <c r="AL85" s="15">
@@ -6634,7 +6634,7 @@
       <c r="K86" s="12" t="n"/>
       <c r="L86" s="14" t="n"/>
       <c r="M86" s="15">
-        <f>IF(TODAY()&lt;F86, 0, IF(TODAY()&gt;G86, H86, H86 * (TODAY()-F86)/(G86-F86+1)))</f>
+        <f>IF(TODAY()&lt;F86, 0, IF(TODAY()&gt;G86, H86, H86 * (TODAY()-F86)/MAX(1, G86-F86+1)))</f>
         <v/>
       </c>
       <c r="N86" s="15">
@@ -6655,7 +6655,7 @@
       <c r="W86" s="12" t="n"/>
       <c r="X86" s="14" t="n"/>
       <c r="Y86" s="15">
-        <f>IF(TODAY()&lt;R86, 0, IF(TODAY()&gt;S86, T86, T86 * (TODAY()-R86)/(S86-R86+1)))</f>
+        <f>IF(TODAY()&lt;R86, 0, IF(TODAY()&gt;S86, T86, T86 * (TODAY()-R86)/MAX(1, S86-R86+1)))</f>
         <v/>
       </c>
       <c r="Z86" s="15">
@@ -6676,7 +6676,7 @@
       <c r="AI86" s="12" t="n"/>
       <c r="AJ86" s="14" t="n"/>
       <c r="AK86" s="15">
-        <f>IF(TODAY()&lt;AD86, 0, IF(TODAY()&gt;AE86, AF86, AF86 * (TODAY()-AD86)/(AE86-AD86+1)))</f>
+        <f>IF(TODAY()&lt;AD86, 0, IF(TODAY()&gt;AE86, AF86, AF86 * (TODAY()-AD86)/MAX(1, AE86-AD86+1)))</f>
         <v/>
       </c>
       <c r="AL86" s="15">
@@ -6702,7 +6702,7 @@
       <c r="K87" s="12" t="n"/>
       <c r="L87" s="14" t="n"/>
       <c r="M87" s="15">
-        <f>IF(TODAY()&lt;F87, 0, IF(TODAY()&gt;G87, H87, H87 * (TODAY()-F87)/(G87-F87+1)))</f>
+        <f>IF(TODAY()&lt;F87, 0, IF(TODAY()&gt;G87, H87, H87 * (TODAY()-F87)/MAX(1, G87-F87+1)))</f>
         <v/>
       </c>
       <c r="N87" s="15">
@@ -6723,7 +6723,7 @@
       <c r="W87" s="12" t="n"/>
       <c r="X87" s="14" t="n"/>
       <c r="Y87" s="15">
-        <f>IF(TODAY()&lt;R87, 0, IF(TODAY()&gt;S87, T87, T87 * (TODAY()-R87)/(S87-R87+1)))</f>
+        <f>IF(TODAY()&lt;R87, 0, IF(TODAY()&gt;S87, T87, T87 * (TODAY()-R87)/MAX(1, S87-R87+1)))</f>
         <v/>
       </c>
       <c r="Z87" s="15">
@@ -6744,7 +6744,7 @@
       <c r="AI87" s="12" t="n"/>
       <c r="AJ87" s="14" t="n"/>
       <c r="AK87" s="15">
-        <f>IF(TODAY()&lt;AD87, 0, IF(TODAY()&gt;AE87, AF87, AF87 * (TODAY()-AD87)/(AE87-AD87+1)))</f>
+        <f>IF(TODAY()&lt;AD87, 0, IF(TODAY()&gt;AE87, AF87, AF87 * (TODAY()-AD87)/MAX(1, AE87-AD87+1)))</f>
         <v/>
       </c>
       <c r="AL87" s="15">
@@ -6770,7 +6770,7 @@
       <c r="K88" s="12" t="n"/>
       <c r="L88" s="14" t="n"/>
       <c r="M88" s="15">
-        <f>IF(TODAY()&lt;F88, 0, IF(TODAY()&gt;G88, H88, H88 * (TODAY()-F88)/(G88-F88+1)))</f>
+        <f>IF(TODAY()&lt;F88, 0, IF(TODAY()&gt;G88, H88, H88 * (TODAY()-F88)/MAX(1, G88-F88+1)))</f>
         <v/>
       </c>
       <c r="N88" s="15">
@@ -6791,7 +6791,7 @@
       <c r="W88" s="12" t="n"/>
       <c r="X88" s="14" t="n"/>
       <c r="Y88" s="15">
-        <f>IF(TODAY()&lt;R88, 0, IF(TODAY()&gt;S88, T88, T88 * (TODAY()-R88)/(S88-R88+1)))</f>
+        <f>IF(TODAY()&lt;R88, 0, IF(TODAY()&gt;S88, T88, T88 * (TODAY()-R88)/MAX(1, S88-R88+1)))</f>
         <v/>
       </c>
       <c r="Z88" s="15">
@@ -6812,7 +6812,7 @@
       <c r="AI88" s="12" t="n"/>
       <c r="AJ88" s="14" t="n"/>
       <c r="AK88" s="15">
-        <f>IF(TODAY()&lt;AD88, 0, IF(TODAY()&gt;AE88, AF88, AF88 * (TODAY()-AD88)/(AE88-AD88+1)))</f>
+        <f>IF(TODAY()&lt;AD88, 0, IF(TODAY()&gt;AE88, AF88, AF88 * (TODAY()-AD88)/MAX(1, AE88-AD88+1)))</f>
         <v/>
       </c>
       <c r="AL88" s="15">
@@ -6838,7 +6838,7 @@
       <c r="K89" s="12" t="n"/>
       <c r="L89" s="14" t="n"/>
       <c r="M89" s="15">
-        <f>IF(TODAY()&lt;F89, 0, IF(TODAY()&gt;G89, H89, H89 * (TODAY()-F89)/(G89-F89+1)))</f>
+        <f>IF(TODAY()&lt;F89, 0, IF(TODAY()&gt;G89, H89, H89 * (TODAY()-F89)/MAX(1, G89-F89+1)))</f>
         <v/>
       </c>
       <c r="N89" s="15">
@@ -6859,7 +6859,7 @@
       <c r="W89" s="12" t="n"/>
       <c r="X89" s="14" t="n"/>
       <c r="Y89" s="15">
-        <f>IF(TODAY()&lt;R89, 0, IF(TODAY()&gt;S89, T89, T89 * (TODAY()-R89)/(S89-R89+1)))</f>
+        <f>IF(TODAY()&lt;R89, 0, IF(TODAY()&gt;S89, T89, T89 * (TODAY()-R89)/MAX(1, S89-R89+1)))</f>
         <v/>
       </c>
       <c r="Z89" s="15">
@@ -6880,7 +6880,7 @@
       <c r="AI89" s="12" t="n"/>
       <c r="AJ89" s="14" t="n"/>
       <c r="AK89" s="15">
-        <f>IF(TODAY()&lt;AD89, 0, IF(TODAY()&gt;AE89, AF89, AF89 * (TODAY()-AD89)/(AE89-AD89+1)))</f>
+        <f>IF(TODAY()&lt;AD89, 0, IF(TODAY()&gt;AE89, AF89, AF89 * (TODAY()-AD89)/MAX(1, AE89-AD89+1)))</f>
         <v/>
       </c>
       <c r="AL89" s="15">
@@ -6906,7 +6906,7 @@
       <c r="K90" s="12" t="n"/>
       <c r="L90" s="14" t="n"/>
       <c r="M90" s="15">
-        <f>IF(TODAY()&lt;F90, 0, IF(TODAY()&gt;G90, H90, H90 * (TODAY()-F90)/(G90-F90+1)))</f>
+        <f>IF(TODAY()&lt;F90, 0, IF(TODAY()&gt;G90, H90, H90 * (TODAY()-F90)/MAX(1, G90-F90+1)))</f>
         <v/>
       </c>
       <c r="N90" s="15">
@@ -6927,7 +6927,7 @@
       <c r="W90" s="12" t="n"/>
       <c r="X90" s="14" t="n"/>
       <c r="Y90" s="15">
-        <f>IF(TODAY()&lt;R90, 0, IF(TODAY()&gt;S90, T90, T90 * (TODAY()-R90)/(S90-R90+1)))</f>
+        <f>IF(TODAY()&lt;R90, 0, IF(TODAY()&gt;S90, T90, T90 * (TODAY()-R90)/MAX(1, S90-R90+1)))</f>
         <v/>
       </c>
       <c r="Z90" s="15">
@@ -6948,7 +6948,7 @@
       <c r="AI90" s="12" t="n"/>
       <c r="AJ90" s="14" t="n"/>
       <c r="AK90" s="15">
-        <f>IF(TODAY()&lt;AD90, 0, IF(TODAY()&gt;AE90, AF90, AF90 * (TODAY()-AD90)/(AE90-AD90+1)))</f>
+        <f>IF(TODAY()&lt;AD90, 0, IF(TODAY()&gt;AE90, AF90, AF90 * (TODAY()-AD90)/MAX(1, AE90-AD90+1)))</f>
         <v/>
       </c>
       <c r="AL90" s="15">
@@ -6974,7 +6974,7 @@
       <c r="K91" s="12" t="n"/>
       <c r="L91" s="14" t="n"/>
       <c r="M91" s="15">
-        <f>IF(TODAY()&lt;F91, 0, IF(TODAY()&gt;G91, H91, H91 * (TODAY()-F91)/(G91-F91+1)))</f>
+        <f>IF(TODAY()&lt;F91, 0, IF(TODAY()&gt;G91, H91, H91 * (TODAY()-F91)/MAX(1, G91-F91+1)))</f>
         <v/>
       </c>
       <c r="N91" s="15">
@@ -6995,7 +6995,7 @@
       <c r="W91" s="12" t="n"/>
       <c r="X91" s="14" t="n"/>
       <c r="Y91" s="15">
-        <f>IF(TODAY()&lt;R91, 0, IF(TODAY()&gt;S91, T91, T91 * (TODAY()-R91)/(S91-R91+1)))</f>
+        <f>IF(TODAY()&lt;R91, 0, IF(TODAY()&gt;S91, T91, T91 * (TODAY()-R91)/MAX(1, S91-R91+1)))</f>
         <v/>
       </c>
       <c r="Z91" s="15">
@@ -7016,7 +7016,7 @@
       <c r="AI91" s="12" t="n"/>
       <c r="AJ91" s="14" t="n"/>
       <c r="AK91" s="15">
-        <f>IF(TODAY()&lt;AD91, 0, IF(TODAY()&gt;AE91, AF91, AF91 * (TODAY()-AD91)/(AE91-AD91+1)))</f>
+        <f>IF(TODAY()&lt;AD91, 0, IF(TODAY()&gt;AE91, AF91, AF91 * (TODAY()-AD91)/MAX(1, AE91-AD91+1)))</f>
         <v/>
       </c>
       <c r="AL91" s="15">
@@ -7042,7 +7042,7 @@
       <c r="K92" s="12" t="n"/>
       <c r="L92" s="14" t="n"/>
       <c r="M92" s="15">
-        <f>IF(TODAY()&lt;F92, 0, IF(TODAY()&gt;G92, H92, H92 * (TODAY()-F92)/(G92-F92+1)))</f>
+        <f>IF(TODAY()&lt;F92, 0, IF(TODAY()&gt;G92, H92, H92 * (TODAY()-F92)/MAX(1, G92-F92+1)))</f>
         <v/>
       </c>
       <c r="N92" s="15">
@@ -7063,7 +7063,7 @@
       <c r="W92" s="12" t="n"/>
       <c r="X92" s="14" t="n"/>
       <c r="Y92" s="15">
-        <f>IF(TODAY()&lt;R92, 0, IF(TODAY()&gt;S92, T92, T92 * (TODAY()-R92)/(S92-R92+1)))</f>
+        <f>IF(TODAY()&lt;R92, 0, IF(TODAY()&gt;S92, T92, T92 * (TODAY()-R92)/MAX(1, S92-R92+1)))</f>
         <v/>
       </c>
       <c r="Z92" s="15">
@@ -7084,7 +7084,7 @@
       <c r="AI92" s="12" t="n"/>
       <c r="AJ92" s="14" t="n"/>
       <c r="AK92" s="15">
-        <f>IF(TODAY()&lt;AD92, 0, IF(TODAY()&gt;AE92, AF92, AF92 * (TODAY()-AD92)/(AE92-AD92+1)))</f>
+        <f>IF(TODAY()&lt;AD92, 0, IF(TODAY()&gt;AE92, AF92, AF92 * (TODAY()-AD92)/MAX(1, AE92-AD92+1)))</f>
         <v/>
       </c>
       <c r="AL92" s="15">
@@ -7110,7 +7110,7 @@
       <c r="K93" s="12" t="n"/>
       <c r="L93" s="14" t="n"/>
       <c r="M93" s="15">
-        <f>IF(TODAY()&lt;F93, 0, IF(TODAY()&gt;G93, H93, H93 * (TODAY()-F93)/(G93-F93+1)))</f>
+        <f>IF(TODAY()&lt;F93, 0, IF(TODAY()&gt;G93, H93, H93 * (TODAY()-F93)/MAX(1, G93-F93+1)))</f>
         <v/>
       </c>
       <c r="N93" s="15">
@@ -7131,7 +7131,7 @@
       <c r="W93" s="12" t="n"/>
       <c r="X93" s="14" t="n"/>
       <c r="Y93" s="15">
-        <f>IF(TODAY()&lt;R93, 0, IF(TODAY()&gt;S93, T93, T93 * (TODAY()-R93)/(S93-R93+1)))</f>
+        <f>IF(TODAY()&lt;R93, 0, IF(TODAY()&gt;S93, T93, T93 * (TODAY()-R93)/MAX(1, S93-R93+1)))</f>
         <v/>
       </c>
       <c r="Z93" s="15">
@@ -7152,7 +7152,7 @@
       <c r="AI93" s="12" t="n"/>
       <c r="AJ93" s="14" t="n"/>
       <c r="AK93" s="15">
-        <f>IF(TODAY()&lt;AD93, 0, IF(TODAY()&gt;AE93, AF93, AF93 * (TODAY()-AD93)/(AE93-AD93+1)))</f>
+        <f>IF(TODAY()&lt;AD93, 0, IF(TODAY()&gt;AE93, AF93, AF93 * (TODAY()-AD93)/MAX(1, AE93-AD93+1)))</f>
         <v/>
       </c>
       <c r="AL93" s="15">
@@ -7178,7 +7178,7 @@
       <c r="K94" s="12" t="n"/>
       <c r="L94" s="14" t="n"/>
       <c r="M94" s="15">
-        <f>IF(TODAY()&lt;F94, 0, IF(TODAY()&gt;G94, H94, H94 * (TODAY()-F94)/(G94-F94+1)))</f>
+        <f>IF(TODAY()&lt;F94, 0, IF(TODAY()&gt;G94, H94, H94 * (TODAY()-F94)/MAX(1, G94-F94+1)))</f>
         <v/>
       </c>
       <c r="N94" s="15">
@@ -7199,7 +7199,7 @@
       <c r="W94" s="12" t="n"/>
       <c r="X94" s="14" t="n"/>
       <c r="Y94" s="15">
-        <f>IF(TODAY()&lt;R94, 0, IF(TODAY()&gt;S94, T94, T94 * (TODAY()-R94)/(S94-R94+1)))</f>
+        <f>IF(TODAY()&lt;R94, 0, IF(TODAY()&gt;S94, T94, T94 * (TODAY()-R94)/MAX(1, S94-R94+1)))</f>
         <v/>
       </c>
       <c r="Z94" s="15">
@@ -7220,7 +7220,7 @@
       <c r="AI94" s="12" t="n"/>
       <c r="AJ94" s="14" t="n"/>
       <c r="AK94" s="15">
-        <f>IF(TODAY()&lt;AD94, 0, IF(TODAY()&gt;AE94, AF94, AF94 * (TODAY()-AD94)/(AE94-AD94+1)))</f>
+        <f>IF(TODAY()&lt;AD94, 0, IF(TODAY()&gt;AE94, AF94, AF94 * (TODAY()-AD94)/MAX(1, AE94-AD94+1)))</f>
         <v/>
       </c>
       <c r="AL94" s="15">
@@ -7246,7 +7246,7 @@
       <c r="K95" s="12" t="n"/>
       <c r="L95" s="14" t="n"/>
       <c r="M95" s="15">
-        <f>IF(TODAY()&lt;F95, 0, IF(TODAY()&gt;G95, H95, H95 * (TODAY()-F95)/(G95-F95+1)))</f>
+        <f>IF(TODAY()&lt;F95, 0, IF(TODAY()&gt;G95, H95, H95 * (TODAY()-F95)/MAX(1, G95-F95+1)))</f>
         <v/>
       </c>
       <c r="N95" s="15">
@@ -7267,7 +7267,7 @@
       <c r="W95" s="12" t="n"/>
       <c r="X95" s="14" t="n"/>
       <c r="Y95" s="15">
-        <f>IF(TODAY()&lt;R95, 0, IF(TODAY()&gt;S95, T95, T95 * (TODAY()-R95)/(S95-R95+1)))</f>
+        <f>IF(TODAY()&lt;R95, 0, IF(TODAY()&gt;S95, T95, T95 * (TODAY()-R95)/MAX(1, S95-R95+1)))</f>
         <v/>
       </c>
       <c r="Z95" s="15">
@@ -7288,7 +7288,7 @@
       <c r="AI95" s="12" t="n"/>
       <c r="AJ95" s="14" t="n"/>
       <c r="AK95" s="15">
-        <f>IF(TODAY()&lt;AD95, 0, IF(TODAY()&gt;AE95, AF95, AF95 * (TODAY()-AD95)/(AE95-AD95+1)))</f>
+        <f>IF(TODAY()&lt;AD95, 0, IF(TODAY()&gt;AE95, AF95, AF95 * (TODAY()-AD95)/MAX(1, AE95-AD95+1)))</f>
         <v/>
       </c>
       <c r="AL95" s="15">
@@ -7314,7 +7314,7 @@
       <c r="K96" s="12" t="n"/>
       <c r="L96" s="14" t="n"/>
       <c r="M96" s="15">
-        <f>IF(TODAY()&lt;F96, 0, IF(TODAY()&gt;G96, H96, H96 * (TODAY()-F96)/(G96-F96+1)))</f>
+        <f>IF(TODAY()&lt;F96, 0, IF(TODAY()&gt;G96, H96, H96 * (TODAY()-F96)/MAX(1, G96-F96+1)))</f>
         <v/>
       </c>
       <c r="N96" s="15">
@@ -7335,7 +7335,7 @@
       <c r="W96" s="12" t="n"/>
       <c r="X96" s="14" t="n"/>
       <c r="Y96" s="15">
-        <f>IF(TODAY()&lt;R96, 0, IF(TODAY()&gt;S96, T96, T96 * (TODAY()-R96)/(S96-R96+1)))</f>
+        <f>IF(TODAY()&lt;R96, 0, IF(TODAY()&gt;S96, T96, T96 * (TODAY()-R96)/MAX(1, S96-R96+1)))</f>
         <v/>
       </c>
       <c r="Z96" s="15">
@@ -7356,7 +7356,7 @@
       <c r="AI96" s="12" t="n"/>
       <c r="AJ96" s="14" t="n"/>
       <c r="AK96" s="15">
-        <f>IF(TODAY()&lt;AD96, 0, IF(TODAY()&gt;AE96, AF96, AF96 * (TODAY()-AD96)/(AE96-AD96+1)))</f>
+        <f>IF(TODAY()&lt;AD96, 0, IF(TODAY()&gt;AE96, AF96, AF96 * (TODAY()-AD96)/MAX(1, AE96-AD96+1)))</f>
         <v/>
       </c>
       <c r="AL96" s="15">
@@ -7382,7 +7382,7 @@
       <c r="K97" s="12" t="n"/>
       <c r="L97" s="14" t="n"/>
       <c r="M97" s="15">
-        <f>IF(TODAY()&lt;F97, 0, IF(TODAY()&gt;G97, H97, H97 * (TODAY()-F97)/(G97-F97+1)))</f>
+        <f>IF(TODAY()&lt;F97, 0, IF(TODAY()&gt;G97, H97, H97 * (TODAY()-F97)/MAX(1, G97-F97+1)))</f>
         <v/>
       </c>
       <c r="N97" s="15">
@@ -7403,7 +7403,7 @@
       <c r="W97" s="12" t="n"/>
       <c r="X97" s="14" t="n"/>
       <c r="Y97" s="15">
-        <f>IF(TODAY()&lt;R97, 0, IF(TODAY()&gt;S97, T97, T97 * (TODAY()-R97)/(S97-R97+1)))</f>
+        <f>IF(TODAY()&lt;R97, 0, IF(TODAY()&gt;S97, T97, T97 * (TODAY()-R97)/MAX(1, S97-R97+1)))</f>
         <v/>
       </c>
       <c r="Z97" s="15">
@@ -7424,7 +7424,7 @@
       <c r="AI97" s="12" t="n"/>
       <c r="AJ97" s="14" t="n"/>
       <c r="AK97" s="15">
-        <f>IF(TODAY()&lt;AD97, 0, IF(TODAY()&gt;AE97, AF97, AF97 * (TODAY()-AD97)/(AE97-AD97+1)))</f>
+        <f>IF(TODAY()&lt;AD97, 0, IF(TODAY()&gt;AE97, AF97, AF97 * (TODAY()-AD97)/MAX(1, AE97-AD97+1)))</f>
         <v/>
       </c>
       <c r="AL97" s="15">
@@ -7450,7 +7450,7 @@
       <c r="K98" s="12" t="n"/>
       <c r="L98" s="14" t="n"/>
       <c r="M98" s="15">
-        <f>IF(TODAY()&lt;F98, 0, IF(TODAY()&gt;G98, H98, H98 * (TODAY()-F98)/(G98-F98+1)))</f>
+        <f>IF(TODAY()&lt;F98, 0, IF(TODAY()&gt;G98, H98, H98 * (TODAY()-F98)/MAX(1, G98-F98+1)))</f>
         <v/>
       </c>
       <c r="N98" s="15">
@@ -7471,7 +7471,7 @@
       <c r="W98" s="12" t="n"/>
       <c r="X98" s="14" t="n"/>
       <c r="Y98" s="15">
-        <f>IF(TODAY()&lt;R98, 0, IF(TODAY()&gt;S98, T98, T98 * (TODAY()-R98)/(S98-R98+1)))</f>
+        <f>IF(TODAY()&lt;R98, 0, IF(TODAY()&gt;S98, T98, T98 * (TODAY()-R98)/MAX(1, S98-R98+1)))</f>
         <v/>
       </c>
       <c r="Z98" s="15">
@@ -7492,7 +7492,7 @@
       <c r="AI98" s="12" t="n"/>
       <c r="AJ98" s="14" t="n"/>
       <c r="AK98" s="15">
-        <f>IF(TODAY()&lt;AD98, 0, IF(TODAY()&gt;AE98, AF98, AF98 * (TODAY()-AD98)/(AE98-AD98+1)))</f>
+        <f>IF(TODAY()&lt;AD98, 0, IF(TODAY()&gt;AE98, AF98, AF98 * (TODAY()-AD98)/MAX(1, AE98-AD98+1)))</f>
         <v/>
       </c>
       <c r="AL98" s="15">
@@ -7518,7 +7518,7 @@
       <c r="K99" s="12" t="n"/>
       <c r="L99" s="14" t="n"/>
       <c r="M99" s="15">
-        <f>IF(TODAY()&lt;F99, 0, IF(TODAY()&gt;G99, H99, H99 * (TODAY()-F99)/(G99-F99+1)))</f>
+        <f>IF(TODAY()&lt;F99, 0, IF(TODAY()&gt;G99, H99, H99 * (TODAY()-F99)/MAX(1, G99-F99+1)))</f>
         <v/>
       </c>
       <c r="N99" s="15">
@@ -7539,7 +7539,7 @@
       <c r="W99" s="12" t="n"/>
       <c r="X99" s="14" t="n"/>
       <c r="Y99" s="15">
-        <f>IF(TODAY()&lt;R99, 0, IF(TODAY()&gt;S99, T99, T99 * (TODAY()-R99)/(S99-R99+1)))</f>
+        <f>IF(TODAY()&lt;R99, 0, IF(TODAY()&gt;S99, T99, T99 * (TODAY()-R99)/MAX(1, S99-R99+1)))</f>
         <v/>
       </c>
       <c r="Z99" s="15">
@@ -7560,7 +7560,7 @@
       <c r="AI99" s="12" t="n"/>
       <c r="AJ99" s="14" t="n"/>
       <c r="AK99" s="15">
-        <f>IF(TODAY()&lt;AD99, 0, IF(TODAY()&gt;AE99, AF99, AF99 * (TODAY()-AD99)/(AE99-AD99+1)))</f>
+        <f>IF(TODAY()&lt;AD99, 0, IF(TODAY()&gt;AE99, AF99, AF99 * (TODAY()-AD99)/MAX(1, AE99-AD99+1)))</f>
         <v/>
       </c>
       <c r="AL99" s="15">
@@ -7586,7 +7586,7 @@
       <c r="K100" s="12" t="n"/>
       <c r="L100" s="14" t="n"/>
       <c r="M100" s="15">
-        <f>IF(TODAY()&lt;F100, 0, IF(TODAY()&gt;G100, H100, H100 * (TODAY()-F100)/(G100-F100+1)))</f>
+        <f>IF(TODAY()&lt;F100, 0, IF(TODAY()&gt;G100, H100, H100 * (TODAY()-F100)/MAX(1, G100-F100+1)))</f>
         <v/>
       </c>
       <c r="N100" s="15">
@@ -7607,7 +7607,7 @@
       <c r="W100" s="12" t="n"/>
       <c r="X100" s="14" t="n"/>
       <c r="Y100" s="15">
-        <f>IF(TODAY()&lt;R100, 0, IF(TODAY()&gt;S100, T100, T100 * (TODAY()-R100)/(S100-R100+1)))</f>
+        <f>IF(TODAY()&lt;R100, 0, IF(TODAY()&gt;S100, T100, T100 * (TODAY()-R100)/MAX(1, S100-R100+1)))</f>
         <v/>
       </c>
       <c r="Z100" s="15">
@@ -7628,7 +7628,7 @@
       <c r="AI100" s="12" t="n"/>
       <c r="AJ100" s="14" t="n"/>
       <c r="AK100" s="15">
-        <f>IF(TODAY()&lt;AD100, 0, IF(TODAY()&gt;AE100, AF100, AF100 * (TODAY()-AD100)/(AE100-AD100+1)))</f>
+        <f>IF(TODAY()&lt;AD100, 0, IF(TODAY()&gt;AE100, AF100, AF100 * (TODAY()-AD100)/MAX(1, AE100-AD100+1)))</f>
         <v/>
       </c>
       <c r="AL100" s="15">
@@ -7654,7 +7654,7 @@
       <c r="K101" s="12" t="n"/>
       <c r="L101" s="14" t="n"/>
       <c r="M101" s="15">
-        <f>IF(TODAY()&lt;F101, 0, IF(TODAY()&gt;G101, H101, H101 * (TODAY()-F101)/(G101-F101+1)))</f>
+        <f>IF(TODAY()&lt;F101, 0, IF(TODAY()&gt;G101, H101, H101 * (TODAY()-F101)/MAX(1, G101-F101+1)))</f>
         <v/>
       </c>
       <c r="N101" s="15">
@@ -7675,7 +7675,7 @@
       <c r="W101" s="12" t="n"/>
       <c r="X101" s="14" t="n"/>
       <c r="Y101" s="15">
-        <f>IF(TODAY()&lt;R101, 0, IF(TODAY()&gt;S101, T101, T101 * (TODAY()-R101)/(S101-R101+1)))</f>
+        <f>IF(TODAY()&lt;R101, 0, IF(TODAY()&gt;S101, T101, T101 * (TODAY()-R101)/MAX(1, S101-R101+1)))</f>
         <v/>
       </c>
       <c r="Z101" s="15">
@@ -7696,7 +7696,7 @@
       <c r="AI101" s="12" t="n"/>
       <c r="AJ101" s="14" t="n"/>
       <c r="AK101" s="15">
-        <f>IF(TODAY()&lt;AD101, 0, IF(TODAY()&gt;AE101, AF101, AF101 * (TODAY()-AD101)/(AE101-AD101+1)))</f>
+        <f>IF(TODAY()&lt;AD101, 0, IF(TODAY()&gt;AE101, AF101, AF101 * (TODAY()-AD101)/MAX(1, AE101-AD101+1)))</f>
         <v/>
       </c>
       <c r="AL101" s="15">
@@ -7722,7 +7722,7 @@
       <c r="K102" s="18" t="n"/>
       <c r="L102" s="20" t="n"/>
       <c r="M102" s="21">
-        <f>IF(TODAY()&lt;F102, 0, IF(TODAY()&gt;G102, H102, H102 * (TODAY()-F102)/(G102-F102+1)))</f>
+        <f>IF(TODAY()&lt;F102, 0, IF(TODAY()&gt;G102, H102, H102 * (TODAY()-F102)/MAX(1, G102-F102+1)))</f>
         <v/>
       </c>
       <c r="N102" s="21">
@@ -7743,7 +7743,7 @@
       <c r="W102" s="18" t="n"/>
       <c r="X102" s="20" t="n"/>
       <c r="Y102" s="21">
-        <f>IF(TODAY()&lt;R102, 0, IF(TODAY()&gt;S102, T102, T102 * (TODAY()-R102)/(S102-R102+1)))</f>
+        <f>IF(TODAY()&lt;R102, 0, IF(TODAY()&gt;S102, T102, T102 * (TODAY()-R102)/MAX(1, S102-R102+1)))</f>
         <v/>
       </c>
       <c r="Z102" s="21">
@@ -7764,7 +7764,7 @@
       <c r="AI102" s="18" t="n"/>
       <c r="AJ102" s="20" t="n"/>
       <c r="AK102" s="21">
-        <f>IF(TODAY()&lt;AD102, 0, IF(TODAY()&gt;AE102, AF102, AF102 * (TODAY()-AD102)/(AE102-AD102+1)))</f>
+        <f>IF(TODAY()&lt;AD102, 0, IF(TODAY()&gt;AE102, AF102, AF102 * (TODAY()-AD102)/MAX(1, AE102-AD102+1)))</f>
         <v/>
       </c>
       <c r="AL102" s="21">
